--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="137">
   <si>
     <t>Buy Date</t>
   </si>
@@ -788,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S107"/>
+  <dimension ref="A1:S108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -6637,6 +6637,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108" spans="1:18">
+      <c r="A108" t="s">
+        <v>52</v>
+      </c>
+      <c r="B108" t="s">
+        <v>122</v>
+      </c>
+      <c r="C108" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108" t="s">
+        <v>127</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>951.25</v>
+      </c>
+      <c r="G108">
+        <v>10</v>
+      </c>
+      <c r="H108">
+        <v>10</v>
+      </c>
+      <c r="I108">
+        <v>9512.5</v>
+      </c>
+      <c r="J108">
+        <v>951.25</v>
+      </c>
+      <c r="L108">
+        <v>903.6900000000001</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="139">
   <si>
     <t>Buy Date</t>
   </si>
@@ -175,6 +175,9 @@
     <t>2026-03-02</t>
   </si>
   <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -383,6 +386,9 @@
   </si>
   <si>
     <t>AUBANK</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -788,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S108"/>
+  <dimension ref="A1:S112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -865,13 +871,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -901,7 +907,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -921,13 +927,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -945,7 +951,7 @@
         <v>9856</v>
       </c>
       <c r="J3">
-        <v>1372.3</v>
+        <v>1351.3</v>
       </c>
       <c r="L3">
         <v>1293.6</v>
@@ -957,13 +963,13 @@
         <v>492.8000000000002</v>
       </c>
       <c r="P3">
-        <v>561.2</v>
+        <v>477.2</v>
       </c>
       <c r="Q3">
-        <v>1054</v>
+        <v>970</v>
       </c>
       <c r="R3">
-        <v>10.69</v>
+        <v>9.84</v>
       </c>
       <c r="S3" t="s">
         <v>34</v>
@@ -974,13 +980,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1010,7 +1016,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1030,13 +1036,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1066,7 +1072,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1086,13 +1092,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1122,7 +1128,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1142,13 +1148,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1166,7 +1172,7 @@
         <v>8960</v>
       </c>
       <c r="J7">
-        <v>1279.7</v>
+        <v>1245.3</v>
       </c>
       <c r="L7">
         <v>1216</v>
@@ -1178,13 +1184,13 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-2.1</v>
+        <v>-242.9</v>
       </c>
       <c r="Q7">
-        <v>-2.1</v>
+        <v>-242.9</v>
       </c>
       <c r="R7">
-        <v>-0.02</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1192,13 +1198,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1228,7 +1234,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1248,13 +1254,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1284,7 +1290,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1304,13 +1310,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1340,7 +1346,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1360,13 +1366,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1387,7 +1393,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1396,7 +1402,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1411,7 +1417,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1419,13 +1425,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1455,7 +1461,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1478,13 +1484,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1514,7 +1520,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1534,13 +1540,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1570,7 +1576,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1590,13 +1596,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1626,7 +1632,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1646,13 +1652,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1682,7 +1688,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1702,13 +1708,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1726,7 +1732,7 @@
         <v>9282</v>
       </c>
       <c r="J17">
-        <v>9776</v>
+        <v>9652.5</v>
       </c>
       <c r="L17">
         <v>9282</v>
@@ -1738,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>494</v>
+        <v>370.5</v>
       </c>
       <c r="Q17">
-        <v>494</v>
+        <v>370.5</v>
       </c>
       <c r="R17">
-        <v>5.32</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1752,13 +1758,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1788,7 +1794,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1808,13 +1814,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1844,7 +1850,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1864,13 +1870,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1900,7 +1906,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1920,13 +1926,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1947,7 +1953,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1956,7 +1962,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -1976,13 +1982,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2003,7 +2009,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2012,7 +2018,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2032,13 +2038,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2068,7 +2074,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2088,13 +2094,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2124,7 +2130,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2144,13 +2150,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2180,7 +2186,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2200,13 +2206,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2227,7 +2233,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2236,7 +2242,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2256,13 +2262,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2292,7 +2298,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2312,13 +2318,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2348,7 +2354,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2368,13 +2374,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2404,7 +2410,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2424,13 +2430,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2460,7 +2466,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2480,13 +2486,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2507,7 +2513,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2516,7 +2522,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2536,13 +2542,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2572,7 +2578,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2592,13 +2598,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2628,7 +2634,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2648,13 +2654,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2675,7 +2681,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2684,7 +2690,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2704,13 +2710,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2731,7 +2737,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2740,7 +2746,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2760,13 +2766,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2796,7 +2802,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2816,13 +2822,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2852,7 +2858,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2872,13 +2878,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2908,7 +2914,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2931,13 +2937,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2967,7 +2973,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -2987,13 +2993,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3023,7 +3029,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3043,13 +3049,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3079,7 +3085,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3099,13 +3105,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3126,7 +3132,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3135,7 +3141,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3155,13 +3161,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3182,7 +3188,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3191,7 +3197,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3211,13 +3217,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3229,7 +3235,7 @@
         <v>27</v>
       </c>
       <c r="H44">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I44">
         <v>9686.25</v>
@@ -3237,23 +3243,29 @@
       <c r="J44">
         <v>374.8</v>
       </c>
+      <c r="K44" t="s">
+        <v>53</v>
+      </c>
       <c r="L44">
         <v>358.75</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>358.75</v>
+      </c>
+      <c r="N44" t="s">
+        <v>136</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>433.35</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>433.35</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>4.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3261,13 +3273,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3297,7 +3309,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3317,13 +3329,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3341,7 +3353,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>377.55</v>
+        <v>365.8</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3353,13 +3365,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>436.8</v>
+        <v>272.3</v>
       </c>
       <c r="Q46">
-        <v>921.6900000000001</v>
+        <v>757.1900000000001</v>
       </c>
       <c r="R46">
-        <v>9.5</v>
+        <v>7.81</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3370,13 +3382,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3406,7 +3418,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3426,13 +3438,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3462,7 +3474,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3482,13 +3494,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3518,7 +3530,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3541,13 +3553,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3577,7 +3589,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3597,13 +3609,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3633,7 +3645,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3653,13 +3665,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3689,7 +3701,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3712,13 +3724,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3748,7 +3760,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3768,13 +3780,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3804,7 +3816,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3827,13 +3839,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3863,7 +3875,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3886,13 +3898,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3922,7 +3934,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3942,13 +3954,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3969,7 +3981,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -3978,7 +3990,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -3998,13 +4010,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4034,7 +4046,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4054,13 +4066,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4090,7 +4102,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4113,13 +4125,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4137,7 +4149,7 @@
         <v>9944.179999999998</v>
       </c>
       <c r="J60">
-        <v>165.07</v>
+        <v>154.61</v>
       </c>
       <c r="L60">
         <v>152.37</v>
@@ -4149,13 +4161,13 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>290.16</v>
+        <v>-358.36</v>
       </c>
       <c r="Q60">
-        <v>290.16</v>
+        <v>-358.36</v>
       </c>
       <c r="R60">
-        <v>2.92</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4163,13 +4175,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4199,7 +4211,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4222,13 +4234,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4258,7 +4270,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4273,7 +4285,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4281,13 +4293,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4317,7 +4329,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4337,13 +4349,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4373,7 +4385,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4393,13 +4405,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4429,7 +4441,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4449,13 +4461,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4473,7 +4485,7 @@
         <v>9877.15</v>
       </c>
       <c r="J66">
-        <v>282.2</v>
+        <v>276.95</v>
       </c>
       <c r="L66">
         <v>266.95</v>
@@ -4485,13 +4497,13 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>564.25</v>
+        <v>370</v>
       </c>
       <c r="Q66">
-        <v>564.25</v>
+        <v>370</v>
       </c>
       <c r="R66">
-        <v>5.71</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4499,13 +4511,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4535,7 +4547,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4555,13 +4567,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D68" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4591,7 +4603,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4611,13 +4623,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D69" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4638,7 +4650,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4647,7 +4659,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4667,13 +4679,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D70" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4703,7 +4715,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4723,13 +4735,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4747,7 +4759,7 @@
         <v>9785.75</v>
       </c>
       <c r="J71">
-        <v>779.15</v>
+        <v>771.85</v>
       </c>
       <c r="L71">
         <v>752.75</v>
@@ -4759,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>343.2</v>
+        <v>248.3</v>
       </c>
       <c r="Q71">
-        <v>343.2</v>
+        <v>248.3</v>
       </c>
       <c r="R71">
-        <v>3.51</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4773,13 +4785,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4791,7 +4803,7 @@
         <v>80</v>
       </c>
       <c r="H72">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>9952.799999999999</v>
@@ -4799,23 +4811,29 @@
       <c r="J72">
         <v>128.65</v>
       </c>
+      <c r="K72" t="s">
+        <v>53</v>
+      </c>
       <c r="L72">
         <v>124.41</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>124.41</v>
+      </c>
+      <c r="N72" t="s">
+        <v>136</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>339.2</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>339.2</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>3.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -4823,13 +4841,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4859,7 +4877,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4879,13 +4897,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4915,7 +4933,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -4935,13 +4953,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4971,7 +4989,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -4991,13 +5009,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5027,7 +5045,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5047,13 +5065,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5083,7 +5101,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5103,13 +5121,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5127,7 +5145,7 @@
         <v>6019</v>
       </c>
       <c r="J78">
-        <v>5959</v>
+        <v>5889.5</v>
       </c>
       <c r="L78">
         <v>5718.05</v>
@@ -5139,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>-60</v>
+        <v>-129.5</v>
       </c>
       <c r="Q78">
-        <v>-60</v>
+        <v>-129.5</v>
       </c>
       <c r="R78">
-        <v>-1</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -5153,13 +5171,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5189,7 +5207,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5209,13 +5227,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5227,7 +5245,7 @@
         <v>28</v>
       </c>
       <c r="H80">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>9713.200000000001</v>
@@ -5235,23 +5253,29 @@
       <c r="J80">
         <v>338.95</v>
       </c>
+      <c r="K80" t="s">
+        <v>53</v>
+      </c>
       <c r="L80">
         <v>329.55</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>329.55</v>
+      </c>
+      <c r="N80" t="s">
+        <v>136</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>-485.799999999999</v>
       </c>
       <c r="P80">
-        <v>-222.6</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>-222.6</v>
+        <v>-485.799999999999</v>
       </c>
       <c r="R80">
-        <v>-2.29</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5259,13 +5283,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5277,7 +5301,7 @@
         <v>7</v>
       </c>
       <c r="H81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I81">
         <v>9902.200000000001</v>
@@ -5285,23 +5309,29 @@
       <c r="J81">
         <v>1374</v>
       </c>
+      <c r="K81" t="s">
+        <v>53</v>
+      </c>
       <c r="L81">
         <v>1343.87</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>1326</v>
+      </c>
+      <c r="N81" t="s">
+        <v>137</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>-620.1999999999994</v>
       </c>
       <c r="P81">
-        <v>-284.2</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>-284.2</v>
+        <v>-620.1999999999994</v>
       </c>
       <c r="R81">
-        <v>-2.87</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -5309,13 +5339,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5327,7 +5357,7 @@
         <v>34</v>
       </c>
       <c r="H82">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I82">
         <v>9773.299999999999</v>
@@ -5335,23 +5365,29 @@
       <c r="J82">
         <v>315.2</v>
       </c>
+      <c r="K82" t="s">
+        <v>53</v>
+      </c>
       <c r="L82">
         <v>301.82</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>301.82</v>
+      </c>
+      <c r="N82" t="s">
+        <v>136</v>
       </c>
       <c r="O82">
-        <v>488.6650000000001</v>
+        <v>732.9550000000002</v>
       </c>
       <c r="P82">
-        <v>471.75</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>960.42</v>
+        <v>732.9550000000002</v>
       </c>
       <c r="R82">
-        <v>9.83</v>
+        <v>7.5</v>
       </c>
       <c r="S82" t="s">
         <v>50</v>
@@ -5362,13 +5398,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5386,7 +5422,7 @@
         <v>9485.6</v>
       </c>
       <c r="J83">
-        <v>617.65</v>
+        <v>591.25</v>
       </c>
       <c r="L83">
         <v>563.21</v>
@@ -5398,13 +5434,13 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>396.8</v>
+        <v>-25.6</v>
       </c>
       <c r="Q83">
-        <v>396.8</v>
+        <v>-25.6</v>
       </c>
       <c r="R83">
-        <v>4.18</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5412,13 +5448,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5430,7 +5466,7 @@
         <v>9</v>
       </c>
       <c r="H84">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I84">
         <v>9114.75</v>
@@ -5438,23 +5474,29 @@
       <c r="J84">
         <v>978.25</v>
       </c>
+      <c r="K84" t="s">
+        <v>53</v>
+      </c>
       <c r="L84">
         <v>962.11</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>962.11</v>
+      </c>
+      <c r="N84" t="s">
+        <v>136</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>-455.7599999999999</v>
       </c>
       <c r="P84">
-        <v>-310.5</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>-310.5</v>
+        <v>-455.7599999999999</v>
       </c>
       <c r="R84">
-        <v>-3.41</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -5462,13 +5504,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5480,7 +5522,7 @@
         <v>4</v>
       </c>
       <c r="H85">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I85">
         <v>9588.799999999999</v>
@@ -5488,23 +5530,29 @@
       <c r="J85">
         <v>2307.1</v>
       </c>
+      <c r="K85" t="s">
+        <v>53</v>
+      </c>
       <c r="L85">
         <v>2277.34</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>2260.7</v>
+      </c>
+      <c r="N85" t="s">
+        <v>137</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>-546</v>
       </c>
       <c r="P85">
-        <v>-360.4</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>-360.4</v>
+        <v>-546</v>
       </c>
       <c r="R85">
-        <v>-3.76</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -5512,13 +5560,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5530,7 +5578,7 @@
         <v>23</v>
       </c>
       <c r="H86">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I86">
         <v>9589.85</v>
@@ -5538,23 +5586,29 @@
       <c r="J86">
         <v>406.2</v>
       </c>
+      <c r="K86" t="s">
+        <v>53</v>
+      </c>
       <c r="L86">
         <v>396.1</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>396.1</v>
+      </c>
+      <c r="N86" t="s">
+        <v>136</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>-479.5499999999992</v>
       </c>
       <c r="P86">
-        <v>-247.25</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>-247.25</v>
+        <v>-479.5499999999992</v>
       </c>
       <c r="R86">
-        <v>-2.58</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -5562,13 +5616,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C87" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5586,7 +5640,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1294.4</v>
+        <v>1291.2</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5598,13 +5652,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>67.2</v>
+        <v>44.8</v>
       </c>
       <c r="Q87">
-        <v>67.2</v>
+        <v>44.8</v>
       </c>
       <c r="R87">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5612,13 +5666,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D88" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5648,7 +5702,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5668,13 +5722,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5692,7 +5746,7 @@
         <v>9791.1</v>
       </c>
       <c r="J89">
-        <v>940</v>
+        <v>921.8</v>
       </c>
       <c r="L89">
         <v>845.6</v>
@@ -5704,13 +5758,13 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>548.9</v>
+        <v>348.7</v>
       </c>
       <c r="Q89">
-        <v>548.9</v>
+        <v>348.7</v>
       </c>
       <c r="R89">
-        <v>5.61</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -5718,13 +5772,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5742,7 +5796,7 @@
         <v>9117.200000000001</v>
       </c>
       <c r="J90">
-        <v>2320.6</v>
+        <v>2261.3</v>
       </c>
       <c r="L90">
         <v>2165.34</v>
@@ -5754,13 +5808,13 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>165.2</v>
+        <v>-72</v>
       </c>
       <c r="Q90">
-        <v>165.2</v>
+        <v>-72</v>
       </c>
       <c r="R90">
-        <v>1.81</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -5768,13 +5822,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5792,7 +5846,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>296.8</v>
+        <v>291.95</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5804,13 +5858,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>70.95</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="Q91">
-        <v>70.95</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="R91">
-        <v>0.73</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5818,13 +5872,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5854,7 +5908,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -5874,13 +5928,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C93" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5898,7 +5952,7 @@
         <v>9961.9</v>
       </c>
       <c r="J93">
-        <v>126.05</v>
+        <v>121.37</v>
       </c>
       <c r="L93">
         <v>119.79</v>
@@ -5910,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>-3.95</v>
+        <v>-373.67</v>
       </c>
       <c r="Q93">
-        <v>-3.95</v>
+        <v>-373.67</v>
       </c>
       <c r="R93">
-        <v>-0.04</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -5924,13 +5978,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D94" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -5942,7 +5996,7 @@
         <v>57</v>
       </c>
       <c r="H94">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I94">
         <v>9935.1</v>
@@ -5950,23 +6004,29 @@
       <c r="J94">
         <v>179.11</v>
       </c>
+      <c r="K94" t="s">
+        <v>53</v>
+      </c>
       <c r="L94">
         <v>174.3</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>174.3</v>
+      </c>
+      <c r="N94" t="s">
+        <v>136</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>274.17</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>274.17</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>2.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:19">
@@ -5974,13 +6034,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5992,7 +6052,7 @@
         <v>15</v>
       </c>
       <c r="H95">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I95">
         <v>9962.25</v>
@@ -6000,23 +6060,29 @@
       <c r="J95">
         <v>653.55</v>
       </c>
+      <c r="K95" t="s">
+        <v>53</v>
+      </c>
       <c r="L95">
         <v>630.9400000000001</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>630.9400000000001</v>
+      </c>
+      <c r="N95" t="s">
+        <v>136</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>-498.1499999999988</v>
       </c>
       <c r="P95">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>-159</v>
+        <v>-498.1499999999988</v>
       </c>
       <c r="R95">
-        <v>-1.6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -6024,13 +6090,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D96" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6060,7 +6126,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6080,13 +6146,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6116,7 +6182,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6136,13 +6202,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C98" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6160,7 +6226,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>426.25</v>
+        <v>435.15</v>
       </c>
       <c r="L98">
         <v>409.4</v>
@@ -6172,13 +6238,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>-108.1</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="Q98">
-        <v>-108.1</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R98">
-        <v>-1.09</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -6186,13 +6252,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6204,7 +6270,7 @@
         <v>2</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I99">
         <v>7862.6</v>
@@ -6212,23 +6278,29 @@
       <c r="J99">
         <v>3848.5</v>
       </c>
+      <c r="K99" t="s">
+        <v>53</v>
+      </c>
       <c r="L99">
         <v>3734.74</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>3734.74</v>
+      </c>
+      <c r="N99" t="s">
+        <v>136</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>-393.1200000000008</v>
       </c>
       <c r="P99">
-        <v>-165.6</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>-165.6</v>
+        <v>-393.1200000000008</v>
       </c>
       <c r="R99">
-        <v>-2.11</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -6236,13 +6308,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6254,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>5737.5</v>
@@ -6262,23 +6334,29 @@
       <c r="J100">
         <v>5591.5</v>
       </c>
+      <c r="K100" t="s">
+        <v>53</v>
+      </c>
       <c r="L100">
         <v>5450.62</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>5450.62</v>
+      </c>
+      <c r="N100" t="s">
+        <v>136</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>-286.8800000000001</v>
       </c>
       <c r="P100">
-        <v>-146</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>-146</v>
+        <v>-286.8800000000001</v>
       </c>
       <c r="R100">
-        <v>-2.54</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -6286,13 +6364,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6304,7 +6382,7 @@
         <v>10</v>
       </c>
       <c r="H101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I101">
         <v>9882.5</v>
@@ -6312,23 +6390,29 @@
       <c r="J101">
         <v>966.2</v>
       </c>
+      <c r="K101" t="s">
+        <v>53</v>
+      </c>
       <c r="L101">
         <v>938.84</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>938.84</v>
+      </c>
+      <c r="N101" t="s">
+        <v>136</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>-494.0999999999997</v>
       </c>
       <c r="P101">
-        <v>-220.5</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>-220.5</v>
+        <v>-494.0999999999997</v>
       </c>
       <c r="R101">
-        <v>-2.23</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -6336,13 +6420,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6354,7 +6438,7 @@
         <v>19</v>
       </c>
       <c r="H102">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I102">
         <v>9507.6</v>
@@ -6362,23 +6446,29 @@
       <c r="J102">
         <v>490.75</v>
       </c>
+      <c r="K102" t="s">
+        <v>53</v>
+      </c>
       <c r="L102">
         <v>475.38</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>475.38</v>
+      </c>
+      <c r="N102" t="s">
+        <v>136</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>-475.3799999999997</v>
       </c>
       <c r="P102">
-        <v>-183.35</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>-183.35</v>
+        <v>-475.3799999999997</v>
       </c>
       <c r="R102">
-        <v>-1.93</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -6386,13 +6476,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6422,7 +6512,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6442,13 +6532,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D104" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6460,7 +6550,7 @@
         <v>16</v>
       </c>
       <c r="H104">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I104">
         <v>9661.6</v>
@@ -6468,23 +6558,29 @@
       <c r="J104">
         <v>590.2</v>
       </c>
+      <c r="K104" t="s">
+        <v>53</v>
+      </c>
       <c r="L104">
         <v>573.66</v>
       </c>
       <c r="M104">
-        <v>0</v>
+        <v>573.66</v>
+      </c>
+      <c r="N104" t="s">
+        <v>136</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>-483.0400000000009</v>
       </c>
       <c r="P104">
-        <v>-218.4</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>-218.4</v>
+        <v>-483.0400000000009</v>
       </c>
       <c r="R104">
-        <v>-2.26</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -6492,13 +6588,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D105" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6516,7 +6612,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1752.5</v>
+        <v>1750.5</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6528,13 +6624,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6542,13 +6638,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D106" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6566,7 +6662,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1354</v>
+        <v>1318.7</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6578,13 +6674,13 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>-247.1</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>-247.1</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6592,13 +6688,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6616,7 +6712,7 @@
         <v>9939.049999999999</v>
       </c>
       <c r="J107">
-        <v>903.55</v>
+        <v>871.95</v>
       </c>
       <c r="L107">
         <v>858.37</v>
@@ -6628,13 +6724,13 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>-347.6</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>-347.6</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -6642,13 +6738,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D108" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6666,7 +6762,7 @@
         <v>9512.5</v>
       </c>
       <c r="J108">
-        <v>951.25</v>
+        <v>946.1</v>
       </c>
       <c r="L108">
         <v>903.6900000000001</v>
@@ -6678,12 +6774,212 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>-51.5</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>-51.5</v>
       </c>
       <c r="R108">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="A109" t="s">
+        <v>53</v>
+      </c>
+      <c r="B109" t="s">
+        <v>87</v>
+      </c>
+      <c r="C109" t="s">
+        <v>126</v>
+      </c>
+      <c r="D109" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>442.3</v>
+      </c>
+      <c r="G109">
+        <v>22</v>
+      </c>
+      <c r="H109">
+        <v>22</v>
+      </c>
+      <c r="I109">
+        <v>9730.6</v>
+      </c>
+      <c r="J109">
+        <v>442.3</v>
+      </c>
+      <c r="L109">
+        <v>420.19</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>0</v>
+      </c>
+      <c r="R109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
+      <c r="A110" t="s">
+        <v>53</v>
+      </c>
+      <c r="B110" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110" t="s">
+        <v>126</v>
+      </c>
+      <c r="D110" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>196.73</v>
+      </c>
+      <c r="G110">
+        <v>50</v>
+      </c>
+      <c r="H110">
+        <v>50</v>
+      </c>
+      <c r="I110">
+        <v>9836.5</v>
+      </c>
+      <c r="J110">
+        <v>196.73</v>
+      </c>
+      <c r="L110">
+        <v>186.89</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
+      <c r="A111" t="s">
+        <v>53</v>
+      </c>
+      <c r="B111" t="s">
+        <v>124</v>
+      </c>
+      <c r="C111" t="s">
+        <v>127</v>
+      </c>
+      <c r="D111" t="s">
+        <v>129</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>7666</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>7666</v>
+      </c>
+      <c r="J111">
+        <v>7666</v>
+      </c>
+      <c r="L111">
+        <v>7282.7</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
+      <c r="A112" t="s">
+        <v>53</v>
+      </c>
+      <c r="B112" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112" t="s">
+        <v>125</v>
+      </c>
+      <c r="D112" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>2076.5</v>
+      </c>
+      <c r="G112">
+        <v>4</v>
+      </c>
+      <c r="H112">
+        <v>4</v>
+      </c>
+      <c r="I112">
+        <v>8306</v>
+      </c>
+      <c r="J112">
+        <v>2076.5</v>
+      </c>
+      <c r="L112">
+        <v>1972.67</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="139">
   <si>
     <t>Buy Date</t>
   </si>
@@ -794,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S112"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -5266,13 +5266,13 @@
         <v>136</v>
       </c>
       <c r="O80">
-        <v>-485.799999999999</v>
+        <v>-485.7999999999991</v>
       </c>
       <c r="P80">
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>-485.799999999999</v>
+        <v>-485.7999999999991</v>
       </c>
       <c r="R80">
         <v>-5</v>
@@ -6073,13 +6073,13 @@
         <v>136</v>
       </c>
       <c r="O95">
-        <v>-498.1499999999988</v>
+        <v>-498.1499999999989</v>
       </c>
       <c r="P95">
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>-498.1499999999988</v>
+        <v>-498.1499999999989</v>
       </c>
       <c r="R95">
         <v>-5</v>
@@ -6980,6 +6980,106 @@
         <v>0</v>
       </c>
       <c r="R112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
+      <c r="A113" t="s">
+        <v>53</v>
+      </c>
+      <c r="B113" t="s">
+        <v>89</v>
+      </c>
+      <c r="C113" t="s">
+        <v>126</v>
+      </c>
+      <c r="D113" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>122.88</v>
+      </c>
+      <c r="G113">
+        <v>81</v>
+      </c>
+      <c r="H113">
+        <v>81</v>
+      </c>
+      <c r="I113">
+        <v>9953.279999999999</v>
+      </c>
+      <c r="J113">
+        <v>122.88</v>
+      </c>
+      <c r="L113">
+        <v>116.74</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
+      <c r="A114" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" t="s">
+        <v>126</v>
+      </c>
+      <c r="D114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>170.44</v>
+      </c>
+      <c r="G114">
+        <v>58</v>
+      </c>
+      <c r="H114">
+        <v>58</v>
+      </c>
+      <c r="I114">
+        <v>9885.52</v>
+      </c>
+      <c r="J114">
+        <v>170.44</v>
+      </c>
+      <c r="L114">
+        <v>161.92</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="141">
   <si>
     <t>Buy Date</t>
   </si>
@@ -178,6 +178,9 @@
     <t>2026-03-04</t>
   </si>
   <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -389,6 +392,9 @@
   </si>
   <si>
     <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>DABUR</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -794,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -871,13 +877,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -907,7 +913,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -927,13 +933,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -951,7 +957,7 @@
         <v>9856</v>
       </c>
       <c r="J3">
-        <v>1351.3</v>
+        <v>1349.1</v>
       </c>
       <c r="L3">
         <v>1293.6</v>
@@ -963,13 +969,13 @@
         <v>492.8000000000002</v>
       </c>
       <c r="P3">
-        <v>477.2</v>
+        <v>468.4</v>
       </c>
       <c r="Q3">
-        <v>970</v>
+        <v>961.2</v>
       </c>
       <c r="R3">
-        <v>9.84</v>
+        <v>9.75</v>
       </c>
       <c r="S3" t="s">
         <v>34</v>
@@ -980,13 +986,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1016,7 +1022,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1036,13 +1042,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1072,7 +1078,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1092,13 +1098,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1128,7 +1134,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1148,13 +1154,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1172,7 +1178,7 @@
         <v>8960</v>
       </c>
       <c r="J7">
-        <v>1245.3</v>
+        <v>1250.9</v>
       </c>
       <c r="L7">
         <v>1216</v>
@@ -1184,13 +1190,13 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-242.9</v>
+        <v>-203.7</v>
       </c>
       <c r="Q7">
-        <v>-242.9</v>
+        <v>-203.7</v>
       </c>
       <c r="R7">
-        <v>-2.71</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1198,13 +1204,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1234,7 +1240,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1254,13 +1260,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1290,7 +1296,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1310,13 +1316,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1346,7 +1352,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1366,13 +1372,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1393,7 +1399,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1402,7 +1408,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1417,7 +1423,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1425,13 +1431,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1461,7 +1467,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1484,13 +1490,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1520,7 +1526,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1540,13 +1546,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1576,7 +1582,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1596,13 +1602,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1632,7 +1638,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1652,13 +1658,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1688,7 +1694,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1708,13 +1714,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1732,7 +1738,7 @@
         <v>9282</v>
       </c>
       <c r="J17">
-        <v>9652.5</v>
+        <v>9804.5</v>
       </c>
       <c r="L17">
         <v>9282</v>
@@ -1744,13 +1750,13 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>370.5</v>
+        <v>522.5</v>
       </c>
       <c r="Q17">
-        <v>370.5</v>
+        <v>522.5</v>
       </c>
       <c r="R17">
-        <v>3.99</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1758,13 +1764,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1794,7 +1800,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1814,13 +1820,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1850,7 +1856,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1870,13 +1876,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1906,7 +1912,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1926,13 +1932,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1953,7 +1959,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1962,7 +1968,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -1982,13 +1988,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2009,7 +2015,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2018,7 +2024,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2038,13 +2044,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2074,7 +2080,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2094,13 +2100,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2130,7 +2136,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2150,13 +2156,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2186,7 +2192,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2206,13 +2212,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2233,7 +2239,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2242,7 +2248,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2262,13 +2268,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2298,7 +2304,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2318,13 +2324,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2354,7 +2360,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2374,13 +2380,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2410,7 +2416,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2430,13 +2436,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2466,7 +2472,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2486,13 +2492,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2513,7 +2519,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2522,7 +2528,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2542,13 +2548,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2578,7 +2584,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2598,13 +2604,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2634,7 +2640,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2654,13 +2660,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2681,7 +2687,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2690,7 +2696,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2710,13 +2716,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2737,7 +2743,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2746,7 +2752,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2766,13 +2772,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2802,7 +2808,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2822,13 +2828,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2858,7 +2864,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2878,13 +2884,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2914,7 +2920,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2937,13 +2943,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2973,7 +2979,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -2993,13 +2999,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3029,7 +3035,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3049,13 +3055,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3085,7 +3091,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3105,13 +3111,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3132,7 +3138,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3141,7 +3147,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3161,13 +3167,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3188,7 +3194,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3197,7 +3203,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3217,13 +3223,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3253,7 +3259,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3273,13 +3279,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3309,7 +3315,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3329,13 +3335,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3353,7 +3359,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>365.8</v>
+        <v>378.05</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3365,13 +3371,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>272.3</v>
+        <v>443.8</v>
       </c>
       <c r="Q46">
-        <v>757.1900000000001</v>
+        <v>928.6900000000001</v>
       </c>
       <c r="R46">
-        <v>7.81</v>
+        <v>9.58</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3382,13 +3388,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3418,7 +3424,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3438,13 +3444,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3474,7 +3480,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3494,13 +3500,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3530,7 +3536,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3553,13 +3559,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3589,7 +3595,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3609,13 +3615,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3645,7 +3651,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3665,13 +3671,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3701,7 +3707,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3724,13 +3730,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3760,7 +3766,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3780,13 +3786,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3816,7 +3822,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3839,13 +3845,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3875,7 +3881,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3898,13 +3904,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3934,7 +3940,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3954,13 +3960,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3981,7 +3987,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -3990,7 +3996,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4010,13 +4016,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4046,7 +4052,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4066,13 +4072,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4102,7 +4108,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4125,13 +4131,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4149,7 +4155,7 @@
         <v>9944.179999999998</v>
       </c>
       <c r="J60">
-        <v>154.61</v>
+        <v>156.73</v>
       </c>
       <c r="L60">
         <v>152.37</v>
@@ -4161,13 +4167,13 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>-358.36</v>
+        <v>-226.92</v>
       </c>
       <c r="Q60">
-        <v>-358.36</v>
+        <v>-226.92</v>
       </c>
       <c r="R60">
-        <v>-3.6</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4175,13 +4181,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4211,7 +4217,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4234,13 +4240,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4270,7 +4276,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4285,7 +4291,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4293,13 +4299,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4329,7 +4335,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4349,13 +4355,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4385,7 +4391,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4405,13 +4411,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4441,7 +4447,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4461,13 +4467,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4485,7 +4491,7 @@
         <v>9877.15</v>
       </c>
       <c r="J66">
-        <v>276.95</v>
+        <v>276.35</v>
       </c>
       <c r="L66">
         <v>266.95</v>
@@ -4497,13 +4503,13 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>370</v>
+        <v>347.8</v>
       </c>
       <c r="Q66">
-        <v>370</v>
+        <v>347.8</v>
       </c>
       <c r="R66">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4511,13 +4517,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D67" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4547,7 +4553,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4567,13 +4573,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4603,7 +4609,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4623,13 +4629,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4650,7 +4656,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4659,7 +4665,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4679,13 +4685,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4715,7 +4721,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4735,13 +4741,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4759,7 +4765,7 @@
         <v>9785.75</v>
       </c>
       <c r="J71">
-        <v>771.85</v>
+        <v>778.85</v>
       </c>
       <c r="L71">
         <v>752.75</v>
@@ -4771,13 +4777,13 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>248.3</v>
+        <v>339.3</v>
       </c>
       <c r="Q71">
-        <v>248.3</v>
+        <v>339.3</v>
       </c>
       <c r="R71">
-        <v>2.54</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4785,13 +4791,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D72" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4821,7 +4827,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4841,13 +4847,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4877,7 +4883,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4897,13 +4903,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4933,7 +4939,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -4953,13 +4959,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4989,7 +4995,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5009,13 +5015,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5045,7 +5051,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5065,13 +5071,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D77" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5101,7 +5107,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5121,13 +5127,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5145,7 +5151,7 @@
         <v>6019</v>
       </c>
       <c r="J78">
-        <v>5889.5</v>
+        <v>5963</v>
       </c>
       <c r="L78">
         <v>5718.05</v>
@@ -5157,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>-129.5</v>
+        <v>-56</v>
       </c>
       <c r="Q78">
-        <v>-129.5</v>
+        <v>-56</v>
       </c>
       <c r="R78">
-        <v>-2.15</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -5171,13 +5177,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D79" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5207,7 +5213,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5227,13 +5233,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5263,7 +5269,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5283,13 +5289,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5319,7 +5325,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5339,13 +5345,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5375,7 +5381,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5398,13 +5404,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D83" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5422,7 +5428,7 @@
         <v>9485.6</v>
       </c>
       <c r="J83">
-        <v>591.25</v>
+        <v>595.65</v>
       </c>
       <c r="L83">
         <v>563.21</v>
@@ -5434,13 +5440,13 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>-25.6</v>
+        <v>44.8</v>
       </c>
       <c r="Q83">
-        <v>-25.6</v>
+        <v>44.8</v>
       </c>
       <c r="R83">
-        <v>-0.27</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5448,13 +5454,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5484,7 +5490,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5504,13 +5510,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5540,7 +5546,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5560,13 +5566,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5596,7 +5602,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5616,13 +5622,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5640,7 +5646,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1291.2</v>
+        <v>1313.5</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5652,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>44.8</v>
+        <v>200.9</v>
       </c>
       <c r="Q87">
-        <v>44.8</v>
+        <v>200.9</v>
       </c>
       <c r="R87">
-        <v>0.5</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5666,13 +5672,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C88" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5702,7 +5708,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5722,16 +5728,16 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89">
         <v>890.1</v>
@@ -5740,7 +5746,7 @@
         <v>11</v>
       </c>
       <c r="H89">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I89">
         <v>9791.1</v>
@@ -5748,23 +5754,29 @@
       <c r="J89">
         <v>921.8</v>
       </c>
+      <c r="K89" t="s">
+        <v>54</v>
+      </c>
       <c r="L89">
-        <v>845.6</v>
+        <v>934.61</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>930</v>
+      </c>
+      <c r="N89" t="s">
+        <v>139</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>438.8999999999997</v>
       </c>
       <c r="P89">
-        <v>348.7</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>348.7</v>
+        <v>438.8999999999997</v>
       </c>
       <c r="R89">
-        <v>3.56</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -5772,13 +5784,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5796,7 +5808,7 @@
         <v>9117.200000000001</v>
       </c>
       <c r="J90">
-        <v>2261.3</v>
+        <v>2255</v>
       </c>
       <c r="L90">
         <v>2165.34</v>
@@ -5808,13 +5820,13 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>-72</v>
+        <v>-97.2</v>
       </c>
       <c r="Q90">
-        <v>-72</v>
+        <v>-97.2</v>
       </c>
       <c r="R90">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -5822,13 +5834,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D91" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5846,7 +5858,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>291.95</v>
+        <v>299.45</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5858,13 +5870,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>-89.09999999999999</v>
+        <v>158.4</v>
       </c>
       <c r="Q91">
-        <v>-89.09999999999999</v>
+        <v>158.4</v>
       </c>
       <c r="R91">
-        <v>-0.92</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5872,13 +5884,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C92" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5908,7 +5920,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -5928,13 +5940,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5952,7 +5964,7 @@
         <v>9961.9</v>
       </c>
       <c r="J93">
-        <v>121.37</v>
+        <v>122.2</v>
       </c>
       <c r="L93">
         <v>119.79</v>
@@ -5964,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>-373.67</v>
+        <v>-308.1</v>
       </c>
       <c r="Q93">
-        <v>-373.67</v>
+        <v>-308.1</v>
       </c>
       <c r="R93">
-        <v>-3.75</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -5978,13 +5990,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6014,7 +6026,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6034,13 +6046,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C95" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D95" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6070,7 +6082,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6090,13 +6102,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C96" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6126,7 +6138,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6146,13 +6158,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D97" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6182,7 +6194,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6202,13 +6214,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6226,7 +6238,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>435.15</v>
+        <v>449.4</v>
       </c>
       <c r="L98">
         <v>409.4</v>
@@ -6238,13 +6250,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>96.59999999999999</v>
+        <v>424.35</v>
       </c>
       <c r="Q98">
-        <v>96.59999999999999</v>
+        <v>424.35</v>
       </c>
       <c r="R98">
-        <v>0.97</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -6252,13 +6264,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6288,7 +6300,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6308,13 +6320,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C100" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6344,7 +6356,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6364,13 +6376,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6400,7 +6412,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6420,13 +6432,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6456,7 +6468,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6476,13 +6488,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6512,7 +6524,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6532,13 +6544,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D104" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6568,7 +6580,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6588,13 +6600,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C105" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D105" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6612,7 +6624,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1750.5</v>
+        <v>1784.5</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6624,13 +6636,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>-10</v>
+        <v>160</v>
       </c>
       <c r="Q105">
-        <v>-10</v>
+        <v>160</v>
       </c>
       <c r="R105">
-        <v>-0.11</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6638,13 +6650,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6662,7 +6674,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1318.7</v>
+        <v>1352.5</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6674,13 +6686,13 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>-247.1</v>
+        <v>-10.5</v>
       </c>
       <c r="Q106">
-        <v>-247.1</v>
+        <v>-10.5</v>
       </c>
       <c r="R106">
-        <v>-2.61</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6688,13 +6700,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D107" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6712,7 +6724,7 @@
         <v>9939.049999999999</v>
       </c>
       <c r="J107">
-        <v>871.95</v>
+        <v>884.55</v>
       </c>
       <c r="L107">
         <v>858.37</v>
@@ -6724,13 +6736,13 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>-347.6</v>
+        <v>-209</v>
       </c>
       <c r="Q107">
-        <v>-347.6</v>
+        <v>-209</v>
       </c>
       <c r="R107">
-        <v>-3.5</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -6738,13 +6750,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C108" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D108" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6762,7 +6774,7 @@
         <v>9512.5</v>
       </c>
       <c r="J108">
-        <v>946.1</v>
+        <v>973.45</v>
       </c>
       <c r="L108">
         <v>903.6900000000001</v>
@@ -6774,13 +6786,13 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>-51.5</v>
+        <v>222</v>
       </c>
       <c r="Q108">
-        <v>-51.5</v>
+        <v>222</v>
       </c>
       <c r="R108">
-        <v>-0.54</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6788,13 +6800,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D109" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6812,7 +6824,7 @@
         <v>9730.6</v>
       </c>
       <c r="J109">
-        <v>442.3</v>
+        <v>451.4</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6824,13 +6836,13 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>200.2</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>200.2</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6838,13 +6850,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C110" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D110" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6862,7 +6874,7 @@
         <v>9836.5</v>
       </c>
       <c r="J110">
-        <v>196.73</v>
+        <v>200.57</v>
       </c>
       <c r="L110">
         <v>186.89</v>
@@ -6874,13 +6886,13 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6888,13 +6900,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C111" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6912,7 +6924,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7666</v>
+        <v>7775</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -6924,13 +6936,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6938,13 +6950,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D112" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6962,7 +6974,7 @@
         <v>8306</v>
       </c>
       <c r="J112">
-        <v>2076.5</v>
+        <v>2089.2</v>
       </c>
       <c r="L112">
         <v>1972.67</v>
@@ -6974,13 +6986,13 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>50.8</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>50.8</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -6988,13 +7000,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C113" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7009,10 +7021,10 @@
         <v>81</v>
       </c>
       <c r="I113">
-        <v>9953.279999999999</v>
+        <v>9953.280000000001</v>
       </c>
       <c r="J113">
-        <v>122.88</v>
+        <v>126.34</v>
       </c>
       <c r="L113">
         <v>116.74</v>
@@ -7024,13 +7036,13 @@
         <v>0</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>280.26</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>280.26</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -7038,13 +7050,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C114" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D114" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7062,7 +7074,7 @@
         <v>9885.52</v>
       </c>
       <c r="J114">
-        <v>170.44</v>
+        <v>171.54</v>
       </c>
       <c r="L114">
         <v>161.92</v>
@@ -7074,12 +7086,162 @@
         <v>0</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="R114">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
+      <c r="A115" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" t="s">
+        <v>127</v>
+      </c>
+      <c r="D115" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>341.85</v>
+      </c>
+      <c r="G115">
+        <v>29</v>
+      </c>
+      <c r="H115">
+        <v>29</v>
+      </c>
+      <c r="I115">
+        <v>9913.650000000001</v>
+      </c>
+      <c r="J115">
+        <v>341.85</v>
+      </c>
+      <c r="L115">
+        <v>324.76</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>0</v>
+      </c>
+      <c r="R115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
+      <c r="A116" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" t="s">
+        <v>95</v>
+      </c>
+      <c r="C116" t="s">
+        <v>127</v>
+      </c>
+      <c r="D116" t="s">
+        <v>131</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>3790.9</v>
+      </c>
+      <c r="G116">
+        <v>2</v>
+      </c>
+      <c r="H116">
+        <v>2</v>
+      </c>
+      <c r="I116">
+        <v>7581.8</v>
+      </c>
+      <c r="J116">
+        <v>3790.9</v>
+      </c>
+      <c r="L116">
+        <v>3601.36</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>0</v>
+      </c>
+      <c r="R116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
+      <c r="A117" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" t="s">
+        <v>126</v>
+      </c>
+      <c r="C117" t="s">
+        <v>127</v>
+      </c>
+      <c r="D117" t="s">
+        <v>131</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>487.9</v>
+      </c>
+      <c r="G117">
+        <v>20</v>
+      </c>
+      <c r="H117">
+        <v>20</v>
+      </c>
+      <c r="I117">
+        <v>9758</v>
+      </c>
+      <c r="J117">
+        <v>487.9</v>
+      </c>
+      <c r="L117">
+        <v>463.5</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>0</v>
+      </c>
+      <c r="R117">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="142">
   <si>
     <t>Buy Date</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -800,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S117"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -877,13 +880,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -913,7 +916,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -933,10 +936,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
         <v>131</v>
@@ -951,7 +954,7 @@
         <v>8</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>9856</v>
@@ -959,23 +962,29 @@
       <c r="J3">
         <v>1349.1</v>
       </c>
+      <c r="K3" t="s">
+        <v>55</v>
+      </c>
       <c r="L3">
         <v>1293.6</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1282.2</v>
+      </c>
+      <c r="N3" t="s">
+        <v>140</v>
       </c>
       <c r="O3">
-        <v>492.8000000000002</v>
+        <v>693.6000000000004</v>
       </c>
       <c r="P3">
-        <v>468.4</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>961.2</v>
+        <v>693.6000000000004</v>
       </c>
       <c r="R3">
-        <v>9.75</v>
+        <v>7.04</v>
       </c>
       <c r="S3" t="s">
         <v>34</v>
@@ -986,13 +995,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1022,7 +1031,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1042,13 +1051,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1078,7 +1087,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1098,13 +1107,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1134,7 +1143,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1154,13 +1163,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1178,7 +1187,7 @@
         <v>8960</v>
       </c>
       <c r="J7">
-        <v>1250.9</v>
+        <v>1235.8</v>
       </c>
       <c r="L7">
         <v>1216</v>
@@ -1190,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-203.7</v>
+        <v>-309.4</v>
       </c>
       <c r="Q7">
-        <v>-203.7</v>
+        <v>-309.4</v>
       </c>
       <c r="R7">
-        <v>-2.27</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1204,13 +1213,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1240,7 +1249,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1260,13 +1269,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1296,7 +1305,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1316,13 +1325,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1352,7 +1361,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1372,13 +1381,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1399,7 +1408,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1408,7 +1417,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1423,7 +1432,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1431,13 +1440,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1467,7 +1476,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1490,13 +1499,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1526,7 +1535,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1546,13 +1555,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1582,7 +1591,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1602,13 +1611,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1638,7 +1647,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1658,13 +1667,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1694,7 +1703,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1714,13 +1723,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1738,7 +1747,7 @@
         <v>9282</v>
       </c>
       <c r="J17">
-        <v>9804.5</v>
+        <v>9383</v>
       </c>
       <c r="L17">
         <v>9282</v>
@@ -1750,13 +1759,13 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>522.5</v>
+        <v>101</v>
       </c>
       <c r="Q17">
-        <v>522.5</v>
+        <v>101</v>
       </c>
       <c r="R17">
-        <v>5.63</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1764,13 +1773,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1800,7 +1809,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1820,13 +1829,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1856,7 +1865,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1876,13 +1885,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1912,7 +1921,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1932,13 +1941,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1959,7 +1968,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1968,7 +1977,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -1988,13 +1997,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2015,7 +2024,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2024,7 +2033,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2044,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2080,7 +2089,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2100,13 +2109,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2136,7 +2145,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2156,13 +2165,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2192,7 +2201,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2212,13 +2221,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2239,7 +2248,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2248,7 +2257,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2268,13 +2277,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2304,7 +2313,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2324,13 +2333,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2360,7 +2369,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2380,13 +2389,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2416,7 +2425,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2436,13 +2445,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2472,7 +2481,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2492,13 +2501,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2519,7 +2528,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2528,7 +2537,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2548,13 +2557,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2584,7 +2593,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2604,13 +2613,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2640,7 +2649,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2660,13 +2669,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2687,7 +2696,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2696,7 +2705,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2716,13 +2725,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2743,7 +2752,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2752,7 +2761,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2772,13 +2781,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2808,7 +2817,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2828,13 +2837,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2864,7 +2873,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2884,13 +2893,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2920,7 +2929,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2943,13 +2952,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2979,7 +2988,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -2999,13 +3008,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3035,7 +3044,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3055,13 +3064,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3091,7 +3100,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3111,13 +3120,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3138,7 +3147,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3147,7 +3156,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3167,13 +3176,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3194,7 +3203,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3203,7 +3212,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3223,13 +3232,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3259,7 +3268,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3279,13 +3288,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3315,7 +3324,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3335,13 +3344,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3359,7 +3368,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>378.05</v>
+        <v>376.25</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3371,13 +3380,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>443.8</v>
+        <v>418.6</v>
       </c>
       <c r="Q46">
-        <v>928.6900000000001</v>
+        <v>903.49</v>
       </c>
       <c r="R46">
-        <v>9.58</v>
+        <v>9.32</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3388,13 +3397,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3424,7 +3433,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3444,13 +3453,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3480,7 +3489,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3500,13 +3509,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3536,7 +3545,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3559,13 +3568,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3595,7 +3604,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3615,13 +3624,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3651,7 +3660,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3671,13 +3680,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3707,7 +3716,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3730,13 +3739,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3766,7 +3775,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3786,13 +3795,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3822,7 +3831,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3845,13 +3854,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3881,7 +3890,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3904,13 +3913,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3940,7 +3949,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3960,13 +3969,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3987,7 +3996,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -3996,7 +4005,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4016,13 +4025,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4052,7 +4061,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4072,13 +4081,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4108,7 +4117,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4131,10 +4140,10 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
         <v>131</v>
@@ -4149,7 +4158,7 @@
         <v>62</v>
       </c>
       <c r="H60">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>9944.179999999998</v>
@@ -4157,23 +4166,29 @@
       <c r="J60">
         <v>156.73</v>
       </c>
+      <c r="K60" t="s">
+        <v>55</v>
+      </c>
       <c r="L60">
         <v>152.37</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="N60" t="s">
+        <v>140</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>-520.1799999999992</v>
       </c>
       <c r="P60">
-        <v>-226.92</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>-226.92</v>
+        <v>-520.1799999999992</v>
       </c>
       <c r="R60">
-        <v>-2.28</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4181,13 +4196,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4217,7 +4232,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4240,13 +4255,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4276,7 +4291,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4291,7 +4306,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4299,13 +4314,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4335,7 +4350,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4355,13 +4370,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4391,7 +4406,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4411,13 +4426,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4447,7 +4462,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4467,13 +4482,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4491,7 +4506,7 @@
         <v>9877.15</v>
       </c>
       <c r="J66">
-        <v>276.35</v>
+        <v>270.8</v>
       </c>
       <c r="L66">
         <v>266.95</v>
@@ -4503,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>347.8</v>
+        <v>142.45</v>
       </c>
       <c r="Q66">
-        <v>347.8</v>
+        <v>142.45</v>
       </c>
       <c r="R66">
-        <v>3.52</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4517,13 +4532,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4553,7 +4568,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4573,13 +4588,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4609,7 +4624,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4629,13 +4644,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4656,7 +4671,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4665,7 +4680,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4685,13 +4700,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4721,7 +4736,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4741,13 +4756,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4765,7 +4780,7 @@
         <v>9785.75</v>
       </c>
       <c r="J71">
-        <v>778.85</v>
+        <v>778</v>
       </c>
       <c r="L71">
         <v>752.75</v>
@@ -4777,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>339.3</v>
+        <v>328.25</v>
       </c>
       <c r="Q71">
-        <v>339.3</v>
+        <v>328.25</v>
       </c>
       <c r="R71">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4791,13 +4806,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C72" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4827,7 +4842,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4847,13 +4862,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4883,7 +4898,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4903,13 +4918,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4939,7 +4954,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -4959,13 +4974,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4995,7 +5010,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5015,13 +5030,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5051,7 +5066,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5071,13 +5086,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D77" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5107,7 +5122,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5127,13 +5142,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D78" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5151,7 +5166,7 @@
         <v>6019</v>
       </c>
       <c r="J78">
-        <v>5963</v>
+        <v>5890</v>
       </c>
       <c r="L78">
         <v>5718.05</v>
@@ -5163,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>-56</v>
+        <v>-129</v>
       </c>
       <c r="Q78">
-        <v>-56</v>
+        <v>-129</v>
       </c>
       <c r="R78">
-        <v>-0.93</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -5177,13 +5192,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D79" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5213,7 +5228,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5233,13 +5248,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5269,7 +5284,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5289,13 +5304,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D81" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5325,7 +5340,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5345,13 +5360,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D82" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5381,7 +5396,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5404,13 +5419,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5428,7 +5443,7 @@
         <v>9485.6</v>
       </c>
       <c r="J83">
-        <v>595.65</v>
+        <v>575</v>
       </c>
       <c r="L83">
         <v>563.21</v>
@@ -5440,13 +5455,13 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>44.8</v>
+        <v>-285.6</v>
       </c>
       <c r="Q83">
-        <v>44.8</v>
+        <v>-285.6</v>
       </c>
       <c r="R83">
-        <v>0.47</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5454,13 +5469,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5490,7 +5505,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5510,13 +5525,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D85" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5546,7 +5561,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5566,13 +5581,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5602,7 +5617,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5622,13 +5637,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5646,7 +5661,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1313.5</v>
+        <v>1287</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5658,13 +5673,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>200.9</v>
+        <v>15.4</v>
       </c>
       <c r="Q87">
-        <v>200.9</v>
+        <v>15.4</v>
       </c>
       <c r="R87">
-        <v>2.23</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5672,13 +5687,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5708,7 +5723,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5728,13 +5743,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5764,7 +5779,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5784,13 +5799,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5808,7 +5823,7 @@
         <v>9117.200000000001</v>
       </c>
       <c r="J90">
-        <v>2255</v>
+        <v>2194.6</v>
       </c>
       <c r="L90">
         <v>2165.34</v>
@@ -5820,13 +5835,13 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>-97.2</v>
+        <v>-338.8</v>
       </c>
       <c r="Q90">
-        <v>-97.2</v>
+        <v>-338.8</v>
       </c>
       <c r="R90">
-        <v>-1.07</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -5834,13 +5849,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C91" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5858,7 +5873,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>299.45</v>
+        <v>295.2</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5870,13 +5885,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>158.4</v>
+        <v>18.15</v>
       </c>
       <c r="Q91">
-        <v>158.4</v>
+        <v>18.15</v>
       </c>
       <c r="R91">
-        <v>1.63</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5884,13 +5899,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C92" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D92" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5920,7 +5935,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -5940,10 +5955,10 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
         <v>131</v>
@@ -5958,7 +5973,7 @@
         <v>79</v>
       </c>
       <c r="H93">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I93">
         <v>9961.9</v>
@@ -5966,23 +5981,29 @@
       <c r="J93">
         <v>122.2</v>
       </c>
+      <c r="K93" t="s">
+        <v>55</v>
+      </c>
       <c r="L93">
         <v>119.79</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>116.25</v>
+      </c>
+      <c r="N93" t="s">
+        <v>140</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>-778.1499999999995</v>
       </c>
       <c r="P93">
-        <v>-308.1</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>-308.1</v>
+        <v>-778.1499999999995</v>
       </c>
       <c r="R93">
-        <v>-3.09</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -5990,13 +6011,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C94" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6026,7 +6047,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6046,13 +6067,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6082,7 +6103,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6102,13 +6123,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C96" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6138,7 +6159,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6158,13 +6179,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6194,7 +6215,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6214,13 +6235,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D98" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6238,7 +6259,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>449.4</v>
+        <v>437.65</v>
       </c>
       <c r="L98">
         <v>409.4</v>
@@ -6250,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>424.35</v>
+        <v>154.1</v>
       </c>
       <c r="Q98">
-        <v>424.35</v>
+        <v>154.1</v>
       </c>
       <c r="R98">
-        <v>4.28</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -6264,13 +6285,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D99" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6300,7 +6321,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6320,13 +6341,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6356,7 +6377,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6376,13 +6397,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D101" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6412,7 +6433,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6432,13 +6453,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6468,7 +6489,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6488,13 +6509,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D103" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6524,7 +6545,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6544,13 +6565,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C104" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6580,7 +6601,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6600,13 +6621,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6624,7 +6645,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1784.5</v>
+        <v>1807.4</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6636,13 +6657,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>160</v>
+        <v>274.5</v>
       </c>
       <c r="Q105">
-        <v>160</v>
+        <v>274.5</v>
       </c>
       <c r="R105">
-        <v>1.83</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6650,13 +6671,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C106" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6674,7 +6695,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1352.5</v>
+        <v>1331.4</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6686,13 +6707,13 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>-10.5</v>
+        <v>-158.2</v>
       </c>
       <c r="Q106">
-        <v>-10.5</v>
+        <v>-158.2</v>
       </c>
       <c r="R106">
-        <v>-0.11</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6700,10 +6721,10 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D107" t="s">
         <v>131</v>
@@ -6718,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="H107">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I107">
         <v>9939.049999999999</v>
@@ -6726,23 +6747,29 @@
       <c r="J107">
         <v>884.55</v>
       </c>
+      <c r="K107" t="s">
+        <v>55</v>
+      </c>
       <c r="L107">
         <v>858.37</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>841</v>
+      </c>
+      <c r="N107" t="s">
+        <v>140</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>-688.0499999999995</v>
       </c>
       <c r="P107">
-        <v>-209</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>-209</v>
+        <v>-688.0499999999995</v>
       </c>
       <c r="R107">
-        <v>-2.1</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -6750,13 +6777,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C108" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6774,7 +6801,7 @@
         <v>9512.5</v>
       </c>
       <c r="J108">
-        <v>973.45</v>
+        <v>931.65</v>
       </c>
       <c r="L108">
         <v>903.6900000000001</v>
@@ -6786,13 +6813,13 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>222</v>
+        <v>-196</v>
       </c>
       <c r="Q108">
-        <v>222</v>
+        <v>-196</v>
       </c>
       <c r="R108">
-        <v>2.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6800,13 +6827,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C109" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6824,7 +6851,7 @@
         <v>9730.6</v>
       </c>
       <c r="J109">
-        <v>451.4</v>
+        <v>438.5</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6836,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>200.2</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="Q109">
-        <v>200.2</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="R109">
-        <v>2.06</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6850,13 +6877,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C110" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6874,7 +6901,7 @@
         <v>9836.5</v>
       </c>
       <c r="J110">
-        <v>200.57</v>
+        <v>191.01</v>
       </c>
       <c r="L110">
         <v>186.89</v>
@@ -6886,13 +6913,13 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>192</v>
+        <v>-286</v>
       </c>
       <c r="Q110">
-        <v>192</v>
+        <v>-286</v>
       </c>
       <c r="R110">
-        <v>1.95</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6900,13 +6927,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6924,7 +6951,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7775</v>
+        <v>7779</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -6936,13 +6963,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q111">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="R111">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6950,10 +6977,10 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D112" t="s">
         <v>131</v>
@@ -6968,7 +6995,7 @@
         <v>4</v>
       </c>
       <c r="H112">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I112">
         <v>8306</v>
@@ -6976,23 +7003,29 @@
       <c r="J112">
         <v>2089.2</v>
       </c>
+      <c r="K112" t="s">
+        <v>55</v>
+      </c>
       <c r="L112">
         <v>1972.67</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>1972.67</v>
+      </c>
+      <c r="N112" t="s">
+        <v>139</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>-415.3199999999997</v>
       </c>
       <c r="P112">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>50.8</v>
+        <v>-415.3199999999997</v>
       </c>
       <c r="R112">
-        <v>0.61</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -7000,10 +7033,10 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D113" t="s">
         <v>131</v>
@@ -7018,7 +7051,7 @@
         <v>81</v>
       </c>
       <c r="H113">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I113">
         <v>9953.280000000001</v>
@@ -7026,23 +7059,29 @@
       <c r="J113">
         <v>126.34</v>
       </c>
+      <c r="K113" t="s">
+        <v>55</v>
+      </c>
       <c r="L113">
         <v>116.74</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>116.74</v>
+      </c>
+      <c r="N113" t="s">
+        <v>139</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>-497.34</v>
       </c>
       <c r="P113">
-        <v>280.26</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>280.26</v>
+        <v>-497.34</v>
       </c>
       <c r="R113">
-        <v>2.82</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -7050,10 +7089,10 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D114" t="s">
         <v>131</v>
@@ -7068,7 +7107,7 @@
         <v>58</v>
       </c>
       <c r="H114">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I114">
         <v>9885.52</v>
@@ -7076,23 +7115,29 @@
       <c r="J114">
         <v>171.54</v>
       </c>
+      <c r="K114" t="s">
+        <v>55</v>
+      </c>
       <c r="L114">
         <v>161.92</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="N114" t="s">
+        <v>140</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>-721.5199999999999</v>
       </c>
       <c r="P114">
-        <v>63.8</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>63.8</v>
+        <v>-721.5199999999999</v>
       </c>
       <c r="R114">
-        <v>0.65</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -7100,10 +7145,10 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D115" t="s">
         <v>131</v>
@@ -7118,31 +7163,37 @@
         <v>29</v>
       </c>
       <c r="H115">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>9913.650000000001</v>
+        <v>9913.65</v>
       </c>
       <c r="J115">
         <v>341.85</v>
       </c>
+      <c r="K115" t="s">
+        <v>55</v>
+      </c>
       <c r="L115">
         <v>324.76</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>324.76</v>
+      </c>
+      <c r="N115" t="s">
+        <v>139</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>-495.6100000000009</v>
       </c>
       <c r="P115">
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>-495.6100000000009</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -7150,10 +7201,10 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C116" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D116" t="s">
         <v>131</v>
@@ -7168,7 +7219,7 @@
         <v>2</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116">
         <v>7581.8</v>
@@ -7176,23 +7227,29 @@
       <c r="J116">
         <v>3790.9</v>
       </c>
+      <c r="K116" t="s">
+        <v>55</v>
+      </c>
       <c r="L116">
         <v>3601.36</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>3601.36</v>
+      </c>
+      <c r="N116" t="s">
+        <v>139</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>-379.0799999999999</v>
       </c>
       <c r="P116">
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>-379.0799999999999</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -7200,13 +7257,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7224,7 +7281,7 @@
         <v>9758</v>
       </c>
       <c r="J117">
-        <v>487.9</v>
+        <v>466.7</v>
       </c>
       <c r="L117">
         <v>463.5</v>
@@ -7236,12 +7293,62 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>-424</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>-424</v>
       </c>
       <c r="R117">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
+      <c r="A118" t="s">
+        <v>55</v>
+      </c>
+      <c r="B118" t="s">
+        <v>79</v>
+      </c>
+      <c r="C118" t="s">
+        <v>129</v>
+      </c>
+      <c r="D118" t="s">
+        <v>132</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>1144.1</v>
+      </c>
+      <c r="G118">
+        <v>8</v>
+      </c>
+      <c r="H118">
+        <v>8</v>
+      </c>
+      <c r="I118">
+        <v>9152.799999999999</v>
+      </c>
+      <c r="J118">
+        <v>1144.1</v>
+      </c>
+      <c r="L118">
+        <v>1086.89</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="143">
   <si>
     <t>Buy Date</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -803,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S118"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -880,13 +883,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -916,7 +919,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -936,13 +939,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -972,7 +975,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -995,13 +998,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1031,7 +1034,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1051,13 +1054,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1087,7 +1090,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1107,13 +1110,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1143,7 +1146,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1163,13 +1166,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1187,7 +1190,7 @@
         <v>8960</v>
       </c>
       <c r="J7">
-        <v>1235.8</v>
+        <v>1241.2</v>
       </c>
       <c r="L7">
         <v>1216</v>
@@ -1199,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-309.4</v>
+        <v>-271.6</v>
       </c>
       <c r="Q7">
-        <v>-309.4</v>
+        <v>-271.6</v>
       </c>
       <c r="R7">
-        <v>-3.45</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1213,13 +1216,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1249,7 +1252,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1269,13 +1272,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1305,7 +1308,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1325,13 +1328,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1361,7 +1364,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1381,13 +1384,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1408,7 +1411,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1417,7 +1420,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1432,7 +1435,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1440,13 +1443,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1476,7 +1479,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1499,13 +1502,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1535,7 +1538,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1555,13 +1558,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1591,7 +1594,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1611,13 +1614,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1647,7 +1650,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1667,13 +1670,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1703,7 +1706,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1723,13 +1726,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1747,7 +1750,7 @@
         <v>9282</v>
       </c>
       <c r="J17">
-        <v>9383</v>
+        <v>9610</v>
       </c>
       <c r="L17">
         <v>9282</v>
@@ -1759,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>101</v>
+        <v>328</v>
       </c>
       <c r="Q17">
-        <v>101</v>
+        <v>328</v>
       </c>
       <c r="R17">
-        <v>1.09</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1773,13 +1776,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1809,7 +1812,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1829,13 +1832,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1865,7 +1868,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1885,13 +1888,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1921,7 +1924,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1941,13 +1944,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1968,7 +1971,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1977,7 +1980,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -1997,13 +2000,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2024,7 +2027,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2033,7 +2036,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2053,13 +2056,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2089,7 +2092,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2109,13 +2112,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2145,7 +2148,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2165,13 +2168,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2201,7 +2204,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2221,13 +2224,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2248,7 +2251,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2257,7 +2260,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2277,13 +2280,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2313,7 +2316,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2333,13 +2336,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2369,7 +2372,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2389,13 +2392,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2425,7 +2428,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2445,13 +2448,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2481,7 +2484,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2501,13 +2504,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2528,7 +2531,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2537,7 +2540,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2557,13 +2560,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2593,7 +2596,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2613,13 +2616,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2649,7 +2652,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2669,13 +2672,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2696,7 +2699,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2705,7 +2708,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2725,13 +2728,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2752,7 +2755,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2761,7 +2764,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2781,13 +2784,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2817,7 +2820,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2837,13 +2840,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2873,7 +2876,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2893,13 +2896,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2929,7 +2932,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2952,13 +2955,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2988,7 +2991,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3008,13 +3011,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3044,7 +3047,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3064,13 +3067,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3100,7 +3103,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3120,13 +3123,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3147,7 +3150,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3156,7 +3159,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3176,13 +3179,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3203,7 +3206,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3212,7 +3215,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3232,13 +3235,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3268,7 +3271,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3288,13 +3291,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3324,7 +3327,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3344,13 +3347,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3368,7 +3371,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>376.25</v>
+        <v>377.3</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3380,13 +3383,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>418.6</v>
+        <v>433.3</v>
       </c>
       <c r="Q46">
-        <v>903.49</v>
+        <v>918.1900000000001</v>
       </c>
       <c r="R46">
-        <v>9.32</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3397,13 +3400,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3433,7 +3436,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3453,13 +3456,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3489,7 +3492,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3509,13 +3512,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3545,7 +3548,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3568,13 +3571,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3604,7 +3607,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3624,13 +3627,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3660,7 +3663,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3680,13 +3683,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3716,7 +3719,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3739,13 +3742,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3775,7 +3778,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3795,13 +3798,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3831,7 +3834,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3854,13 +3857,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3890,7 +3893,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3913,13 +3916,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3949,7 +3952,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3969,13 +3972,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3996,7 +3999,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4005,7 +4008,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4025,13 +4028,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4061,7 +4064,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4081,13 +4084,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4117,7 +4120,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4140,13 +4143,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4176,7 +4179,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4196,13 +4199,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4232,7 +4235,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4255,13 +4258,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4291,7 +4294,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4306,7 +4309,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4314,13 +4317,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4350,7 +4353,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4370,13 +4373,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4406,7 +4409,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4426,13 +4429,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4462,7 +4465,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4482,10 +4485,10 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D66" t="s">
         <v>132</v>
@@ -4500,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="H66">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>9877.15</v>
@@ -4508,23 +4511,29 @@
       <c r="J66">
         <v>270.8</v>
       </c>
+      <c r="K66" t="s">
+        <v>56</v>
+      </c>
       <c r="L66">
         <v>266.95</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>266.95</v>
+      </c>
+      <c r="N66" t="s">
+        <v>140</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>142.45</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>142.45</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4532,13 +4541,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D67" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4568,7 +4577,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4588,13 +4597,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C68" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4624,7 +4633,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4644,13 +4653,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4671,7 +4680,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4680,7 +4689,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4700,13 +4709,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4736,7 +4745,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4756,13 +4765,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4780,7 +4789,7 @@
         <v>9785.75</v>
       </c>
       <c r="J71">
-        <v>778</v>
+        <v>789.9</v>
       </c>
       <c r="L71">
         <v>752.75</v>
@@ -4792,13 +4801,13 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>328.25</v>
+        <v>482.95</v>
       </c>
       <c r="Q71">
-        <v>328.25</v>
+        <v>482.95</v>
       </c>
       <c r="R71">
-        <v>3.35</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4806,13 +4815,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D72" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4842,7 +4851,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4862,13 +4871,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D73" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4898,7 +4907,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4918,13 +4927,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D74" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4954,7 +4963,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -4974,13 +4983,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5010,7 +5019,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5030,13 +5039,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5066,7 +5075,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5086,13 +5095,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D77" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5122,7 +5131,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5142,13 +5151,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5166,7 +5175,7 @@
         <v>6019</v>
       </c>
       <c r="J78">
-        <v>5890</v>
+        <v>5968</v>
       </c>
       <c r="L78">
         <v>5718.05</v>
@@ -5178,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>-129</v>
+        <v>-51</v>
       </c>
       <c r="Q78">
-        <v>-129</v>
+        <v>-51</v>
       </c>
       <c r="R78">
-        <v>-2.14</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -5192,13 +5201,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D79" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5228,7 +5237,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5248,13 +5257,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5284,7 +5293,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5304,13 +5313,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5340,7 +5349,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5360,13 +5369,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5396,7 +5405,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5419,13 +5428,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D83" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5443,7 +5452,7 @@
         <v>9485.6</v>
       </c>
       <c r="J83">
-        <v>575</v>
+        <v>589.95</v>
       </c>
       <c r="L83">
         <v>563.21</v>
@@ -5455,13 +5464,13 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>-285.6</v>
+        <v>-46.4</v>
       </c>
       <c r="Q83">
-        <v>-285.6</v>
+        <v>-46.4</v>
       </c>
       <c r="R83">
-        <v>-3.01</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5469,13 +5478,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5505,7 +5514,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5525,13 +5534,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5561,7 +5570,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5581,13 +5590,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5617,7 +5626,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5637,13 +5646,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5661,7 +5670,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1287</v>
+        <v>1314.6</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5673,13 +5682,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>15.4</v>
+        <v>208.6</v>
       </c>
       <c r="Q87">
-        <v>15.4</v>
+        <v>208.6</v>
       </c>
       <c r="R87">
-        <v>0.17</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5687,13 +5696,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5723,7 +5732,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5743,13 +5752,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5779,7 +5788,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5799,13 +5808,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D90" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5823,7 +5832,7 @@
         <v>9117.200000000001</v>
       </c>
       <c r="J90">
-        <v>2194.6</v>
+        <v>2190.2</v>
       </c>
       <c r="L90">
         <v>2165.34</v>
@@ -5835,13 +5844,13 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>-338.8</v>
+        <v>-356.4</v>
       </c>
       <c r="Q90">
-        <v>-338.8</v>
+        <v>-356.4</v>
       </c>
       <c r="R90">
-        <v>-3.72</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -5849,13 +5858,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5873,7 +5882,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>295.2</v>
+        <v>298.65</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5885,13 +5894,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>18.15</v>
+        <v>132</v>
       </c>
       <c r="Q91">
-        <v>18.15</v>
+        <v>132</v>
       </c>
       <c r="R91">
-        <v>0.19</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5899,13 +5908,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5935,7 +5944,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -5955,13 +5964,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5991,7 +6000,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6011,13 +6020,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6047,7 +6056,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6067,13 +6076,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6103,7 +6112,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6123,13 +6132,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6159,7 +6168,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6179,13 +6188,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C97" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6215,7 +6224,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6235,13 +6244,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6259,7 +6268,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>437.65</v>
+        <v>443.55</v>
       </c>
       <c r="L98">
         <v>409.4</v>
@@ -6271,13 +6280,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>154.1</v>
+        <v>289.8</v>
       </c>
       <c r="Q98">
-        <v>154.1</v>
+        <v>289.8</v>
       </c>
       <c r="R98">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -6285,13 +6294,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6321,7 +6330,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6341,13 +6350,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6377,7 +6386,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6397,13 +6406,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D101" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6433,7 +6442,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6453,13 +6462,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D102" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6489,7 +6498,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6509,13 +6518,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D103" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6545,7 +6554,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6565,13 +6574,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D104" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6601,7 +6610,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6621,13 +6630,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D105" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6645,7 +6654,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1807.4</v>
+        <v>1812.8</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6657,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>274.5</v>
+        <v>301.5</v>
       </c>
       <c r="Q105">
-        <v>274.5</v>
+        <v>301.5</v>
       </c>
       <c r="R105">
-        <v>3.13</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6671,13 +6680,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6695,7 +6704,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1331.4</v>
+        <v>1358</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6707,13 +6716,13 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>-158.2</v>
+        <v>28</v>
       </c>
       <c r="Q106">
-        <v>-158.2</v>
+        <v>28</v>
       </c>
       <c r="R106">
-        <v>-1.67</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6721,13 +6730,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6757,7 +6766,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6777,13 +6786,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D108" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6801,7 +6810,7 @@
         <v>9512.5</v>
       </c>
       <c r="J108">
-        <v>931.65</v>
+        <v>938.5</v>
       </c>
       <c r="L108">
         <v>903.6900000000001</v>
@@ -6813,13 +6822,13 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>-196</v>
+        <v>-127.5</v>
       </c>
       <c r="Q108">
-        <v>-196</v>
+        <v>-127.5</v>
       </c>
       <c r="R108">
-        <v>-2.06</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6827,13 +6836,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C109" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D109" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6851,7 +6860,7 @@
         <v>9730.6</v>
       </c>
       <c r="J109">
-        <v>438.5</v>
+        <v>445.45</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6863,13 +6872,13 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>-83.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="Q109">
-        <v>-83.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="R109">
-        <v>-0.86</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6877,13 +6886,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D110" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6901,7 +6910,7 @@
         <v>9836.5</v>
       </c>
       <c r="J110">
-        <v>191.01</v>
+        <v>195</v>
       </c>
       <c r="L110">
         <v>186.89</v>
@@ -6913,13 +6922,13 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>-286</v>
+        <v>-86.5</v>
       </c>
       <c r="Q110">
-        <v>-286</v>
+        <v>-86.5</v>
       </c>
       <c r="R110">
-        <v>-2.91</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6927,13 +6936,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C111" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D111" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6951,7 +6960,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7779</v>
+        <v>7803</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -6963,13 +6972,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="Q111">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="R111">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6977,13 +6986,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C112" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D112" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7013,7 +7022,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7033,13 +7042,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C113" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7069,7 +7078,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7089,13 +7098,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C114" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D114" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7125,7 +7134,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7145,13 +7154,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7181,7 +7190,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7201,13 +7210,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D116" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7237,7 +7246,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7257,13 +7266,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7281,7 +7290,7 @@
         <v>9758</v>
       </c>
       <c r="J117">
-        <v>466.7</v>
+        <v>480.9</v>
       </c>
       <c r="L117">
         <v>463.5</v>
@@ -7293,13 +7302,13 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>-424</v>
+        <v>-140</v>
       </c>
       <c r="Q117">
-        <v>-424</v>
+        <v>-140</v>
       </c>
       <c r="R117">
-        <v>-4.35</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -7307,13 +7316,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C118" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D118" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7331,7 +7340,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1144.1</v>
+        <v>1187.2</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7343,12 +7352,212 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>344.8</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>344.8</v>
       </c>
       <c r="R118">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
+      <c r="A119" t="s">
+        <v>56</v>
+      </c>
+      <c r="B119" t="s">
+        <v>116</v>
+      </c>
+      <c r="C119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D119" t="s">
+        <v>133</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>334.4</v>
+      </c>
+      <c r="G119">
+        <v>29</v>
+      </c>
+      <c r="H119">
+        <v>29</v>
+      </c>
+      <c r="I119">
+        <v>9697.599999999999</v>
+      </c>
+      <c r="J119">
+        <v>334.4</v>
+      </c>
+      <c r="L119">
+        <v>317.68</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
+      <c r="A120" t="s">
+        <v>56</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+      <c r="C120" t="s">
+        <v>130</v>
+      </c>
+      <c r="D120" t="s">
+        <v>133</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>1314.7</v>
+      </c>
+      <c r="G120">
+        <v>7</v>
+      </c>
+      <c r="H120">
+        <v>7</v>
+      </c>
+      <c r="I120">
+        <v>9202.9</v>
+      </c>
+      <c r="J120">
+        <v>1314.7</v>
+      </c>
+      <c r="L120">
+        <v>1248.96</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
+      <c r="A121" t="s">
+        <v>56</v>
+      </c>
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" t="s">
+        <v>129</v>
+      </c>
+      <c r="D121" t="s">
+        <v>133</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>856.9</v>
+      </c>
+      <c r="G121">
+        <v>11</v>
+      </c>
+      <c r="H121">
+        <v>11</v>
+      </c>
+      <c r="I121">
+        <v>9425.9</v>
+      </c>
+      <c r="J121">
+        <v>856.9</v>
+      </c>
+      <c r="L121">
+        <v>814.05</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18">
+      <c r="A122" t="s">
+        <v>56</v>
+      </c>
+      <c r="B122" t="s">
+        <v>57</v>
+      </c>
+      <c r="C122" t="s">
+        <v>129</v>
+      </c>
+      <c r="D122" t="s">
+        <v>133</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>1996.5</v>
+      </c>
+      <c r="G122">
+        <v>5</v>
+      </c>
+      <c r="H122">
+        <v>5</v>
+      </c>
+      <c r="I122">
+        <v>9982.5</v>
+      </c>
+      <c r="J122">
+        <v>1996.5</v>
+      </c>
+      <c r="L122">
+        <v>1896.67</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -7387,7 +7387,7 @@
         <v>29</v>
       </c>
       <c r="I119">
-        <v>9697.599999999999</v>
+        <v>9697.6</v>
       </c>
       <c r="J119">
         <v>334.4</v>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="145">
   <si>
     <t>Buy Date</t>
   </si>
@@ -187,6 +187,9 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -401,6 +404,9 @@
   </si>
   <si>
     <t>DABUR</t>
+  </si>
+  <si>
+    <t>HINDCOPPER</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -806,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -883,13 +889,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -919,7 +925,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -939,13 +945,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -975,7 +981,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -998,13 +1004,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1034,7 +1040,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1054,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1090,7 +1096,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1110,13 +1116,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1146,7 +1152,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1166,13 +1172,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1184,7 +1190,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>8960</v>
@@ -1192,23 +1198,29 @@
       <c r="J7">
         <v>1241.2</v>
       </c>
+      <c r="K7" t="s">
+        <v>57</v>
+      </c>
       <c r="L7">
         <v>1216</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1216</v>
+      </c>
+      <c r="N7" t="s">
+        <v>142</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-448</v>
       </c>
       <c r="P7">
-        <v>-271.6</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>-271.6</v>
+        <v>-448</v>
       </c>
       <c r="R7">
-        <v>-3.03</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1216,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1252,7 +1264,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1272,13 +1284,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1308,7 +1320,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1328,13 +1340,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1364,7 +1376,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1384,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1411,7 +1423,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1420,7 +1432,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1435,7 +1447,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1443,13 +1455,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1479,7 +1491,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1502,13 +1514,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1538,7 +1550,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1558,13 +1570,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1594,7 +1606,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1614,13 +1626,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1650,7 +1662,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1670,13 +1682,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1706,7 +1718,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1726,13 +1738,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1744,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>9282</v>
@@ -1752,23 +1764,29 @@
       <c r="J17">
         <v>9610</v>
       </c>
+      <c r="K17" t="s">
+        <v>57</v>
+      </c>
       <c r="L17">
         <v>9282</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>9280</v>
+      </c>
+      <c r="N17" t="s">
+        <v>143</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="P17">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>328</v>
+        <v>-2</v>
       </c>
       <c r="R17">
-        <v>3.53</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1776,13 +1794,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1812,7 +1830,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1832,13 +1850,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1868,7 +1886,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1888,13 +1906,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1924,7 +1942,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1944,13 +1962,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1971,7 +1989,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1980,7 +1998,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2000,13 +2018,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2027,7 +2045,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2036,7 +2054,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2056,13 +2074,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2092,7 +2110,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2112,13 +2130,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2148,7 +2166,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2168,13 +2186,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2204,7 +2222,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2224,13 +2242,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2251,7 +2269,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2260,7 +2278,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2280,13 +2298,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2316,7 +2334,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2336,13 +2354,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2372,7 +2390,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2392,13 +2410,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2428,7 +2446,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2448,13 +2466,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2484,7 +2502,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2504,13 +2522,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2531,7 +2549,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2540,7 +2558,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2560,13 +2578,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2596,7 +2614,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2616,13 +2634,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2652,7 +2670,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2672,13 +2690,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2699,7 +2717,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2708,7 +2726,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2728,13 +2746,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2755,7 +2773,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2764,7 +2782,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2784,13 +2802,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2820,7 +2838,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2840,13 +2858,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2876,7 +2894,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2896,13 +2914,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2932,7 +2950,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2955,13 +2973,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2991,7 +3009,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3011,13 +3029,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3047,7 +3065,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3067,13 +3085,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3103,7 +3121,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3123,13 +3141,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3150,7 +3168,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3159,7 +3177,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3179,13 +3197,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3206,7 +3224,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3215,7 +3233,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3235,13 +3253,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3271,7 +3289,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3291,13 +3309,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3327,7 +3345,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3347,13 +3365,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3371,7 +3389,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>377.3</v>
+        <v>390.55</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3383,13 +3401,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>433.3</v>
+        <v>618.8</v>
       </c>
       <c r="Q46">
-        <v>918.1900000000001</v>
+        <v>1103.69</v>
       </c>
       <c r="R46">
-        <v>9.470000000000001</v>
+        <v>11.38</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3400,13 +3418,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3436,7 +3454,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3456,13 +3474,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3492,7 +3510,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3512,13 +3530,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D49" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3548,7 +3566,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3571,13 +3589,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D50" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3607,7 +3625,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3627,13 +3645,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3663,7 +3681,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3683,13 +3701,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3719,7 +3737,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3742,13 +3760,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3778,7 +3796,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3798,13 +3816,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3834,7 +3852,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3857,13 +3875,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3893,7 +3911,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3916,13 +3934,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3952,7 +3970,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3972,13 +3990,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D57" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3999,7 +4017,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4008,7 +4026,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4028,13 +4046,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D58" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4064,7 +4082,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4084,13 +4102,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4120,7 +4138,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4143,13 +4161,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4179,7 +4197,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4199,13 +4217,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4235,7 +4253,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4258,13 +4276,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4294,7 +4312,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4309,7 +4327,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4317,13 +4335,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4353,7 +4371,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4373,13 +4391,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4409,7 +4427,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4429,13 +4447,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D65" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4465,7 +4483,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4485,13 +4503,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4521,7 +4539,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4541,13 +4559,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D67" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4577,7 +4595,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4597,13 +4615,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4633,7 +4651,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4653,13 +4671,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4680,7 +4698,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4689,7 +4707,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4709,13 +4727,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4745,7 +4763,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4765,13 +4783,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4783,7 +4801,7 @@
         <v>13</v>
       </c>
       <c r="H71">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>9785.75</v>
@@ -4791,23 +4809,29 @@
       <c r="J71">
         <v>789.9</v>
       </c>
+      <c r="K71" t="s">
+        <v>57</v>
+      </c>
       <c r="L71">
         <v>752.75</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>752.75</v>
+      </c>
+      <c r="N71" t="s">
+        <v>142</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>482.95</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>482.95</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>4.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4815,13 +4839,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4851,7 +4875,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4871,13 +4895,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D73" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4907,7 +4931,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4927,13 +4951,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D74" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4963,7 +4987,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -4983,13 +5007,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5019,7 +5043,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5039,13 +5063,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D76" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5075,7 +5099,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5095,13 +5119,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C77" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5131,7 +5155,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5151,13 +5175,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5169,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78">
         <v>6019</v>
@@ -5177,23 +5201,29 @@
       <c r="J78">
         <v>5968</v>
       </c>
+      <c r="K78" t="s">
+        <v>57</v>
+      </c>
       <c r="L78">
         <v>5718.05</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>5718.05</v>
+      </c>
+      <c r="N78" t="s">
+        <v>142</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>-300.9499999999998</v>
       </c>
       <c r="P78">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>-51</v>
+        <v>-300.9499999999998</v>
       </c>
       <c r="R78">
-        <v>-0.85</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -5201,13 +5231,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D79" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5237,7 +5267,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5257,13 +5287,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D80" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5293,7 +5323,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5313,13 +5343,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5349,7 +5379,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5369,13 +5399,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5405,7 +5435,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5428,13 +5458,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5452,7 +5482,7 @@
         <v>9485.6</v>
       </c>
       <c r="J83">
-        <v>589.95</v>
+        <v>583</v>
       </c>
       <c r="L83">
         <v>563.21</v>
@@ -5464,13 +5494,13 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>-46.4</v>
+        <v>-157.6</v>
       </c>
       <c r="Q83">
-        <v>-46.4</v>
+        <v>-157.6</v>
       </c>
       <c r="R83">
-        <v>-0.49</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5478,13 +5508,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5514,7 +5544,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5534,13 +5564,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D85" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5570,7 +5600,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5590,13 +5620,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5626,7 +5656,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5646,13 +5676,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5670,7 +5700,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1314.6</v>
+        <v>1319</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5682,13 +5712,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>208.6</v>
+        <v>239.4</v>
       </c>
       <c r="Q87">
-        <v>208.6</v>
+        <v>239.4</v>
       </c>
       <c r="R87">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5696,13 +5726,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D88" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5732,7 +5762,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5752,13 +5782,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5788,7 +5818,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5808,13 +5838,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D90" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5826,7 +5856,7 @@
         <v>4</v>
       </c>
       <c r="H90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I90">
         <v>9117.200000000001</v>
@@ -5834,23 +5864,29 @@
       <c r="J90">
         <v>2190.2</v>
       </c>
+      <c r="K90" t="s">
+        <v>57</v>
+      </c>
       <c r="L90">
         <v>2165.34</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>2165.1</v>
+      </c>
+      <c r="N90" t="s">
+        <v>143</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>-456.8000000000011</v>
       </c>
       <c r="P90">
-        <v>-356.4</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>-356.4</v>
+        <v>-456.8000000000011</v>
       </c>
       <c r="R90">
-        <v>-3.91</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -5858,13 +5894,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D91" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5882,7 +5918,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>298.65</v>
+        <v>303.6</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5894,13 +5930,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>132</v>
+        <v>295.35</v>
       </c>
       <c r="Q91">
-        <v>132</v>
+        <v>295.35</v>
       </c>
       <c r="R91">
-        <v>1.36</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5908,13 +5944,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5944,7 +5980,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -5964,13 +6000,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6000,7 +6036,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6020,13 +6056,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D94" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6056,7 +6092,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6076,13 +6112,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C95" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6112,7 +6148,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6132,13 +6168,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6168,7 +6204,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6188,13 +6224,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6224,7 +6260,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6244,16 +6280,16 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98">
         <v>430.95</v>
@@ -6268,10 +6304,10 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>443.55</v>
+        <v>470.1</v>
       </c>
       <c r="L98">
-        <v>409.4</v>
+        <v>430.95</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -6280,13 +6316,13 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>289.8</v>
+        <v>900.45</v>
       </c>
       <c r="Q98">
-        <v>289.8</v>
+        <v>900.45</v>
       </c>
       <c r="R98">
-        <v>2.92</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -6294,13 +6330,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6330,7 +6366,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6350,13 +6386,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6386,7 +6422,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6406,13 +6442,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6442,7 +6478,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6462,13 +6498,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D102" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6498,7 +6534,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6518,13 +6554,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C103" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D103" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6554,7 +6590,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6574,13 +6610,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6610,7 +6646,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6630,13 +6666,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C105" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D105" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6654,7 +6690,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1812.8</v>
+        <v>1825.3</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6666,13 +6702,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>301.5</v>
+        <v>364</v>
       </c>
       <c r="Q105">
-        <v>301.5</v>
+        <v>364</v>
       </c>
       <c r="R105">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6680,13 +6716,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D106" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6704,7 +6740,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6716,13 +6752,13 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6730,13 +6766,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D107" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6766,7 +6802,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6786,13 +6822,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C108" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D108" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6804,7 +6840,7 @@
         <v>10</v>
       </c>
       <c r="H108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>9512.5</v>
@@ -6812,23 +6848,29 @@
       <c r="J108">
         <v>938.5</v>
       </c>
+      <c r="K108" t="s">
+        <v>57</v>
+      </c>
       <c r="L108">
         <v>903.6900000000001</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>903.6900000000001</v>
+      </c>
+      <c r="N108" t="s">
+        <v>142</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>-475.5999999999995</v>
       </c>
       <c r="P108">
-        <v>-127.5</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>-127.5</v>
+        <v>-475.5999999999995</v>
       </c>
       <c r="R108">
-        <v>-1.34</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6836,13 +6878,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C109" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D109" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6860,7 +6902,7 @@
         <v>9730.6</v>
       </c>
       <c r="J109">
-        <v>445.45</v>
+        <v>442.05</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6872,13 +6914,13 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>69.3</v>
+        <v>-5.5</v>
       </c>
       <c r="Q109">
-        <v>69.3</v>
+        <v>-5.5</v>
       </c>
       <c r="R109">
-        <v>0.71</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6886,13 +6928,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C110" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D110" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6910,7 +6952,7 @@
         <v>9836.5</v>
       </c>
       <c r="J110">
-        <v>195</v>
+        <v>193.47</v>
       </c>
       <c r="L110">
         <v>186.89</v>
@@ -6922,13 +6964,13 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>-86.5</v>
+        <v>-163</v>
       </c>
       <c r="Q110">
-        <v>-86.5</v>
+        <v>-163</v>
       </c>
       <c r="R110">
-        <v>-0.88</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6936,13 +6978,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C111" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D111" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6960,7 +7002,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7803</v>
+        <v>7574.5</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -6972,13 +7014,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>137</v>
+        <v>-91.5</v>
       </c>
       <c r="Q111">
-        <v>137</v>
+        <v>-91.5</v>
       </c>
       <c r="R111">
-        <v>1.79</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6986,13 +7028,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C112" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7022,7 +7064,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7042,13 +7084,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C113" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D113" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7078,7 +7120,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7098,13 +7140,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C114" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D114" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7134,7 +7176,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7154,13 +7196,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7190,7 +7232,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7210,13 +7252,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7246,7 +7288,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7266,13 +7308,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7284,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="H117">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I117">
         <v>9758</v>
@@ -7292,23 +7334,29 @@
       <c r="J117">
         <v>480.9</v>
       </c>
+      <c r="K117" t="s">
+        <v>57</v>
+      </c>
       <c r="L117">
         <v>463.5</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>463.5</v>
+      </c>
+      <c r="N117" t="s">
+        <v>142</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>-487.9999999999995</v>
       </c>
       <c r="P117">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>-140</v>
+        <v>-487.9999999999995</v>
       </c>
       <c r="R117">
-        <v>-1.43</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -7316,13 +7364,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D118" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7340,7 +7388,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1187.2</v>
+        <v>1225</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7352,13 +7400,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>344.8</v>
+        <v>647.2</v>
       </c>
       <c r="Q118">
-        <v>344.8</v>
+        <v>647.2</v>
       </c>
       <c r="R118">
-        <v>3.77</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7366,13 +7414,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D119" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7390,7 +7438,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>334.4</v>
+        <v>343.5</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7402,13 +7450,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>263.9</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>263.9</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7416,13 +7464,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C120" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7434,7 +7482,7 @@
         <v>7</v>
       </c>
       <c r="H120">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>9202.9</v>
@@ -7442,23 +7490,29 @@
       <c r="J120">
         <v>1314.7</v>
       </c>
+      <c r="K120" t="s">
+        <v>57</v>
+      </c>
       <c r="L120">
         <v>1248.96</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>1243.2</v>
+      </c>
+      <c r="N120" t="s">
+        <v>143</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>-500.5</v>
       </c>
       <c r="P120">
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>-500.5</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="121" spans="1:18">
@@ -7466,13 +7520,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D121" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7490,7 +7544,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>856.9</v>
+        <v>866.55</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7502,13 +7556,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>106.15</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>106.15</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7516,13 +7570,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C122" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D122" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7540,7 +7594,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>1996.5</v>
+        <v>2002</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7552,12 +7606,262 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="R122">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18">
+      <c r="A123" t="s">
+        <v>57</v>
+      </c>
+      <c r="B123" t="s">
+        <v>107</v>
+      </c>
+      <c r="C123" t="s">
+        <v>131</v>
+      </c>
+      <c r="D123" t="s">
+        <v>135</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>152.35</v>
+      </c>
+      <c r="G123">
+        <v>65</v>
+      </c>
+      <c r="H123">
+        <v>65</v>
+      </c>
+      <c r="I123">
+        <v>9902.75</v>
+      </c>
+      <c r="J123">
+        <v>152.35</v>
+      </c>
+      <c r="L123">
+        <v>144.73</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18">
+      <c r="A124" t="s">
+        <v>57</v>
+      </c>
+      <c r="B124" t="s">
+        <v>78</v>
+      </c>
+      <c r="C124" t="s">
+        <v>132</v>
+      </c>
+      <c r="D124" t="s">
+        <v>135</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>4129.6</v>
+      </c>
+      <c r="G124">
+        <v>2</v>
+      </c>
+      <c r="H124">
+        <v>2</v>
+      </c>
+      <c r="I124">
+        <v>8259.200000000001</v>
+      </c>
+      <c r="J124">
+        <v>4129.6</v>
+      </c>
+      <c r="L124">
+        <v>3923.12</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18">
+      <c r="A125" t="s">
+        <v>57</v>
+      </c>
+      <c r="B125" t="s">
+        <v>121</v>
+      </c>
+      <c r="C125" t="s">
+        <v>133</v>
+      </c>
+      <c r="D125" t="s">
+        <v>135</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>415.9</v>
+      </c>
+      <c r="G125">
+        <v>24</v>
+      </c>
+      <c r="H125">
+        <v>24</v>
+      </c>
+      <c r="I125">
+        <v>9981.599999999999</v>
+      </c>
+      <c r="J125">
+        <v>415.9</v>
+      </c>
+      <c r="L125">
+        <v>395.1</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18">
+      <c r="A126" t="s">
+        <v>57</v>
+      </c>
+      <c r="B126" t="s">
+        <v>115</v>
+      </c>
+      <c r="C126" t="s">
+        <v>133</v>
+      </c>
+      <c r="D126" t="s">
+        <v>135</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>149.11</v>
+      </c>
+      <c r="G126">
+        <v>67</v>
+      </c>
+      <c r="H126">
+        <v>67</v>
+      </c>
+      <c r="I126">
+        <v>9990.370000000001</v>
+      </c>
+      <c r="J126">
+        <v>149.11</v>
+      </c>
+      <c r="L126">
+        <v>141.65</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18">
+      <c r="A127" t="s">
+        <v>57</v>
+      </c>
+      <c r="B127" t="s">
+        <v>130</v>
+      </c>
+      <c r="C127" t="s">
+        <v>132</v>
+      </c>
+      <c r="D127" t="s">
+        <v>135</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>527.35</v>
+      </c>
+      <c r="G127">
+        <v>18</v>
+      </c>
+      <c r="H127">
+        <v>18</v>
+      </c>
+      <c r="I127">
+        <v>9492.300000000001</v>
+      </c>
+      <c r="J127">
+        <v>527.35</v>
+      </c>
+      <c r="L127">
+        <v>500.98</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="146">
   <si>
     <t>Buy Date</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -812,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S127"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -889,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -925,7 +928,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -945,13 +948,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -981,7 +984,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1004,13 +1007,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1040,7 +1043,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1060,13 +1063,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1096,7 +1099,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1116,13 +1119,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1152,7 +1155,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1172,13 +1175,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1208,7 +1211,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1228,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1264,7 +1267,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1284,13 +1287,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1320,7 +1323,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1340,13 +1343,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1376,7 +1379,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1396,13 +1399,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1423,7 +1426,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1432,7 +1435,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1447,7 +1450,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1455,13 +1458,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1491,7 +1494,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1514,13 +1517,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1550,7 +1553,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1570,13 +1573,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1606,7 +1609,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1626,13 +1629,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1662,7 +1665,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1682,13 +1685,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1718,7 +1721,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1738,13 +1741,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1774,7 +1777,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1794,13 +1797,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1830,7 +1833,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1850,13 +1853,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1886,7 +1889,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1906,13 +1909,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1942,7 +1945,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1962,13 +1965,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1989,7 +1992,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -1998,7 +2001,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2018,13 +2021,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2045,7 +2048,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2054,7 +2057,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2074,13 +2077,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2110,7 +2113,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2130,13 +2133,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2166,7 +2169,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2186,13 +2189,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2222,7 +2225,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2242,13 +2245,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2269,7 +2272,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2278,7 +2281,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2298,13 +2301,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2334,7 +2337,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2354,13 +2357,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2390,7 +2393,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2410,13 +2413,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2446,7 +2449,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2466,13 +2469,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2502,7 +2505,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2522,13 +2525,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2549,7 +2552,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2558,7 +2561,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2578,13 +2581,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2614,7 +2617,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2634,13 +2637,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2670,7 +2673,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2690,13 +2693,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2717,7 +2720,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2726,7 +2729,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2746,13 +2749,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2773,7 +2776,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2782,7 +2785,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2802,13 +2805,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2838,7 +2841,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2858,13 +2861,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2894,7 +2897,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2914,13 +2917,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2950,7 +2953,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2973,13 +2976,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3009,7 +3012,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3029,13 +3032,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3065,7 +3068,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3085,13 +3088,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3121,7 +3124,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3141,13 +3144,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3168,7 +3171,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3177,7 +3180,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3197,13 +3200,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3224,7 +3227,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3233,7 +3236,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3253,13 +3256,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3289,7 +3292,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3309,13 +3312,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3345,7 +3348,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3365,13 +3368,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3389,7 +3392,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>390.55</v>
+        <v>384.45</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3401,13 +3404,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>618.8</v>
+        <v>533.4</v>
       </c>
       <c r="Q46">
-        <v>1103.69</v>
+        <v>1018.29</v>
       </c>
       <c r="R46">
-        <v>11.38</v>
+        <v>10.5</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3418,13 +3421,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3454,7 +3457,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3474,13 +3477,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3510,7 +3513,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3530,13 +3533,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3566,7 +3569,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3589,13 +3592,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3625,7 +3628,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3645,13 +3648,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3681,7 +3684,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3701,13 +3704,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3737,7 +3740,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3760,13 +3763,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3796,7 +3799,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3816,13 +3819,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3852,7 +3855,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3875,13 +3878,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3911,7 +3914,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3934,13 +3937,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3970,7 +3973,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3990,13 +3993,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4017,7 +4020,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4026,7 +4029,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4046,13 +4049,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4082,7 +4085,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4102,13 +4105,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4138,7 +4141,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4161,13 +4164,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4197,7 +4200,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4217,13 +4220,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4253,7 +4256,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4276,13 +4279,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4312,7 +4315,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4327,7 +4330,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4335,13 +4338,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4371,7 +4374,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4391,13 +4394,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4427,7 +4430,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4447,13 +4450,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4483,7 +4486,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4503,13 +4506,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4539,7 +4542,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4559,13 +4562,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4595,7 +4598,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4615,13 +4618,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4651,7 +4654,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4671,13 +4674,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4698,7 +4701,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4707,7 +4710,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4727,13 +4730,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D70" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4763,7 +4766,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4783,13 +4786,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D71" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4819,7 +4822,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4839,13 +4842,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4875,7 +4878,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4895,13 +4898,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D73" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4931,7 +4934,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4951,13 +4954,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4987,7 +4990,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5007,13 +5010,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D75" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5043,7 +5046,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5063,13 +5066,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D76" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5099,7 +5102,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5119,13 +5122,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5155,7 +5158,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5175,13 +5178,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D78" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5211,7 +5214,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5231,13 +5234,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D79" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5267,7 +5270,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5287,13 +5290,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5323,7 +5326,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5343,13 +5346,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5379,7 +5382,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5399,13 +5402,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D82" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5435,7 +5438,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5458,10 +5461,10 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
         <v>135</v>
@@ -5476,7 +5479,7 @@
         <v>16</v>
       </c>
       <c r="H83">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I83">
         <v>9485.6</v>
@@ -5484,23 +5487,29 @@
       <c r="J83">
         <v>583</v>
       </c>
+      <c r="K83" t="s">
+        <v>58</v>
+      </c>
       <c r="L83">
         <v>563.21</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>563.21</v>
+      </c>
+      <c r="N83" t="s">
+        <v>143</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>-474.2399999999998</v>
       </c>
       <c r="P83">
-        <v>-157.6</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>-157.6</v>
+        <v>-474.2399999999998</v>
       </c>
       <c r="R83">
-        <v>-1.66</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5508,13 +5517,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5544,7 +5553,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5564,13 +5573,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5600,7 +5609,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5620,13 +5629,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5656,7 +5665,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5676,13 +5685,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D87" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5700,7 +5709,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1319</v>
+        <v>1292.3</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5712,13 +5721,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>239.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q87">
-        <v>239.4</v>
+        <v>52.5</v>
       </c>
       <c r="R87">
-        <v>2.66</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5726,13 +5735,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5762,7 +5771,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5782,13 +5791,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5818,7 +5827,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5838,13 +5847,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5874,7 +5883,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5894,13 +5903,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5918,7 +5927,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>303.6</v>
+        <v>300.95</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5930,13 +5939,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>295.35</v>
+        <v>207.9</v>
       </c>
       <c r="Q91">
-        <v>295.35</v>
+        <v>207.9</v>
       </c>
       <c r="R91">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5944,13 +5953,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5980,7 +5989,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6000,13 +6009,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6036,7 +6045,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6056,13 +6065,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D94" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6092,7 +6101,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6112,13 +6121,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C95" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6148,7 +6157,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6168,13 +6177,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6204,7 +6213,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6219,18 +6228,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:19">
       <c r="A97" t="s">
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6260,7 +6269,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6275,21 +6284,21 @@
         <v>-5.7</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:19">
       <c r="A98" t="s">
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C98" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D98" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98">
         <v>430.95</v>
@@ -6298,45 +6307,48 @@
         <v>23</v>
       </c>
       <c r="H98">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I98">
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>470.1</v>
+        <v>467</v>
       </c>
       <c r="L98">
-        <v>430.95</v>
+        <v>452.5</v>
       </c>
       <c r="M98">
         <v>0</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>474.0450000000003</v>
       </c>
       <c r="P98">
-        <v>900.45</v>
+        <v>432.6</v>
       </c>
       <c r="Q98">
-        <v>900.45</v>
+        <v>906.65</v>
       </c>
       <c r="R98">
-        <v>9.08</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18">
+        <v>9.15</v>
+      </c>
+      <c r="S98" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
       <c r="A99" t="s">
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D99" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6366,7 +6378,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6381,18 +6393,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:19">
       <c r="A100" t="s">
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6422,7 +6434,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6437,18 +6449,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:19">
       <c r="A101" t="s">
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6478,7 +6490,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6493,18 +6505,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:19">
       <c r="A102" t="s">
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6534,7 +6546,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6549,18 +6561,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:19">
       <c r="A103" t="s">
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C103" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6590,7 +6602,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6605,18 +6617,18 @@
         <v>-6.61</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:19">
       <c r="A104" t="s">
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6646,7 +6658,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6661,18 +6673,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:19">
       <c r="A105" t="s">
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C105" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D105" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6690,7 +6702,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1825.3</v>
+        <v>1801.6</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6702,27 +6714,27 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>364</v>
+        <v>245.5</v>
       </c>
       <c r="Q105">
-        <v>364</v>
+        <v>245.5</v>
       </c>
       <c r="R105">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
       <c r="A106" t="s">
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C106" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6740,7 +6752,7 @@
         <v>9478</v>
       </c>
       <c r="J106">
-        <v>1354</v>
+        <v>1310.2</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6752,27 +6764,27 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>-306.6</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>-306.6</v>
       </c>
       <c r="R106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
       <c r="A107" t="s">
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D107" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6802,7 +6814,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6817,18 +6829,18 @@
         <v>-6.92</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:19">
       <c r="A108" t="s">
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C108" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6858,7 +6870,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6873,18 +6885,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:19">
       <c r="A109" t="s">
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C109" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6902,7 +6914,7 @@
         <v>9730.6</v>
       </c>
       <c r="J109">
-        <v>442.05</v>
+        <v>423.95</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6914,24 +6926,24 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>-5.5</v>
+        <v>-403.7</v>
       </c>
       <c r="Q109">
-        <v>-5.5</v>
+        <v>-403.7</v>
       </c>
       <c r="R109">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
       <c r="A110" t="s">
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C110" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
         <v>135</v>
@@ -6946,7 +6958,7 @@
         <v>50</v>
       </c>
       <c r="H110">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I110">
         <v>9836.5</v>
@@ -6954,37 +6966,43 @@
       <c r="J110">
         <v>193.47</v>
       </c>
+      <c r="K110" t="s">
+        <v>58</v>
+      </c>
       <c r="L110">
         <v>186.89</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>186.89</v>
+      </c>
+      <c r="N110" t="s">
+        <v>143</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>-492.0000000000002</v>
       </c>
       <c r="P110">
-        <v>-163</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>-163</v>
+        <v>-492.0000000000002</v>
       </c>
       <c r="R110">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
       <c r="A111" t="s">
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7002,7 +7020,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7574.5</v>
+        <v>7550</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -7014,27 +7032,27 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>-91.5</v>
+        <v>-116</v>
       </c>
       <c r="Q111">
-        <v>-91.5</v>
+        <v>-116</v>
       </c>
       <c r="R111">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
       <c r="A112" t="s">
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D112" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7064,7 +7082,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7084,13 +7102,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C113" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D113" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7120,7 +7138,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7140,13 +7158,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D114" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7176,7 +7194,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7196,13 +7214,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7232,7 +7250,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7252,13 +7270,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7288,7 +7306,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7308,13 +7326,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D117" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7344,16 +7362,16 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O117">
-        <v>-487.9999999999995</v>
+        <v>-487.9999999999996</v>
       </c>
       <c r="P117">
         <v>0</v>
       </c>
       <c r="Q117">
-        <v>-487.9999999999995</v>
+        <v>-487.9999999999996</v>
       </c>
       <c r="R117">
         <v>-5</v>
@@ -7364,13 +7382,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7388,7 +7406,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1225</v>
+        <v>1143.3</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7400,13 +7418,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>647.2</v>
+        <v>-6.4</v>
       </c>
       <c r="Q118">
-        <v>647.2</v>
+        <v>-6.4</v>
       </c>
       <c r="R118">
-        <v>7.07</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7414,13 +7432,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7438,7 +7456,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>343.5</v>
+        <v>331.5</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7450,13 +7468,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>263.9</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="Q119">
-        <v>263.9</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="R119">
-        <v>2.72</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7464,13 +7482,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C120" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D120" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7500,7 +7518,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7520,13 +7538,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C121" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D121" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7544,7 +7562,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>866.55</v>
+        <v>861.35</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7556,13 +7574,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>106.15</v>
+        <v>48.95</v>
       </c>
       <c r="Q121">
-        <v>106.15</v>
+        <v>48.95</v>
       </c>
       <c r="R121">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7570,13 +7588,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C122" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7594,7 +7612,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>2002</v>
+        <v>1961.1</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7606,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>27.5</v>
+        <v>-177</v>
       </c>
       <c r="Q122">
-        <v>27.5</v>
+        <v>-177</v>
       </c>
       <c r="R122">
-        <v>0.28</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7620,13 +7638,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C123" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7644,7 +7662,7 @@
         <v>9902.75</v>
       </c>
       <c r="J123">
-        <v>152.35</v>
+        <v>147.78</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7656,13 +7674,13 @@
         <v>0</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>-297.05</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>-297.05</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="124" spans="1:18">
@@ -7670,13 +7688,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D124" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7694,7 +7712,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4129.6</v>
+        <v>4073.2</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7706,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>-112.8</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>-112.8</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7720,13 +7738,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D125" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7741,10 +7759,10 @@
         <v>24</v>
       </c>
       <c r="I125">
-        <v>9981.599999999999</v>
+        <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>415.9</v>
+        <v>405.6</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7756,13 +7774,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>-247.2</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>-247.2</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7770,13 +7788,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C126" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D126" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7794,7 +7812,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>149.11</v>
+        <v>146.57</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7806,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>-170.18</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>-170.18</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7820,10 +7838,10 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D127" t="s">
         <v>135</v>
@@ -7838,30 +7856,86 @@
         <v>18</v>
       </c>
       <c r="H127">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I127">
-        <v>9492.300000000001</v>
+        <v>9492.299999999999</v>
       </c>
       <c r="J127">
         <v>527.35</v>
       </c>
+      <c r="K127" t="s">
+        <v>58</v>
+      </c>
       <c r="L127">
         <v>500.98</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>500.98</v>
+      </c>
+      <c r="N127" t="s">
+        <v>143</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>-474.6600000000001</v>
       </c>
       <c r="P127">
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>-474.6600000000001</v>
       </c>
       <c r="R127">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18">
+      <c r="A128" t="s">
+        <v>58</v>
+      </c>
+      <c r="B128" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" t="s">
+        <v>133</v>
+      </c>
+      <c r="D128" t="s">
+        <v>136</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>264.1</v>
+      </c>
+      <c r="G128">
+        <v>37</v>
+      </c>
+      <c r="H128">
+        <v>37</v>
+      </c>
+      <c r="I128">
+        <v>9771.700000000001</v>
+      </c>
+      <c r="J128">
+        <v>264.1</v>
+      </c>
+      <c r="L128">
+        <v>250.9</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="147">
   <si>
     <t>Buy Date</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -928,7 +931,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -984,7 +987,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1043,7 +1046,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1099,7 +1102,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1155,7 +1158,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1211,7 +1214,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1267,7 +1270,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1323,7 +1326,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1379,7 +1382,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1435,7 +1438,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1494,7 +1497,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1553,7 +1556,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1609,7 +1612,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1665,7 +1668,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1721,7 +1724,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1777,7 +1780,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1833,7 +1836,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1889,7 +1892,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1945,7 +1948,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2001,7 +2004,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2057,7 +2060,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2113,7 +2116,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2169,7 +2172,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2225,7 +2228,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2281,7 +2284,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2337,7 +2340,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2393,7 +2396,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2449,7 +2452,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2505,7 +2508,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2561,7 +2564,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2617,7 +2620,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2673,7 +2676,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2729,7 +2732,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2785,7 +2788,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2841,7 +2844,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2897,7 +2900,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2953,7 +2956,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3012,7 +3015,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3068,7 +3071,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3124,7 +3127,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3180,7 +3183,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3236,7 +3239,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3292,7 +3295,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3348,7 +3351,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3392,7 +3395,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>384.45</v>
+        <v>382.4</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3404,13 +3407,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>533.4</v>
+        <v>504.7</v>
       </c>
       <c r="Q46">
-        <v>1018.29</v>
+        <v>989.59</v>
       </c>
       <c r="R46">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3457,7 +3460,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3513,7 +3516,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3569,7 +3572,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3628,7 +3631,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3684,7 +3687,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3740,7 +3743,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3799,7 +3802,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3855,7 +3858,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3914,7 +3917,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3973,7 +3976,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4029,7 +4032,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4085,7 +4088,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4141,7 +4144,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4200,7 +4203,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4256,7 +4259,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4315,7 +4318,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4330,7 +4333,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4374,7 +4377,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4430,7 +4433,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4486,7 +4489,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4542,7 +4545,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4598,7 +4601,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4654,7 +4657,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4710,7 +4713,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4766,7 +4769,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4822,7 +4825,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4878,7 +4881,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4934,7 +4937,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4990,7 +4993,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5046,7 +5049,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5102,7 +5105,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5158,7 +5161,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5214,7 +5217,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5270,7 +5273,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5326,7 +5329,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5382,7 +5385,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5438,7 +5441,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5497,7 +5500,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5553,7 +5556,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5609,7 +5612,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5665,7 +5668,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5709,7 +5712,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1292.3</v>
+        <v>1276.9</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5721,13 +5724,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>52.5</v>
+        <v>-55.3</v>
       </c>
       <c r="Q87">
-        <v>52.5</v>
+        <v>-55.3</v>
       </c>
       <c r="R87">
-        <v>0.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5771,7 +5774,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5827,7 +5830,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5883,7 +5886,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5927,7 +5930,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>300.95</v>
+        <v>297.75</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5939,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>207.9</v>
+        <v>102.3</v>
       </c>
       <c r="Q91">
-        <v>207.9</v>
+        <v>102.3</v>
       </c>
       <c r="R91">
-        <v>2.14</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5989,7 +5992,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6045,7 +6048,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6101,7 +6104,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6157,7 +6160,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6213,7 +6216,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6269,7 +6272,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6313,7 +6316,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>467</v>
+        <v>460.3</v>
       </c>
       <c r="L98">
         <v>452.5</v>
@@ -6325,13 +6328,13 @@
         <v>474.0450000000003</v>
       </c>
       <c r="P98">
-        <v>432.6</v>
+        <v>352.2</v>
       </c>
       <c r="Q98">
-        <v>906.65</v>
+        <v>826.25</v>
       </c>
       <c r="R98">
-        <v>9.15</v>
+        <v>8.34</v>
       </c>
       <c r="S98" t="s">
         <v>58</v>
@@ -6378,7 +6381,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6434,7 +6437,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6490,7 +6493,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6546,7 +6549,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6602,7 +6605,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6658,7 +6661,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6702,7 +6705,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1801.6</v>
+        <v>1783.2</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6714,13 +6717,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>245.5</v>
+        <v>153.5</v>
       </c>
       <c r="Q105">
-        <v>245.5</v>
+        <v>153.5</v>
       </c>
       <c r="R105">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6734,7 +6737,7 @@
         <v>132</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6746,7 +6749,7 @@
         <v>7</v>
       </c>
       <c r="H106">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I106">
         <v>9478</v>
@@ -6754,23 +6757,29 @@
       <c r="J106">
         <v>1310.2</v>
       </c>
+      <c r="K106" t="s">
+        <v>143</v>
+      </c>
       <c r="L106">
         <v>1286.3</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>1286.3</v>
+      </c>
+      <c r="N106" t="s">
+        <v>144</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>-473.9000000000003</v>
       </c>
       <c r="P106">
-        <v>-306.6</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>-306.6</v>
+        <v>-473.9000000000003</v>
       </c>
       <c r="R106">
-        <v>-3.23</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -6814,7 +6823,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6870,7 +6879,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6896,7 +6905,7 @@
         <v>133</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6908,7 +6917,7 @@
         <v>22</v>
       </c>
       <c r="H109">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I109">
         <v>9730.6</v>
@@ -6916,23 +6925,29 @@
       <c r="J109">
         <v>423.95</v>
       </c>
+      <c r="K109" t="s">
+        <v>143</v>
+      </c>
       <c r="L109">
         <v>420.19</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>420.19</v>
+      </c>
+      <c r="N109" t="s">
+        <v>144</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>-486.4200000000003</v>
       </c>
       <c r="P109">
-        <v>-403.7</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>-403.7</v>
+        <v>-486.4200000000003</v>
       </c>
       <c r="R109">
-        <v>-4.15</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -6976,7 +6991,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7020,7 +7035,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7550</v>
+        <v>7490</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -7032,13 +7047,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>-116</v>
+        <v>-176</v>
       </c>
       <c r="Q111">
-        <v>-116</v>
+        <v>-176</v>
       </c>
       <c r="R111">
-        <v>-1.51</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -7082,7 +7097,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7138,7 +7153,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7194,7 +7209,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7250,7 +7265,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7306,7 +7321,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7362,7 +7377,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7406,7 +7421,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1143.3</v>
+        <v>1133</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7418,13 +7433,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-6.4</v>
+        <v>-88.8</v>
       </c>
       <c r="Q118">
-        <v>-6.4</v>
+        <v>-88.8</v>
       </c>
       <c r="R118">
-        <v>-0.07000000000000001</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7456,7 +7471,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>331.5</v>
+        <v>332.45</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7468,13 +7483,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>-84.09999999999999</v>
+        <v>-56.55</v>
       </c>
       <c r="Q119">
-        <v>-84.09999999999999</v>
+        <v>-56.55</v>
       </c>
       <c r="R119">
-        <v>-0.87</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7518,7 +7533,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7562,7 +7577,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>861.35</v>
+        <v>866.95</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7574,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>48.95</v>
+        <v>110.55</v>
       </c>
       <c r="Q121">
-        <v>48.95</v>
+        <v>110.55</v>
       </c>
       <c r="R121">
-        <v>0.52</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7612,7 +7627,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>1961.1</v>
+        <v>1978</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7624,13 +7639,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>-177</v>
+        <v>-92.5</v>
       </c>
       <c r="Q122">
-        <v>-177</v>
+        <v>-92.5</v>
       </c>
       <c r="R122">
-        <v>-1.77</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7644,7 +7659,7 @@
         <v>132</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7656,7 +7671,7 @@
         <v>65</v>
       </c>
       <c r="H123">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I123">
         <v>9902.75</v>
@@ -7664,23 +7679,29 @@
       <c r="J123">
         <v>147.78</v>
       </c>
+      <c r="K123" t="s">
+        <v>143</v>
+      </c>
       <c r="L123">
         <v>144.73</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>144.73</v>
+      </c>
+      <c r="N123" t="s">
+        <v>144</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>-495.3000000000003</v>
       </c>
       <c r="P123">
-        <v>-297.05</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>-297.05</v>
+        <v>-495.3000000000003</v>
       </c>
       <c r="R123">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="124" spans="1:18">
@@ -7712,7 +7733,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4073.2</v>
+        <v>4090.8</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7724,13 +7745,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>-112.8</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="Q124">
-        <v>-112.8</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="R124">
-        <v>-1.37</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7762,7 +7783,7 @@
         <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>405.6</v>
+        <v>406.25</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7774,13 +7795,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>-247.2</v>
+        <v>-231.6</v>
       </c>
       <c r="Q125">
-        <v>-247.2</v>
+        <v>-231.6</v>
       </c>
       <c r="R125">
-        <v>-2.48</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7812,7 +7833,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>146.57</v>
+        <v>154.06</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7824,13 +7845,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>-170.18</v>
+        <v>331.65</v>
       </c>
       <c r="Q126">
-        <v>-170.18</v>
+        <v>331.65</v>
       </c>
       <c r="R126">
-        <v>-1.7</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7874,7 +7895,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7918,7 +7939,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>264.1</v>
+        <v>260.45</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7930,13 +7951,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>-135.05</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>-135.05</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="148">
   <si>
     <t>Buy Date</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -818,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -895,13 +898,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -931,7 +934,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -951,13 +954,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -987,7 +990,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1010,13 +1013,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1046,7 +1049,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1066,13 +1069,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1102,7 +1105,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1122,13 +1125,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1158,7 +1161,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1178,13 +1181,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1214,7 +1217,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1234,13 +1237,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1270,7 +1273,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1290,13 +1293,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1326,7 +1329,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1346,13 +1349,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1382,7 +1385,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1402,13 +1405,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1429,7 +1432,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1438,7 +1441,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1453,7 +1456,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1461,13 +1464,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1497,7 +1500,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1520,13 +1523,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1556,7 +1559,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1576,13 +1579,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1612,7 +1615,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1632,13 +1635,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1668,7 +1671,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1688,13 +1691,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1724,7 +1727,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1744,13 +1747,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1780,7 +1783,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1800,13 +1803,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1836,7 +1839,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1856,13 +1859,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1892,7 +1895,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1912,13 +1915,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1948,7 +1951,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1968,13 +1971,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1995,7 +1998,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2004,7 +2007,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2024,13 +2027,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2051,7 +2054,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2060,7 +2063,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2080,13 +2083,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2116,7 +2119,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2136,13 +2139,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2172,7 +2175,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2192,13 +2195,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2228,7 +2231,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2248,13 +2251,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2275,7 +2278,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2284,7 +2287,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2304,13 +2307,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2340,7 +2343,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2360,13 +2363,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2396,7 +2399,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2416,13 +2419,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2452,7 +2455,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2472,13 +2475,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2508,7 +2511,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2528,13 +2531,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2555,7 +2558,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2564,7 +2567,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2584,13 +2587,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2620,7 +2623,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2640,13 +2643,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2676,7 +2679,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2696,13 +2699,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2723,7 +2726,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2732,7 +2735,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2752,13 +2755,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2779,7 +2782,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2788,7 +2791,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2808,13 +2811,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2844,7 +2847,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2864,13 +2867,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2900,7 +2903,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2920,13 +2923,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2956,7 +2959,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2979,13 +2982,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3015,7 +3018,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3035,13 +3038,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3071,7 +3074,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3091,13 +3094,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3127,7 +3130,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3147,13 +3150,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3174,7 +3177,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3183,7 +3186,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3203,13 +3206,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3230,7 +3233,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3239,7 +3242,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3259,13 +3262,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3295,7 +3298,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3315,13 +3318,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3351,7 +3354,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3371,13 +3374,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3395,7 +3398,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>382.4</v>
+        <v>383.35</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3407,13 +3410,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>504.7</v>
+        <v>518</v>
       </c>
       <c r="Q46">
-        <v>989.59</v>
+        <v>1002.89</v>
       </c>
       <c r="R46">
-        <v>10.2</v>
+        <v>10.34</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3424,13 +3427,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3460,7 +3463,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3480,13 +3483,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3516,7 +3519,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3536,13 +3539,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3572,7 +3575,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3595,13 +3598,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3631,7 +3634,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3651,13 +3654,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3687,7 +3690,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3707,13 +3710,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3743,7 +3746,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3766,13 +3769,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3802,7 +3805,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3822,13 +3825,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3858,7 +3861,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3881,13 +3884,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3917,7 +3920,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3940,13 +3943,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3976,7 +3979,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3996,13 +3999,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4023,7 +4026,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4032,7 +4035,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4052,13 +4055,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4088,7 +4091,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4108,13 +4111,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4144,7 +4147,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4167,13 +4170,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4203,7 +4206,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4223,13 +4226,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4259,7 +4262,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4282,13 +4285,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4318,7 +4321,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4333,7 +4336,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4341,13 +4344,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4377,7 +4380,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4397,13 +4400,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4433,7 +4436,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4453,13 +4456,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4489,7 +4492,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4509,13 +4512,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4545,7 +4548,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4565,13 +4568,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4601,7 +4604,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4621,13 +4624,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4657,7 +4660,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4677,13 +4680,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4704,7 +4707,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4713,7 +4716,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4733,13 +4736,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C70" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4769,7 +4772,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4789,13 +4792,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4825,7 +4828,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4845,13 +4848,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4881,7 +4884,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4901,13 +4904,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C73" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4937,7 +4940,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4957,13 +4960,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4993,7 +4996,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5013,13 +5016,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5049,7 +5052,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5069,13 +5072,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5105,7 +5108,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5125,13 +5128,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5161,7 +5164,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5181,13 +5184,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5217,7 +5220,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5237,13 +5240,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5273,7 +5276,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5293,13 +5296,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5329,7 +5332,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5349,13 +5352,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5385,7 +5388,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5405,13 +5408,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5441,7 +5444,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5464,13 +5467,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C83" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5500,7 +5503,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5520,13 +5523,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C84" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5556,7 +5559,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5576,13 +5579,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C85" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5612,7 +5615,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5632,13 +5635,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D86" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5668,7 +5671,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5688,13 +5691,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D87" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5712,7 +5715,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1276.9</v>
+        <v>1283.8</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5724,13 +5727,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-55.3</v>
+        <v>-7</v>
       </c>
       <c r="Q87">
-        <v>-55.3</v>
+        <v>-7</v>
       </c>
       <c r="R87">
-        <v>-0.61</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5738,13 +5741,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5774,7 +5777,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5794,13 +5797,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5830,7 +5833,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5850,13 +5853,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5886,7 +5889,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5906,13 +5909,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D91" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5930,7 +5933,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>297.75</v>
+        <v>298.5</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5942,13 +5945,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>102.3</v>
+        <v>127.05</v>
       </c>
       <c r="Q91">
-        <v>102.3</v>
+        <v>127.05</v>
       </c>
       <c r="R91">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5956,13 +5959,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5992,7 +5995,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6012,13 +6015,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6048,7 +6051,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6068,13 +6071,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D94" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6104,7 +6107,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6124,13 +6127,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6160,7 +6163,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6180,13 +6183,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6216,7 +6219,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6236,13 +6239,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6272,7 +6275,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6292,13 +6295,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6316,7 +6319,7 @@
         <v>9911.85</v>
       </c>
       <c r="J98">
-        <v>460.3</v>
+        <v>462.25</v>
       </c>
       <c r="L98">
         <v>452.5</v>
@@ -6328,13 +6331,13 @@
         <v>474.0450000000003</v>
       </c>
       <c r="P98">
-        <v>352.2</v>
+        <v>375.6</v>
       </c>
       <c r="Q98">
-        <v>826.25</v>
+        <v>849.65</v>
       </c>
       <c r="R98">
-        <v>8.34</v>
+        <v>8.57</v>
       </c>
       <c r="S98" t="s">
         <v>58</v>
@@ -6345,13 +6348,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6381,7 +6384,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6401,13 +6404,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C100" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6437,7 +6440,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6457,13 +6460,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6493,7 +6496,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6513,13 +6516,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D102" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6549,7 +6552,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6569,13 +6572,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C103" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6605,7 +6608,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6625,13 +6628,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C104" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D104" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6661,7 +6664,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6681,13 +6684,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C105" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6705,7 +6708,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1783.2</v>
+        <v>1794.4</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6717,13 +6720,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>153.5</v>
+        <v>209.5</v>
       </c>
       <c r="Q105">
-        <v>153.5</v>
+        <v>209.5</v>
       </c>
       <c r="R105">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6731,13 +6734,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D106" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6758,7 +6761,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6767,7 +6770,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6787,13 +6790,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C107" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D107" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6823,7 +6826,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6843,13 +6846,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D108" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6879,7 +6882,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6899,13 +6902,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C109" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6926,7 +6929,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6935,7 +6938,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6955,13 +6958,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C110" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D110" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6991,7 +6994,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7011,13 +7014,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D111" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7035,7 +7038,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7490</v>
+        <v>7500</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -7047,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>-176</v>
+        <v>-166</v>
       </c>
       <c r="Q111">
-        <v>-176</v>
+        <v>-166</v>
       </c>
       <c r="R111">
-        <v>-2.3</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -7061,13 +7064,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D112" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7097,7 +7100,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7117,13 +7120,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C113" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D113" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7153,7 +7156,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7173,13 +7176,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C114" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7209,7 +7212,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7229,13 +7232,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D115" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7265,7 +7268,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7285,13 +7288,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C116" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D116" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7321,7 +7324,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7341,13 +7344,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7377,7 +7380,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7397,13 +7400,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7421,7 +7424,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1133</v>
+        <v>1157.3</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7433,13 +7436,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-88.8</v>
+        <v>105.6</v>
       </c>
       <c r="Q118">
-        <v>-88.8</v>
+        <v>105.6</v>
       </c>
       <c r="R118">
-        <v>-0.97</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7447,13 +7450,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7471,7 +7474,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>332.45</v>
+        <v>337.7</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7483,13 +7486,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>-56.55</v>
+        <v>95.7</v>
       </c>
       <c r="Q119">
-        <v>-56.55</v>
+        <v>95.7</v>
       </c>
       <c r="R119">
-        <v>-0.58</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7497,13 +7500,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C120" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D120" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7533,7 +7536,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7553,13 +7556,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C121" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7577,7 +7580,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>866.95</v>
+        <v>868.65</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7589,13 +7592,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>110.55</v>
+        <v>129.25</v>
       </c>
       <c r="Q121">
-        <v>110.55</v>
+        <v>129.25</v>
       </c>
       <c r="R121">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7603,13 +7606,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C122" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7627,7 +7630,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>1978</v>
+        <v>1975.4</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7639,13 +7642,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>-92.5</v>
+        <v>-105.5</v>
       </c>
       <c r="Q122">
-        <v>-92.5</v>
+        <v>-105.5</v>
       </c>
       <c r="R122">
-        <v>-0.93</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7653,13 +7656,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C123" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7680,7 +7683,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7689,7 +7692,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7709,13 +7712,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C124" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D124" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7733,7 +7736,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4090.8</v>
+        <v>4090.5</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7745,13 +7748,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>-77.59999999999999</v>
+        <v>-78.2</v>
       </c>
       <c r="Q124">
-        <v>-77.59999999999999</v>
+        <v>-78.2</v>
       </c>
       <c r="R124">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7759,13 +7762,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7783,7 +7786,7 @@
         <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>406.25</v>
+        <v>418.05</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7795,13 +7798,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>-231.6</v>
+        <v>51.6</v>
       </c>
       <c r="Q125">
-        <v>-231.6</v>
+        <v>51.6</v>
       </c>
       <c r="R125">
-        <v>-2.32</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7809,13 +7812,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C126" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D126" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7833,7 +7836,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>154.06</v>
+        <v>155.6</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7845,13 +7848,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>331.65</v>
+        <v>434.83</v>
       </c>
       <c r="Q126">
-        <v>331.65</v>
+        <v>434.83</v>
       </c>
       <c r="R126">
-        <v>3.32</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7859,13 +7862,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D127" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7895,7 +7898,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7915,13 +7918,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D128" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7939,7 +7942,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>260.45</v>
+        <v>264.75</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7951,13 +7954,163 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>-135.05</v>
+        <v>24.05</v>
       </c>
       <c r="Q128">
-        <v>-135.05</v>
+        <v>24.05</v>
       </c>
       <c r="R128">
-        <v>-1.38</v>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
+      <c r="A129" t="s">
+        <v>59</v>
+      </c>
+      <c r="B129" t="s">
+        <v>100</v>
+      </c>
+      <c r="C129" t="s">
+        <v>133</v>
+      </c>
+      <c r="D129" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>3634.5</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+      <c r="H129">
+        <v>2</v>
+      </c>
+      <c r="I129">
+        <v>7269</v>
+      </c>
+      <c r="J129">
+        <v>3634.5</v>
+      </c>
+      <c r="L129">
+        <v>3452.77</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>0</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
+      <c r="A130" t="s">
+        <v>59</v>
+      </c>
+      <c r="B130" t="s">
+        <v>98</v>
+      </c>
+      <c r="C130" t="s">
+        <v>133</v>
+      </c>
+      <c r="D130" t="s">
+        <v>137</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>2238.2</v>
+      </c>
+      <c r="G130">
+        <v>4</v>
+      </c>
+      <c r="H130">
+        <v>4</v>
+      </c>
+      <c r="I130">
+        <v>8952.799999999999</v>
+      </c>
+      <c r="J130">
+        <v>2238.2</v>
+      </c>
+      <c r="L130">
+        <v>2126.29</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
+      <c r="A131" t="s">
+        <v>59</v>
+      </c>
+      <c r="B131" t="s">
+        <v>77</v>
+      </c>
+      <c r="C131" t="s">
+        <v>133</v>
+      </c>
+      <c r="D131" t="s">
+        <v>137</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>1317.1</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131">
+        <v>7</v>
+      </c>
+      <c r="I131">
+        <v>9219.699999999999</v>
+      </c>
+      <c r="J131">
+        <v>1317.1</v>
+      </c>
+      <c r="L131">
+        <v>1251.24</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>0</v>
+      </c>
+      <c r="R131">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="151">
   <si>
     <t>Buy Date</t>
   </si>
@@ -196,6 +196,9 @@
     <t>2026-03-17</t>
   </si>
   <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -413,6 +416,12 @@
   </si>
   <si>
     <t>HINDCOPPER</t>
+  </si>
+  <si>
+    <t>RVNL</t>
+  </si>
+  <si>
+    <t>VBL</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -821,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S131"/>
+  <dimension ref="A1:S134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -898,13 +907,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -934,7 +943,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -954,13 +963,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -990,7 +999,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1013,13 +1022,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1049,7 +1058,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1069,13 +1078,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1105,7 +1114,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1125,13 +1134,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1161,7 +1170,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1181,13 +1190,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1217,7 +1226,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1237,13 +1246,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1273,7 +1282,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1293,13 +1302,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1329,7 +1338,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1349,13 +1358,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1385,7 +1394,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1405,13 +1414,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1432,7 +1441,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1441,7 +1450,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1456,7 +1465,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1464,13 +1473,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1500,7 +1509,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1523,13 +1532,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1559,7 +1568,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1579,13 +1588,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1615,7 +1624,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1635,13 +1644,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1671,7 +1680,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1691,13 +1700,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1727,7 +1736,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1747,13 +1756,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1783,7 +1792,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1803,13 +1812,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1839,7 +1848,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1859,13 +1868,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1895,7 +1904,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1915,13 +1924,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1951,7 +1960,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1971,13 +1980,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -1998,7 +2007,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2007,7 +2016,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2027,13 +2036,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2054,7 +2063,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2063,7 +2072,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2083,13 +2092,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2119,7 +2128,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2139,13 +2148,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2175,7 +2184,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2195,13 +2204,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2231,7 +2240,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2251,13 +2260,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2278,7 +2287,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2287,7 +2296,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2307,13 +2316,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2343,7 +2352,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2363,13 +2372,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2399,7 +2408,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2419,13 +2428,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2455,7 +2464,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2475,13 +2484,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2511,7 +2520,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2531,13 +2540,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2558,7 +2567,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2567,7 +2576,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2587,13 +2596,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2623,7 +2632,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2643,13 +2652,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2679,7 +2688,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2699,13 +2708,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2726,7 +2735,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2735,7 +2744,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2755,13 +2764,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2782,7 +2791,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2791,7 +2800,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2811,13 +2820,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2847,7 +2856,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2867,13 +2876,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2903,7 +2912,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2923,13 +2932,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2959,7 +2968,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2982,13 +2991,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3018,7 +3027,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3038,13 +3047,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3074,7 +3083,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3094,13 +3103,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3130,7 +3139,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3150,13 +3159,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3177,7 +3186,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3186,7 +3195,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3206,13 +3215,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3233,7 +3242,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3242,7 +3251,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3262,13 +3271,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3298,7 +3307,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3318,13 +3327,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3354,7 +3363,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3374,13 +3383,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3398,7 +3407,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>383.35</v>
+        <v>378.5</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3410,13 +3419,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>518</v>
+        <v>450.1</v>
       </c>
       <c r="Q46">
-        <v>1002.89</v>
+        <v>934.99</v>
       </c>
       <c r="R46">
-        <v>10.34</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3427,13 +3436,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3463,7 +3472,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3483,13 +3492,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3519,7 +3528,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3539,13 +3548,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3575,7 +3584,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3598,13 +3607,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3634,7 +3643,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3654,13 +3663,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3690,7 +3699,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3710,13 +3719,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3746,7 +3755,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3769,13 +3778,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3805,7 +3814,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3825,13 +3834,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3861,7 +3870,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3884,13 +3893,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3920,7 +3929,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3943,13 +3952,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3979,7 +3988,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -3999,13 +4008,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C57" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4026,7 +4035,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4035,7 +4044,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4055,13 +4064,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4091,7 +4100,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4111,13 +4120,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4147,7 +4156,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4170,13 +4179,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C60" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4206,7 +4215,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4226,13 +4235,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C61" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4262,7 +4271,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4285,13 +4294,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4321,7 +4330,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4336,7 +4345,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4344,13 +4353,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D63" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4380,7 +4389,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4400,13 +4409,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4436,7 +4445,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4456,13 +4465,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4492,7 +4501,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4512,13 +4521,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4548,7 +4557,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4568,13 +4577,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D67" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4604,7 +4613,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4624,13 +4633,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4660,7 +4669,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4680,13 +4689,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4707,7 +4716,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4716,7 +4725,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4736,13 +4745,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4772,7 +4781,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4792,13 +4801,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D71" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4828,7 +4837,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4848,13 +4857,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4884,7 +4893,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4904,13 +4913,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4940,7 +4949,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4960,13 +4969,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4996,7 +5005,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5016,13 +5025,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5052,7 +5061,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5072,13 +5081,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5108,7 +5117,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5128,13 +5137,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5164,7 +5173,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5184,13 +5193,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C78" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5220,7 +5229,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5240,13 +5249,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D79" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5276,7 +5285,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5296,13 +5305,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D80" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5332,7 +5341,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5352,13 +5361,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D81" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5388,7 +5397,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5408,13 +5417,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D82" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5444,7 +5453,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5467,13 +5476,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C83" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D83" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5503,7 +5512,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5523,13 +5532,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C84" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5559,7 +5568,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5579,13 +5588,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D85" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5615,7 +5624,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5635,13 +5644,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C86" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5671,7 +5680,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5691,13 +5700,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C87" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5715,7 +5724,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1283.8</v>
+        <v>1294.8</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5727,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-7</v>
+        <v>70</v>
       </c>
       <c r="Q87">
-        <v>-7</v>
+        <v>70</v>
       </c>
       <c r="R87">
-        <v>-0.08</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5741,13 +5750,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D88" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5777,7 +5786,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5797,13 +5806,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5833,7 +5842,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5853,13 +5862,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D90" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5889,7 +5898,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5909,13 +5918,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5933,7 +5942,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>298.5</v>
+        <v>299.4</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5945,13 +5954,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>127.05</v>
+        <v>156.75</v>
       </c>
       <c r="Q91">
-        <v>127.05</v>
+        <v>156.75</v>
       </c>
       <c r="R91">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5959,13 +5968,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5995,7 +6004,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6015,13 +6024,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D93" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6051,7 +6060,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6071,13 +6080,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C94" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D94" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6107,7 +6116,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6127,13 +6136,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C95" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6163,7 +6172,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6183,13 +6192,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6219,7 +6228,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6239,13 +6248,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6275,7 +6284,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6295,13 +6304,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6313,7 +6322,7 @@
         <v>23</v>
       </c>
       <c r="H98">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I98">
         <v>9911.85</v>
@@ -6321,23 +6330,29 @@
       <c r="J98">
         <v>462.25</v>
       </c>
+      <c r="K98" t="s">
+        <v>60</v>
+      </c>
       <c r="L98">
         <v>452.5</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>452.5</v>
+      </c>
+      <c r="N98" t="s">
+        <v>148</v>
       </c>
       <c r="O98">
-        <v>474.0450000000003</v>
+        <v>732.6450000000004</v>
       </c>
       <c r="P98">
-        <v>375.6</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>849.65</v>
+        <v>732.6450000000004</v>
       </c>
       <c r="R98">
-        <v>8.57</v>
+        <v>7.39</v>
       </c>
       <c r="S98" t="s">
         <v>58</v>
@@ -6348,13 +6363,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C99" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6384,7 +6399,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6404,13 +6419,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C100" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6440,7 +6455,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6460,13 +6475,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6496,7 +6511,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6516,13 +6531,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6552,7 +6567,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6572,13 +6587,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C103" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6608,7 +6623,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6628,13 +6643,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6664,7 +6679,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6684,13 +6699,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6708,7 +6723,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1794.4</v>
+        <v>1778.3</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6720,13 +6735,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>209.5</v>
+        <v>129</v>
       </c>
       <c r="Q105">
-        <v>209.5</v>
+        <v>129</v>
       </c>
       <c r="R105">
-        <v>2.39</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6734,13 +6749,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C106" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6761,7 +6776,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6770,7 +6785,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6790,13 +6805,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D107" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6826,7 +6841,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6846,13 +6861,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C108" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D108" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6882,7 +6897,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6902,13 +6917,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C109" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6929,7 +6944,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6938,7 +6953,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6958,13 +6973,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C110" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D110" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6994,7 +7009,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7014,13 +7029,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C111" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7038,7 +7053,7 @@
         <v>7666</v>
       </c>
       <c r="J111">
-        <v>7500</v>
+        <v>7471</v>
       </c>
       <c r="L111">
         <v>7282.7</v>
@@ -7050,13 +7065,13 @@
         <v>0</v>
       </c>
       <c r="P111">
-        <v>-166</v>
+        <v>-195</v>
       </c>
       <c r="Q111">
-        <v>-166</v>
+        <v>-195</v>
       </c>
       <c r="R111">
-        <v>-2.17</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -7064,13 +7079,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C112" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7100,7 +7115,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7120,13 +7135,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C113" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7156,7 +7171,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7176,13 +7191,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C114" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D114" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7212,7 +7227,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7232,13 +7247,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D115" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7268,7 +7283,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7288,13 +7303,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C116" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7324,7 +7339,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7344,13 +7359,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C117" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D117" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7380,7 +7395,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7400,13 +7415,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C118" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7424,7 +7439,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1157.3</v>
+        <v>1179.2</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7436,13 +7451,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>105.6</v>
+        <v>280.8</v>
       </c>
       <c r="Q118">
-        <v>105.6</v>
+        <v>280.8</v>
       </c>
       <c r="R118">
-        <v>1.15</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7450,13 +7465,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7474,7 +7489,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>337.7</v>
+        <v>348.05</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7486,13 +7501,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>95.7</v>
+        <v>395.85</v>
       </c>
       <c r="Q119">
-        <v>95.7</v>
+        <v>395.85</v>
       </c>
       <c r="R119">
-        <v>0.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7500,13 +7515,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7536,7 +7551,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7556,13 +7571,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C121" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7580,7 +7595,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>868.65</v>
+        <v>891.3</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7592,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>129.25</v>
+        <v>378.4</v>
       </c>
       <c r="Q121">
-        <v>129.25</v>
+        <v>378.4</v>
       </c>
       <c r="R121">
-        <v>1.37</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7606,13 +7621,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7630,7 +7645,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>1975.4</v>
+        <v>2007.2</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7642,13 +7657,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>-105.5</v>
+        <v>53.5</v>
       </c>
       <c r="Q122">
-        <v>-105.5</v>
+        <v>53.5</v>
       </c>
       <c r="R122">
-        <v>-1.06</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7656,13 +7671,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C123" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7683,7 +7698,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7692,7 +7707,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7712,13 +7727,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C124" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7736,7 +7751,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4090.5</v>
+        <v>4145.5</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7748,13 +7763,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>-78.2</v>
+        <v>31.8</v>
       </c>
       <c r="Q124">
-        <v>-78.2</v>
+        <v>31.8</v>
       </c>
       <c r="R124">
-        <v>-0.95</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7762,13 +7777,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7786,7 +7801,7 @@
         <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>418.05</v>
+        <v>432.25</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7798,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>51.6</v>
+        <v>392.4</v>
       </c>
       <c r="Q125">
-        <v>51.6</v>
+        <v>392.4</v>
       </c>
       <c r="R125">
-        <v>0.52</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7812,13 +7827,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C126" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7836,7 +7851,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>155.6</v>
+        <v>154.07</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7848,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>434.83</v>
+        <v>332.32</v>
       </c>
       <c r="Q126">
-        <v>434.83</v>
+        <v>332.32</v>
       </c>
       <c r="R126">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7862,13 +7877,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7898,7 +7913,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7918,13 +7933,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C128" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D128" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7942,7 +7957,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>264.75</v>
+        <v>265</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7954,13 +7969,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>24.05</v>
+        <v>33.3</v>
       </c>
       <c r="Q128">
-        <v>24.05</v>
+        <v>33.3</v>
       </c>
       <c r="R128">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -7968,13 +7983,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C129" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D129" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7992,7 +8007,7 @@
         <v>7269</v>
       </c>
       <c r="J129">
-        <v>3634.5</v>
+        <v>3640.9</v>
       </c>
       <c r="L129">
         <v>3452.77</v>
@@ -8004,13 +8019,13 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -8018,13 +8033,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C130" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D130" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8042,7 +8057,7 @@
         <v>8952.799999999999</v>
       </c>
       <c r="J130">
-        <v>2238.2</v>
+        <v>2262.1</v>
       </c>
       <c r="L130">
         <v>2126.29</v>
@@ -8054,13 +8069,13 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -8068,13 +8083,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C131" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8089,10 +8104,10 @@
         <v>7</v>
       </c>
       <c r="I131">
-        <v>9219.699999999999</v>
+        <v>9219.700000000001</v>
       </c>
       <c r="J131">
-        <v>1317.1</v>
+        <v>1343.9</v>
       </c>
       <c r="L131">
         <v>1251.24</v>
@@ -8104,12 +8119,162 @@
         <v>0</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>187.6</v>
       </c>
       <c r="R131">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18">
+      <c r="A132" t="s">
+        <v>60</v>
+      </c>
+      <c r="B132" t="s">
+        <v>134</v>
+      </c>
+      <c r="C132" t="s">
+        <v>136</v>
+      </c>
+      <c r="D132" t="s">
+        <v>140</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>275.1</v>
+      </c>
+      <c r="G132">
+        <v>36</v>
+      </c>
+      <c r="H132">
+        <v>36</v>
+      </c>
+      <c r="I132">
+        <v>9903.6</v>
+      </c>
+      <c r="J132">
+        <v>275.1</v>
+      </c>
+      <c r="L132">
+        <v>261.35</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>0</v>
+      </c>
+      <c r="R132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18">
+      <c r="A133" t="s">
+        <v>60</v>
+      </c>
+      <c r="B133" t="s">
+        <v>110</v>
+      </c>
+      <c r="C133" t="s">
+        <v>136</v>
+      </c>
+      <c r="D133" t="s">
+        <v>140</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>150.95</v>
+      </c>
+      <c r="G133">
+        <v>66</v>
+      </c>
+      <c r="H133">
+        <v>66</v>
+      </c>
+      <c r="I133">
+        <v>9962.699999999999</v>
+      </c>
+      <c r="J133">
+        <v>150.95</v>
+      </c>
+      <c r="L133">
+        <v>143.4</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18">
+      <c r="A134" t="s">
+        <v>60</v>
+      </c>
+      <c r="B134" t="s">
+        <v>135</v>
+      </c>
+      <c r="C134" t="s">
+        <v>136</v>
+      </c>
+      <c r="D134" t="s">
+        <v>140</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>415.1</v>
+      </c>
+      <c r="G134">
+        <v>24</v>
+      </c>
+      <c r="H134">
+        <v>24</v>
+      </c>
+      <c r="I134">
+        <v>9962.400000000001</v>
+      </c>
+      <c r="J134">
+        <v>415.1</v>
+      </c>
+      <c r="L134">
+        <v>394.35</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="152">
   <si>
     <t>Buy Date</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -830,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S134"/>
+  <dimension ref="A1:S136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -907,13 +910,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -943,7 +946,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -963,13 +966,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -999,7 +1002,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1022,13 +1025,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1058,7 +1061,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1078,13 +1081,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1114,7 +1117,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1134,13 +1137,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1170,7 +1173,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1190,13 +1193,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1226,7 +1229,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1246,13 +1249,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1282,7 +1285,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1302,13 +1305,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1338,7 +1341,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1358,13 +1361,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1394,7 +1397,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1414,13 +1417,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1441,7 +1444,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1450,7 +1453,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1465,7 +1468,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1473,13 +1476,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1509,7 +1512,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1532,13 +1535,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1568,7 +1571,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1588,13 +1591,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1624,7 +1627,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1644,13 +1647,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1680,7 +1683,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1700,13 +1703,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1736,7 +1739,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1756,13 +1759,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1792,7 +1795,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1812,13 +1815,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1848,7 +1851,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1868,13 +1871,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1904,7 +1907,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1924,13 +1927,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1960,7 +1963,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1980,13 +1983,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2007,7 +2010,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2016,7 +2019,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2036,13 +2039,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2063,7 +2066,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2072,7 +2075,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2092,13 +2095,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2128,7 +2131,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2148,13 +2151,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2184,7 +2187,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2204,13 +2207,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2240,7 +2243,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2260,13 +2263,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2287,7 +2290,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2296,7 +2299,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2316,13 +2319,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2352,7 +2355,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2372,13 +2375,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2408,7 +2411,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2428,13 +2431,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2464,7 +2467,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2484,13 +2487,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2520,7 +2523,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2540,13 +2543,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2567,7 +2570,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2576,7 +2579,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2596,13 +2599,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2632,7 +2635,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2652,13 +2655,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2688,7 +2691,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2708,13 +2711,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2735,7 +2738,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2744,7 +2747,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2764,13 +2767,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2791,7 +2794,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2800,7 +2803,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2820,13 +2823,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2856,7 +2859,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2876,13 +2879,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2912,7 +2915,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2932,13 +2935,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2968,7 +2971,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2991,13 +2994,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3027,7 +3030,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3047,13 +3050,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3083,7 +3086,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3103,13 +3106,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3139,7 +3142,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3159,13 +3162,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3186,7 +3189,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3195,7 +3198,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3215,13 +3218,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3242,7 +3245,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3251,7 +3254,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3271,13 +3274,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3307,7 +3310,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3327,13 +3330,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3363,7 +3366,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3383,13 +3386,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3407,7 +3410,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>378.5</v>
+        <v>374.05</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3419,13 +3422,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>450.1</v>
+        <v>387.8</v>
       </c>
       <c r="Q46">
-        <v>934.99</v>
+        <v>872.6900000000001</v>
       </c>
       <c r="R46">
-        <v>9.640000000000001</v>
+        <v>9</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3436,13 +3439,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3472,7 +3475,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3492,13 +3495,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3528,7 +3531,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3548,13 +3551,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3584,7 +3587,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3607,13 +3610,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3643,7 +3646,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3663,13 +3666,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3699,7 +3702,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3719,13 +3722,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3755,7 +3758,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3778,13 +3781,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3814,7 +3817,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3834,13 +3837,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3870,7 +3873,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3893,13 +3896,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3929,7 +3932,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3952,13 +3955,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3988,7 +3991,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4008,13 +4011,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4035,7 +4038,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4044,7 +4047,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4064,13 +4067,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4100,7 +4103,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4120,13 +4123,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4156,7 +4159,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4179,13 +4182,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4215,7 +4218,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4235,13 +4238,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4271,7 +4274,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4294,13 +4297,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4330,7 +4333,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4345,7 +4348,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4353,13 +4356,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4389,7 +4392,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4409,13 +4412,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4445,7 +4448,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4465,13 +4468,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4501,7 +4504,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4521,13 +4524,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4557,7 +4560,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4577,13 +4580,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4613,7 +4616,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4633,13 +4636,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4669,7 +4672,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4689,13 +4692,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4716,7 +4719,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4725,7 +4728,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4745,13 +4748,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4781,7 +4784,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4801,13 +4804,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4837,7 +4840,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4857,13 +4860,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4893,7 +4896,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4913,13 +4916,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4949,7 +4952,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4969,13 +4972,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5005,7 +5008,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5025,13 +5028,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5061,7 +5064,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5081,13 +5084,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5117,7 +5120,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5137,13 +5140,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5173,7 +5176,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5193,13 +5196,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D78" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5229,7 +5232,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5249,13 +5252,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5285,7 +5288,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5305,13 +5308,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5341,7 +5344,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5361,13 +5364,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C81" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5397,7 +5400,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5417,13 +5420,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C82" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5453,7 +5456,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5476,13 +5479,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D83" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5512,7 +5515,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5532,13 +5535,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5568,7 +5571,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5588,13 +5591,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5624,7 +5627,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5644,13 +5647,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5680,7 +5683,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5700,13 +5703,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D87" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5724,7 +5727,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1294.8</v>
+        <v>1274.5</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5736,13 +5739,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>70</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="Q87">
-        <v>70</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="R87">
-        <v>0.78</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5750,13 +5753,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C88" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D88" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5786,7 +5789,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5806,13 +5809,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5842,7 +5845,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5862,13 +5865,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5898,7 +5901,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5918,13 +5921,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5942,7 +5945,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>299.4</v>
+        <v>296.7</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5954,13 +5957,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>156.75</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="Q91">
-        <v>156.75</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="R91">
-        <v>1.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5968,13 +5971,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6004,7 +6007,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6024,13 +6027,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C93" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D93" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6060,7 +6063,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6080,13 +6083,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C94" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6116,7 +6119,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6136,13 +6139,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6172,7 +6175,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6192,13 +6195,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D96" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6228,7 +6231,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6248,13 +6251,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6284,7 +6287,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6304,13 +6307,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D98" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6340,7 +6343,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6363,13 +6366,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C99" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D99" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6399,7 +6402,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6419,13 +6422,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C100" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6455,7 +6458,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6475,13 +6478,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C101" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D101" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6511,7 +6514,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6531,13 +6534,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6567,7 +6570,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6587,13 +6590,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C103" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6623,7 +6626,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6643,13 +6646,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D104" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6679,7 +6682,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6699,13 +6702,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C105" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6723,7 +6726,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1778.3</v>
+        <v>1744.4</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6735,13 +6738,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>129</v>
+        <v>-40.5</v>
       </c>
       <c r="Q105">
-        <v>129</v>
+        <v>-40.5</v>
       </c>
       <c r="R105">
-        <v>1.47</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6749,13 +6752,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C106" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D106" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6776,7 +6779,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6785,7 +6788,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6805,13 +6808,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D107" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6841,7 +6844,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6861,13 +6864,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6897,7 +6900,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6917,13 +6920,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C109" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6944,7 +6947,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6953,7 +6956,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6973,13 +6976,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7009,7 +7012,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7029,10 +7032,10 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C111" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D111" t="s">
         <v>140</v>
@@ -7047,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111">
         <v>7666</v>
@@ -7055,23 +7058,29 @@
       <c r="J111">
         <v>7471</v>
       </c>
+      <c r="K111" t="s">
+        <v>61</v>
+      </c>
       <c r="L111">
         <v>7282.7</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>7282.7</v>
+      </c>
+      <c r="N111" t="s">
+        <v>149</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>-383.3000000000002</v>
       </c>
       <c r="P111">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>-195</v>
+        <v>-383.3000000000002</v>
       </c>
       <c r="R111">
-        <v>-2.54</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -7079,13 +7088,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7115,7 +7124,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7135,13 +7144,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7171,7 +7180,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7191,13 +7200,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7227,7 +7236,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7247,13 +7256,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7283,7 +7292,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7303,13 +7312,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C116" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D116" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7339,7 +7348,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7359,13 +7368,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7395,7 +7404,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7415,13 +7424,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C118" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D118" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7439,7 +7448,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1179.2</v>
+        <v>1138.1</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7451,13 +7460,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>280.8</v>
+        <v>-48</v>
       </c>
       <c r="Q118">
-        <v>280.8</v>
+        <v>-48</v>
       </c>
       <c r="R118">
-        <v>3.07</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7465,13 +7474,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D119" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7489,7 +7498,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>348.05</v>
+        <v>333.4</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7501,13 +7510,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>395.85</v>
+        <v>-29</v>
       </c>
       <c r="Q119">
-        <v>395.85</v>
+        <v>-29</v>
       </c>
       <c r="R119">
-        <v>4.08</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7515,13 +7524,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C120" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7551,7 +7560,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7571,13 +7580,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D121" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7595,7 +7604,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>891.3</v>
+        <v>854.9</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7607,13 +7616,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>378.4</v>
+        <v>-22</v>
       </c>
       <c r="Q121">
-        <v>378.4</v>
+        <v>-22</v>
       </c>
       <c r="R121">
-        <v>4.01</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7621,13 +7630,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7645,7 +7654,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>2007.2</v>
+        <v>1936.8</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7657,13 +7666,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>53.5</v>
+        <v>-298.5</v>
       </c>
       <c r="Q122">
-        <v>53.5</v>
+        <v>-298.5</v>
       </c>
       <c r="R122">
-        <v>0.54</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7671,13 +7680,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C123" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D123" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7698,7 +7707,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7707,7 +7716,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7727,13 +7736,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C124" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7751,7 +7760,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4145.5</v>
+        <v>4037.9</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7763,13 +7772,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>31.8</v>
+        <v>-183.4</v>
       </c>
       <c r="Q124">
-        <v>31.8</v>
+        <v>-183.4</v>
       </c>
       <c r="R124">
-        <v>0.39</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7777,13 +7786,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7801,7 +7810,7 @@
         <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>432.25</v>
+        <v>411.85</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7813,13 +7822,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>392.4</v>
+        <v>-97.2</v>
       </c>
       <c r="Q125">
-        <v>392.4</v>
+        <v>-97.2</v>
       </c>
       <c r="R125">
-        <v>3.93</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7827,13 +7836,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C126" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D126" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7851,7 +7860,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>154.07</v>
+        <v>151.01</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7863,13 +7872,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>332.32</v>
+        <v>127.3</v>
       </c>
       <c r="Q126">
-        <v>332.32</v>
+        <v>127.3</v>
       </c>
       <c r="R126">
-        <v>3.33</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7877,13 +7886,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7913,7 +7922,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7933,13 +7942,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D128" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7957,7 +7966,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>265</v>
+        <v>269.1</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7969,13 +7978,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>33.3</v>
+        <v>185</v>
       </c>
       <c r="Q128">
-        <v>33.3</v>
+        <v>185</v>
       </c>
       <c r="R128">
-        <v>0.34</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -7983,13 +7992,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C129" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D129" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8007,7 +8016,7 @@
         <v>7269</v>
       </c>
       <c r="J129">
-        <v>3640.9</v>
+        <v>3481.9</v>
       </c>
       <c r="L129">
         <v>3452.77</v>
@@ -8019,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>12.8</v>
+        <v>-305.2</v>
       </c>
       <c r="Q129">
-        <v>12.8</v>
+        <v>-305.2</v>
       </c>
       <c r="R129">
-        <v>0.18</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -8033,13 +8042,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D130" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8057,7 +8066,7 @@
         <v>8952.799999999999</v>
       </c>
       <c r="J130">
-        <v>2262.1</v>
+        <v>2186</v>
       </c>
       <c r="L130">
         <v>2126.29</v>
@@ -8069,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>95.59999999999999</v>
+        <v>-208.8</v>
       </c>
       <c r="Q130">
-        <v>95.59999999999999</v>
+        <v>-208.8</v>
       </c>
       <c r="R130">
-        <v>1.07</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -8083,13 +8092,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D131" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8107,7 +8116,7 @@
         <v>9219.700000000001</v>
       </c>
       <c r="J131">
-        <v>1343.9</v>
+        <v>1294.3</v>
       </c>
       <c r="L131">
         <v>1251.24</v>
@@ -8119,13 +8128,13 @@
         <v>0</v>
       </c>
       <c r="P131">
-        <v>187.6</v>
+        <v>-159.6</v>
       </c>
       <c r="Q131">
-        <v>187.6</v>
+        <v>-159.6</v>
       </c>
       <c r="R131">
-        <v>2.03</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -8133,10 +8142,10 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D132" t="s">
         <v>140</v>
@@ -8151,7 +8160,7 @@
         <v>36</v>
       </c>
       <c r="H132">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I132">
         <v>9903.6</v>
@@ -8159,23 +8168,29 @@
       <c r="J132">
         <v>275.1</v>
       </c>
+      <c r="K132" t="s">
+        <v>61</v>
+      </c>
       <c r="L132">
         <v>261.35</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>261.35</v>
+      </c>
+      <c r="N132" t="s">
+        <v>149</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>-495</v>
       </c>
       <c r="P132">
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>-495</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:18">
@@ -8183,13 +8198,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D133" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8204,10 +8219,10 @@
         <v>66</v>
       </c>
       <c r="I133">
-        <v>9962.699999999999</v>
+        <v>9962.700000000001</v>
       </c>
       <c r="J133">
-        <v>150.95</v>
+        <v>144.27</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8219,13 +8234,13 @@
         <v>0</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>-440.88</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>-440.88</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="134" spans="1:18">
@@ -8233,13 +8248,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C134" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D134" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8254,10 +8269,10 @@
         <v>24</v>
       </c>
       <c r="I134">
-        <v>9962.400000000001</v>
+        <v>9962.4</v>
       </c>
       <c r="J134">
-        <v>415.1</v>
+        <v>404.65</v>
       </c>
       <c r="L134">
         <v>394.35</v>
@@ -8269,12 +8284,112 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>-250.8</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>-250.8</v>
       </c>
       <c r="R134">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18">
+      <c r="A135" t="s">
+        <v>61</v>
+      </c>
+      <c r="B135" t="s">
+        <v>69</v>
+      </c>
+      <c r="C135" t="s">
+        <v>137</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>3079</v>
+      </c>
+      <c r="G135">
+        <v>3</v>
+      </c>
+      <c r="H135">
+        <v>3</v>
+      </c>
+      <c r="I135">
+        <v>9237</v>
+      </c>
+      <c r="J135">
+        <v>3079</v>
+      </c>
+      <c r="L135">
+        <v>2925.05</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18">
+      <c r="A136" t="s">
+        <v>61</v>
+      </c>
+      <c r="B136" t="s">
+        <v>98</v>
+      </c>
+      <c r="C136" t="s">
+        <v>139</v>
+      </c>
+      <c r="D136" t="s">
+        <v>141</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>454.2</v>
+      </c>
+      <c r="G136">
+        <v>22</v>
+      </c>
+      <c r="H136">
+        <v>22</v>
+      </c>
+      <c r="I136">
+        <v>9992.4</v>
+      </c>
+      <c r="J136">
+        <v>454.2</v>
+      </c>
+      <c r="L136">
+        <v>431.49</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="153">
   <si>
     <t>Buy Date</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -946,7 +949,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1002,7 +1005,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1061,7 +1064,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1117,7 +1120,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1173,7 +1176,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1229,7 +1232,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1285,7 +1288,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1341,7 +1344,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1397,7 +1400,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1453,7 +1456,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1512,7 +1515,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1571,7 +1574,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1627,7 +1630,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1683,7 +1686,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1739,7 +1742,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1795,7 +1798,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1851,7 +1854,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1907,7 +1910,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1963,7 +1966,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2019,7 +2022,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2075,7 +2078,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2131,7 +2134,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2187,7 +2190,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2243,7 +2246,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2299,7 +2302,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2355,7 +2358,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2411,7 +2414,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2467,7 +2470,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2523,7 +2526,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2579,7 +2582,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2635,7 +2638,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2691,7 +2694,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2747,7 +2750,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2803,7 +2806,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2859,7 +2862,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2915,7 +2918,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2971,7 +2974,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3030,7 +3033,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3086,7 +3089,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3142,7 +3145,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3198,7 +3201,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3254,7 +3257,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3310,7 +3313,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3366,7 +3369,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3410,7 +3413,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>374.05</v>
+        <v>380.95</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3422,13 +3425,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>387.8</v>
+        <v>484.4</v>
       </c>
       <c r="Q46">
-        <v>872.6900000000001</v>
+        <v>969.29</v>
       </c>
       <c r="R46">
-        <v>9</v>
+        <v>9.99</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3475,7 +3478,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3531,7 +3534,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3587,7 +3590,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3646,7 +3649,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3702,7 +3705,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3758,7 +3761,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3817,7 +3820,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3873,7 +3876,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3932,7 +3935,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3991,7 +3994,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4047,7 +4050,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4103,7 +4106,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4159,7 +4162,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4218,7 +4221,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4274,7 +4277,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4333,7 +4336,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4348,7 +4351,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4392,7 +4395,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4448,7 +4451,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4504,7 +4507,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4560,7 +4563,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4616,7 +4619,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4672,7 +4675,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4728,7 +4731,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4784,7 +4787,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4840,7 +4843,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4896,7 +4899,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4952,7 +4955,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5008,7 +5011,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5064,7 +5067,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5120,7 +5123,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5176,7 +5179,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5232,7 +5235,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5288,7 +5291,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5344,7 +5347,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5400,7 +5403,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5456,7 +5459,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5515,7 +5518,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5571,7 +5574,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5627,7 +5630,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5683,7 +5686,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5727,7 +5730,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1274.5</v>
+        <v>1298.9</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5739,13 +5742,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-72.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="Q87">
-        <v>-72.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="R87">
-        <v>-0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5789,7 +5792,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5845,7 +5848,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5901,7 +5904,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5945,7 +5948,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>296.7</v>
+        <v>297.6</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5957,13 +5960,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>67.65000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="Q91">
-        <v>67.65000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="R91">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6007,7 +6010,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6063,7 +6066,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6119,7 +6122,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6175,7 +6178,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6231,7 +6234,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6287,7 +6290,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6343,7 +6346,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6402,7 +6405,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6458,7 +6461,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6514,7 +6517,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6570,7 +6573,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6626,7 +6629,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6682,7 +6685,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6726,7 +6729,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1744.4</v>
+        <v>1777.1</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6738,13 +6741,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>-40.5</v>
+        <v>123</v>
       </c>
       <c r="Q105">
-        <v>-40.5</v>
+        <v>123</v>
       </c>
       <c r="R105">
-        <v>-0.46</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6788,7 +6791,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6844,7 +6847,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6900,7 +6903,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6956,7 +6959,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7012,7 +7015,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7068,7 +7071,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7124,7 +7127,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7180,7 +7183,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7236,7 +7239,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7292,7 +7295,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7348,7 +7351,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7404,7 +7407,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7448,7 +7451,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1138.1</v>
+        <v>1186.5</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7460,13 +7463,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-48</v>
+        <v>339.2</v>
       </c>
       <c r="Q118">
-        <v>-48</v>
+        <v>339.2</v>
       </c>
       <c r="R118">
-        <v>-0.52</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7498,7 +7501,7 @@
         <v>9697.6</v>
       </c>
       <c r="J119">
-        <v>333.4</v>
+        <v>330.5</v>
       </c>
       <c r="L119">
         <v>317.68</v>
@@ -7510,13 +7513,13 @@
         <v>0</v>
       </c>
       <c r="P119">
-        <v>-29</v>
+        <v>-113.1</v>
       </c>
       <c r="Q119">
-        <v>-29</v>
+        <v>-113.1</v>
       </c>
       <c r="R119">
-        <v>-0.3</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7560,7 +7563,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7604,7 +7607,7 @@
         <v>9425.9</v>
       </c>
       <c r="J121">
-        <v>854.9</v>
+        <v>863.1</v>
       </c>
       <c r="L121">
         <v>814.05</v>
@@ -7616,13 +7619,13 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>-22</v>
+        <v>68.2</v>
       </c>
       <c r="Q121">
-        <v>-22</v>
+        <v>68.2</v>
       </c>
       <c r="R121">
-        <v>-0.23</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7654,7 +7657,7 @@
         <v>9982.5</v>
       </c>
       <c r="J122">
-        <v>1936.8</v>
+        <v>1927.1</v>
       </c>
       <c r="L122">
         <v>1896.67</v>
@@ -7666,13 +7669,13 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>-298.5</v>
+        <v>-347</v>
       </c>
       <c r="Q122">
-        <v>-298.5</v>
+        <v>-347</v>
       </c>
       <c r="R122">
-        <v>-2.99</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7716,7 +7719,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7760,7 +7763,7 @@
         <v>8259.200000000001</v>
       </c>
       <c r="J124">
-        <v>4037.9</v>
+        <v>4106.6</v>
       </c>
       <c r="L124">
         <v>3923.12</v>
@@ -7772,13 +7775,13 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>-183.4</v>
+        <v>-46</v>
       </c>
       <c r="Q124">
-        <v>-183.4</v>
+        <v>-46</v>
       </c>
       <c r="R124">
-        <v>-2.22</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7810,7 +7813,7 @@
         <v>9981.6</v>
       </c>
       <c r="J125">
-        <v>411.85</v>
+        <v>412.85</v>
       </c>
       <c r="L125">
         <v>395.1</v>
@@ -7822,13 +7825,13 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>-97.2</v>
+        <v>-73.2</v>
       </c>
       <c r="Q125">
-        <v>-97.2</v>
+        <v>-73.2</v>
       </c>
       <c r="R125">
-        <v>-0.97</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7860,7 +7863,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>151.01</v>
+        <v>151.54</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7872,13 +7875,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>127.3</v>
+        <v>162.81</v>
       </c>
       <c r="Q126">
-        <v>127.3</v>
+        <v>162.81</v>
       </c>
       <c r="R126">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7922,7 +7925,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7966,7 +7969,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>269.1</v>
+        <v>265.4</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7978,13 +7981,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>185</v>
+        <v>48.1</v>
       </c>
       <c r="Q128">
-        <v>185</v>
+        <v>48.1</v>
       </c>
       <c r="R128">
-        <v>1.89</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -8016,7 +8019,7 @@
         <v>7269</v>
       </c>
       <c r="J129">
-        <v>3481.9</v>
+        <v>3559.6</v>
       </c>
       <c r="L129">
         <v>3452.77</v>
@@ -8028,13 +8031,13 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>-305.2</v>
+        <v>-149.8</v>
       </c>
       <c r="Q129">
-        <v>-305.2</v>
+        <v>-149.8</v>
       </c>
       <c r="R129">
-        <v>-4.2</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -8066,7 +8069,7 @@
         <v>8952.799999999999</v>
       </c>
       <c r="J130">
-        <v>2186</v>
+        <v>2195.4</v>
       </c>
       <c r="L130">
         <v>2126.29</v>
@@ -8078,13 +8081,13 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>-208.8</v>
+        <v>-171.2</v>
       </c>
       <c r="Q130">
-        <v>-208.8</v>
+        <v>-171.2</v>
       </c>
       <c r="R130">
-        <v>-2.33</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -8116,7 +8119,7 @@
         <v>9219.700000000001</v>
       </c>
       <c r="J131">
-        <v>1294.3</v>
+        <v>1281.2</v>
       </c>
       <c r="L131">
         <v>1251.24</v>
@@ -8128,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="P131">
-        <v>-159.6</v>
+        <v>-251.3</v>
       </c>
       <c r="Q131">
-        <v>-159.6</v>
+        <v>-251.3</v>
       </c>
       <c r="R131">
-        <v>-1.73</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -8178,7 +8181,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8204,7 +8207,7 @@
         <v>137</v>
       </c>
       <c r="D133" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8216,7 +8219,7 @@
         <v>66</v>
       </c>
       <c r="H133">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I133">
         <v>9962.700000000001</v>
@@ -8224,23 +8227,29 @@
       <c r="J133">
         <v>144.27</v>
       </c>
+      <c r="K133" t="s">
+        <v>149</v>
+      </c>
       <c r="L133">
         <v>143.4</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>143.4</v>
+      </c>
+      <c r="N133" t="s">
+        <v>150</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>-498.2999999999989</v>
       </c>
       <c r="P133">
-        <v>-440.88</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>-440.88</v>
+        <v>-498.2999999999989</v>
       </c>
       <c r="R133">
-        <v>-4.43</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="134" spans="1:18">
@@ -8272,7 +8281,7 @@
         <v>9962.4</v>
       </c>
       <c r="J134">
-        <v>404.65</v>
+        <v>401.45</v>
       </c>
       <c r="L134">
         <v>394.35</v>
@@ -8284,13 +8293,13 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>-250.8</v>
+        <v>-327.6</v>
       </c>
       <c r="Q134">
-        <v>-250.8</v>
+        <v>-327.6</v>
       </c>
       <c r="R134">
-        <v>-2.52</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="135" spans="1:18">
@@ -8322,7 +8331,7 @@
         <v>9237</v>
       </c>
       <c r="J135">
-        <v>3079</v>
+        <v>3129.6</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8334,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>151.8</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>151.8</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8372,7 +8381,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>454.2</v>
+        <v>468.15</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8384,13 +8393,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>306.9</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>306.9</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>3.07</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="154">
   <si>
     <t>Buy Date</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -836,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S136"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -913,13 +916,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -949,7 +952,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -969,13 +972,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1005,7 +1008,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1028,13 +1031,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1064,7 +1067,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1084,13 +1087,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1120,7 +1123,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1140,13 +1143,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1176,7 +1179,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1196,13 +1199,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1232,7 +1235,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1252,13 +1255,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1288,7 +1291,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1308,13 +1311,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1344,7 +1347,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1364,13 +1367,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1400,7 +1403,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1420,13 +1423,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1447,7 +1450,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1456,7 +1459,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1471,7 +1474,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1479,13 +1482,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1515,7 +1518,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1538,13 +1541,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1574,7 +1577,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1594,13 +1597,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1630,7 +1633,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1650,13 +1653,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1686,7 +1689,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1706,13 +1709,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1742,7 +1745,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1762,13 +1765,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1798,7 +1801,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1818,13 +1821,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1854,7 +1857,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1874,13 +1877,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1910,7 +1913,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1930,13 +1933,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1966,7 +1969,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1986,13 +1989,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2013,7 +2016,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2022,7 +2025,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2042,13 +2045,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2069,7 +2072,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2078,7 +2081,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2098,13 +2101,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2134,7 +2137,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2154,13 +2157,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2190,7 +2193,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2210,13 +2213,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2246,7 +2249,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2266,13 +2269,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2293,7 +2296,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2302,7 +2305,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2322,13 +2325,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2358,7 +2361,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2378,13 +2381,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2414,7 +2417,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2434,13 +2437,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2470,7 +2473,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2490,13 +2493,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2526,7 +2529,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2546,13 +2549,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2573,7 +2576,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2582,7 +2585,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2602,13 +2605,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2638,7 +2641,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2658,13 +2661,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2694,7 +2697,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2714,13 +2717,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2741,7 +2744,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2750,7 +2753,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2770,13 +2773,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2797,7 +2800,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2806,7 +2809,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2826,13 +2829,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2862,7 +2865,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2882,13 +2885,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2918,7 +2921,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2938,13 +2941,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2974,7 +2977,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -2997,13 +3000,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3033,7 +3036,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3053,13 +3056,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3089,7 +3092,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3109,13 +3112,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3145,7 +3148,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3165,13 +3168,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3192,7 +3195,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3201,7 +3204,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3221,13 +3224,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3248,7 +3251,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3257,7 +3260,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3277,13 +3280,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3313,7 +3316,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3333,13 +3336,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3369,7 +3372,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3389,13 +3392,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3413,7 +3416,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>380.95</v>
+        <v>372.4</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3425,13 +3428,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>484.4</v>
+        <v>364.7</v>
       </c>
       <c r="Q46">
-        <v>969.29</v>
+        <v>849.59</v>
       </c>
       <c r="R46">
-        <v>9.99</v>
+        <v>8.76</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3442,13 +3445,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3478,7 +3481,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3498,13 +3501,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3534,7 +3537,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3554,13 +3557,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3590,7 +3593,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3613,13 +3616,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3649,7 +3652,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3669,13 +3672,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3705,7 +3708,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3725,13 +3728,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3761,7 +3764,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3784,13 +3787,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3820,7 +3823,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3840,13 +3843,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3876,7 +3879,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3899,13 +3902,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3935,7 +3938,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3958,13 +3961,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3994,7 +3997,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4014,13 +4017,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4041,7 +4044,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4050,7 +4053,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4070,13 +4073,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4106,7 +4109,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4126,13 +4129,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4162,7 +4165,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4185,13 +4188,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4221,7 +4224,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4241,13 +4244,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4277,7 +4280,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4300,13 +4303,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4336,7 +4339,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4351,7 +4354,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4359,13 +4362,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4395,7 +4398,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4415,13 +4418,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4451,7 +4454,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4471,13 +4474,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4507,7 +4510,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4527,13 +4530,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4563,7 +4566,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4583,13 +4586,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4619,7 +4622,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4639,13 +4642,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4675,7 +4678,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4695,13 +4698,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4722,7 +4725,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4731,7 +4734,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4751,13 +4754,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4787,7 +4790,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4807,13 +4810,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4843,7 +4846,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4863,13 +4866,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D72" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4899,7 +4902,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4919,13 +4922,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4955,7 +4958,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4975,13 +4978,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5011,7 +5014,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5031,13 +5034,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D75" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5067,7 +5070,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5087,13 +5090,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D76" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5123,7 +5126,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5143,13 +5146,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D77" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5179,7 +5182,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5199,13 +5202,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D78" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5235,7 +5238,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5255,13 +5258,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C79" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5291,7 +5294,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5311,13 +5314,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5347,7 +5350,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5367,13 +5370,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5403,7 +5406,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5423,13 +5426,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C82" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D82" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5459,7 +5462,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5482,13 +5485,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5518,7 +5521,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5538,13 +5541,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C84" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D84" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5574,7 +5577,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5594,13 +5597,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5630,7 +5633,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5650,13 +5653,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5686,7 +5689,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5706,13 +5709,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5730,7 +5733,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1298.9</v>
+        <v>1253.3</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5742,13 +5745,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>98.7</v>
+        <v>-220.5</v>
       </c>
       <c r="Q87">
-        <v>98.7</v>
+        <v>-220.5</v>
       </c>
       <c r="R87">
-        <v>1.1</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5756,13 +5759,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D88" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5792,7 +5795,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5812,13 +5815,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C89" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5848,7 +5851,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5868,13 +5871,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D90" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5904,7 +5907,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5924,13 +5927,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C91" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D91" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5948,7 +5951,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>297.6</v>
+        <v>302.1</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5960,13 +5963,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>97.34999999999999</v>
+        <v>245.85</v>
       </c>
       <c r="Q91">
-        <v>97.34999999999999</v>
+        <v>245.85</v>
       </c>
       <c r="R91">
-        <v>1</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5974,13 +5977,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D92" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6010,7 +6013,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6030,13 +6033,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D93" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6066,7 +6069,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6086,13 +6089,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C94" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6122,7 +6125,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6142,13 +6145,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D95" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6178,7 +6181,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6198,13 +6201,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D96" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6234,7 +6237,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6254,13 +6257,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D97" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6290,7 +6293,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6310,13 +6313,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C98" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6346,7 +6349,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6369,13 +6372,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D99" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6405,7 +6408,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6425,13 +6428,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D100" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6461,7 +6464,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6481,13 +6484,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D101" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6517,7 +6520,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6537,13 +6540,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D102" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6573,7 +6576,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6593,13 +6596,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C103" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6629,7 +6632,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6649,13 +6652,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D104" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6685,7 +6688,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6705,13 +6708,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C105" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D105" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6729,7 +6732,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1777.1</v>
+        <v>1758.4</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6741,13 +6744,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>123</v>
+        <v>29.5</v>
       </c>
       <c r="Q105">
-        <v>123</v>
+        <v>29.5</v>
       </c>
       <c r="R105">
-        <v>1.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6755,13 +6758,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D106" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6782,7 +6785,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6791,7 +6794,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6811,13 +6814,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6847,7 +6850,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6867,13 +6870,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6903,7 +6906,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6923,13 +6926,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C109" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D109" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6950,7 +6953,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6959,7 +6962,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6979,13 +6982,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C110" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D110" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7015,7 +7018,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7035,13 +7038,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7071,7 +7074,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7091,13 +7094,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C112" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7127,7 +7130,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7147,13 +7150,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7183,7 +7186,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7203,13 +7206,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C114" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7239,7 +7242,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7259,13 +7262,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C115" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D115" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7295,7 +7298,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7315,13 +7318,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C116" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D116" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7351,7 +7354,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7371,13 +7374,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D117" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7407,7 +7410,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7427,13 +7430,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7451,7 +7454,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1186.5</v>
+        <v>1106.2</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7463,13 +7466,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>339.2</v>
+        <v>-303.2</v>
       </c>
       <c r="Q118">
-        <v>339.2</v>
+        <v>-303.2</v>
       </c>
       <c r="R118">
-        <v>3.71</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7477,10 +7480,10 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D119" t="s">
         <v>141</v>
@@ -7495,7 +7498,7 @@
         <v>29</v>
       </c>
       <c r="H119">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>9697.6</v>
@@ -7503,23 +7506,29 @@
       <c r="J119">
         <v>330.5</v>
       </c>
+      <c r="K119" t="s">
+        <v>62</v>
+      </c>
       <c r="L119">
         <v>317.68</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>317.68</v>
+      </c>
+      <c r="N119" t="s">
+        <v>151</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>-484.8799999999991</v>
       </c>
       <c r="P119">
-        <v>-113.1</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>-113.1</v>
+        <v>-484.8799999999991</v>
       </c>
       <c r="R119">
-        <v>-1.17</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -7527,13 +7536,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7563,7 +7572,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7583,10 +7592,10 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C121" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D121" t="s">
         <v>141</v>
@@ -7601,7 +7610,7 @@
         <v>11</v>
       </c>
       <c r="H121">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I121">
         <v>9425.9</v>
@@ -7609,23 +7618,29 @@
       <c r="J121">
         <v>863.1</v>
       </c>
+      <c r="K121" t="s">
+        <v>62</v>
+      </c>
       <c r="L121">
         <v>814.05</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>814.05</v>
+      </c>
+      <c r="N121" t="s">
+        <v>151</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>-471.3500000000003</v>
       </c>
       <c r="P121">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>68.2</v>
+        <v>-471.3500000000003</v>
       </c>
       <c r="R121">
-        <v>0.72</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -7633,10 +7648,10 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C122" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D122" t="s">
         <v>141</v>
@@ -7651,7 +7666,7 @@
         <v>5</v>
       </c>
       <c r="H122">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I122">
         <v>9982.5</v>
@@ -7659,23 +7674,29 @@
       <c r="J122">
         <v>1927.1</v>
       </c>
+      <c r="K122" t="s">
+        <v>62</v>
+      </c>
       <c r="L122">
         <v>1896.67</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>1896.67</v>
+      </c>
+      <c r="N122" t="s">
+        <v>151</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>-499.1499999999996</v>
       </c>
       <c r="P122">
-        <v>-347</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>-347</v>
+        <v>-499.1499999999996</v>
       </c>
       <c r="R122">
-        <v>-3.48</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -7683,13 +7704,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C123" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D123" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7710,7 +7731,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7719,7 +7740,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7739,10 +7760,10 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C124" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>141</v>
@@ -7757,7 +7778,7 @@
         <v>2</v>
       </c>
       <c r="H124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I124">
         <v>8259.200000000001</v>
@@ -7765,23 +7786,29 @@
       <c r="J124">
         <v>4106.6</v>
       </c>
+      <c r="K124" t="s">
+        <v>62</v>
+      </c>
       <c r="L124">
         <v>3923.12</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3923.12</v>
+      </c>
+      <c r="N124" t="s">
+        <v>151</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>-412.9600000000009</v>
       </c>
       <c r="P124">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>-46</v>
+        <v>-412.9600000000009</v>
       </c>
       <c r="R124">
-        <v>-0.5600000000000001</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -7789,10 +7816,10 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C125" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D125" t="s">
         <v>141</v>
@@ -7807,7 +7834,7 @@
         <v>24</v>
       </c>
       <c r="H125">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I125">
         <v>9981.6</v>
@@ -7815,23 +7842,29 @@
       <c r="J125">
         <v>412.85</v>
       </c>
+      <c r="K125" t="s">
+        <v>62</v>
+      </c>
       <c r="L125">
         <v>395.1</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>395.1</v>
+      </c>
+      <c r="N125" t="s">
+        <v>151</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>-499.1999999999989</v>
       </c>
       <c r="P125">
-        <v>-73.2</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>-73.2</v>
+        <v>-499.1999999999989</v>
       </c>
       <c r="R125">
-        <v>-0.73</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -7839,13 +7872,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C126" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D126" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7863,7 +7896,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>151.54</v>
+        <v>147.85</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7875,13 +7908,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>162.81</v>
+        <v>-84.42</v>
       </c>
       <c r="Q126">
-        <v>162.81</v>
+        <v>-84.42</v>
       </c>
       <c r="R126">
-        <v>1.63</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7889,13 +7922,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C127" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7925,7 +7958,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7945,13 +7978,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D128" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7969,7 +8002,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>265.4</v>
+        <v>265.45</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -7981,13 +8014,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>48.1</v>
+        <v>49.95</v>
       </c>
       <c r="Q128">
-        <v>48.1</v>
+        <v>49.95</v>
       </c>
       <c r="R128">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -7995,10 +8028,10 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D129" t="s">
         <v>141</v>
@@ -8013,7 +8046,7 @@
         <v>2</v>
       </c>
       <c r="H129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I129">
         <v>7269</v>
@@ -8021,23 +8054,29 @@
       <c r="J129">
         <v>3559.6</v>
       </c>
+      <c r="K129" t="s">
+        <v>62</v>
+      </c>
       <c r="L129">
         <v>3452.77</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3452.77</v>
+      </c>
+      <c r="N129" t="s">
+        <v>151</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>-363.46</v>
       </c>
       <c r="P129">
-        <v>-149.8</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>-149.8</v>
+        <v>-363.46</v>
       </c>
       <c r="R129">
-        <v>-2.06</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -8045,10 +8084,10 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D130" t="s">
         <v>141</v>
@@ -8063,7 +8102,7 @@
         <v>4</v>
       </c>
       <c r="H130">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I130">
         <v>8952.799999999999</v>
@@ -8071,23 +8110,29 @@
       <c r="J130">
         <v>2195.4</v>
       </c>
+      <c r="K130" t="s">
+        <v>62</v>
+      </c>
       <c r="L130">
         <v>2126.29</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>2126.29</v>
+      </c>
+      <c r="N130" t="s">
+        <v>151</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>-447.6399999999994</v>
       </c>
       <c r="P130">
-        <v>-171.2</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>-171.2</v>
+        <v>-447.6399999999994</v>
       </c>
       <c r="R130">
-        <v>-1.91</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -8095,10 +8140,10 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C131" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D131" t="s">
         <v>141</v>
@@ -8113,7 +8158,7 @@
         <v>7</v>
       </c>
       <c r="H131">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I131">
         <v>9219.700000000001</v>
@@ -8121,23 +8166,29 @@
       <c r="J131">
         <v>1281.2</v>
       </c>
+      <c r="K131" t="s">
+        <v>62</v>
+      </c>
       <c r="L131">
         <v>1251.24</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>1251.24</v>
+      </c>
+      <c r="N131" t="s">
+        <v>151</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>-461.0199999999993</v>
       </c>
       <c r="P131">
-        <v>-251.3</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>-251.3</v>
+        <v>-461.0199999999993</v>
       </c>
       <c r="R131">
-        <v>-2.73</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -8145,13 +8196,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D132" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8181,7 +8232,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8201,13 +8252,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C133" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D133" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8228,7 +8279,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8237,7 +8288,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8257,10 +8308,10 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D134" t="s">
         <v>141</v>
@@ -8275,7 +8326,7 @@
         <v>24</v>
       </c>
       <c r="H134">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I134">
         <v>9962.4</v>
@@ -8283,23 +8334,29 @@
       <c r="J134">
         <v>401.45</v>
       </c>
+      <c r="K134" t="s">
+        <v>62</v>
+      </c>
       <c r="L134">
         <v>394.35</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>394.35</v>
+      </c>
+      <c r="N134" t="s">
+        <v>151</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>-498</v>
       </c>
       <c r="P134">
-        <v>-327.6</v>
+        <v>0</v>
       </c>
       <c r="Q134">
-        <v>-327.6</v>
+        <v>-498</v>
       </c>
       <c r="R134">
-        <v>-3.29</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="135" spans="1:18">
@@ -8307,13 +8364,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C135" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D135" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8331,7 +8388,7 @@
         <v>9237</v>
       </c>
       <c r="J135">
-        <v>3129.6</v>
+        <v>2988.3</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8343,13 +8400,13 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>151.8</v>
+        <v>-272.1</v>
       </c>
       <c r="Q135">
-        <v>151.8</v>
+        <v>-272.1</v>
       </c>
       <c r="R135">
-        <v>1.64</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8357,13 +8414,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D136" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8381,7 +8438,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>468.15</v>
+        <v>455.25</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8393,13 +8450,63 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>306.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q136">
-        <v>306.9</v>
+        <v>23.1</v>
       </c>
       <c r="R136">
-        <v>3.07</v>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18">
+      <c r="A137" t="s">
+        <v>62</v>
+      </c>
+      <c r="B137" t="s">
+        <v>108</v>
+      </c>
+      <c r="C137" t="s">
+        <v>138</v>
+      </c>
+      <c r="D137" t="s">
+        <v>142</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>3655.6</v>
+      </c>
+      <c r="G137">
+        <v>2</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+      <c r="I137">
+        <v>7311.2</v>
+      </c>
+      <c r="J137">
+        <v>3655.6</v>
+      </c>
+      <c r="L137">
+        <v>3472.82</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="155">
   <si>
     <t>Buy Date</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -839,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S137"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -916,13 +919,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -952,7 +955,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -972,13 +975,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1008,7 +1011,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1031,13 +1034,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1067,7 +1070,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1087,13 +1090,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1123,7 +1126,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1143,13 +1146,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1179,7 +1182,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1199,13 +1202,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1235,7 +1238,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1255,13 +1258,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1291,7 +1294,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1311,13 +1314,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1347,7 +1350,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1367,13 +1370,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1403,7 +1406,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1423,13 +1426,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1450,7 +1453,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1459,7 +1462,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1474,7 +1477,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1482,13 +1485,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1518,7 +1521,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1541,13 +1544,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1577,7 +1580,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1597,13 +1600,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1633,7 +1636,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1653,13 +1656,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1689,7 +1692,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1709,13 +1712,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1745,7 +1748,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1765,13 +1768,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1801,7 +1804,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1821,13 +1824,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1857,7 +1860,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1877,13 +1880,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1913,7 +1916,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1933,13 +1936,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1969,7 +1972,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1989,13 +1992,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2016,7 +2019,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2025,7 +2028,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2045,13 +2048,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2072,7 +2075,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2081,7 +2084,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2101,13 +2104,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2137,7 +2140,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2157,13 +2160,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2193,7 +2196,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2213,13 +2216,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2249,7 +2252,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2269,13 +2272,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2296,7 +2299,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2305,7 +2308,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2325,13 +2328,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2361,7 +2364,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2381,13 +2384,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2417,7 +2420,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2437,13 +2440,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2473,7 +2476,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2493,13 +2496,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2529,7 +2532,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2549,13 +2552,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2576,7 +2579,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2585,7 +2588,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2605,13 +2608,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2641,7 +2644,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2661,13 +2664,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2697,7 +2700,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2717,13 +2720,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2744,7 +2747,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2753,7 +2756,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2773,13 +2776,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2800,7 +2803,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2809,7 +2812,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2829,13 +2832,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2865,7 +2868,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2885,13 +2888,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2921,7 +2924,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2941,13 +2944,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2977,7 +2980,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3000,13 +3003,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3036,7 +3039,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3056,13 +3059,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3092,7 +3095,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3112,13 +3115,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3148,7 +3151,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3168,13 +3171,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3195,7 +3198,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3204,7 +3207,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3224,13 +3227,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3251,7 +3254,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3260,7 +3263,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3280,13 +3283,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3316,7 +3319,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3336,13 +3339,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3372,7 +3375,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3392,13 +3395,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3416,7 +3419,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>372.4</v>
+        <v>375.55</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3428,13 +3431,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>364.7</v>
+        <v>408.8</v>
       </c>
       <c r="Q46">
-        <v>849.59</v>
+        <v>893.6900000000001</v>
       </c>
       <c r="R46">
-        <v>8.76</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3445,13 +3448,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3481,7 +3484,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3501,13 +3504,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3537,7 +3540,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3557,13 +3560,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3593,7 +3596,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3616,13 +3619,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3652,7 +3655,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3672,13 +3675,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3708,7 +3711,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3728,13 +3731,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3764,7 +3767,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3787,13 +3790,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3823,7 +3826,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3843,13 +3846,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3879,7 +3882,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3902,13 +3905,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3938,7 +3941,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3961,13 +3964,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3997,7 +4000,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4017,13 +4020,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4044,7 +4047,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4053,7 +4056,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4073,13 +4076,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4109,7 +4112,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4129,13 +4132,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4165,7 +4168,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4188,13 +4191,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D60" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4224,7 +4227,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4244,13 +4247,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D61" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4280,7 +4283,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4303,13 +4306,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D62" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4339,7 +4342,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4354,7 +4357,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4362,13 +4365,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4398,7 +4401,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4418,13 +4421,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4454,7 +4457,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4474,13 +4477,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4510,7 +4513,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4530,13 +4533,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4566,7 +4569,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4586,13 +4589,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4622,7 +4625,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4642,13 +4645,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4678,7 +4681,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4698,13 +4701,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4725,7 +4728,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4734,7 +4737,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4754,13 +4757,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4790,7 +4793,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4810,13 +4813,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4846,7 +4849,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4866,13 +4869,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4902,7 +4905,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4922,13 +4925,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D73" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4958,7 +4961,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4978,13 +4981,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5014,7 +5017,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5034,13 +5037,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D75" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5070,7 +5073,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5090,13 +5093,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D76" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5126,7 +5129,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5146,13 +5149,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C77" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D77" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5182,7 +5185,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5202,13 +5205,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5238,7 +5241,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5258,13 +5261,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D79" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5294,7 +5297,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5314,13 +5317,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5350,7 +5353,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5370,13 +5373,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D81" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5406,7 +5409,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5426,13 +5429,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D82" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5462,7 +5465,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5485,13 +5488,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5521,7 +5524,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5541,13 +5544,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D84" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5577,7 +5580,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5597,13 +5600,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D85" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5633,7 +5636,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5653,13 +5656,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D86" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5689,7 +5692,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5709,13 +5712,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5733,7 +5736,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1253.3</v>
+        <v>1259.6</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5745,13 +5748,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-220.5</v>
+        <v>-176.4</v>
       </c>
       <c r="Q87">
-        <v>-220.5</v>
+        <v>-176.4</v>
       </c>
       <c r="R87">
-        <v>-2.45</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5759,13 +5762,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C88" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D88" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5795,7 +5798,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5815,13 +5818,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D89" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5851,7 +5854,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5871,13 +5874,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C90" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D90" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5907,7 +5910,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5927,13 +5930,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D91" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5951,7 +5954,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>302.1</v>
+        <v>299</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5963,13 +5966,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>245.85</v>
+        <v>143.55</v>
       </c>
       <c r="Q91">
-        <v>245.85</v>
+        <v>143.55</v>
       </c>
       <c r="R91">
-        <v>2.53</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5977,13 +5980,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C92" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D92" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6013,7 +6016,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6033,13 +6036,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D93" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6069,7 +6072,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6089,13 +6092,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D94" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6125,7 +6128,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6145,13 +6148,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D95" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6181,7 +6184,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6201,13 +6204,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D96" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6237,7 +6240,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6257,13 +6260,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C97" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D97" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6293,7 +6296,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6313,13 +6316,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D98" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6349,7 +6352,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6372,13 +6375,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6408,7 +6411,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6428,13 +6431,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D100" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6464,7 +6467,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6484,13 +6487,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D101" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6520,7 +6523,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6540,13 +6543,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D102" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6576,7 +6579,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6596,13 +6599,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D103" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6632,7 +6635,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6652,13 +6655,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D104" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6688,7 +6691,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6708,13 +6711,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D105" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6732,7 +6735,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1758.4</v>
+        <v>1753.3</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6744,13 +6747,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>29.5</v>
+        <v>4</v>
       </c>
       <c r="Q105">
-        <v>29.5</v>
+        <v>4</v>
       </c>
       <c r="R105">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6758,13 +6761,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6785,7 +6788,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6794,7 +6797,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6814,13 +6817,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6850,7 +6853,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6870,13 +6873,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D108" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6906,7 +6909,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6926,13 +6929,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6953,7 +6956,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6962,7 +6965,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6982,13 +6985,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7018,7 +7021,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7038,13 +7041,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7074,7 +7077,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7094,13 +7097,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C112" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D112" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7130,7 +7133,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7150,13 +7153,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D113" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7186,7 +7189,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7206,13 +7209,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D114" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7242,7 +7245,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7262,13 +7265,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C115" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7298,7 +7301,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7318,13 +7321,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C116" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D116" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7354,7 +7357,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7374,13 +7377,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7410,7 +7413,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7430,13 +7433,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C118" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D118" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7454,7 +7457,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1106.2</v>
+        <v>1120.6</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7466,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-303.2</v>
+        <v>-188</v>
       </c>
       <c r="Q118">
-        <v>-303.2</v>
+        <v>-188</v>
       </c>
       <c r="R118">
-        <v>-3.31</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7480,13 +7483,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7516,16 +7519,16 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O119">
-        <v>-484.8799999999991</v>
+        <v>-484.8799999999992</v>
       </c>
       <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>-484.8799999999991</v>
+        <v>-484.8799999999992</v>
       </c>
       <c r="R119">
         <v>-5</v>
@@ -7536,13 +7539,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C120" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7572,7 +7575,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7592,13 +7595,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C121" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7628,7 +7631,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7648,13 +7651,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C122" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7684,16 +7687,16 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O122">
-        <v>-499.1499999999996</v>
+        <v>-499.1499999999997</v>
       </c>
       <c r="P122">
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>-499.1499999999996</v>
+        <v>-499.1499999999997</v>
       </c>
       <c r="R122">
         <v>-5</v>
@@ -7704,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7731,7 +7734,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7740,7 +7743,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7760,13 +7763,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D124" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7796,7 +7799,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7816,13 +7819,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C125" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7852,7 +7855,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7872,13 +7875,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C126" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7896,7 +7899,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>147.85</v>
+        <v>150.11</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7908,13 +7911,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>-84.42</v>
+        <v>67</v>
       </c>
       <c r="Q126">
-        <v>-84.42</v>
+        <v>67</v>
       </c>
       <c r="R126">
-        <v>-0.85</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7922,13 +7925,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D127" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7958,7 +7961,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7978,13 +7981,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -8002,7 +8005,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>265.45</v>
+        <v>268.05</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -8014,13 +8017,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>49.95</v>
+        <v>146.15</v>
       </c>
       <c r="Q128">
-        <v>49.95</v>
+        <v>146.15</v>
       </c>
       <c r="R128">
-        <v>0.51</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -8028,13 +8031,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8064,7 +8067,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8084,13 +8087,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8120,7 +8123,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8140,13 +8143,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C131" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8176,7 +8179,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8196,13 +8199,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8232,7 +8235,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8252,13 +8255,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C133" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8279,7 +8282,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8288,7 +8291,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8308,13 +8311,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D134" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8344,7 +8347,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8364,13 +8367,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D135" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8388,7 +8391,7 @@
         <v>9237</v>
       </c>
       <c r="J135">
-        <v>2988.3</v>
+        <v>3001.8</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8400,13 +8403,13 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>-272.1</v>
+        <v>-231.6</v>
       </c>
       <c r="Q135">
-        <v>-272.1</v>
+        <v>-231.6</v>
       </c>
       <c r="R135">
-        <v>-2.95</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8414,13 +8417,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C136" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8438,7 +8441,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>455.25</v>
+        <v>442.1</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8450,13 +8453,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>23.1</v>
+        <v>-266.2</v>
       </c>
       <c r="Q136">
-        <v>23.1</v>
+        <v>-266.2</v>
       </c>
       <c r="R136">
-        <v>0.23</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -8464,13 +8467,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D137" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -8488,7 +8491,7 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>3655.6</v>
+        <v>3756.5</v>
       </c>
       <c r="L137">
         <v>3472.82</v>
@@ -8500,12 +8503,62 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>201.8</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>201.8</v>
       </c>
       <c r="R137">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18">
+      <c r="A138" t="s">
+        <v>63</v>
+      </c>
+      <c r="B138" t="s">
+        <v>110</v>
+      </c>
+      <c r="C138" t="s">
+        <v>139</v>
+      </c>
+      <c r="D138" t="s">
+        <v>143</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>839.55</v>
+      </c>
+      <c r="G138">
+        <v>11</v>
+      </c>
+      <c r="H138">
+        <v>11</v>
+      </c>
+      <c r="I138">
+        <v>9235.049999999999</v>
+      </c>
+      <c r="J138">
+        <v>839.55</v>
+      </c>
+      <c r="L138">
+        <v>797.5700000000001</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="158">
   <si>
     <t>Buy Date</t>
   </si>
@@ -208,6 +208,9 @@
     <t>2026-03-24</t>
   </si>
   <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -431,6 +434,12 @@
   </si>
   <si>
     <t>VBL</t>
+  </si>
+  <si>
+    <t>GODREJCP</t>
+  </si>
+  <si>
+    <t>INDUSINDBK</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -842,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:S145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -919,13 +928,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -955,7 +964,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -975,13 +984,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1011,7 +1020,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1034,13 +1043,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1070,7 +1079,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1090,13 +1099,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1126,7 +1135,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1146,13 +1155,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1182,7 +1191,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1202,13 +1211,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1238,7 +1247,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1258,13 +1267,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1294,7 +1303,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1314,13 +1323,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1350,7 +1359,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1370,13 +1379,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1406,7 +1415,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1426,13 +1435,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1453,7 +1462,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1462,7 +1471,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1477,7 +1486,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1485,13 +1494,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1521,7 +1530,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1544,13 +1553,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1580,7 +1589,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1600,13 +1609,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1636,7 +1645,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1656,13 +1665,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1692,7 +1701,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1712,13 +1721,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1748,7 +1757,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1768,13 +1777,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1804,7 +1813,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1824,13 +1833,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1860,7 +1869,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1880,13 +1889,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1916,7 +1925,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1936,13 +1945,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1972,7 +1981,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -1992,13 +2001,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2019,7 +2028,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2028,7 +2037,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2048,13 +2057,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2075,7 +2084,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2084,7 +2093,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2104,13 +2113,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2140,7 +2149,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2160,13 +2169,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2196,7 +2205,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2216,13 +2225,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2252,7 +2261,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2272,13 +2281,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2299,7 +2308,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2308,7 +2317,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2328,13 +2337,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2364,7 +2373,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2384,13 +2393,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2420,7 +2429,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2440,13 +2449,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2476,7 +2485,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2496,13 +2505,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2532,7 +2541,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2552,13 +2561,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2579,7 +2588,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2588,7 +2597,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2608,13 +2617,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2644,7 +2653,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2664,13 +2673,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2700,7 +2709,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2720,13 +2729,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2747,7 +2756,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2756,7 +2765,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2776,13 +2785,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2803,7 +2812,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2812,7 +2821,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2832,13 +2841,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2868,7 +2877,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2888,13 +2897,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2924,7 +2933,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2944,13 +2953,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2980,7 +2989,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3003,13 +3012,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3039,7 +3048,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3059,13 +3068,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3095,7 +3104,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3115,13 +3124,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3151,7 +3160,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3171,13 +3180,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3198,7 +3207,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3207,7 +3216,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3227,13 +3236,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3254,7 +3263,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3263,7 +3272,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3283,13 +3292,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3319,7 +3328,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3339,13 +3348,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3375,7 +3384,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3395,13 +3404,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3419,7 +3428,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>375.55</v>
+        <v>378.4</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3431,13 +3440,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>408.8</v>
+        <v>448.7</v>
       </c>
       <c r="Q46">
-        <v>893.6900000000001</v>
+        <v>933.59</v>
       </c>
       <c r="R46">
-        <v>9.220000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3448,13 +3457,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3484,7 +3493,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3504,13 +3513,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3540,7 +3549,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3560,13 +3569,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3596,7 +3605,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3619,13 +3628,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3655,7 +3664,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3675,13 +3684,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3711,7 +3720,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3731,13 +3740,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D52" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3767,7 +3776,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3790,13 +3799,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3826,7 +3835,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3846,13 +3855,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3882,7 +3891,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3905,13 +3914,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3941,7 +3950,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3964,13 +3973,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4000,7 +4009,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4020,13 +4029,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4047,7 +4056,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4056,7 +4065,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4076,13 +4085,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4112,7 +4121,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4132,13 +4141,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4168,7 +4177,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4191,13 +4200,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4227,7 +4236,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4247,13 +4256,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4283,7 +4292,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4306,13 +4315,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4342,7 +4351,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4357,7 +4366,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4365,13 +4374,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4401,7 +4410,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4421,13 +4430,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4457,7 +4466,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4477,13 +4486,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4513,7 +4522,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4533,13 +4542,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D66" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4569,7 +4578,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4589,13 +4598,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4625,7 +4634,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4645,13 +4654,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C68" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4681,7 +4690,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4701,13 +4710,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4728,7 +4737,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4737,7 +4746,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4757,13 +4766,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4793,7 +4802,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4813,13 +4822,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C71" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4849,7 +4858,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4869,13 +4878,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4905,7 +4914,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4925,13 +4934,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4961,7 +4970,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4981,13 +4990,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D74" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5017,7 +5026,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5037,13 +5046,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5073,7 +5082,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5093,13 +5102,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C76" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D76" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5129,7 +5138,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5149,13 +5158,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D77" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5185,7 +5194,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5205,13 +5214,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D78" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5241,7 +5250,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5261,13 +5270,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5297,7 +5306,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5317,13 +5326,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C80" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D80" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5353,7 +5362,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5373,13 +5382,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D81" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5409,7 +5418,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5429,13 +5438,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C82" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5465,7 +5474,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5488,13 +5497,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C83" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5524,7 +5533,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5544,13 +5553,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D84" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5580,7 +5589,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5600,13 +5609,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C85" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5636,7 +5645,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5656,13 +5665,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5692,7 +5701,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5712,13 +5721,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C87" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D87" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5736,7 +5745,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1259.6</v>
+        <v>1300.7</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5748,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-176.4</v>
+        <v>111.3</v>
       </c>
       <c r="Q87">
-        <v>-176.4</v>
+        <v>111.3</v>
       </c>
       <c r="R87">
-        <v>-1.96</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5762,13 +5771,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5798,7 +5807,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5818,13 +5827,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D89" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5854,7 +5863,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5874,13 +5883,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5910,7 +5919,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5930,13 +5939,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C91" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D91" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5954,7 +5963,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5966,13 +5975,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>143.55</v>
+        <v>11.55</v>
       </c>
       <c r="Q91">
-        <v>143.55</v>
+        <v>11.55</v>
       </c>
       <c r="R91">
-        <v>1.48</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5980,13 +5989,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D92" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6016,7 +6025,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6036,13 +6045,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D93" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6072,7 +6081,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6092,13 +6101,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6128,7 +6137,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6148,13 +6157,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D95" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6184,7 +6193,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6204,13 +6213,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C96" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D96" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6240,7 +6249,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6260,13 +6269,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C97" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6296,7 +6305,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6316,13 +6325,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C98" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6352,7 +6361,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6375,13 +6384,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D99" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6411,7 +6420,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6431,13 +6440,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D100" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6467,7 +6476,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6487,13 +6496,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D101" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6523,7 +6532,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6543,13 +6552,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C102" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D102" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6579,7 +6588,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6599,13 +6608,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D103" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6635,7 +6644,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6655,13 +6664,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D104" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6691,7 +6700,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6711,13 +6720,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C105" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D105" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6735,7 +6744,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1753.3</v>
+        <v>1795.4</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6747,13 +6756,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>4</v>
+        <v>214.5</v>
       </c>
       <c r="Q105">
-        <v>4</v>
+        <v>214.5</v>
       </c>
       <c r="R105">
-        <v>0.05</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6761,13 +6770,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C106" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D106" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6788,7 +6797,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6797,7 +6806,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6817,13 +6826,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D107" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6853,7 +6862,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6873,13 +6882,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D108" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6909,7 +6918,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6929,13 +6938,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D109" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6956,7 +6965,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6965,7 +6974,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6985,13 +6994,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C110" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D110" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7021,7 +7030,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7041,13 +7050,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7077,7 +7086,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7097,13 +7106,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7133,7 +7142,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7153,13 +7162,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C113" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7189,7 +7198,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7209,13 +7218,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C114" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D114" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7245,7 +7254,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7265,13 +7274,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D115" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7301,7 +7310,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7321,13 +7330,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7357,7 +7366,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7377,13 +7386,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C117" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D117" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7413,7 +7422,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7433,13 +7442,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7457,7 +7466,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1120.6</v>
+        <v>1143</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7469,13 +7478,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-188</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="Q118">
-        <v>-188</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="R118">
-        <v>-2.05</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7483,13 +7492,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7519,7 +7528,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7539,13 +7548,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C120" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D120" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7575,7 +7584,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7595,13 +7604,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C121" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D121" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7631,7 +7640,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7651,13 +7660,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C122" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D122" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7687,7 +7696,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7707,13 +7716,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C123" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D123" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7734,7 +7743,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7743,7 +7752,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7763,13 +7772,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D124" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7799,7 +7808,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7819,13 +7828,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C125" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D125" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7855,7 +7864,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7875,13 +7884,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7899,7 +7908,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>150.11</v>
+        <v>153.65</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7911,13 +7920,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>67</v>
+        <v>304.18</v>
       </c>
       <c r="Q126">
-        <v>67</v>
+        <v>304.18</v>
       </c>
       <c r="R126">
-        <v>0.67</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7925,13 +7934,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D127" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7961,7 +7970,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7981,13 +7990,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -8005,7 +8014,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>268.05</v>
+        <v>270.2</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -8017,13 +8026,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>146.15</v>
+        <v>225.7</v>
       </c>
       <c r="Q128">
-        <v>146.15</v>
+        <v>225.7</v>
       </c>
       <c r="R128">
-        <v>1.5</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -8031,13 +8040,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D129" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8067,7 +8076,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8087,13 +8096,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D130" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8123,7 +8132,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8143,13 +8152,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D131" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8179,7 +8188,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8199,13 +8208,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8235,7 +8244,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8255,13 +8264,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8282,7 +8291,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8291,7 +8300,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8311,13 +8320,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D134" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8347,7 +8356,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8367,13 +8376,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C135" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D135" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8391,7 +8400,7 @@
         <v>9237</v>
       </c>
       <c r="J135">
-        <v>3001.8</v>
+        <v>3101.3</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8403,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>-231.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q135">
-        <v>-231.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R135">
-        <v>-2.51</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8417,13 +8426,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D136" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8441,7 +8450,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>442.1</v>
+        <v>443.7</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8453,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-266.2</v>
+        <v>-231</v>
       </c>
       <c r="Q136">
-        <v>-266.2</v>
+        <v>-231</v>
       </c>
       <c r="R136">
-        <v>-2.66</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -8467,13 +8476,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C137" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D137" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -8491,7 +8500,7 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>3756.5</v>
+        <v>3910.8</v>
       </c>
       <c r="L137">
         <v>3472.82</v>
@@ -8503,13 +8512,13 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>201.8</v>
+        <v>510.4</v>
       </c>
       <c r="Q137">
-        <v>201.8</v>
+        <v>510.4</v>
       </c>
       <c r="R137">
-        <v>2.76</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -8517,13 +8526,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C138" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -8541,7 +8550,7 @@
         <v>9235.049999999999</v>
       </c>
       <c r="J138">
-        <v>839.55</v>
+        <v>853.8</v>
       </c>
       <c r="L138">
         <v>797.5700000000001</v>
@@ -8553,12 +8562,362 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>156.75</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>156.75</v>
       </c>
       <c r="R138">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18">
+      <c r="A139" t="s">
+        <v>64</v>
+      </c>
+      <c r="B139" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" t="s">
+        <v>142</v>
+      </c>
+      <c r="D139" t="s">
+        <v>146</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>327.7</v>
+      </c>
+      <c r="G139">
+        <v>30</v>
+      </c>
+      <c r="H139">
+        <v>30</v>
+      </c>
+      <c r="I139">
+        <v>9831</v>
+      </c>
+      <c r="J139">
+        <v>327.7</v>
+      </c>
+      <c r="L139">
+        <v>311.31</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18">
+      <c r="A140" t="s">
+        <v>64</v>
+      </c>
+      <c r="B140" t="s">
+        <v>138</v>
+      </c>
+      <c r="C140" t="s">
+        <v>142</v>
+      </c>
+      <c r="D140" t="s">
+        <v>146</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>268.85</v>
+      </c>
+      <c r="G140">
+        <v>37</v>
+      </c>
+      <c r="H140">
+        <v>37</v>
+      </c>
+      <c r="I140">
+        <v>9947.450000000001</v>
+      </c>
+      <c r="J140">
+        <v>268.85</v>
+      </c>
+      <c r="L140">
+        <v>255.41</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18">
+      <c r="A141" t="s">
+        <v>64</v>
+      </c>
+      <c r="B141" t="s">
+        <v>140</v>
+      </c>
+      <c r="C141" t="s">
+        <v>142</v>
+      </c>
+      <c r="D141" t="s">
+        <v>146</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>1039.6</v>
+      </c>
+      <c r="G141">
+        <v>9</v>
+      </c>
+      <c r="H141">
+        <v>9</v>
+      </c>
+      <c r="I141">
+        <v>9356.4</v>
+      </c>
+      <c r="J141">
+        <v>1039.6</v>
+      </c>
+      <c r="L141">
+        <v>987.62</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>0</v>
+      </c>
+      <c r="R141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18">
+      <c r="A142" t="s">
+        <v>64</v>
+      </c>
+      <c r="B142" t="s">
+        <v>69</v>
+      </c>
+      <c r="C142" t="s">
+        <v>142</v>
+      </c>
+      <c r="D142" t="s">
+        <v>146</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>2134.8</v>
+      </c>
+      <c r="G142">
+        <v>4</v>
+      </c>
+      <c r="H142">
+        <v>4</v>
+      </c>
+      <c r="I142">
+        <v>8539.200000000001</v>
+      </c>
+      <c r="J142">
+        <v>2134.8</v>
+      </c>
+      <c r="L142">
+        <v>2028.06</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>0</v>
+      </c>
+      <c r="R142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18">
+      <c r="A143" t="s">
+        <v>64</v>
+      </c>
+      <c r="B143" t="s">
+        <v>99</v>
+      </c>
+      <c r="C143" t="s">
+        <v>144</v>
+      </c>
+      <c r="D143" t="s">
+        <v>146</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>6212.5</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
+        <v>6212.5</v>
+      </c>
+      <c r="J143">
+        <v>6212.5</v>
+      </c>
+      <c r="L143">
+        <v>5901.88</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>0</v>
+      </c>
+      <c r="R143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
+      <c r="A144" t="s">
+        <v>64</v>
+      </c>
+      <c r="B144" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" t="s">
+        <v>142</v>
+      </c>
+      <c r="D144" t="s">
+        <v>146</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>1886.6</v>
+      </c>
+      <c r="G144">
+        <v>5</v>
+      </c>
+      <c r="H144">
+        <v>5</v>
+      </c>
+      <c r="I144">
+        <v>9433</v>
+      </c>
+      <c r="J144">
+        <v>1886.6</v>
+      </c>
+      <c r="L144">
+        <v>1792.27</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>0</v>
+      </c>
+      <c r="R144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
+      <c r="A145" t="s">
+        <v>64</v>
+      </c>
+      <c r="B145" t="s">
+        <v>141</v>
+      </c>
+      <c r="C145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D145" t="s">
+        <v>146</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>818.4</v>
+      </c>
+      <c r="G145">
+        <v>12</v>
+      </c>
+      <c r="H145">
+        <v>12</v>
+      </c>
+      <c r="I145">
+        <v>9820.799999999999</v>
+      </c>
+      <c r="J145">
+        <v>818.4</v>
+      </c>
+      <c r="L145">
+        <v>777.48</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>0</v>
+      </c>
+      <c r="R145">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -3428,7 +3428,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>378.4</v>
+        <v>375.65</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3440,13 +3440,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>448.7</v>
+        <v>410.2</v>
       </c>
       <c r="Q46">
-        <v>933.59</v>
+        <v>895.09</v>
       </c>
       <c r="R46">
-        <v>9.630000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -5745,7 +5745,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1300.7</v>
+        <v>1281.7</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5757,13 +5757,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>111.3</v>
+        <v>-21.7</v>
       </c>
       <c r="Q87">
-        <v>111.3</v>
+        <v>-21.7</v>
       </c>
       <c r="R87">
-        <v>1.24</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5963,7 +5963,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>295</v>
+        <v>295.5</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5975,13 +5975,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>11.55</v>
+        <v>28.05</v>
       </c>
       <c r="Q91">
-        <v>11.55</v>
+        <v>28.05</v>
       </c>
       <c r="R91">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6744,7 +6744,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1795.4</v>
+        <v>1793.6</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6756,13 +6756,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>214.5</v>
+        <v>205.5</v>
       </c>
       <c r="Q105">
-        <v>214.5</v>
+        <v>205.5</v>
       </c>
       <c r="R105">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -7466,7 +7466,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1143</v>
+        <v>1131.4</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7478,13 +7478,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-8.800000000000001</v>
+        <v>-101.6</v>
       </c>
       <c r="Q118">
-        <v>-8.800000000000001</v>
+        <v>-101.6</v>
       </c>
       <c r="R118">
-        <v>-0.1</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7908,7 +7908,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>153.65</v>
+        <v>153.92</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7920,13 +7920,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>304.18</v>
+        <v>322.27</v>
       </c>
       <c r="Q126">
-        <v>304.18</v>
+        <v>322.27</v>
       </c>
       <c r="R126">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -8014,7 +8014,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>270.2</v>
+        <v>281.95</v>
       </c>
       <c r="L128">
         <v>250.9</v>
@@ -8026,13 +8026,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>225.7</v>
+        <v>660.45</v>
       </c>
       <c r="Q128">
-        <v>225.7</v>
+        <v>660.45</v>
       </c>
       <c r="R128">
-        <v>2.31</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -8400,7 +8400,7 @@
         <v>9237</v>
       </c>
       <c r="J135">
-        <v>3101.3</v>
+        <v>3048.9</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8412,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>66.90000000000001</v>
+        <v>-90.3</v>
       </c>
       <c r="Q135">
-        <v>66.90000000000001</v>
+        <v>-90.3</v>
       </c>
       <c r="R135">
-        <v>0.72</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8450,7 +8450,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>443.7</v>
+        <v>445.05</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8462,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-231</v>
+        <v>-201.3</v>
       </c>
       <c r="Q136">
-        <v>-231</v>
+        <v>-201.3</v>
       </c>
       <c r="R136">
-        <v>-2.31</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -8500,7 +8500,7 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>3910.8</v>
+        <v>3903.2</v>
       </c>
       <c r="L137">
         <v>3472.82</v>
@@ -8512,13 +8512,13 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>510.4</v>
+        <v>495.2</v>
       </c>
       <c r="Q137">
-        <v>510.4</v>
+        <v>495.2</v>
       </c>
       <c r="R137">
-        <v>6.98</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -8550,7 +8550,7 @@
         <v>9235.049999999999</v>
       </c>
       <c r="J138">
-        <v>853.8</v>
+        <v>832.5</v>
       </c>
       <c r="L138">
         <v>797.5700000000001</v>
@@ -8562,13 +8562,13 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>156.75</v>
+        <v>-77.55</v>
       </c>
       <c r="Q138">
-        <v>156.75</v>
+        <v>-77.55</v>
       </c>
       <c r="R138">
-        <v>1.7</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="139" spans="1:18">
@@ -8600,7 +8600,7 @@
         <v>9831</v>
       </c>
       <c r="J139">
-        <v>327.7</v>
+        <v>318.45</v>
       </c>
       <c r="L139">
         <v>311.31</v>
@@ -8612,13 +8612,13 @@
         <v>0</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>-277.5</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>-277.5</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="140" spans="1:18">
@@ -8650,7 +8650,7 @@
         <v>9947.450000000001</v>
       </c>
       <c r="J140">
-        <v>268.85</v>
+        <v>264.05</v>
       </c>
       <c r="L140">
         <v>255.41</v>
@@ -8662,13 +8662,13 @@
         <v>0</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>-177.6</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>-177.6</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="141" spans="1:18">
@@ -8700,7 +8700,7 @@
         <v>9356.4</v>
       </c>
       <c r="J141">
-        <v>1039.6</v>
+        <v>1008.7</v>
       </c>
       <c r="L141">
         <v>987.62</v>
@@ -8712,13 +8712,13 @@
         <v>0</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>-278.1</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>-278.1</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="142" spans="1:18">
@@ -8750,7 +8750,7 @@
         <v>8539.200000000001</v>
       </c>
       <c r="J142">
-        <v>2134.8</v>
+        <v>2074.4</v>
       </c>
       <c r="L142">
         <v>2028.06</v>
@@ -8762,13 +8762,13 @@
         <v>0</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>-241.6</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>-241.6</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="143" spans="1:18">
@@ -8800,7 +8800,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6212.5</v>
+        <v>6105</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8812,13 +8812,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>-107.5</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>-107.5</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="144" spans="1:18">
@@ -8850,7 +8850,7 @@
         <v>9433</v>
       </c>
       <c r="J144">
-        <v>1886.6</v>
+        <v>1823</v>
       </c>
       <c r="L144">
         <v>1792.27</v>
@@ -8862,13 +8862,13 @@
         <v>0</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>-318</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>-318</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -8900,7 +8900,7 @@
         <v>9820.799999999999</v>
       </c>
       <c r="J145">
-        <v>818.4</v>
+        <v>792.55</v>
       </c>
       <c r="L145">
         <v>777.48</v>
@@ -8912,13 +8912,13 @@
         <v>0</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>-310.2</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>-310.2</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>-3.16</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="159">
   <si>
     <t>Buy Date</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -964,7 +967,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1020,7 +1023,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1079,7 +1082,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1135,7 +1138,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1191,7 +1194,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1247,7 +1250,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1303,7 +1306,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1359,7 +1362,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1415,7 +1418,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1471,7 +1474,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1530,7 +1533,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1589,7 +1592,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1645,7 +1648,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1701,7 +1704,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1757,7 +1760,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1813,7 +1816,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1869,7 +1872,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1925,7 +1928,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1981,7 +1984,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2037,7 +2040,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2093,7 +2096,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2149,7 +2152,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2205,7 +2208,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2261,7 +2264,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2317,7 +2320,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2373,7 +2376,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2429,7 +2432,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2485,7 +2488,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2541,7 +2544,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2597,7 +2600,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2653,7 +2656,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2709,7 +2712,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2765,7 +2768,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2821,7 +2824,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2877,7 +2880,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2933,7 +2936,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2989,7 +2992,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3048,7 +3051,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3104,7 +3107,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3160,7 +3163,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3216,7 +3219,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3272,7 +3275,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3328,7 +3331,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3384,7 +3387,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3428,7 +3431,7 @@
         <v>9697.799999999999</v>
       </c>
       <c r="J46">
-        <v>375.65</v>
+        <v>370.65</v>
       </c>
       <c r="L46">
         <v>363.67</v>
@@ -3440,13 +3443,13 @@
         <v>484.8900000000007</v>
       </c>
       <c r="P46">
-        <v>410.2</v>
+        <v>340.2</v>
       </c>
       <c r="Q46">
-        <v>895.09</v>
+        <v>825.09</v>
       </c>
       <c r="R46">
-        <v>9.23</v>
+        <v>8.51</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3493,7 +3496,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3549,7 +3552,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3605,7 +3608,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3664,7 +3667,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3720,7 +3723,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3776,7 +3779,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3835,7 +3838,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3891,7 +3894,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3950,7 +3953,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4009,7 +4012,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4065,7 +4068,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4121,7 +4124,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4177,7 +4180,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4236,7 +4239,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4292,7 +4295,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4351,7 +4354,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4366,7 +4369,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4410,7 +4413,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4466,7 +4469,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4522,7 +4525,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4578,7 +4581,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4634,7 +4637,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4690,7 +4693,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4746,7 +4749,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4802,7 +4805,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4858,7 +4861,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4914,7 +4917,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4970,7 +4973,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5026,7 +5029,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5082,7 +5085,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5138,7 +5141,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5194,7 +5197,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5250,7 +5253,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5306,7 +5309,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5362,7 +5365,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5418,7 +5421,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5474,7 +5477,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5533,7 +5536,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5589,7 +5592,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5645,7 +5648,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5701,7 +5704,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5745,7 +5748,7 @@
         <v>8993.6</v>
       </c>
       <c r="J87">
-        <v>1281.7</v>
+        <v>1254.9</v>
       </c>
       <c r="L87">
         <v>1220.56</v>
@@ -5757,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>-21.7</v>
+        <v>-209.3</v>
       </c>
       <c r="Q87">
-        <v>-21.7</v>
+        <v>-209.3</v>
       </c>
       <c r="R87">
-        <v>-0.24</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5807,7 +5810,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5863,7 +5866,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5919,7 +5922,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5963,7 +5966,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>295.5</v>
+        <v>296.1</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5975,13 +5978,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>28.05</v>
+        <v>47.85</v>
       </c>
       <c r="Q91">
-        <v>28.05</v>
+        <v>47.85</v>
       </c>
       <c r="R91">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6025,7 +6028,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6081,7 +6084,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6137,7 +6140,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6193,7 +6196,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6249,7 +6252,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6305,7 +6308,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6361,7 +6364,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6420,7 +6423,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6476,7 +6479,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6532,7 +6535,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6588,7 +6591,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6644,7 +6647,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6700,7 +6703,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6744,7 +6747,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1793.6</v>
+        <v>1757.2</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6756,13 +6759,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>205.5</v>
+        <v>23.5</v>
       </c>
       <c r="Q105">
-        <v>205.5</v>
+        <v>23.5</v>
       </c>
       <c r="R105">
-        <v>2.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6806,7 +6809,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6862,7 +6865,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6918,7 +6921,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6974,7 +6977,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7030,7 +7033,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7086,7 +7089,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7142,7 +7145,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7198,7 +7201,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7254,7 +7257,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7310,7 +7313,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7366,7 +7369,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7422,7 +7425,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7466,7 +7469,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1131.4</v>
+        <v>1113.1</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7478,13 +7481,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-101.6</v>
+        <v>-248</v>
       </c>
       <c r="Q118">
-        <v>-101.6</v>
+        <v>-248</v>
       </c>
       <c r="R118">
-        <v>-1.11</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -7528,7 +7531,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7584,7 +7587,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7640,7 +7643,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7696,7 +7699,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7752,7 +7755,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7808,7 +7811,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7864,7 +7867,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7908,7 +7911,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>153.92</v>
+        <v>150.43</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7920,13 +7923,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>322.27</v>
+        <v>88.44</v>
       </c>
       <c r="Q126">
-        <v>322.27</v>
+        <v>88.44</v>
       </c>
       <c r="R126">
-        <v>3.23</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -7970,7 +7973,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7999,7 +8002,7 @@
         <v>146</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128">
         <v>264.1</v>
@@ -8014,10 +8017,10 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>281.95</v>
+        <v>284.65</v>
       </c>
       <c r="L128">
-        <v>250.9</v>
+        <v>264.1</v>
       </c>
       <c r="M128">
         <v>0</v>
@@ -8026,13 +8029,13 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>660.45</v>
+        <v>760.35</v>
       </c>
       <c r="Q128">
-        <v>660.45</v>
+        <v>760.35</v>
       </c>
       <c r="R128">
-        <v>6.76</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -8076,7 +8079,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8132,7 +8135,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8188,7 +8191,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8244,7 +8247,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8300,7 +8303,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8356,7 +8359,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8382,7 +8385,7 @@
         <v>142</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8394,7 +8397,7 @@
         <v>3</v>
       </c>
       <c r="H135">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I135">
         <v>9237</v>
@@ -8402,23 +8405,29 @@
       <c r="J135">
         <v>3048.9</v>
       </c>
+      <c r="K135" t="s">
+        <v>155</v>
+      </c>
       <c r="L135">
         <v>2925.05</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>2925.05</v>
+      </c>
+      <c r="N135" t="s">
+        <v>156</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>-461.8499999999995</v>
       </c>
       <c r="P135">
-        <v>-90.3</v>
+        <v>0</v>
       </c>
       <c r="Q135">
-        <v>-90.3</v>
+        <v>-461.8499999999995</v>
       </c>
       <c r="R135">
-        <v>-0.98</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -8450,7 +8459,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>445.05</v>
+        <v>450.45</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8462,13 +8471,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-201.3</v>
+        <v>-82.5</v>
       </c>
       <c r="Q136">
-        <v>-201.3</v>
+        <v>-82.5</v>
       </c>
       <c r="R136">
-        <v>-2.01</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -8485,7 +8494,7 @@
         <v>146</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137">
         <v>3655.6</v>
@@ -8500,10 +8509,10 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>3903.2</v>
+        <v>3956.8</v>
       </c>
       <c r="L137">
-        <v>3472.82</v>
+        <v>3655.6</v>
       </c>
       <c r="M137">
         <v>0</v>
@@ -8512,13 +8521,13 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>495.2</v>
+        <v>602.4</v>
       </c>
       <c r="Q137">
-        <v>495.2</v>
+        <v>602.4</v>
       </c>
       <c r="R137">
-        <v>6.77</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -8550,7 +8559,7 @@
         <v>9235.049999999999</v>
       </c>
       <c r="J138">
-        <v>832.5</v>
+        <v>806.9</v>
       </c>
       <c r="L138">
         <v>797.5700000000001</v>
@@ -8562,13 +8571,13 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>-77.55</v>
+        <v>-359.15</v>
       </c>
       <c r="Q138">
-        <v>-77.55</v>
+        <v>-359.15</v>
       </c>
       <c r="R138">
-        <v>-0.84</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="139" spans="1:18">
@@ -8582,7 +8591,7 @@
         <v>142</v>
       </c>
       <c r="D139" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8594,7 +8603,7 @@
         <v>30</v>
       </c>
       <c r="H139">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>9831</v>
@@ -8602,23 +8611,29 @@
       <c r="J139">
         <v>318.45</v>
       </c>
+      <c r="K139" t="s">
+        <v>155</v>
+      </c>
       <c r="L139">
         <v>311.31</v>
       </c>
       <c r="M139">
-        <v>0</v>
+        <v>311.31</v>
+      </c>
+      <c r="N139" t="s">
+        <v>156</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>-491.6999999999996</v>
       </c>
       <c r="P139">
-        <v>-277.5</v>
+        <v>0</v>
       </c>
       <c r="Q139">
-        <v>-277.5</v>
+        <v>-491.6999999999996</v>
       </c>
       <c r="R139">
-        <v>-2.82</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="140" spans="1:18">
@@ -8632,7 +8647,7 @@
         <v>142</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8644,7 +8659,7 @@
         <v>37</v>
       </c>
       <c r="H140">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I140">
         <v>9947.450000000001</v>
@@ -8652,23 +8667,29 @@
       <c r="J140">
         <v>264.05</v>
       </c>
+      <c r="K140" t="s">
+        <v>155</v>
+      </c>
       <c r="L140">
         <v>255.41</v>
       </c>
       <c r="M140">
-        <v>0</v>
+        <v>255.41</v>
+      </c>
+      <c r="N140" t="s">
+        <v>156</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>-497.280000000001</v>
       </c>
       <c r="P140">
-        <v>-177.6</v>
+        <v>0</v>
       </c>
       <c r="Q140">
-        <v>-177.6</v>
+        <v>-497.280000000001</v>
       </c>
       <c r="R140">
-        <v>-1.79</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:18">
@@ -8682,7 +8703,7 @@
         <v>142</v>
       </c>
       <c r="D141" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8694,7 +8715,7 @@
         <v>9</v>
       </c>
       <c r="H141">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>9356.4</v>
@@ -8702,23 +8723,29 @@
       <c r="J141">
         <v>1008.7</v>
       </c>
+      <c r="K141" t="s">
+        <v>155</v>
+      </c>
       <c r="L141">
         <v>987.62</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>987.62</v>
+      </c>
+      <c r="N141" t="s">
+        <v>156</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>-467.8199999999991</v>
       </c>
       <c r="P141">
-        <v>-278.1</v>
+        <v>0</v>
       </c>
       <c r="Q141">
-        <v>-278.1</v>
+        <v>-467.8199999999991</v>
       </c>
       <c r="R141">
-        <v>-2.97</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="142" spans="1:18">
@@ -8750,7 +8777,7 @@
         <v>8539.200000000001</v>
       </c>
       <c r="J142">
-        <v>2074.4</v>
+        <v>2055.2</v>
       </c>
       <c r="L142">
         <v>2028.06</v>
@@ -8762,13 +8789,13 @@
         <v>0</v>
       </c>
       <c r="P142">
-        <v>-241.6</v>
+        <v>-318.4</v>
       </c>
       <c r="Q142">
-        <v>-241.6</v>
+        <v>-318.4</v>
       </c>
       <c r="R142">
-        <v>-2.83</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="143" spans="1:18">
@@ -8800,7 +8827,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6105</v>
+        <v>5941.5</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8812,13 +8839,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>-107.5</v>
+        <v>-271</v>
       </c>
       <c r="Q143">
-        <v>-107.5</v>
+        <v>-271</v>
       </c>
       <c r="R143">
-        <v>-1.73</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="144" spans="1:18">
@@ -8832,7 +8859,7 @@
         <v>142</v>
       </c>
       <c r="D144" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8844,7 +8871,7 @@
         <v>5</v>
       </c>
       <c r="H144">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>9433</v>
@@ -8852,23 +8879,29 @@
       <c r="J144">
         <v>1823</v>
       </c>
+      <c r="K144" t="s">
+        <v>155</v>
+      </c>
       <c r="L144">
         <v>1792.27</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>1792.27</v>
+      </c>
+      <c r="N144" t="s">
+        <v>156</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>-471.6499999999996</v>
       </c>
       <c r="P144">
-        <v>-318</v>
+        <v>0</v>
       </c>
       <c r="Q144">
-        <v>-318</v>
+        <v>-471.6499999999996</v>
       </c>
       <c r="R144">
-        <v>-3.37</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -8882,7 +8915,7 @@
         <v>142</v>
       </c>
       <c r="D145" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8894,7 +8927,7 @@
         <v>12</v>
       </c>
       <c r="H145">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I145">
         <v>9820.799999999999</v>
@@ -8902,23 +8935,29 @@
       <c r="J145">
         <v>792.55</v>
       </c>
+      <c r="K145" t="s">
+        <v>155</v>
+      </c>
       <c r="L145">
         <v>777.48</v>
       </c>
       <c r="M145">
-        <v>0</v>
+        <v>777.48</v>
+      </c>
+      <c r="N145" t="s">
+        <v>156</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>-491.0399999999995</v>
       </c>
       <c r="P145">
-        <v>-310.2</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>-310.2</v>
+        <v>-491.0399999999995</v>
       </c>
       <c r="R145">
-        <v>-3.16</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="159">
   <si>
     <t>Buy Date</t>
   </si>
@@ -211,6 +211,9 @@
     <t>2026-03-25</t>
   </si>
   <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -479,9 +482,6 @@
   </si>
   <si>
     <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -854,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S145"/>
+  <dimension ref="A1:S146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -931,13 +931,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -987,13 +987,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1158,13 +1158,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1214,13 +1214,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1382,13 +1382,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1465,7 +1465,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1489,7 +1489,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1497,13 +1497,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1556,13 +1556,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1724,13 +1724,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1836,13 +1836,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1892,13 +1892,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1948,13 +1948,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2004,13 +2004,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2031,7 +2031,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2060,13 +2060,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2087,7 +2087,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2116,13 +2116,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2284,13 +2284,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2340,13 +2340,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2508,13 +2508,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2564,13 +2564,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2620,13 +2620,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2676,13 +2676,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2732,13 +2732,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2788,13 +2788,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2844,13 +2844,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3015,13 +3015,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3071,13 +3071,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3183,13 +3183,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3239,13 +3239,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3295,13 +3295,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3351,13 +3351,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3407,13 +3407,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3460,13 +3460,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3516,13 +3516,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3572,13 +3572,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3631,13 +3631,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3687,13 +3687,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3743,13 +3743,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3802,13 +3802,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3858,13 +3858,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3917,13 +3917,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3976,13 +3976,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4088,13 +4088,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4144,13 +4144,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4203,13 +4203,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4259,13 +4259,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4318,13 +4318,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4377,13 +4377,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4433,13 +4433,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4489,13 +4489,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C65" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4545,13 +4545,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4601,13 +4601,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4657,13 +4657,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4713,13 +4713,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4769,13 +4769,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4825,13 +4825,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4881,13 +4881,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4937,13 +4937,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4993,13 +4993,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5049,13 +5049,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C75" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5105,13 +5105,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5161,13 +5161,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C77" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5217,13 +5217,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D78" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5273,13 +5273,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5329,13 +5329,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5385,13 +5385,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C81" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5441,13 +5441,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5500,13 +5500,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5556,13 +5556,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5612,13 +5612,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5668,13 +5668,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5774,13 +5774,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5830,13 +5830,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5886,13 +5886,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5942,13 +5942,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C91" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5992,13 +5992,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6048,13 +6048,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C93" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6104,13 +6104,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6160,13 +6160,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6272,13 +6272,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6328,13 +6328,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6387,13 +6387,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6443,13 +6443,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6499,13 +6499,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C101" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6555,13 +6555,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6611,13 +6611,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C103" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6667,13 +6667,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C104" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6723,13 +6723,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C105" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D105" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6773,13 +6773,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6829,13 +6829,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6885,13 +6885,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C108" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6941,13 +6941,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C109" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6968,7 +6968,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6997,13 +6997,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C110" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7053,13 +7053,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7109,13 +7109,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C112" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7165,13 +7165,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C113" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7221,13 +7221,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7277,13 +7277,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7389,13 +7389,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C117" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7445,13 +7445,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C118" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7495,13 +7495,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7551,13 +7551,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C121" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7663,13 +7663,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7746,7 +7746,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7775,13 +7775,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C124" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7831,13 +7831,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7887,13 +7887,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C126" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7937,13 +7937,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7993,13 +7993,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -8043,13 +8043,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8099,13 +8099,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C130" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8155,13 +8155,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8211,13 +8211,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8267,13 +8267,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8294,7 +8294,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8323,13 +8323,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8379,13 +8379,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C135" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8406,7 +8406,7 @@
         <v>3048.9</v>
       </c>
       <c r="K135" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L135">
         <v>2925.05</v>
@@ -8435,13 +8435,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8485,13 +8485,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C137" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -8535,13 +8535,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C138" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -8585,13 +8585,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8612,7 +8612,7 @@
         <v>318.45</v>
       </c>
       <c r="K139" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L139">
         <v>311.31</v>
@@ -8641,13 +8641,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C140" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D140" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8668,7 +8668,7 @@
         <v>264.05</v>
       </c>
       <c r="K140" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L140">
         <v>255.41</v>
@@ -8697,13 +8697,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8724,7 +8724,7 @@
         <v>1008.7</v>
       </c>
       <c r="K141" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L141">
         <v>987.62</v>
@@ -8736,13 +8736,13 @@
         <v>156</v>
       </c>
       <c r="O141">
-        <v>-467.8199999999991</v>
+        <v>-467.8199999999992</v>
       </c>
       <c r="P141">
         <v>0</v>
       </c>
       <c r="Q141">
-        <v>-467.8199999999991</v>
+        <v>-467.8199999999992</v>
       </c>
       <c r="R141">
         <v>-5</v>
@@ -8753,13 +8753,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C142" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D142" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8803,13 +8803,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D143" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8853,13 +8853,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C144" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8880,7 +8880,7 @@
         <v>1823</v>
       </c>
       <c r="K144" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L144">
         <v>1792.27</v>
@@ -8892,13 +8892,13 @@
         <v>156</v>
       </c>
       <c r="O144">
-        <v>-471.6499999999996</v>
+        <v>-471.6499999999997</v>
       </c>
       <c r="P144">
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>-471.6499999999996</v>
+        <v>-471.6499999999997</v>
       </c>
       <c r="R144">
         <v>-5</v>
@@ -8909,13 +8909,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C145" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8936,7 +8936,7 @@
         <v>792.55</v>
       </c>
       <c r="K145" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="L145">
         <v>777.48</v>
@@ -8958,6 +8958,56 @@
       </c>
       <c r="R145">
         <v>-5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
+      <c r="A146" t="s">
+        <v>65</v>
+      </c>
+      <c r="B146" t="s">
+        <v>73</v>
+      </c>
+      <c r="C146" t="s">
+        <v>143</v>
+      </c>
+      <c r="D146" t="s">
+        <v>147</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>2935</v>
+      </c>
+      <c r="G146">
+        <v>3</v>
+      </c>
+      <c r="H146">
+        <v>3</v>
+      </c>
+      <c r="I146">
+        <v>8805</v>
+      </c>
+      <c r="J146">
+        <v>2935</v>
+      </c>
+      <c r="L146">
+        <v>2788.25</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>0</v>
+      </c>
+      <c r="R146">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="160">
   <si>
     <t>Buy Date</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -854,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S146"/>
+  <dimension ref="A1:S149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -931,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -967,7 +970,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -987,13 +990,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1023,7 +1026,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1046,13 +1049,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1082,7 +1085,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1102,13 +1105,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1138,7 +1141,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1158,13 +1161,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1194,7 +1197,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1214,13 +1217,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1250,7 +1253,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1270,13 +1273,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1306,7 +1309,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1326,13 +1329,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1362,7 +1365,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1382,13 +1385,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1418,7 +1421,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1438,13 +1441,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1465,7 +1468,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1474,7 +1477,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1489,7 +1492,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1497,13 +1500,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1533,7 +1536,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1556,13 +1559,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1592,7 +1595,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1612,13 +1615,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1648,7 +1651,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1668,13 +1671,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1704,7 +1707,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1724,13 +1727,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1760,7 +1763,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1780,13 +1783,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1816,7 +1819,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1836,13 +1839,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1872,7 +1875,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1892,13 +1895,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1928,7 +1931,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1948,13 +1951,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1984,7 +1987,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2004,13 +2007,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2031,7 +2034,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2040,7 +2043,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2060,13 +2063,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2087,7 +2090,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2096,7 +2099,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2116,13 +2119,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2152,7 +2155,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2172,13 +2175,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2208,7 +2211,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2228,13 +2231,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2264,7 +2267,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2284,13 +2287,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2311,7 +2314,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2320,7 +2323,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2340,13 +2343,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2376,7 +2379,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2396,13 +2399,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2432,7 +2435,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2452,13 +2455,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2488,7 +2491,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2508,13 +2511,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2544,7 +2547,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2564,13 +2567,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2591,7 +2594,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2600,7 +2603,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2620,13 +2623,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2656,7 +2659,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2676,13 +2679,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2712,7 +2715,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2732,13 +2735,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2759,7 +2762,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2768,7 +2771,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2788,13 +2791,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2815,7 +2818,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2824,7 +2827,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2844,13 +2847,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2880,7 +2883,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2900,13 +2903,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2936,7 +2939,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2956,13 +2959,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2992,7 +2995,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3015,13 +3018,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3051,7 +3054,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3071,13 +3074,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3107,7 +3110,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3127,13 +3130,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3163,7 +3166,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3183,13 +3186,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3210,7 +3213,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3219,7 +3222,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3239,13 +3242,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3266,7 +3269,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3275,7 +3278,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3295,13 +3298,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3331,7 +3334,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3351,13 +3354,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3387,7 +3390,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3407,10 +3410,10 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
         <v>147</v>
@@ -3425,7 +3428,7 @@
         <v>28</v>
       </c>
       <c r="H46">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I46">
         <v>9697.799999999999</v>
@@ -3433,23 +3436,29 @@
       <c r="J46">
         <v>370.65</v>
       </c>
+      <c r="K46" t="s">
+        <v>66</v>
+      </c>
       <c r="L46">
         <v>363.67</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>363.67</v>
+      </c>
+      <c r="N46" t="s">
+        <v>157</v>
       </c>
       <c r="O46">
-        <v>484.8900000000007</v>
+        <v>727.3700000000006</v>
       </c>
       <c r="P46">
-        <v>340.2</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>825.09</v>
+        <v>727.3700000000006</v>
       </c>
       <c r="R46">
-        <v>8.51</v>
+        <v>7.5</v>
       </c>
       <c r="S46" t="s">
         <v>49</v>
@@ -3460,13 +3469,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3496,7 +3505,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3516,13 +3525,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3552,7 +3561,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3572,13 +3581,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3608,7 +3617,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3631,13 +3640,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3667,7 +3676,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3687,13 +3696,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3723,7 +3732,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3743,13 +3752,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3779,7 +3788,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3802,13 +3811,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3838,7 +3847,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3858,13 +3867,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3894,7 +3903,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3917,13 +3926,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3953,7 +3962,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3976,13 +3985,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4012,7 +4021,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4032,13 +4041,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4059,7 +4068,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4068,7 +4077,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4088,13 +4097,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4124,7 +4133,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4144,13 +4153,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4180,7 +4189,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4203,13 +4212,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4239,7 +4248,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4259,13 +4268,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C61" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4295,7 +4304,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4318,13 +4327,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4354,7 +4363,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4369,7 +4378,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4377,13 +4386,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4413,7 +4422,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4433,13 +4442,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4469,7 +4478,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4489,13 +4498,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4525,7 +4534,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4545,13 +4554,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4581,7 +4590,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4601,13 +4610,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4637,7 +4646,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4657,13 +4666,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4693,7 +4702,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4713,13 +4722,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4740,7 +4749,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4749,7 +4758,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4769,13 +4778,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4805,7 +4814,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4825,13 +4834,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4861,7 +4870,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4881,13 +4890,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4917,7 +4926,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4937,13 +4946,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4973,7 +4982,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -4993,13 +5002,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5029,7 +5038,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5049,13 +5058,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5085,7 +5094,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5105,13 +5114,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C76" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5141,7 +5150,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5161,13 +5170,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5197,7 +5206,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5217,13 +5226,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5253,7 +5262,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5273,13 +5282,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5309,7 +5318,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5329,13 +5338,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5365,7 +5374,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5385,13 +5394,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5421,7 +5430,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5441,13 +5450,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5477,7 +5486,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5500,13 +5509,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C83" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5536,7 +5545,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5556,13 +5565,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5592,7 +5601,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5612,13 +5621,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5648,7 +5657,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5668,13 +5677,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5704,7 +5713,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5724,10 +5733,10 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D87" t="s">
         <v>147</v>
@@ -5742,7 +5751,7 @@
         <v>7</v>
       </c>
       <c r="H87">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I87">
         <v>8993.6</v>
@@ -5750,23 +5759,29 @@
       <c r="J87">
         <v>1254.9</v>
       </c>
+      <c r="K87" t="s">
+        <v>66</v>
+      </c>
       <c r="L87">
         <v>1220.56</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>1220.56</v>
+      </c>
+      <c r="N87" t="s">
+        <v>157</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>-449.6800000000001</v>
       </c>
       <c r="P87">
-        <v>-209.3</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>-209.3</v>
+        <v>-449.6800000000001</v>
       </c>
       <c r="R87">
-        <v>-2.33</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5774,13 +5789,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5810,7 +5825,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5830,13 +5845,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5866,7 +5881,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5886,13 +5901,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5922,7 +5937,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5942,13 +5957,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C91" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5966,7 +5981,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>296.1</v>
+        <v>292.8</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5978,13 +5993,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>47.85</v>
+        <v>-61.05</v>
       </c>
       <c r="Q91">
-        <v>47.85</v>
+        <v>-61.05</v>
       </c>
       <c r="R91">
-        <v>0.49</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -5992,13 +6007,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C92" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6028,7 +6043,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6048,13 +6063,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D93" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6084,7 +6099,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6104,13 +6119,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6140,7 +6155,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6160,13 +6175,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6196,7 +6211,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6216,13 +6231,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6252,7 +6267,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6272,13 +6287,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D97" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6308,7 +6323,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6328,13 +6343,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D98" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6364,7 +6379,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6387,13 +6402,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C99" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6423,7 +6438,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6443,13 +6458,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6479,7 +6494,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6499,13 +6514,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C101" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6535,7 +6550,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6555,13 +6570,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C102" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6591,7 +6606,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6611,13 +6626,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C103" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6647,7 +6662,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6667,13 +6682,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C104" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D104" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6703,7 +6718,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6723,13 +6738,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6747,7 +6762,7 @@
         <v>8762.5</v>
       </c>
       <c r="J105">
-        <v>1757.2</v>
+        <v>1728.5</v>
       </c>
       <c r="L105">
         <v>1664.88</v>
@@ -6759,13 +6774,13 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>23.5</v>
+        <v>-120</v>
       </c>
       <c r="Q105">
-        <v>23.5</v>
+        <v>-120</v>
       </c>
       <c r="R105">
-        <v>0.27</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6773,13 +6788,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C106" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6800,7 +6815,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6809,7 +6824,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6829,13 +6844,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6865,7 +6880,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6885,13 +6900,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6921,7 +6936,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6941,13 +6956,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6968,7 +6983,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6977,7 +6992,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -6997,13 +7012,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D110" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7033,7 +7048,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7053,13 +7068,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7089,7 +7104,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7109,13 +7124,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C112" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7145,7 +7160,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7160,18 +7175,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:19">
       <c r="A113" t="s">
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C113" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7201,7 +7216,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7216,18 +7231,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:19">
       <c r="A114" t="s">
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7257,7 +7272,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7272,18 +7287,18 @@
         <v>-7.3</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:19">
       <c r="A115" t="s">
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C115" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7313,7 +7328,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7328,18 +7343,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:19">
       <c r="A116" t="s">
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D116" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7369,7 +7384,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7384,18 +7399,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="117" spans="1:18">
+    <row r="117" spans="1:19">
       <c r="A117" t="s">
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7425,7 +7440,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7440,18 +7455,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:19">
       <c r="A118" t="s">
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C118" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D118" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7469,7 +7484,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1113.1</v>
+        <v>1137.4</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7481,27 +7496,27 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-248</v>
+        <v>-53.6</v>
       </c>
       <c r="Q118">
-        <v>-248</v>
+        <v>-53.6</v>
       </c>
       <c r="R118">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
       <c r="A119" t="s">
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7531,7 +7546,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7546,18 +7561,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:19">
       <c r="A120" t="s">
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C120" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D120" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7587,7 +7602,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7602,18 +7617,18 @@
         <v>-5.44</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:19">
       <c r="A121" t="s">
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C121" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D121" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7643,7 +7658,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7658,18 +7673,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:19">
       <c r="A122" t="s">
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7699,7 +7714,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7714,18 +7729,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="123" spans="1:18">
+    <row r="123" spans="1:19">
       <c r="A123" t="s">
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C123" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D123" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7746,7 +7761,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7755,7 +7770,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7770,18 +7785,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:19">
       <c r="A124" t="s">
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D124" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7811,7 +7826,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7826,18 +7841,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="125" spans="1:18">
+    <row r="125" spans="1:19">
       <c r="A125" t="s">
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7867,7 +7882,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7882,18 +7897,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:19">
       <c r="A126" t="s">
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D126" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7911,7 +7926,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>150.43</v>
+        <v>157.11</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7923,27 +7938,27 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>88.44</v>
+        <v>536</v>
       </c>
       <c r="Q126">
-        <v>88.44</v>
+        <v>536</v>
       </c>
       <c r="R126">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
       <c r="A127" t="s">
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C127" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D127" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7973,7 +7988,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -7988,21 +8003,21 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:19">
       <c r="A128" t="s">
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C128" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D128" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128">
         <v>264.1</v>
@@ -8011,45 +8026,48 @@
         <v>37</v>
       </c>
       <c r="H128">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I128">
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>284.65</v>
+        <v>288.05</v>
       </c>
       <c r="L128">
-        <v>264.1</v>
+        <v>277.31</v>
       </c>
       <c r="M128">
         <v>0</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>475.3800000000005</v>
       </c>
       <c r="P128">
-        <v>760.35</v>
+        <v>455.05</v>
       </c>
       <c r="Q128">
-        <v>760.35</v>
+        <v>930.4299999999999</v>
       </c>
       <c r="R128">
-        <v>7.78</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18">
+        <v>9.52</v>
+      </c>
+      <c r="S128" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
       <c r="A129" t="s">
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8079,7 +8097,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8094,18 +8112,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:19">
       <c r="A130" t="s">
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C130" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8135,7 +8153,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8150,18 +8168,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
+    <row r="131" spans="1:19">
       <c r="A131" t="s">
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C131" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8191,7 +8209,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8206,18 +8224,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
+    <row r="132" spans="1:19">
       <c r="A132" t="s">
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8247,7 +8265,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8262,18 +8280,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
+    <row r="133" spans="1:19">
       <c r="A133" t="s">
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8294,7 +8312,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8303,7 +8321,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8318,18 +8336,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
+    <row r="134" spans="1:19">
       <c r="A134" t="s">
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8359,7 +8377,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8374,18 +8392,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
+    <row r="135" spans="1:19">
       <c r="A135" t="s">
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C135" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8415,7 +8433,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8430,18 +8448,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
+    <row r="136" spans="1:19">
       <c r="A136" t="s">
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D136" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8459,7 +8477,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>450.45</v>
+        <v>449.4</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8471,30 +8489,30 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-82.5</v>
+        <v>-105.6</v>
       </c>
       <c r="Q136">
-        <v>-82.5</v>
+        <v>-105.6</v>
       </c>
       <c r="R136">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19">
       <c r="A137" t="s">
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C137" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D137" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137">
         <v>3655.6</v>
@@ -8503,45 +8521,48 @@
         <v>2</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137">
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>3956.8</v>
+        <v>4271.1</v>
       </c>
       <c r="L137">
-        <v>3655.6</v>
+        <v>3838.38</v>
       </c>
       <c r="M137">
         <v>0</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>365.5600000000004</v>
       </c>
       <c r="P137">
-        <v>602.4</v>
+        <v>615.5</v>
       </c>
       <c r="Q137">
-        <v>602.4</v>
+        <v>981.0599999999999</v>
       </c>
       <c r="R137">
-        <v>8.24</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18">
+        <v>13.42</v>
+      </c>
+      <c r="S137" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19">
       <c r="A138" t="s">
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C138" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D138" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -8559,7 +8580,7 @@
         <v>9235.049999999999</v>
       </c>
       <c r="J138">
-        <v>806.9</v>
+        <v>851.95</v>
       </c>
       <c r="L138">
         <v>797.5700000000001</v>
@@ -8571,27 +8592,27 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>-359.15</v>
+        <v>136.4</v>
       </c>
       <c r="Q138">
-        <v>-359.15</v>
+        <v>136.4</v>
       </c>
       <c r="R138">
-        <v>-3.89</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19">
       <c r="A139" t="s">
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C139" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D139" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8621,7 +8642,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8636,18 +8657,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
+    <row r="140" spans="1:19">
       <c r="A140" t="s">
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8677,7 +8698,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8692,18 +8713,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
+    <row r="141" spans="1:19">
       <c r="A141" t="s">
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C141" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8733,7 +8754,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8748,18 +8769,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:19">
       <c r="A142" t="s">
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D142" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8777,7 +8798,7 @@
         <v>8539.200000000001</v>
       </c>
       <c r="J142">
-        <v>2055.2</v>
+        <v>2064.7</v>
       </c>
       <c r="L142">
         <v>2028.06</v>
@@ -8789,27 +8810,27 @@
         <v>0</v>
       </c>
       <c r="P142">
-        <v>-318.4</v>
+        <v>-280.4</v>
       </c>
       <c r="Q142">
-        <v>-318.4</v>
+        <v>-280.4</v>
       </c>
       <c r="R142">
-        <v>-3.73</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19">
       <c r="A143" t="s">
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C143" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D143" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8827,7 +8848,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>5941.5</v>
+        <v>6063</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8839,27 +8860,27 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>-271</v>
+        <v>-149.5</v>
       </c>
       <c r="Q143">
-        <v>-271</v>
+        <v>-149.5</v>
       </c>
       <c r="R143">
-        <v>-4.36</v>
-      </c>
-    </row>
-    <row r="144" spans="1:18">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19">
       <c r="A144" t="s">
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C144" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D144" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8889,7 +8910,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8909,13 +8930,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8945,7 +8966,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -8965,13 +8986,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C146" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D146" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -8989,7 +9010,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>2935</v>
+        <v>3017</v>
       </c>
       <c r="L146">
         <v>2788.25</v>
@@ -9001,12 +9022,162 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="R146">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
+      <c r="A147" t="s">
+        <v>66</v>
+      </c>
+      <c r="B147" t="s">
+        <v>143</v>
+      </c>
+      <c r="C147" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" t="s">
+        <v>148</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>785.65</v>
+      </c>
+      <c r="G147">
+        <v>12</v>
+      </c>
+      <c r="H147">
+        <v>12</v>
+      </c>
+      <c r="I147">
+        <v>9427.799999999999</v>
+      </c>
+      <c r="J147">
+        <v>785.65</v>
+      </c>
+      <c r="L147">
+        <v>746.37</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>0</v>
+      </c>
+      <c r="R147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
+      <c r="A148" t="s">
+        <v>66</v>
+      </c>
+      <c r="B148" t="s">
+        <v>126</v>
+      </c>
+      <c r="C148" t="s">
+        <v>144</v>
+      </c>
+      <c r="D148" t="s">
+        <v>148</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>322.1</v>
+      </c>
+      <c r="G148">
+        <v>31</v>
+      </c>
+      <c r="H148">
+        <v>31</v>
+      </c>
+      <c r="I148">
+        <v>9985.1</v>
+      </c>
+      <c r="J148">
+        <v>322.1</v>
+      </c>
+      <c r="L148">
+        <v>306</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>0</v>
+      </c>
+      <c r="R148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
+      <c r="A149" t="s">
+        <v>66</v>
+      </c>
+      <c r="B149" t="s">
+        <v>67</v>
+      </c>
+      <c r="C149" t="s">
+        <v>144</v>
+      </c>
+      <c r="D149" t="s">
+        <v>148</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>1842.5</v>
+      </c>
+      <c r="G149">
+        <v>5</v>
+      </c>
+      <c r="H149">
+        <v>5</v>
+      </c>
+      <c r="I149">
+        <v>9212.5</v>
+      </c>
+      <c r="J149">
+        <v>1842.5</v>
+      </c>
+      <c r="L149">
+        <v>1750.38</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>0</v>
+      </c>
+      <c r="R149">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="161">
   <si>
     <t>Buy Date</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -857,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S149"/>
+  <dimension ref="A1:S150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -934,13 +937,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -970,7 +973,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -990,13 +993,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1026,7 +1029,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1049,13 +1052,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1085,7 +1088,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1105,13 +1108,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1141,7 +1144,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1161,13 +1164,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1197,7 +1200,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1217,13 +1220,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1253,7 +1256,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1273,13 +1276,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1309,7 +1312,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1329,13 +1332,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1365,7 +1368,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1385,13 +1388,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1421,7 +1424,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1441,13 +1444,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1468,7 +1471,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1477,7 +1480,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1492,7 +1495,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1500,13 +1503,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1536,7 +1539,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1559,13 +1562,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1595,7 +1598,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1615,13 +1618,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1651,7 +1654,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1671,13 +1674,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1707,7 +1710,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1727,13 +1730,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1763,7 +1766,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1783,13 +1786,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1819,7 +1822,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1839,13 +1842,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1875,7 +1878,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1895,13 +1898,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1931,7 +1934,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1951,13 +1954,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1987,7 +1990,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2007,13 +2010,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2034,7 +2037,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2043,7 +2046,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2063,13 +2066,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2090,7 +2093,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2099,7 +2102,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2119,13 +2122,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2155,7 +2158,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2175,13 +2178,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2211,7 +2214,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2231,13 +2234,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2267,7 +2270,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2287,13 +2290,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2314,7 +2317,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2323,7 +2326,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2343,13 +2346,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2379,7 +2382,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2399,13 +2402,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2435,7 +2438,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2455,13 +2458,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2491,7 +2494,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2511,13 +2514,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2547,7 +2550,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2567,13 +2570,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2594,7 +2597,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2603,7 +2606,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2623,13 +2626,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2659,7 +2662,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2679,13 +2682,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2715,7 +2718,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2735,13 +2738,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2762,7 +2765,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2771,7 +2774,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2791,13 +2794,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2818,7 +2821,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2827,7 +2830,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2847,13 +2850,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2883,7 +2886,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2903,13 +2906,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2939,7 +2942,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2959,13 +2962,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2995,7 +2998,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3018,13 +3021,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3054,7 +3057,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3074,13 +3077,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3110,7 +3113,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3130,13 +3133,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3166,7 +3169,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3186,13 +3189,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3213,7 +3216,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3222,7 +3225,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3242,13 +3245,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3269,7 +3272,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3278,7 +3281,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3298,13 +3301,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3334,7 +3337,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3354,13 +3357,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3390,7 +3393,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3410,13 +3413,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3446,7 +3449,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3469,13 +3472,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3505,7 +3508,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3525,13 +3528,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3561,7 +3564,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3581,13 +3584,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3617,7 +3620,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3640,13 +3643,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3676,7 +3679,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3696,13 +3699,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3732,7 +3735,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3752,13 +3755,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3788,7 +3791,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3811,13 +3814,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3847,7 +3850,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3867,13 +3870,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3903,7 +3906,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3926,13 +3929,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3962,7 +3965,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3985,13 +3988,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4021,7 +4024,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4041,13 +4044,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4068,7 +4071,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4077,7 +4080,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4097,13 +4100,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D58" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4133,7 +4136,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4153,13 +4156,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4189,7 +4192,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4212,13 +4215,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C60" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4248,7 +4251,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4268,13 +4271,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4304,7 +4307,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4327,13 +4330,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4363,7 +4366,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4378,7 +4381,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4386,13 +4389,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4422,7 +4425,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4442,13 +4445,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4478,7 +4481,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4498,13 +4501,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4534,7 +4537,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4554,13 +4557,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4590,7 +4593,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4610,13 +4613,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4646,7 +4649,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4666,13 +4669,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4702,7 +4705,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4722,13 +4725,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4749,7 +4752,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4758,7 +4761,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4778,13 +4781,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4814,7 +4817,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4834,13 +4837,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4870,7 +4873,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4890,13 +4893,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C72" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4926,7 +4929,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4946,13 +4949,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4982,7 +4985,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5002,13 +5005,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5038,7 +5041,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5058,13 +5061,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5094,7 +5097,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5114,13 +5117,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5150,7 +5153,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5170,13 +5173,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5206,7 +5209,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5226,13 +5229,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5262,7 +5265,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5282,13 +5285,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5318,7 +5321,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5338,13 +5341,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C80" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5374,7 +5377,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5394,13 +5397,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C81" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D81" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5430,7 +5433,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5450,13 +5453,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5486,7 +5489,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5509,13 +5512,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C83" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D83" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5545,7 +5548,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5565,13 +5568,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5601,7 +5604,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5621,13 +5624,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C85" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5657,7 +5660,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5677,13 +5680,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D86" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5713,7 +5716,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5733,13 +5736,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5769,7 +5772,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5789,13 +5792,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5825,7 +5828,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5845,13 +5848,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5881,7 +5884,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5901,13 +5904,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5937,7 +5940,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5957,13 +5960,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D91" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5981,7 +5984,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>292.8</v>
+        <v>289.95</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5993,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>-61.05</v>
+        <v>-155.1</v>
       </c>
       <c r="Q91">
-        <v>-61.05</v>
+        <v>-155.1</v>
       </c>
       <c r="R91">
-        <v>-0.63</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6007,13 +6010,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6043,7 +6046,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6063,13 +6066,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D93" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6099,7 +6102,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6119,13 +6122,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D94" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6155,7 +6158,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6175,13 +6178,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6211,7 +6214,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6231,13 +6234,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6267,7 +6270,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6287,13 +6290,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6323,7 +6326,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6343,13 +6346,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6379,7 +6382,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6402,13 +6405,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6438,7 +6441,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6458,13 +6461,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6494,7 +6497,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6514,13 +6517,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C101" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D101" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6550,7 +6553,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6570,13 +6573,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D102" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6606,7 +6609,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6626,13 +6629,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6662,7 +6665,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6682,13 +6685,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6718,7 +6721,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6738,10 +6741,10 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D105" t="s">
         <v>148</v>
@@ -6756,7 +6759,7 @@
         <v>5</v>
       </c>
       <c r="H105">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I105">
         <v>8762.5</v>
@@ -6764,23 +6767,29 @@
       <c r="J105">
         <v>1728.5</v>
       </c>
+      <c r="K105" t="s">
+        <v>67</v>
+      </c>
       <c r="L105">
         <v>1664.88</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>1664.88</v>
+      </c>
+      <c r="N105" t="s">
+        <v>158</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>-438.0999999999995</v>
       </c>
       <c r="P105">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>-120</v>
+        <v>-438.0999999999995</v>
       </c>
       <c r="R105">
-        <v>-1.37</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -6788,13 +6797,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D106" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6815,7 +6824,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6824,7 +6833,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6844,13 +6853,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D107" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6880,7 +6889,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6900,13 +6909,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D108" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6936,7 +6945,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6956,13 +6965,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C109" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6983,7 +6992,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -6992,7 +7001,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7012,13 +7021,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C110" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D110" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7048,7 +7057,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7068,13 +7077,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D111" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7104,7 +7113,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7124,13 +7133,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C112" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D112" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7160,7 +7169,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7180,13 +7189,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7216,7 +7225,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7236,13 +7245,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7272,7 +7281,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7292,13 +7301,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D115" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7328,7 +7337,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7348,13 +7357,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C116" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D116" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7384,7 +7393,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7404,13 +7413,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D117" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7440,7 +7449,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7460,13 +7469,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C118" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D118" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7484,7 +7493,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1137.4</v>
+        <v>1137.9</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7496,13 +7505,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-53.6</v>
+        <v>-49.6</v>
       </c>
       <c r="Q118">
-        <v>-53.6</v>
+        <v>-49.6</v>
       </c>
       <c r="R118">
-        <v>-0.59</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7510,13 +7519,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C119" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D119" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7546,7 +7555,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7566,13 +7575,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D120" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7602,7 +7611,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7622,13 +7631,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C121" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D121" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7658,7 +7667,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7678,13 +7687,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C122" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D122" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7714,7 +7723,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7734,13 +7743,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D123" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7761,7 +7770,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7770,7 +7779,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7790,13 +7799,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C124" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D124" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7826,7 +7835,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7846,13 +7855,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D125" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7882,7 +7891,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7902,13 +7911,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D126" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7926,7 +7935,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>157.11</v>
+        <v>159.97</v>
       </c>
       <c r="L126">
         <v>141.65</v>
@@ -7938,13 +7947,13 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>536</v>
+        <v>727.62</v>
       </c>
       <c r="Q126">
-        <v>536</v>
+        <v>727.62</v>
       </c>
       <c r="R126">
-        <v>5.37</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -7952,13 +7961,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7988,7 +7997,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8008,13 +8017,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D128" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8032,7 +8041,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>288.05</v>
+        <v>287.2</v>
       </c>
       <c r="L128">
         <v>277.31</v>
@@ -8044,13 +8053,13 @@
         <v>475.3800000000005</v>
       </c>
       <c r="P128">
-        <v>455.05</v>
+        <v>438.9</v>
       </c>
       <c r="Q128">
-        <v>930.4299999999999</v>
+        <v>914.28</v>
       </c>
       <c r="R128">
-        <v>9.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="S128" t="s">
         <v>66</v>
@@ -8061,13 +8070,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D129" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8097,7 +8106,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8117,13 +8126,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C130" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8153,7 +8162,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8173,13 +8182,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8209,7 +8218,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8229,13 +8238,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8265,7 +8274,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8285,13 +8294,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D133" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8312,7 +8321,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8321,7 +8330,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8341,13 +8350,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D134" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8377,7 +8386,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8397,13 +8406,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C135" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D135" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8433,7 +8442,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8453,13 +8462,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D136" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8477,7 +8486,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>449.4</v>
+        <v>449.35</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8489,13 +8498,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-105.6</v>
+        <v>-106.7</v>
       </c>
       <c r="Q136">
-        <v>-105.6</v>
+        <v>-106.7</v>
       </c>
       <c r="R136">
-        <v>-1.06</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8503,16 +8512,16 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C137" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D137" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137">
         <v>3655.6</v>
@@ -8527,10 +8536,10 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>4271.1</v>
+        <v>4362.4</v>
       </c>
       <c r="L137">
-        <v>3838.38</v>
+        <v>4021.16</v>
       </c>
       <c r="M137">
         <v>0</v>
@@ -8539,13 +8548,13 @@
         <v>365.5600000000004</v>
       </c>
       <c r="P137">
-        <v>615.5</v>
+        <v>706.8</v>
       </c>
       <c r="Q137">
-        <v>981.0599999999999</v>
+        <v>1072.36</v>
       </c>
       <c r="R137">
-        <v>13.42</v>
+        <v>14.67</v>
       </c>
       <c r="S137" t="s">
         <v>66</v>
@@ -8556,13 +8565,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C138" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D138" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -8580,7 +8589,7 @@
         <v>9235.049999999999</v>
       </c>
       <c r="J138">
-        <v>851.95</v>
+        <v>856</v>
       </c>
       <c r="L138">
         <v>797.5700000000001</v>
@@ -8592,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>136.4</v>
+        <v>180.95</v>
       </c>
       <c r="Q138">
-        <v>136.4</v>
+        <v>180.95</v>
       </c>
       <c r="R138">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -8606,13 +8615,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C139" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D139" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8642,7 +8651,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8662,13 +8671,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C140" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8698,7 +8707,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8718,13 +8727,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D141" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8754,7 +8763,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8774,10 +8783,10 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C142" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D142" t="s">
         <v>148</v>
@@ -8792,7 +8801,7 @@
         <v>4</v>
       </c>
       <c r="H142">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I142">
         <v>8539.200000000001</v>
@@ -8800,23 +8809,29 @@
       <c r="J142">
         <v>2064.7</v>
       </c>
+      <c r="K142" t="s">
+        <v>67</v>
+      </c>
       <c r="L142">
         <v>2028.06</v>
       </c>
       <c r="M142">
-        <v>0</v>
+        <v>2028.06</v>
+      </c>
+      <c r="N142" t="s">
+        <v>158</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>-426.9600000000009</v>
       </c>
       <c r="P142">
-        <v>-280.4</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>-280.4</v>
+        <v>-426.9600000000009</v>
       </c>
       <c r="R142">
-        <v>-3.28</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -8824,13 +8839,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C143" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D143" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8848,7 +8863,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6063</v>
+        <v>6142</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8860,13 +8875,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>-149.5</v>
+        <v>-70.5</v>
       </c>
       <c r="Q143">
-        <v>-149.5</v>
+        <v>-70.5</v>
       </c>
       <c r="R143">
-        <v>-2.41</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8874,13 +8889,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C144" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D144" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8910,7 +8925,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8930,13 +8945,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C145" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D145" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8966,7 +8981,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -8986,13 +9001,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C146" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D146" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -9010,7 +9025,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3017</v>
+        <v>3026.6</v>
       </c>
       <c r="L146">
         <v>2788.25</v>
@@ -9022,13 +9037,13 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>246</v>
+        <v>274.8</v>
       </c>
       <c r="Q146">
-        <v>246</v>
+        <v>274.8</v>
       </c>
       <c r="R146">
-        <v>2.79</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -9036,13 +9051,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C147" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9060,7 +9075,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>785.65</v>
+        <v>778.7</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9072,13 +9087,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -9086,13 +9101,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C148" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D148" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -9110,7 +9125,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>322.1</v>
+        <v>324.8</v>
       </c>
       <c r="L148">
         <v>306</v>
@@ -9122,13 +9137,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -9136,13 +9151,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C149" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D149" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -9160,7 +9175,7 @@
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>1842.5</v>
+        <v>1834.2</v>
       </c>
       <c r="L149">
         <v>1750.38</v>
@@ -9172,12 +9187,62 @@
         <v>0</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>-41.5</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>-41.5</v>
       </c>
       <c r="R149">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
+      <c r="A150" t="s">
+        <v>67</v>
+      </c>
+      <c r="B150" t="s">
+        <v>142</v>
+      </c>
+      <c r="C150" t="s">
+        <v>145</v>
+      </c>
+      <c r="D150" t="s">
+        <v>149</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <v>403.7</v>
+      </c>
+      <c r="G150">
+        <v>24</v>
+      </c>
+      <c r="H150">
+        <v>24</v>
+      </c>
+      <c r="I150">
+        <v>9688.799999999999</v>
+      </c>
+      <c r="J150">
+        <v>403.7</v>
+      </c>
+      <c r="L150">
+        <v>383.51</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>0</v>
+      </c>
+      <c r="R150">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="162">
   <si>
     <t>Buy Date</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -860,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S150"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -937,13 +940,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -973,7 +976,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -993,13 +996,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1029,7 +1032,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1052,13 +1055,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1088,7 +1091,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1108,13 +1111,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1144,7 +1147,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1164,13 +1167,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1200,7 +1203,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1220,13 +1223,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1256,7 +1259,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1276,13 +1279,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1312,7 +1315,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1332,13 +1335,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1368,7 +1371,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1388,13 +1391,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1424,7 +1427,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1444,13 +1447,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1471,7 +1474,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1480,7 +1483,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1495,7 +1498,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1503,13 +1506,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1539,7 +1542,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1562,13 +1565,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1598,7 +1601,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1618,13 +1621,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1654,7 +1657,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1674,13 +1677,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1710,7 +1713,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1730,13 +1733,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1766,7 +1769,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1786,13 +1789,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1822,7 +1825,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1842,13 +1845,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1878,7 +1881,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1898,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1934,7 +1937,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1954,13 +1957,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1990,7 +1993,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2010,13 +2013,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2037,7 +2040,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2046,7 +2049,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2066,13 +2069,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2093,7 +2096,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2102,7 +2105,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2122,13 +2125,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2158,7 +2161,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2178,13 +2181,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2214,7 +2217,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2234,13 +2237,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2270,7 +2273,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2290,13 +2293,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2317,7 +2320,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2326,7 +2329,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2346,13 +2349,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2382,7 +2385,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2402,13 +2405,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2438,7 +2441,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2458,13 +2461,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2494,7 +2497,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2514,13 +2517,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2550,7 +2553,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2570,13 +2573,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2597,7 +2600,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2606,7 +2609,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2626,13 +2629,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2662,7 +2665,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2682,13 +2685,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2718,7 +2721,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2738,13 +2741,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2765,7 +2768,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2774,7 +2777,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2794,13 +2797,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2821,7 +2824,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2830,7 +2833,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2850,13 +2853,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2886,7 +2889,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2906,13 +2909,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2942,7 +2945,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2962,13 +2965,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -2998,7 +3001,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3021,13 +3024,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3057,7 +3060,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3077,13 +3080,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3113,7 +3116,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3133,13 +3136,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3169,7 +3172,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3189,13 +3192,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3216,7 +3219,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3225,7 +3228,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3245,13 +3248,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3272,7 +3275,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3281,7 +3284,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3301,13 +3304,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3337,7 +3340,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3357,13 +3360,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3393,7 +3396,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3413,13 +3416,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3449,7 +3452,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3472,13 +3475,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3508,7 +3511,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3528,13 +3531,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3564,7 +3567,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3584,13 +3587,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3620,7 +3623,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3643,13 +3646,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3679,7 +3682,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3699,13 +3702,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3735,7 +3738,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3755,13 +3758,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3791,7 +3794,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3814,13 +3817,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3850,7 +3853,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3870,13 +3873,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3906,7 +3909,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3929,13 +3932,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3965,7 +3968,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3988,13 +3991,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4024,7 +4027,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4044,13 +4047,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4071,7 +4074,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4080,7 +4083,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4100,13 +4103,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4136,7 +4139,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4156,13 +4159,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4192,7 +4195,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4215,13 +4218,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D60" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4251,7 +4254,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4271,13 +4274,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4307,7 +4310,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4330,13 +4333,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4366,7 +4369,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4381,7 +4384,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4389,13 +4392,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4425,7 +4428,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4445,13 +4448,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4481,7 +4484,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4501,13 +4504,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4537,7 +4540,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4557,13 +4560,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4593,7 +4596,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4613,13 +4616,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4649,7 +4652,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4669,13 +4672,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4705,7 +4708,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4725,13 +4728,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4752,7 +4755,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4761,7 +4764,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4781,13 +4784,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4817,7 +4820,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4837,13 +4840,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4873,7 +4876,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4893,13 +4896,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4929,7 +4932,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4949,13 +4952,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4985,7 +4988,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5005,13 +5008,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5041,7 +5044,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5061,13 +5064,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5097,7 +5100,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5117,13 +5120,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5153,7 +5156,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5173,13 +5176,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5209,7 +5212,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5229,13 +5232,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5265,7 +5268,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5285,13 +5288,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D79" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5321,7 +5324,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5341,13 +5344,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5377,7 +5380,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5397,13 +5400,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5433,7 +5436,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5453,13 +5456,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D82" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5489,7 +5492,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5512,13 +5515,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5548,7 +5551,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5568,13 +5571,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C84" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D84" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5604,7 +5607,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5624,13 +5627,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D85" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5660,7 +5663,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5680,13 +5683,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C86" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D86" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5716,7 +5719,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5736,13 +5739,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D87" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5772,7 +5775,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5792,13 +5795,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5828,7 +5831,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5848,13 +5851,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D89" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5884,7 +5887,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5904,13 +5907,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5940,7 +5943,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5960,13 +5963,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D91" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5984,7 +5987,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>289.95</v>
+        <v>295.15</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5996,13 +5999,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>-155.1</v>
+        <v>16.5</v>
       </c>
       <c r="Q91">
-        <v>-155.1</v>
+        <v>16.5</v>
       </c>
       <c r="R91">
-        <v>-1.6</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6010,13 +6013,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D92" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6046,7 +6049,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6066,13 +6069,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C93" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D93" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6102,7 +6105,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6122,13 +6125,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C94" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6158,7 +6161,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6178,13 +6181,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D95" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6214,7 +6217,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6234,13 +6237,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C96" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6270,7 +6273,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6290,13 +6293,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D97" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6326,7 +6329,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6346,13 +6349,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D98" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6382,7 +6385,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6405,13 +6408,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D99" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6441,7 +6444,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6461,13 +6464,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D100" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6497,7 +6500,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6517,13 +6520,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6553,7 +6556,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6573,13 +6576,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D102" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6609,7 +6612,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6629,13 +6632,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D103" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6665,7 +6668,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6685,13 +6688,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D104" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6721,7 +6724,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6741,13 +6744,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C105" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D105" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6777,7 +6780,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6797,13 +6800,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D106" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6824,7 +6827,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6833,7 +6836,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6853,13 +6856,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D107" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6889,7 +6892,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6909,13 +6912,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D108" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6945,7 +6948,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6965,13 +6968,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D109" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6992,7 +6995,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7001,7 +7004,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7021,13 +7024,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D110" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7057,7 +7060,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7077,13 +7080,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D111" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7113,7 +7116,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7133,13 +7136,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7169,7 +7172,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7189,13 +7192,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7225,7 +7228,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7245,13 +7248,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7281,7 +7284,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7301,13 +7304,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7337,7 +7340,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7357,13 +7360,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7393,7 +7396,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7413,13 +7416,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D117" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7449,7 +7452,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7469,13 +7472,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D118" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7493,7 +7496,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1137.9</v>
+        <v>1134</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7505,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-49.6</v>
+        <v>-80.8</v>
       </c>
       <c r="Q118">
-        <v>-49.6</v>
+        <v>-80.8</v>
       </c>
       <c r="R118">
-        <v>-0.54</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7519,13 +7522,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C119" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D119" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7555,7 +7558,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7575,13 +7578,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D120" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7611,7 +7614,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7631,13 +7634,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D121" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7667,7 +7670,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7687,13 +7690,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C122" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D122" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7723,7 +7726,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7743,13 +7746,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D123" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7770,7 +7773,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7779,7 +7782,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7799,13 +7802,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D124" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7835,7 +7838,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7855,13 +7858,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C125" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D125" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7891,7 +7894,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7911,16 +7914,16 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C126" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D126" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F126">
         <v>149.11</v>
@@ -7929,31 +7932,34 @@
         <v>67</v>
       </c>
       <c r="H126">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I126">
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>159.97</v>
+        <v>163.26</v>
       </c>
       <c r="L126">
-        <v>141.65</v>
+        <v>156.57</v>
       </c>
       <c r="M126">
         <v>0</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>492.063</v>
       </c>
       <c r="P126">
-        <v>727.62</v>
+        <v>481.1</v>
       </c>
       <c r="Q126">
-        <v>727.62</v>
+        <v>973.16</v>
       </c>
       <c r="R126">
-        <v>7.28</v>
+        <v>9.74</v>
+      </c>
+      <c r="S126" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -7961,13 +7967,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C127" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D127" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7997,7 +8003,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8017,13 +8023,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D128" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8041,7 +8047,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>287.2</v>
+        <v>281.85</v>
       </c>
       <c r="L128">
         <v>277.31</v>
@@ -8053,13 +8059,13 @@
         <v>475.3800000000005</v>
       </c>
       <c r="P128">
-        <v>438.9</v>
+        <v>337.25</v>
       </c>
       <c r="Q128">
-        <v>914.28</v>
+        <v>812.63</v>
       </c>
       <c r="R128">
-        <v>9.359999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="S128" t="s">
         <v>66</v>
@@ -8070,13 +8076,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C129" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D129" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8106,7 +8112,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8126,13 +8132,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8162,7 +8168,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8182,13 +8188,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8218,7 +8224,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8238,13 +8244,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8274,7 +8280,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8294,13 +8300,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D133" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8321,7 +8327,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8330,7 +8336,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8350,13 +8356,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D134" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8386,7 +8392,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8406,13 +8412,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D135" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8442,7 +8448,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8462,13 +8468,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C136" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D136" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8486,7 +8492,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>449.35</v>
+        <v>459.55</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8498,13 +8504,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-106.7</v>
+        <v>117.7</v>
       </c>
       <c r="Q136">
-        <v>-106.7</v>
+        <v>117.7</v>
       </c>
       <c r="R136">
-        <v>-1.07</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8512,13 +8518,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D137" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8536,7 +8542,7 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>4362.4</v>
+        <v>4551.3</v>
       </c>
       <c r="L137">
         <v>4021.16</v>
@@ -8548,13 +8554,13 @@
         <v>365.5600000000004</v>
       </c>
       <c r="P137">
-        <v>706.8</v>
+        <v>895.7</v>
       </c>
       <c r="Q137">
-        <v>1072.36</v>
+        <v>1261.26</v>
       </c>
       <c r="R137">
-        <v>14.67</v>
+        <v>17.25</v>
       </c>
       <c r="S137" t="s">
         <v>66</v>
@@ -8565,16 +8571,16 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D138" t="s">
         <v>149</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138">
         <v>839.55</v>
@@ -8583,7 +8589,7 @@
         <v>11</v>
       </c>
       <c r="H138">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I138">
         <v>9235.049999999999</v>
@@ -8591,23 +8597,29 @@
       <c r="J138">
         <v>856</v>
       </c>
+      <c r="K138" t="s">
+        <v>68</v>
+      </c>
       <c r="L138">
-        <v>797.5700000000001</v>
+        <v>881.53</v>
       </c>
       <c r="M138">
-        <v>0</v>
+        <v>857</v>
+      </c>
+      <c r="N138" t="s">
+        <v>160</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>191.9500000000005</v>
       </c>
       <c r="P138">
-        <v>180.95</v>
+        <v>0</v>
       </c>
       <c r="Q138">
-        <v>180.95</v>
+        <v>191.9500000000005</v>
       </c>
       <c r="R138">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -8615,13 +8627,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C139" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D139" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8651,7 +8663,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8671,13 +8683,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C140" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D140" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8707,7 +8719,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8727,13 +8739,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D141" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8763,7 +8775,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8783,13 +8795,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C142" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D142" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8819,7 +8831,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8839,13 +8851,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C143" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D143" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8863,7 +8875,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6142</v>
+        <v>6193.5</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8875,13 +8887,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>-70.5</v>
+        <v>-19</v>
       </c>
       <c r="Q143">
-        <v>-70.5</v>
+        <v>-19</v>
       </c>
       <c r="R143">
-        <v>-1.13</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8889,13 +8901,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D144" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8925,7 +8937,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8945,13 +8957,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8981,7 +8993,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9001,13 +9013,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C146" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D146" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -9025,7 +9037,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3026.6</v>
+        <v>3048</v>
       </c>
       <c r="L146">
         <v>2788.25</v>
@@ -9037,13 +9049,13 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>274.8</v>
+        <v>339</v>
       </c>
       <c r="Q146">
-        <v>274.8</v>
+        <v>339</v>
       </c>
       <c r="R146">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -9051,13 +9063,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D147" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9075,7 +9087,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>778.7</v>
+        <v>786.2</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9087,13 +9099,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>-83.40000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="Q147">
-        <v>-83.40000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="R147">
-        <v>-0.88</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -9101,13 +9113,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C148" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D148" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -9125,7 +9137,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>324.8</v>
+        <v>327.55</v>
       </c>
       <c r="L148">
         <v>306</v>
@@ -9137,13 +9149,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>83.7</v>
+        <v>168.95</v>
       </c>
       <c r="Q148">
-        <v>83.7</v>
+        <v>168.95</v>
       </c>
       <c r="R148">
-        <v>0.84</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -9151,13 +9163,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C149" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D149" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -9175,7 +9187,7 @@
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>1834.2</v>
+        <v>1902.2</v>
       </c>
       <c r="L149">
         <v>1750.38</v>
@@ -9187,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="P149">
-        <v>-41.5</v>
+        <v>298.5</v>
       </c>
       <c r="Q149">
-        <v>-41.5</v>
+        <v>298.5</v>
       </c>
       <c r="R149">
-        <v>-0.45</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -9201,13 +9213,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D150" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9225,7 +9237,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>403.7</v>
+        <v>401</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9237,12 +9249,112 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>-64.8</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>-64.8</v>
       </c>
       <c r="R150">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
+      <c r="A151" t="s">
+        <v>68</v>
+      </c>
+      <c r="B151" t="s">
+        <v>89</v>
+      </c>
+      <c r="C151" t="s">
+        <v>148</v>
+      </c>
+      <c r="D151" t="s">
+        <v>150</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151">
+        <v>4246.1</v>
+      </c>
+      <c r="G151">
+        <v>2</v>
+      </c>
+      <c r="H151">
+        <v>2</v>
+      </c>
+      <c r="I151">
+        <v>8492.200000000001</v>
+      </c>
+      <c r="J151">
+        <v>4246.1</v>
+      </c>
+      <c r="L151">
+        <v>4033.8</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>0</v>
+      </c>
+      <c r="R151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
+      <c r="A152" t="s">
+        <v>68</v>
+      </c>
+      <c r="B152" t="s">
+        <v>112</v>
+      </c>
+      <c r="C152" t="s">
+        <v>147</v>
+      </c>
+      <c r="D152" t="s">
+        <v>150</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>366.1</v>
+      </c>
+      <c r="G152">
+        <v>27</v>
+      </c>
+      <c r="H152">
+        <v>27</v>
+      </c>
+      <c r="I152">
+        <v>9884.700000000001</v>
+      </c>
+      <c r="J152">
+        <v>366.1</v>
+      </c>
+      <c r="L152">
+        <v>347.8</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>0</v>
+      </c>
+      <c r="R152">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="163">
   <si>
     <t>Buy Date</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -863,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S152"/>
+  <dimension ref="A1:S155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -940,13 +943,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -976,7 +979,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -996,13 +999,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1032,7 +1035,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1055,13 +1058,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1091,7 +1094,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1111,13 +1114,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1147,7 +1150,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1167,13 +1170,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1203,7 +1206,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1223,13 +1226,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1259,7 +1262,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1279,13 +1282,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1315,7 +1318,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1335,13 +1338,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1371,7 +1374,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1391,13 +1394,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1427,7 +1430,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1447,13 +1450,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1474,7 +1477,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1483,7 +1486,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1498,7 +1501,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1506,13 +1509,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1542,7 +1545,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1565,13 +1568,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1601,7 +1604,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1621,13 +1624,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1657,7 +1660,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1677,13 +1680,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1713,7 +1716,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1733,13 +1736,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1769,7 +1772,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1789,13 +1792,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1825,7 +1828,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1845,13 +1848,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1881,7 +1884,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1901,13 +1904,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1937,7 +1940,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1957,13 +1960,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1993,7 +1996,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2013,13 +2016,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2040,7 +2043,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2049,7 +2052,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2069,13 +2072,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2096,7 +2099,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2105,7 +2108,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2125,13 +2128,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2161,7 +2164,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2181,13 +2184,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2217,7 +2220,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2237,13 +2240,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2273,7 +2276,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2293,13 +2296,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2320,7 +2323,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2329,7 +2332,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2349,13 +2352,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2385,7 +2388,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2405,13 +2408,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2441,7 +2444,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2461,13 +2464,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2497,7 +2500,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2517,13 +2520,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2553,7 +2556,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2573,13 +2576,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2600,7 +2603,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2609,7 +2612,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2629,13 +2632,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2665,7 +2668,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2685,13 +2688,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2721,7 +2724,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2741,13 +2744,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2768,7 +2771,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2777,7 +2780,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2797,13 +2800,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2824,7 +2827,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2833,7 +2836,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2853,13 +2856,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2889,7 +2892,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2909,13 +2912,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2945,7 +2948,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2965,13 +2968,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3001,7 +3004,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3024,13 +3027,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3060,7 +3063,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3080,13 +3083,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3116,7 +3119,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3136,13 +3139,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3172,7 +3175,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3192,13 +3195,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3219,7 +3222,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3228,7 +3231,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3248,13 +3251,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3275,7 +3278,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3284,7 +3287,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3304,13 +3307,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3340,7 +3343,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3360,13 +3363,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3396,7 +3399,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3416,13 +3419,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3452,7 +3455,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3475,13 +3478,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3511,7 +3514,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3531,13 +3534,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3567,7 +3570,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3587,13 +3590,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3623,7 +3626,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3646,13 +3649,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3682,7 +3685,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3702,13 +3705,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3738,7 +3741,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3758,13 +3761,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3794,7 +3797,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3817,13 +3820,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3853,7 +3856,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3873,13 +3876,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3909,7 +3912,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3932,13 +3935,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3968,7 +3971,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3991,13 +3994,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4027,7 +4030,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4047,13 +4050,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4074,7 +4077,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4083,7 +4086,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4103,13 +4106,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4139,7 +4142,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4159,13 +4162,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4195,7 +4198,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4218,13 +4221,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4254,7 +4257,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4274,13 +4277,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D61" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4310,7 +4313,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4333,13 +4336,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4369,7 +4372,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4384,7 +4387,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4392,13 +4395,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4428,7 +4431,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4448,13 +4451,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4484,7 +4487,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4504,13 +4507,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4540,7 +4543,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4560,13 +4563,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4596,7 +4599,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4616,13 +4619,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4652,7 +4655,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4672,13 +4675,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4708,7 +4711,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4728,13 +4731,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4755,7 +4758,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4764,7 +4767,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4784,13 +4787,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4820,7 +4823,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4840,13 +4843,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4876,7 +4879,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4896,13 +4899,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4932,7 +4935,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4952,13 +4955,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4988,7 +4991,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5008,13 +5011,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5044,7 +5047,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5064,13 +5067,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5100,7 +5103,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5120,13 +5123,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C76" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D76" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5156,7 +5159,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5176,13 +5179,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5212,7 +5215,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5232,13 +5235,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5268,7 +5271,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5288,13 +5291,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D79" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5324,7 +5327,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5344,13 +5347,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D80" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5380,7 +5383,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5400,13 +5403,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C81" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5436,7 +5439,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5456,13 +5459,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D82" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5492,7 +5495,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5515,13 +5518,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D83" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5551,7 +5554,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5571,13 +5574,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D84" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5607,7 +5610,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5627,13 +5630,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D85" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5663,7 +5666,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5683,13 +5686,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D86" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5719,7 +5722,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5739,13 +5742,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D87" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5775,7 +5778,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5795,13 +5798,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5831,7 +5834,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5851,13 +5854,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5887,7 +5890,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5907,13 +5910,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D90" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5943,7 +5946,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5963,13 +5966,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D91" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5987,7 +5990,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>295.15</v>
+        <v>295.4</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -5999,13 +6002,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>16.5</v>
+        <v>24.75</v>
       </c>
       <c r="Q91">
-        <v>16.5</v>
+        <v>24.75</v>
       </c>
       <c r="R91">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6013,13 +6016,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D92" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6049,7 +6052,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6069,13 +6072,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D93" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6105,7 +6108,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6125,13 +6128,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D94" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6161,7 +6164,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6181,13 +6184,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6217,7 +6220,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6237,13 +6240,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D96" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6273,7 +6276,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6293,13 +6296,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6329,7 +6332,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6349,13 +6352,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C98" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D98" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6385,7 +6388,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6408,13 +6411,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D99" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6444,7 +6447,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6464,13 +6467,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D100" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6500,7 +6503,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6520,13 +6523,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6556,7 +6559,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6576,13 +6579,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D102" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6612,7 +6615,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6632,13 +6635,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D103" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6668,7 +6671,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6688,13 +6691,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D104" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6724,7 +6727,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6744,13 +6747,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C105" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6780,7 +6783,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6800,13 +6803,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D106" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6827,7 +6830,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6836,7 +6839,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6856,13 +6859,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6892,7 +6895,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6912,13 +6915,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C108" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6948,7 +6951,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6968,13 +6971,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C109" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6995,7 +6998,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7004,7 +7007,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7024,13 +7027,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C110" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D110" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7060,7 +7063,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7080,13 +7083,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C111" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7116,7 +7119,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7136,13 +7139,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7172,7 +7175,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7192,13 +7195,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D113" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7228,7 +7231,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7248,13 +7251,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7284,7 +7287,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7304,13 +7307,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C115" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D115" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7340,7 +7343,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7360,13 +7363,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D116" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7396,7 +7399,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7416,13 +7419,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7452,7 +7455,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7472,13 +7475,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C118" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D118" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7496,7 +7499,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1134</v>
+        <v>1168.2</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7508,13 +7511,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>-80.8</v>
+        <v>192.8</v>
       </c>
       <c r="Q118">
-        <v>-80.8</v>
+        <v>192.8</v>
       </c>
       <c r="R118">
-        <v>-0.88</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7522,13 +7525,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C119" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D119" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7558,7 +7561,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7578,13 +7581,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D120" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7614,7 +7617,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7634,13 +7637,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D121" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7670,7 +7673,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7690,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D122" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7726,7 +7729,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7746,13 +7749,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C123" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D123" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7773,7 +7776,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7782,7 +7785,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7802,13 +7805,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C124" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D124" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7838,7 +7841,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7858,13 +7861,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C125" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D125" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7894,7 +7897,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7914,13 +7917,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C126" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D126" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E126">
         <v>2</v>
@@ -7938,7 +7941,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>163.26</v>
+        <v>163.36</v>
       </c>
       <c r="L126">
         <v>156.57</v>
@@ -7947,16 +7950,16 @@
         <v>0</v>
       </c>
       <c r="O126">
-        <v>492.063</v>
+        <v>492.0630000000001</v>
       </c>
       <c r="P126">
-        <v>481.1</v>
+        <v>484.5</v>
       </c>
       <c r="Q126">
-        <v>973.16</v>
+        <v>976.5599999999999</v>
       </c>
       <c r="R126">
-        <v>9.74</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="S126" t="s">
         <v>68</v>
@@ -7967,13 +7970,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D127" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8003,7 +8006,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8023,13 +8026,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C128" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D128" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8047,7 +8050,7 @@
         <v>9771.700000000001</v>
       </c>
       <c r="J128">
-        <v>281.85</v>
+        <v>286.65</v>
       </c>
       <c r="L128">
         <v>277.31</v>
@@ -8059,13 +8062,13 @@
         <v>475.3800000000005</v>
       </c>
       <c r="P128">
-        <v>337.25</v>
+        <v>428.45</v>
       </c>
       <c r="Q128">
-        <v>812.63</v>
+        <v>903.83</v>
       </c>
       <c r="R128">
-        <v>8.32</v>
+        <v>9.25</v>
       </c>
       <c r="S128" t="s">
         <v>66</v>
@@ -8076,13 +8079,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C129" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D129" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8112,7 +8115,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8132,13 +8135,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D130" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8168,7 +8171,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8188,13 +8191,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D131" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8224,7 +8227,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8244,13 +8247,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D132" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8280,7 +8283,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8300,13 +8303,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8327,7 +8330,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8336,7 +8339,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8356,13 +8359,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D134" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8392,7 +8395,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8412,13 +8415,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D135" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8448,7 +8451,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8468,13 +8471,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D136" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8492,7 +8495,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>459.55</v>
+        <v>463</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8504,13 +8507,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>117.7</v>
+        <v>193.6</v>
       </c>
       <c r="Q136">
-        <v>117.7</v>
+        <v>193.6</v>
       </c>
       <c r="R136">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8518,13 +8521,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D137" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8542,10 +8545,10 @@
         <v>7311.2</v>
       </c>
       <c r="J137">
-        <v>4551.3</v>
+        <v>4466</v>
       </c>
       <c r="L137">
-        <v>4021.16</v>
+        <v>4271.1</v>
       </c>
       <c r="M137">
         <v>0</v>
@@ -8554,13 +8557,13 @@
         <v>365.5600000000004</v>
       </c>
       <c r="P137">
-        <v>895.7</v>
+        <v>810.4</v>
       </c>
       <c r="Q137">
-        <v>1261.26</v>
+        <v>1175.96</v>
       </c>
       <c r="R137">
-        <v>17.25</v>
+        <v>16.08</v>
       </c>
       <c r="S137" t="s">
         <v>66</v>
@@ -8571,13 +8574,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D138" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8607,7 +8610,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8627,13 +8630,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C139" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D139" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8663,7 +8666,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8683,13 +8686,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C140" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D140" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8719,7 +8722,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8739,13 +8742,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D141" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8775,7 +8778,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8795,13 +8798,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C142" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8831,7 +8834,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8851,13 +8854,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C143" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D143" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8875,7 +8878,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6193.5</v>
+        <v>6269</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8887,13 +8890,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>-19</v>
+        <v>56.5</v>
       </c>
       <c r="Q143">
-        <v>-19</v>
+        <v>56.5</v>
       </c>
       <c r="R143">
-        <v>-0.31</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8901,13 +8904,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C144" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D144" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8937,7 +8940,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8957,13 +8960,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D145" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8993,7 +8996,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9013,13 +9016,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C146" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D146" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -9037,7 +9040,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3048</v>
+        <v>3075.5</v>
       </c>
       <c r="L146">
         <v>2788.25</v>
@@ -9049,13 +9052,13 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>339</v>
+        <v>421.5</v>
       </c>
       <c r="Q146">
-        <v>339</v>
+        <v>421.5</v>
       </c>
       <c r="R146">
-        <v>3.85</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -9063,13 +9066,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9087,7 +9090,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>786.2</v>
+        <v>784.8</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9099,13 +9102,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>6.6</v>
+        <v>-10.2</v>
       </c>
       <c r="Q147">
-        <v>6.6</v>
+        <v>-10.2</v>
       </c>
       <c r="R147">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -9113,13 +9116,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C148" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D148" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -9137,7 +9140,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>327.55</v>
+        <v>329.35</v>
       </c>
       <c r="L148">
         <v>306</v>
@@ -9149,13 +9152,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>168.95</v>
+        <v>224.75</v>
       </c>
       <c r="Q148">
-        <v>168.95</v>
+        <v>224.75</v>
       </c>
       <c r="R148">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -9163,13 +9166,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C149" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D149" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -9187,7 +9190,7 @@
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>1902.2</v>
+        <v>1882.1</v>
       </c>
       <c r="L149">
         <v>1750.38</v>
@@ -9199,13 +9202,13 @@
         <v>0</v>
       </c>
       <c r="P149">
-        <v>298.5</v>
+        <v>198</v>
       </c>
       <c r="Q149">
-        <v>298.5</v>
+        <v>198</v>
       </c>
       <c r="R149">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -9213,13 +9216,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C150" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D150" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9237,7 +9240,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>401</v>
+        <v>400.85</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9249,13 +9252,13 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>-64.8</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="Q150">
-        <v>-64.8</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="R150">
-        <v>-0.67</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="151" spans="1:18">
@@ -9263,13 +9266,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C151" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D151" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9287,7 +9290,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4246.1</v>
+        <v>4230.6</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9299,13 +9302,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="152" spans="1:18">
@@ -9313,13 +9316,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C152" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D152" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9337,7 +9340,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>366.1</v>
+        <v>368.85</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9349,12 +9352,162 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>74.25</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>74.25</v>
       </c>
       <c r="R152">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
+      <c r="A153" t="s">
+        <v>69</v>
+      </c>
+      <c r="B153" t="s">
+        <v>145</v>
+      </c>
+      <c r="C153" t="s">
+        <v>147</v>
+      </c>
+      <c r="D153" t="s">
+        <v>151</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>1029.15</v>
+      </c>
+      <c r="G153">
+        <v>9</v>
+      </c>
+      <c r="H153">
+        <v>9</v>
+      </c>
+      <c r="I153">
+        <v>9262.35</v>
+      </c>
+      <c r="J153">
+        <v>1029.15</v>
+      </c>
+      <c r="L153">
+        <v>977.6900000000001</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>0</v>
+      </c>
+      <c r="R153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
+      <c r="A154" t="s">
+        <v>69</v>
+      </c>
+      <c r="B154" t="s">
+        <v>74</v>
+      </c>
+      <c r="C154" t="s">
+        <v>147</v>
+      </c>
+      <c r="D154" t="s">
+        <v>151</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>2110.6</v>
+      </c>
+      <c r="G154">
+        <v>4</v>
+      </c>
+      <c r="H154">
+        <v>4</v>
+      </c>
+      <c r="I154">
+        <v>8442.4</v>
+      </c>
+      <c r="J154">
+        <v>2110.6</v>
+      </c>
+      <c r="L154">
+        <v>2005.07</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
+      <c r="A155" t="s">
+        <v>69</v>
+      </c>
+      <c r="B155" t="s">
+        <v>87</v>
+      </c>
+      <c r="C155" t="s">
+        <v>147</v>
+      </c>
+      <c r="D155" t="s">
+        <v>151</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155">
+        <v>1234.1</v>
+      </c>
+      <c r="G155">
+        <v>8</v>
+      </c>
+      <c r="H155">
+        <v>8</v>
+      </c>
+      <c r="I155">
+        <v>9872.799999999999</v>
+      </c>
+      <c r="J155">
+        <v>1234.1</v>
+      </c>
+      <c r="L155">
+        <v>1172.39</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="165">
   <si>
     <t>Buy Date</t>
   </si>
@@ -226,6 +226,9 @@
     <t>2026-04-07</t>
   </si>
   <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -455,6 +458,9 @@
   </si>
   <si>
     <t>INDUSINDBK</t>
+  </si>
+  <si>
+    <t>COLPAL</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -866,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S155"/>
+  <dimension ref="A1:S160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -943,13 +949,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -979,7 +985,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -999,13 +1005,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1035,7 +1041,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1058,13 +1064,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1094,7 +1100,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1114,13 +1120,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1150,7 +1156,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1170,13 +1176,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1206,7 +1212,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1226,13 +1232,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1262,7 +1268,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1282,13 +1288,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1318,7 +1324,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1338,13 +1344,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1374,7 +1380,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1394,13 +1400,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1430,7 +1436,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1450,13 +1456,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1477,7 +1483,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1486,7 +1492,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1501,7 +1507,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1509,13 +1515,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1545,7 +1551,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1568,13 +1574,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1604,7 +1610,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1624,13 +1630,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1660,7 +1666,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1680,13 +1686,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1716,7 +1722,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1736,13 +1742,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1772,7 +1778,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1792,13 +1798,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1828,7 +1834,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1848,13 +1854,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1884,7 +1890,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1904,13 +1910,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1940,7 +1946,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1960,13 +1966,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1996,7 +2002,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2016,13 +2022,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2043,7 +2049,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2052,7 +2058,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2072,13 +2078,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2099,7 +2105,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2108,7 +2114,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2128,13 +2134,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2164,7 +2170,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2184,13 +2190,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2220,7 +2226,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2240,13 +2246,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2276,7 +2282,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2296,13 +2302,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2323,7 +2329,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2332,7 +2338,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2352,13 +2358,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2388,7 +2394,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2408,13 +2414,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2444,7 +2450,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2464,13 +2470,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2500,7 +2506,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2520,13 +2526,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2556,7 +2562,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2576,13 +2582,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2603,7 +2609,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2612,7 +2618,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2632,13 +2638,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2668,7 +2674,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2688,13 +2694,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2724,7 +2730,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2744,13 +2750,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2771,7 +2777,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2780,7 +2786,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2800,13 +2806,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2827,7 +2833,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2836,7 +2842,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2856,13 +2862,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2892,7 +2898,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2912,13 +2918,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2948,7 +2954,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2968,13 +2974,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3004,7 +3010,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3027,13 +3033,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3063,7 +3069,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3083,13 +3089,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3119,7 +3125,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3139,13 +3145,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3175,7 +3181,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3195,13 +3201,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3222,7 +3228,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3231,7 +3237,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3251,13 +3257,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3278,7 +3284,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3287,7 +3293,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3307,13 +3313,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3343,7 +3349,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3363,13 +3369,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3399,7 +3405,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3419,13 +3425,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3455,7 +3461,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3478,13 +3484,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3514,7 +3520,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3534,13 +3540,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3570,7 +3576,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3590,13 +3596,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3626,7 +3632,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3649,13 +3655,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3685,7 +3691,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3705,13 +3711,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3741,7 +3747,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3761,13 +3767,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3797,7 +3803,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3820,13 +3826,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3856,7 +3862,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3876,13 +3882,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3912,7 +3918,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3935,13 +3941,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3971,7 +3977,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -3994,13 +4000,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4030,7 +4036,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4050,13 +4056,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4077,7 +4083,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4086,7 +4092,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4106,13 +4112,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4142,7 +4148,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4162,13 +4168,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D59" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4198,7 +4204,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4221,13 +4227,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4257,7 +4263,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4277,13 +4283,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D61" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4313,7 +4319,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4336,13 +4342,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C62" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4372,7 +4378,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4387,7 +4393,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4395,13 +4401,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D63" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4431,7 +4437,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4451,13 +4457,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4487,7 +4493,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4507,13 +4513,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4543,7 +4549,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4563,13 +4569,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D66" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4599,7 +4605,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4619,13 +4625,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D67" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4655,7 +4661,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4675,13 +4681,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4711,7 +4717,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4731,13 +4737,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4758,7 +4764,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4767,7 +4773,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4787,13 +4793,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4823,7 +4829,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4843,13 +4849,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4879,7 +4885,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4899,13 +4905,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4935,7 +4941,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4955,13 +4961,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4991,7 +4997,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5011,13 +5017,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5047,7 +5053,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5067,13 +5073,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C75" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D75" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5103,7 +5109,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5123,13 +5129,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D76" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5159,7 +5165,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5179,13 +5185,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D77" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5215,7 +5221,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5235,13 +5241,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C78" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5271,7 +5277,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5291,13 +5297,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5327,7 +5333,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5347,13 +5353,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C80" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D80" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5383,7 +5389,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5403,13 +5409,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D81" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5439,7 +5445,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5459,13 +5465,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5495,7 +5501,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5518,13 +5524,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D83" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5554,7 +5560,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5574,13 +5580,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D84" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5610,7 +5616,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5630,13 +5636,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C85" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5666,7 +5672,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5686,13 +5692,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C86" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D86" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5722,7 +5728,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5742,13 +5748,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C87" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D87" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5778,7 +5784,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5798,13 +5804,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D88" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5834,7 +5840,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5854,13 +5860,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D89" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5890,7 +5896,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5910,13 +5916,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C90" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5946,7 +5952,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5966,13 +5972,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C91" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D91" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5990,7 +5996,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>295.4</v>
+        <v>294.85</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6002,13 +6008,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>24.75</v>
+        <v>6.6</v>
       </c>
       <c r="Q91">
-        <v>24.75</v>
+        <v>6.6</v>
       </c>
       <c r="R91">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6016,13 +6022,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D92" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6052,7 +6058,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6072,13 +6078,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C93" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D93" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6108,7 +6114,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6128,13 +6134,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D94" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6164,7 +6170,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6184,13 +6190,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D95" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6220,7 +6226,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6240,13 +6246,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C96" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D96" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6276,7 +6282,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6296,13 +6302,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D97" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6332,7 +6338,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6352,13 +6358,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C98" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D98" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6388,7 +6394,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6411,13 +6417,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C99" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D99" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6447,7 +6453,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6467,13 +6473,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C100" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6503,7 +6509,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6523,13 +6529,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6559,7 +6565,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6579,13 +6585,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D102" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6615,7 +6621,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6635,13 +6641,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D103" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6671,7 +6677,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6691,13 +6697,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C104" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D104" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6727,7 +6733,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6747,13 +6753,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D105" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6783,7 +6789,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6803,13 +6809,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C106" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D106" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6830,7 +6836,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6839,7 +6845,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6859,13 +6865,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6895,7 +6901,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6915,13 +6921,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6951,7 +6957,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6971,13 +6977,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6998,7 +7004,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7007,7 +7013,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7027,13 +7033,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C110" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D110" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7063,7 +7069,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7083,13 +7089,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C111" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D111" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7119,7 +7125,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7139,13 +7145,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D112" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7175,7 +7181,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7195,13 +7201,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D113" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7231,7 +7237,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7251,13 +7257,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D114" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7287,7 +7293,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7307,13 +7313,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7343,7 +7349,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7363,13 +7369,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D116" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7399,7 +7405,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7419,13 +7425,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7455,7 +7461,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7475,13 +7481,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C118" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D118" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7499,7 +7505,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1168.2</v>
+        <v>1213.1</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7511,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>192.8</v>
+        <v>552</v>
       </c>
       <c r="Q118">
-        <v>192.8</v>
+        <v>552</v>
       </c>
       <c r="R118">
-        <v>2.11</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7525,13 +7531,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D119" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7561,7 +7567,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7581,13 +7587,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C120" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D120" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7617,7 +7623,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7637,13 +7643,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D121" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7673,7 +7679,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7693,13 +7699,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D122" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7729,7 +7735,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7749,13 +7755,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D123" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7776,7 +7782,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7785,7 +7791,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7805,13 +7811,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C124" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D124" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7841,7 +7847,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7861,13 +7867,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C125" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D125" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7897,7 +7903,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7917,16 +7923,16 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C126" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D126" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126">
         <v>149.11</v>
@@ -7935,34 +7941,34 @@
         <v>67</v>
       </c>
       <c r="H126">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I126">
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>163.36</v>
+        <v>169.31</v>
       </c>
       <c r="L126">
-        <v>156.57</v>
+        <v>164.02</v>
       </c>
       <c r="M126">
         <v>0</v>
       </c>
       <c r="O126">
-        <v>492.0630000000001</v>
+        <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>484.5</v>
+        <v>363.6</v>
       </c>
       <c r="Q126">
-        <v>976.5599999999999</v>
+        <v>1213.53</v>
       </c>
       <c r="R126">
-        <v>9.779999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="S126" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -7970,13 +7976,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C127" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D127" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8006,7 +8012,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8026,13 +8032,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C128" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D128" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8044,7 +8050,7 @@
         <v>37</v>
       </c>
       <c r="H128">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I128">
         <v>9771.700000000001</v>
@@ -8052,23 +8058,29 @@
       <c r="J128">
         <v>286.65</v>
       </c>
+      <c r="K128" t="s">
+        <v>70</v>
+      </c>
       <c r="L128">
         <v>277.31</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>277.31</v>
+      </c>
+      <c r="N128" t="s">
+        <v>162</v>
       </c>
       <c r="O128">
-        <v>475.3800000000005</v>
+        <v>726.3700000000001</v>
       </c>
       <c r="P128">
-        <v>428.45</v>
+        <v>0</v>
       </c>
       <c r="Q128">
-        <v>903.83</v>
+        <v>726.3700000000001</v>
       </c>
       <c r="R128">
-        <v>9.25</v>
+        <v>7.43</v>
       </c>
       <c r="S128" t="s">
         <v>66</v>
@@ -8079,13 +8091,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C129" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D129" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8115,7 +8127,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8135,13 +8147,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C130" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D130" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8171,7 +8183,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8191,13 +8203,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C131" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D131" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8227,7 +8239,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8247,13 +8259,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D132" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8283,7 +8295,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8303,13 +8315,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C133" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D133" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8330,7 +8342,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8339,7 +8351,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8359,13 +8371,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C134" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8395,7 +8407,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8415,13 +8427,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C135" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8451,7 +8463,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8471,13 +8483,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8495,7 +8507,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>463</v>
+        <v>449.25</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8507,13 +8519,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>193.6</v>
+        <v>-108.9</v>
       </c>
       <c r="Q136">
-        <v>193.6</v>
+        <v>-108.9</v>
       </c>
       <c r="R136">
-        <v>1.94</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8521,13 +8533,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C137" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8539,7 +8551,7 @@
         <v>2</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137">
         <v>7311.2</v>
@@ -8547,23 +8559,29 @@
       <c r="J137">
         <v>4466</v>
       </c>
+      <c r="K137" t="s">
+        <v>70</v>
+      </c>
       <c r="L137">
-        <v>4271.1</v>
+        <v>4362.4</v>
       </c>
       <c r="M137">
-        <v>0</v>
+        <v>4362.4</v>
+      </c>
+      <c r="N137" t="s">
+        <v>162</v>
       </c>
       <c r="O137">
-        <v>365.5600000000004</v>
+        <v>1072.36</v>
       </c>
       <c r="P137">
-        <v>810.4</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>1175.96</v>
+        <v>1072.36</v>
       </c>
       <c r="R137">
-        <v>16.08</v>
+        <v>14.67</v>
       </c>
       <c r="S137" t="s">
         <v>66</v>
@@ -8574,13 +8592,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C138" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D138" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8610,7 +8628,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8630,13 +8648,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C139" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D139" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8666,7 +8684,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8686,13 +8704,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D140" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8722,7 +8740,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8742,13 +8760,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C141" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D141" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8778,7 +8796,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8798,13 +8816,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C142" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D142" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8834,7 +8852,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8854,13 +8872,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C143" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D143" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8878,7 +8896,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6269</v>
+        <v>6565</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8890,13 +8908,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>56.5</v>
+        <v>352.5</v>
       </c>
       <c r="Q143">
-        <v>56.5</v>
+        <v>352.5</v>
       </c>
       <c r="R143">
-        <v>0.91</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8904,13 +8922,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C144" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D144" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8940,7 +8958,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8955,18 +8973,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
+    <row r="145" spans="1:19">
       <c r="A145" t="s">
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C145" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D145" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -8996,7 +9014,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9011,21 +9029,21 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="146" spans="1:18">
+    <row r="146" spans="1:19">
       <c r="A146" t="s">
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C146" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D146" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146">
         <v>2935</v>
@@ -9034,45 +9052,48 @@
         <v>3</v>
       </c>
       <c r="H146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I146">
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3075.5</v>
+        <v>3226.1</v>
       </c>
       <c r="L146">
-        <v>2788.25</v>
+        <v>3081.75</v>
       </c>
       <c r="M146">
         <v>0</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>421.5</v>
+        <v>582.2</v>
       </c>
       <c r="Q146">
-        <v>421.5</v>
+        <v>875.7</v>
       </c>
       <c r="R146">
-        <v>4.79</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="S146" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
       <c r="A147" t="s">
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C147" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D147" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9090,7 +9111,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>784.8</v>
+        <v>835.95</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9102,27 +9123,27 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>-10.2</v>
+        <v>603.6</v>
       </c>
       <c r="Q147">
-        <v>-10.2</v>
+        <v>603.6</v>
       </c>
       <c r="R147">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
       <c r="A148" t="s">
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C148" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D148" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -9140,7 +9161,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>329.35</v>
+        <v>342.65</v>
       </c>
       <c r="L148">
         <v>306</v>
@@ -9152,30 +9173,30 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>224.75</v>
+        <v>637.05</v>
       </c>
       <c r="Q148">
-        <v>224.75</v>
+        <v>637.05</v>
       </c>
       <c r="R148">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
       <c r="A149" t="s">
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C149" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D149" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149">
         <v>1842.5</v>
@@ -9184,45 +9205,48 @@
         <v>5</v>
       </c>
       <c r="H149">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I149">
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>1882.1</v>
+        <v>2043.8</v>
       </c>
       <c r="L149">
-        <v>1750.38</v>
+        <v>1934.62</v>
       </c>
       <c r="M149">
         <v>0</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>368.5000000000005</v>
       </c>
       <c r="P149">
-        <v>198</v>
+        <v>603.9</v>
       </c>
       <c r="Q149">
-        <v>198</v>
+        <v>972.4</v>
       </c>
       <c r="R149">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18">
+        <v>10.56</v>
+      </c>
+      <c r="S149" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
       <c r="A150" t="s">
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C150" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D150" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9240,7 +9264,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>400.85</v>
+        <v>421.9</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9252,27 +9276,27 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>-68.40000000000001</v>
+        <v>436.8</v>
       </c>
       <c r="Q150">
-        <v>-68.40000000000001</v>
+        <v>436.8</v>
       </c>
       <c r="R150">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19">
       <c r="A151" t="s">
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C151" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D151" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9290,7 +9314,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4230.6</v>
+        <v>4492.5</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9302,27 +9326,27 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>-31</v>
+        <v>492.8</v>
       </c>
       <c r="Q151">
-        <v>-31</v>
+        <v>492.8</v>
       </c>
       <c r="R151">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19">
       <c r="A152" t="s">
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C152" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D152" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9340,7 +9364,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>368.85</v>
+        <v>374.15</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9352,27 +9376,27 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>74.25</v>
+        <v>217.35</v>
       </c>
       <c r="Q152">
-        <v>74.25</v>
+        <v>217.35</v>
       </c>
       <c r="R152">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19">
       <c r="A153" t="s">
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C153" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D153" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9390,7 +9414,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1029.15</v>
+        <v>1075.15</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9402,27 +9426,27 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="R153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19">
       <c r="A154" t="s">
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C154" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D154" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9440,7 +9464,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2110.6</v>
+        <v>2145.6</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9452,27 +9476,27 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="R154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19">
       <c r="A155" t="s">
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C155" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D155" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9490,7 +9514,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1234.1</v>
+        <v>1246.4</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9502,12 +9526,262 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19">
+      <c r="A156" t="s">
+        <v>70</v>
+      </c>
+      <c r="B156" t="s">
+        <v>80</v>
+      </c>
+      <c r="C156" t="s">
+        <v>151</v>
+      </c>
+      <c r="D156" t="s">
+        <v>153</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>204.18</v>
+      </c>
+      <c r="G156">
+        <v>48</v>
+      </c>
+      <c r="H156">
+        <v>48</v>
+      </c>
+      <c r="I156">
+        <v>9800.639999999999</v>
+      </c>
+      <c r="J156">
+        <v>204.18</v>
+      </c>
+      <c r="L156">
+        <v>193.97</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
+      <c r="A157" t="s">
+        <v>70</v>
+      </c>
+      <c r="B157" t="s">
+        <v>148</v>
+      </c>
+      <c r="C157" t="s">
+        <v>149</v>
+      </c>
+      <c r="D157" t="s">
+        <v>153</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>1907</v>
+      </c>
+      <c r="G157">
+        <v>5</v>
+      </c>
+      <c r="H157">
+        <v>5</v>
+      </c>
+      <c r="I157">
+        <v>9535</v>
+      </c>
+      <c r="J157">
+        <v>1907</v>
+      </c>
+      <c r="L157">
+        <v>1811.65</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>0</v>
+      </c>
+      <c r="R157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
+      <c r="A158" t="s">
+        <v>70</v>
+      </c>
+      <c r="B158" t="s">
+        <v>72</v>
+      </c>
+      <c r="C158" t="s">
+        <v>151</v>
+      </c>
+      <c r="D158" t="s">
+        <v>153</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>1333</v>
+      </c>
+      <c r="G158">
+        <v>7</v>
+      </c>
+      <c r="H158">
+        <v>7</v>
+      </c>
+      <c r="I158">
+        <v>9331</v>
+      </c>
+      <c r="J158">
+        <v>1333</v>
+      </c>
+      <c r="L158">
+        <v>1266.35</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="Q158">
+        <v>0</v>
+      </c>
+      <c r="R158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
+      <c r="A159" t="s">
+        <v>70</v>
+      </c>
+      <c r="B159" t="s">
+        <v>140</v>
+      </c>
+      <c r="C159" t="s">
+        <v>151</v>
+      </c>
+      <c r="D159" t="s">
+        <v>153</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="F159">
+        <v>967.8</v>
+      </c>
+      <c r="G159">
+        <v>10</v>
+      </c>
+      <c r="H159">
+        <v>10</v>
+      </c>
+      <c r="I159">
+        <v>9678</v>
+      </c>
+      <c r="J159">
+        <v>967.8</v>
+      </c>
+      <c r="L159">
+        <v>919.41</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="Q159">
+        <v>0</v>
+      </c>
+      <c r="R159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
+      <c r="A160" t="s">
+        <v>70</v>
+      </c>
+      <c r="B160" t="s">
+        <v>83</v>
+      </c>
+      <c r="C160" t="s">
+        <v>149</v>
+      </c>
+      <c r="D160" t="s">
+        <v>153</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>541.6</v>
+      </c>
+      <c r="G160">
+        <v>18</v>
+      </c>
+      <c r="H160">
+        <v>18</v>
+      </c>
+      <c r="I160">
+        <v>9748.800000000001</v>
+      </c>
+      <c r="J160">
+        <v>541.6</v>
+      </c>
+      <c r="L160">
+        <v>514.52</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+      <c r="Q160">
+        <v>0</v>
+      </c>
+      <c r="R160">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="167">
   <si>
     <t>Buy Date</t>
   </si>
@@ -229,6 +229,9 @@
     <t>2026-04-08</t>
   </si>
   <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -461,6 +464,9 @@
   </si>
   <si>
     <t>COLPAL</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -872,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S160"/>
+  <dimension ref="A1:S164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -949,13 +955,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -985,7 +991,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1005,13 +1011,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1041,7 +1047,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1064,13 +1070,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1100,7 +1106,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1120,13 +1126,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1156,7 +1162,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1176,13 +1182,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1212,7 +1218,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1232,13 +1238,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1268,7 +1274,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1288,13 +1294,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1324,7 +1330,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1344,13 +1350,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1380,7 +1386,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1400,13 +1406,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1436,7 +1442,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1456,13 +1462,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1483,7 +1489,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1492,7 +1498,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1507,7 +1513,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1515,13 +1521,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1551,7 +1557,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1574,13 +1580,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1610,7 +1616,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1630,13 +1636,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1666,7 +1672,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1686,13 +1692,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1722,7 +1728,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1742,13 +1748,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1778,7 +1784,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1798,13 +1804,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1834,7 +1840,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1854,13 +1860,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1890,7 +1896,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1910,13 +1916,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1946,7 +1952,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1966,13 +1972,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2002,7 +2008,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2022,13 +2028,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2049,7 +2055,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2058,7 +2064,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2078,13 +2084,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2105,7 +2111,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2114,7 +2120,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2134,13 +2140,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2170,7 +2176,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2190,13 +2196,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2226,7 +2232,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2246,13 +2252,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2282,7 +2288,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2302,13 +2308,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2329,7 +2335,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2338,7 +2344,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2358,13 +2364,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2394,7 +2400,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2414,13 +2420,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2450,7 +2456,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2470,13 +2476,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2506,7 +2512,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2526,13 +2532,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2562,7 +2568,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2582,13 +2588,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2609,7 +2615,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2618,7 +2624,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2638,13 +2644,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2674,7 +2680,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2694,13 +2700,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2730,7 +2736,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2750,13 +2756,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2777,7 +2783,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2786,7 +2792,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2806,13 +2812,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2833,7 +2839,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2842,7 +2848,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2862,13 +2868,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2898,7 +2904,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2918,13 +2924,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2954,7 +2960,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2974,13 +2980,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3010,7 +3016,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3033,13 +3039,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3069,7 +3075,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3089,13 +3095,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3125,7 +3131,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3145,13 +3151,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3181,7 +3187,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3201,13 +3207,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3228,7 +3234,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3237,7 +3243,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3257,13 +3263,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3284,7 +3290,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3293,7 +3299,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3313,13 +3319,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3349,7 +3355,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3369,13 +3375,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3405,7 +3411,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3425,13 +3431,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3461,7 +3467,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3484,13 +3490,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3520,7 +3526,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3540,13 +3546,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3576,7 +3582,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3596,13 +3602,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3632,7 +3638,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3655,13 +3661,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3691,7 +3697,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3711,13 +3717,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3747,7 +3753,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3767,13 +3773,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3803,7 +3809,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3826,13 +3832,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3862,7 +3868,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3882,13 +3888,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3918,7 +3924,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3941,13 +3947,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3977,7 +3983,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4000,13 +4006,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4036,7 +4042,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4056,13 +4062,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4083,7 +4089,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4092,7 +4098,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4112,13 +4118,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4148,7 +4154,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4168,13 +4174,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4204,7 +4210,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4227,13 +4233,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4263,7 +4269,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4283,13 +4289,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4319,7 +4325,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4342,13 +4348,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4378,7 +4384,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4393,7 +4399,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4401,13 +4407,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4437,7 +4443,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4457,13 +4463,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4493,7 +4499,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4513,13 +4519,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4549,7 +4555,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4569,13 +4575,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4605,7 +4611,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4625,13 +4631,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4661,7 +4667,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4681,13 +4687,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D68" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4717,7 +4723,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4737,13 +4743,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D69" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4764,7 +4770,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4773,7 +4779,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4793,13 +4799,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4829,7 +4835,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4849,13 +4855,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D71" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4885,7 +4891,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4905,13 +4911,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D72" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4941,7 +4947,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4961,13 +4967,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4997,7 +5003,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5017,13 +5023,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5053,7 +5059,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5073,13 +5079,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5109,7 +5115,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5129,13 +5135,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D76" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5165,7 +5171,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5185,13 +5191,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5221,7 +5227,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5241,13 +5247,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D78" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5277,7 +5283,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5297,13 +5303,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5333,7 +5339,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5353,13 +5359,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C80" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5389,7 +5395,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5409,13 +5415,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C81" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D81" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5445,7 +5451,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5465,13 +5471,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D82" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5501,7 +5507,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5524,13 +5530,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D83" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5560,7 +5566,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5580,13 +5586,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C84" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D84" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5616,7 +5622,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5636,13 +5642,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D85" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5672,7 +5678,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5692,13 +5698,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C86" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D86" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5728,7 +5734,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5748,13 +5754,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5784,7 +5790,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5804,13 +5810,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D88" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5840,7 +5846,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5860,13 +5866,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C89" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D89" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5896,7 +5902,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5916,13 +5922,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D90" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5952,7 +5958,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5972,13 +5978,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5996,7 +6002,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>294.85</v>
+        <v>298.1</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6008,13 +6014,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>6.6</v>
+        <v>113.85</v>
       </c>
       <c r="Q91">
-        <v>6.6</v>
+        <v>113.85</v>
       </c>
       <c r="R91">
-        <v>0.07000000000000001</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6022,13 +6028,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D92" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6058,7 +6064,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6078,13 +6084,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D93" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6114,7 +6120,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6134,13 +6140,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D94" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6170,7 +6176,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6190,13 +6196,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D95" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6226,7 +6232,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6246,13 +6252,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D96" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6282,7 +6288,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6302,13 +6308,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C97" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D97" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6338,7 +6344,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6358,13 +6364,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D98" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6394,7 +6400,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6417,13 +6423,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D99" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6453,7 +6459,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6473,13 +6479,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D100" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6509,7 +6515,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6529,13 +6535,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C101" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6565,7 +6571,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6585,13 +6591,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C102" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6621,7 +6627,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6641,13 +6647,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C103" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6677,7 +6683,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6697,13 +6703,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C104" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D104" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6733,7 +6739,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6753,13 +6759,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D105" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6789,7 +6795,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6809,13 +6815,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D106" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6836,7 +6842,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6845,7 +6851,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6865,13 +6871,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C107" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D107" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6901,7 +6907,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6921,13 +6927,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C108" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D108" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6957,7 +6963,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6977,13 +6983,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C109" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D109" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7004,7 +7010,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7013,7 +7019,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7033,13 +7039,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C110" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D110" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7069,7 +7075,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7089,13 +7095,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C111" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D111" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7125,7 +7131,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7145,13 +7151,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C112" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D112" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7181,7 +7187,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7201,13 +7207,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D113" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7237,7 +7243,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7257,13 +7263,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D114" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7293,7 +7299,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7313,13 +7319,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D115" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7349,7 +7355,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7369,13 +7375,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D116" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7405,7 +7411,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7425,13 +7431,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C117" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D117" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7461,7 +7467,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7481,13 +7487,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7505,7 +7511,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1213.1</v>
+        <v>1199.6</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7517,13 +7523,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>552</v>
+        <v>444</v>
       </c>
       <c r="Q118">
-        <v>552</v>
+        <v>444</v>
       </c>
       <c r="R118">
-        <v>6.03</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7531,13 +7537,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D119" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7567,7 +7573,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7587,13 +7593,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D120" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7623,7 +7629,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7643,13 +7649,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C121" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D121" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7679,7 +7685,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7699,13 +7705,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C122" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D122" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7735,7 +7741,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7755,13 +7761,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D123" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7782,7 +7788,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7791,7 +7797,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7811,13 +7817,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D124" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7847,7 +7853,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7867,13 +7873,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D125" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7903,7 +7909,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7923,13 +7929,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D126" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -7947,7 +7953,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>169.31</v>
+        <v>172.33</v>
       </c>
       <c r="L126">
         <v>164.02</v>
@@ -7959,13 +7965,13 @@
         <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>363.6</v>
+        <v>417.96</v>
       </c>
       <c r="Q126">
-        <v>1213.53</v>
+        <v>1267.89</v>
       </c>
       <c r="R126">
-        <v>12.15</v>
+        <v>12.69</v>
       </c>
       <c r="S126" t="s">
         <v>70</v>
@@ -7976,13 +7982,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C127" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D127" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8012,7 +8018,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8032,13 +8038,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C128" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D128" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8068,7 +8074,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8091,13 +8097,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C129" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D129" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8127,7 +8133,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8147,13 +8153,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C130" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D130" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8183,7 +8189,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8203,13 +8209,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D131" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8239,7 +8245,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8259,13 +8265,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C132" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D132" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8295,7 +8301,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8315,13 +8321,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C133" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D133" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8342,7 +8348,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8351,7 +8357,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8371,13 +8377,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C134" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D134" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8407,7 +8413,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8427,13 +8433,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C135" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D135" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8463,7 +8469,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8483,13 +8489,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D136" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8507,7 +8513,7 @@
         <v>9992.4</v>
       </c>
       <c r="J136">
-        <v>449.25</v>
+        <v>454.1</v>
       </c>
       <c r="L136">
         <v>431.49</v>
@@ -8519,13 +8525,13 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>-108.9</v>
+        <v>-2.2</v>
       </c>
       <c r="Q136">
-        <v>-108.9</v>
+        <v>-2.2</v>
       </c>
       <c r="R136">
-        <v>-1.09</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8533,13 +8539,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C137" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D137" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8569,7 +8575,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8592,13 +8598,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C138" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8628,7 +8634,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8648,13 +8654,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C139" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8684,7 +8690,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8704,13 +8710,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8740,7 +8746,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8760,13 +8766,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D141" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8796,7 +8802,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8816,13 +8822,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C142" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D142" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8852,7 +8858,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8872,13 +8878,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C143" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D143" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -8896,7 +8902,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6565</v>
+        <v>6614</v>
       </c>
       <c r="L143">
         <v>5901.88</v>
@@ -8908,13 +8914,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>352.5</v>
+        <v>401.5</v>
       </c>
       <c r="Q143">
-        <v>352.5</v>
+        <v>401.5</v>
       </c>
       <c r="R143">
-        <v>5.67</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8922,13 +8928,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C144" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D144" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8958,7 +8964,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8978,13 +8984,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C145" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D145" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9014,7 +9020,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9034,13 +9040,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D146" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E146">
         <v>2</v>
@@ -9058,7 +9064,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3226.1</v>
+        <v>3222.5</v>
       </c>
       <c r="L146">
         <v>3081.75</v>
@@ -9070,13 +9076,13 @@
         <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>582.2</v>
+        <v>575</v>
       </c>
       <c r="Q146">
-        <v>875.7</v>
+        <v>868.5</v>
       </c>
       <c r="R146">
-        <v>9.949999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S146" t="s">
         <v>70</v>
@@ -9087,13 +9093,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C147" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D147" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9111,7 +9117,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>835.95</v>
+        <v>814.55</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9123,13 +9129,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>603.6</v>
+        <v>346.8</v>
       </c>
       <c r="Q147">
-        <v>603.6</v>
+        <v>346.8</v>
       </c>
       <c r="R147">
-        <v>6.4</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9137,16 +9143,16 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C148" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D148" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148">
         <v>322.1</v>
@@ -9161,10 +9167,10 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>342.65</v>
+        <v>346.8</v>
       </c>
       <c r="L148">
-        <v>306</v>
+        <v>322.1</v>
       </c>
       <c r="M148">
         <v>0</v>
@@ -9173,13 +9179,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>637.05</v>
+        <v>765.7</v>
       </c>
       <c r="Q148">
-        <v>637.05</v>
+        <v>765.7</v>
       </c>
       <c r="R148">
-        <v>6.38</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -9187,13 +9193,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C149" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D149" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -9211,7 +9217,7 @@
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>2043.8</v>
+        <v>2040.5</v>
       </c>
       <c r="L149">
         <v>1934.62</v>
@@ -9223,13 +9229,13 @@
         <v>368.5000000000005</v>
       </c>
       <c r="P149">
-        <v>603.9</v>
+        <v>594</v>
       </c>
       <c r="Q149">
-        <v>972.4</v>
+        <v>962.5</v>
       </c>
       <c r="R149">
-        <v>10.56</v>
+        <v>10.45</v>
       </c>
       <c r="S149" t="s">
         <v>70</v>
@@ -9240,13 +9246,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C150" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D150" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9264,7 +9270,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>421.9</v>
+        <v>422.9</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9276,13 +9282,13 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>436.8</v>
+        <v>460.8</v>
       </c>
       <c r="Q150">
-        <v>436.8</v>
+        <v>460.8</v>
       </c>
       <c r="R150">
-        <v>4.51</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -9290,13 +9296,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C151" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D151" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9314,7 +9320,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4492.5</v>
+        <v>4439.8</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9326,13 +9332,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>492.8</v>
+        <v>387.4</v>
       </c>
       <c r="Q151">
-        <v>492.8</v>
+        <v>387.4</v>
       </c>
       <c r="R151">
-        <v>5.8</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -9340,13 +9346,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C152" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9364,7 +9370,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>374.15</v>
+        <v>378.65</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9376,13 +9382,13 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>217.35</v>
+        <v>338.85</v>
       </c>
       <c r="Q152">
-        <v>217.35</v>
+        <v>338.85</v>
       </c>
       <c r="R152">
-        <v>2.2</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9390,13 +9396,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C153" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D153" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9414,7 +9420,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1075.15</v>
+        <v>1063.35</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9426,13 +9432,13 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>414</v>
+        <v>307.8</v>
       </c>
       <c r="Q153">
-        <v>414</v>
+        <v>307.8</v>
       </c>
       <c r="R153">
-        <v>4.47</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -9440,13 +9446,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C154" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9464,7 +9470,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2145.6</v>
+        <v>2133.2</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9476,13 +9482,13 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>140</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q154">
-        <v>140</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="R154">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9490,13 +9496,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C155" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9514,7 +9520,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1246.4</v>
+        <v>1257</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9526,13 +9532,13 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>98.40000000000001</v>
+        <v>183.2</v>
       </c>
       <c r="Q155">
-        <v>98.40000000000001</v>
+        <v>183.2</v>
       </c>
       <c r="R155">
-        <v>1</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -9540,13 +9546,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C156" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D156" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -9564,7 +9570,7 @@
         <v>9800.639999999999</v>
       </c>
       <c r="J156">
-        <v>204.18</v>
+        <v>205.2</v>
       </c>
       <c r="L156">
         <v>193.97</v>
@@ -9576,13 +9582,13 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>48.96</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>48.96</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9590,13 +9596,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C157" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D157" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -9614,7 +9620,7 @@
         <v>9535</v>
       </c>
       <c r="J157">
-        <v>1907</v>
+        <v>1906.7</v>
       </c>
       <c r="L157">
         <v>1811.65</v>
@@ -9626,13 +9632,13 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -9640,13 +9646,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C158" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -9664,7 +9670,7 @@
         <v>9331</v>
       </c>
       <c r="J158">
-        <v>1333</v>
+        <v>1318.5</v>
       </c>
       <c r="L158">
         <v>1266.35</v>
@@ -9676,13 +9682,13 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>-101.5</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -9690,13 +9696,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C159" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -9714,7 +9720,7 @@
         <v>9678</v>
       </c>
       <c r="J159">
-        <v>967.8</v>
+        <v>963</v>
       </c>
       <c r="L159">
         <v>919.41</v>
@@ -9726,13 +9732,13 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -9740,13 +9746,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C160" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D160" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -9761,10 +9767,10 @@
         <v>18</v>
       </c>
       <c r="I160">
-        <v>9748.800000000001</v>
+        <v>9748.799999999999</v>
       </c>
       <c r="J160">
-        <v>541.6</v>
+        <v>541.95</v>
       </c>
       <c r="L160">
         <v>514.52</v>
@@ -9776,12 +9782,212 @@
         <v>0</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R160">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18">
+      <c r="A161" t="s">
+        <v>71</v>
+      </c>
+      <c r="B161" t="s">
+        <v>135</v>
+      </c>
+      <c r="C161" t="s">
+        <v>153</v>
+      </c>
+      <c r="D161" t="s">
+        <v>155</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161">
+        <v>428.05</v>
+      </c>
+      <c r="G161">
+        <v>23</v>
+      </c>
+      <c r="H161">
+        <v>23</v>
+      </c>
+      <c r="I161">
+        <v>9845.15</v>
+      </c>
+      <c r="J161">
+        <v>428.05</v>
+      </c>
+      <c r="L161">
+        <v>406.65</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+      <c r="Q161">
+        <v>0</v>
+      </c>
+      <c r="R161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18">
+      <c r="A162" t="s">
+        <v>71</v>
+      </c>
+      <c r="B162" t="s">
+        <v>87</v>
+      </c>
+      <c r="C162" t="s">
+        <v>153</v>
+      </c>
+      <c r="D162" t="s">
+        <v>155</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>9517</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162">
+        <v>9517</v>
+      </c>
+      <c r="J162">
+        <v>9517</v>
+      </c>
+      <c r="L162">
+        <v>9041.15</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>0</v>
+      </c>
+      <c r="R162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18">
+      <c r="A163" t="s">
+        <v>71</v>
+      </c>
+      <c r="B163" t="s">
+        <v>88</v>
+      </c>
+      <c r="C163" t="s">
+        <v>153</v>
+      </c>
+      <c r="D163" t="s">
+        <v>155</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>277.2</v>
+      </c>
+      <c r="G163">
+        <v>36</v>
+      </c>
+      <c r="H163">
+        <v>36</v>
+      </c>
+      <c r="I163">
+        <v>9979.199999999999</v>
+      </c>
+      <c r="J163">
+        <v>277.2</v>
+      </c>
+      <c r="L163">
+        <v>263.34</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163">
+        <v>0</v>
+      </c>
+      <c r="R163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18">
+      <c r="A164" t="s">
+        <v>71</v>
+      </c>
+      <c r="B164" t="s">
+        <v>150</v>
+      </c>
+      <c r="C164" t="s">
+        <v>153</v>
+      </c>
+      <c r="D164" t="s">
+        <v>155</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="F164">
+        <v>1209.7</v>
+      </c>
+      <c r="G164">
+        <v>8</v>
+      </c>
+      <c r="H164">
+        <v>8</v>
+      </c>
+      <c r="I164">
+        <v>9677.6</v>
+      </c>
+      <c r="J164">
+        <v>1209.7</v>
+      </c>
+      <c r="L164">
+        <v>1149.21</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>0</v>
+      </c>
+      <c r="R164">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="169">
   <si>
     <t>Buy Date</t>
   </si>
@@ -232,6 +232,9 @@
     <t>2026-04-09</t>
   </si>
   <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -467,6 +470,9 @@
   </si>
   <si>
     <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -878,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S164"/>
+  <dimension ref="A1:S167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -955,13 +961,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -991,7 +997,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1011,13 +1017,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1047,7 +1053,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1070,13 +1076,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1106,7 +1112,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1126,13 +1132,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1162,7 +1168,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1182,13 +1188,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1218,7 +1224,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1238,13 +1244,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1274,7 +1280,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1294,13 +1300,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1330,7 +1336,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1350,13 +1356,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1386,7 +1392,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1406,13 +1412,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1442,7 +1448,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1462,13 +1468,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1489,7 +1495,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1498,7 +1504,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1513,7 +1519,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1521,13 +1527,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1557,7 +1563,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1580,13 +1586,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1616,7 +1622,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1636,13 +1642,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1672,7 +1678,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1692,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1728,7 +1734,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1748,13 +1754,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1784,7 +1790,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1804,13 +1810,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1840,7 +1846,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1860,13 +1866,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1896,7 +1902,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1916,13 +1922,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1952,7 +1958,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1972,13 +1978,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2008,7 +2014,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2028,13 +2034,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2055,7 +2061,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2064,7 +2070,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2084,13 +2090,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2111,7 +2117,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2120,7 +2126,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2140,13 +2146,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2176,7 +2182,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2196,13 +2202,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2232,7 +2238,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2252,13 +2258,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2288,7 +2294,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2308,13 +2314,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2335,7 +2341,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2344,7 +2350,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2364,13 +2370,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2400,7 +2406,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2420,13 +2426,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2456,7 +2462,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2476,13 +2482,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2512,7 +2518,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2532,13 +2538,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2568,7 +2574,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2588,13 +2594,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2615,7 +2621,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2624,7 +2630,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2644,13 +2650,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2680,7 +2686,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2700,13 +2706,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2736,7 +2742,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2756,13 +2762,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2783,7 +2789,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2792,7 +2798,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2812,13 +2818,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2839,7 +2845,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2848,7 +2854,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2868,13 +2874,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2904,7 +2910,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2924,13 +2930,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2960,7 +2966,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2980,13 +2986,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3016,7 +3022,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3039,13 +3045,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3075,7 +3081,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3095,13 +3101,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3131,7 +3137,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3151,13 +3157,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3187,7 +3193,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3207,13 +3213,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3234,7 +3240,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3243,7 +3249,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3263,13 +3269,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3290,7 +3296,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3299,7 +3305,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3319,13 +3325,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3355,7 +3361,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3375,13 +3381,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3411,7 +3417,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3431,13 +3437,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3467,7 +3473,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3490,13 +3496,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3526,7 +3532,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3546,13 +3552,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3582,7 +3588,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3602,13 +3608,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3638,7 +3644,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3661,13 +3667,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3697,7 +3703,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3717,13 +3723,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3753,7 +3759,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3773,13 +3779,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3809,7 +3815,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3832,13 +3838,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3868,7 +3874,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3888,13 +3894,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D54" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3924,7 +3930,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3947,13 +3953,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3983,7 +3989,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4006,13 +4012,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4042,7 +4048,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4062,13 +4068,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D57" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4089,7 +4095,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4098,7 +4104,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4118,13 +4124,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D58" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4154,7 +4160,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4174,13 +4180,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4210,7 +4216,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4233,13 +4239,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D60" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4269,7 +4275,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4289,13 +4295,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4325,7 +4331,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4348,13 +4354,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C62" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D62" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4384,7 +4390,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4399,7 +4405,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4407,13 +4413,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C63" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D63" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4443,7 +4449,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4463,13 +4469,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4499,7 +4505,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4519,13 +4525,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4555,7 +4561,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4575,13 +4581,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C66" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4611,7 +4617,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4631,13 +4637,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C67" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4667,7 +4673,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4687,13 +4693,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4723,7 +4729,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4743,13 +4749,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4770,7 +4776,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4779,7 +4785,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4799,13 +4805,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D70" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4835,7 +4841,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4855,13 +4861,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D71" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4891,7 +4897,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4911,13 +4917,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4947,7 +4953,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4967,13 +4973,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D73" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5003,7 +5009,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5023,13 +5029,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D74" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5059,7 +5065,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5079,13 +5085,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5115,7 +5121,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5135,13 +5141,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C76" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D76" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5171,7 +5177,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5191,13 +5197,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D77" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5227,7 +5233,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5247,13 +5253,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5283,7 +5289,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5303,13 +5309,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5339,7 +5345,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5359,13 +5365,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5395,7 +5401,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5415,13 +5421,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C81" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5451,7 +5457,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5471,13 +5477,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D82" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5507,7 +5513,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5530,13 +5536,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5566,7 +5572,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5586,13 +5592,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5622,7 +5628,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5642,13 +5648,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5678,7 +5684,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5698,13 +5704,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C86" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D86" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5734,7 +5740,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5754,13 +5760,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5790,7 +5796,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5810,13 +5816,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C88" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D88" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5846,7 +5852,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5866,13 +5872,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5902,7 +5908,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5922,13 +5928,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D90" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5958,7 +5964,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5978,13 +5984,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D91" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -6002,7 +6008,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>298.1</v>
+        <v>302.75</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6014,13 +6020,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>113.85</v>
+        <v>267.3</v>
       </c>
       <c r="Q91">
-        <v>113.85</v>
+        <v>267.3</v>
       </c>
       <c r="R91">
-        <v>1.17</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6028,13 +6034,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6064,7 +6070,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6084,13 +6090,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6120,7 +6126,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6140,13 +6146,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C94" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D94" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6176,7 +6182,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6196,13 +6202,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D95" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6232,7 +6238,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6252,13 +6258,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C96" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D96" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6288,7 +6294,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6308,13 +6314,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C97" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D97" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6344,7 +6350,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6364,13 +6370,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6400,7 +6406,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6423,13 +6429,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C99" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D99" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6459,7 +6465,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6479,13 +6485,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C100" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6515,7 +6521,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6535,13 +6541,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C101" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D101" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6571,7 +6577,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6591,13 +6597,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D102" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6627,7 +6633,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6647,13 +6653,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6683,7 +6689,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6703,13 +6709,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6739,7 +6745,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6759,13 +6765,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6795,7 +6801,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6815,13 +6821,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D106" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6842,7 +6848,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6851,7 +6857,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6871,13 +6877,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C107" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D107" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6907,7 +6913,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6927,13 +6933,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C108" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D108" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6963,7 +6969,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6983,13 +6989,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D109" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7010,7 +7016,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7019,7 +7025,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7039,13 +7045,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7075,7 +7081,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7095,13 +7101,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C111" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D111" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7131,7 +7137,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7151,13 +7157,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C112" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D112" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7187,7 +7193,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7207,13 +7213,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C113" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7243,7 +7249,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7263,13 +7269,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C114" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D114" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7299,7 +7305,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7319,13 +7325,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C115" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D115" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7355,7 +7361,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7375,13 +7381,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C116" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7411,7 +7417,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7431,13 +7437,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7467,7 +7473,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7487,13 +7493,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C118" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D118" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7511,7 +7517,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1199.6</v>
+        <v>1219.2</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7523,13 +7529,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>444</v>
+        <v>600.8</v>
       </c>
       <c r="Q118">
-        <v>444</v>
+        <v>600.8</v>
       </c>
       <c r="R118">
-        <v>4.85</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7537,13 +7543,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C119" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7573,7 +7579,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7593,13 +7599,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C120" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7629,7 +7635,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7649,13 +7655,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D121" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7685,7 +7691,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7705,13 +7711,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C122" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D122" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7741,7 +7747,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7761,13 +7767,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C123" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D123" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7788,7 +7794,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7797,7 +7803,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7817,13 +7823,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C124" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D124" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7853,7 +7859,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7873,13 +7879,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C125" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D125" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7909,7 +7915,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7929,13 +7935,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D126" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -7953,7 +7959,7 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>172.33</v>
+        <v>175.81</v>
       </c>
       <c r="L126">
         <v>164.02</v>
@@ -7965,13 +7971,13 @@
         <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>417.96</v>
+        <v>480.6</v>
       </c>
       <c r="Q126">
-        <v>1267.89</v>
+        <v>1330.53</v>
       </c>
       <c r="R126">
-        <v>12.69</v>
+        <v>13.32</v>
       </c>
       <c r="S126" t="s">
         <v>70</v>
@@ -7982,13 +7988,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C127" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D127" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8018,7 +8024,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8038,13 +8044,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C128" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D128" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8074,7 +8080,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8097,13 +8103,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D129" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8133,7 +8139,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8153,13 +8159,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8189,7 +8195,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8209,13 +8215,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C131" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D131" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8245,7 +8251,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8265,13 +8271,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D132" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8301,7 +8307,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8321,13 +8327,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C133" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D133" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8348,7 +8354,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8357,7 +8363,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8377,13 +8383,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D134" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8413,7 +8419,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8433,13 +8439,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C135" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D135" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8469,7 +8475,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8489,13 +8495,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C136" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D136" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8507,7 +8513,7 @@
         <v>22</v>
       </c>
       <c r="H136">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>9992.4</v>
@@ -8515,23 +8521,29 @@
       <c r="J136">
         <v>454.1</v>
       </c>
+      <c r="K136" t="s">
+        <v>72</v>
+      </c>
       <c r="L136">
         <v>431.49</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>431.49</v>
+      </c>
+      <c r="N136" t="s">
+        <v>166</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>-499.6199999999995</v>
       </c>
       <c r="P136">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="Q136">
-        <v>-2.2</v>
+        <v>-499.6199999999995</v>
       </c>
       <c r="R136">
-        <v>-0.02</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8539,13 +8551,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C137" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D137" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8575,7 +8587,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8598,13 +8610,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C138" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8634,7 +8646,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8654,13 +8666,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C139" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D139" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8690,7 +8702,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8710,13 +8722,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D140" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8746,7 +8758,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8766,13 +8778,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C141" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D141" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8802,7 +8814,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8822,13 +8834,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C142" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8858,7 +8870,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8878,16 +8890,16 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C143" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F143">
         <v>6212.5</v>
@@ -8902,10 +8914,10 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6614</v>
+        <v>6859.5</v>
       </c>
       <c r="L143">
-        <v>5901.88</v>
+        <v>6523.12</v>
       </c>
       <c r="M143">
         <v>0</v>
@@ -8914,13 +8926,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>401.5</v>
+        <v>647</v>
       </c>
       <c r="Q143">
-        <v>401.5</v>
+        <v>647</v>
       </c>
       <c r="R143">
-        <v>6.46</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8928,13 +8940,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C144" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D144" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8964,7 +8976,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8984,13 +8996,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D145" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9020,7 +9032,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9040,16 +9052,16 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C146" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D146" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146">
         <v>2935</v>
@@ -9064,10 +9076,10 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3222.5</v>
+        <v>3388.5</v>
       </c>
       <c r="L146">
-        <v>3081.75</v>
+        <v>3228.5</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -9076,13 +9088,13 @@
         <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>575</v>
+        <v>907</v>
       </c>
       <c r="Q146">
-        <v>868.5</v>
+        <v>1200.5</v>
       </c>
       <c r="R146">
-        <v>9.859999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="S146" t="s">
         <v>70</v>
@@ -9093,13 +9105,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C147" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D147" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -9117,7 +9129,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>814.55</v>
+        <v>830.9</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9129,13 +9141,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>346.8</v>
+        <v>543</v>
       </c>
       <c r="Q147">
-        <v>346.8</v>
+        <v>543</v>
       </c>
       <c r="R147">
-        <v>3.68</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9143,13 +9155,13 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C148" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D148" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -9167,7 +9179,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>346.8</v>
+        <v>349.8</v>
       </c>
       <c r="L148">
         <v>322.1</v>
@@ -9179,13 +9191,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>765.7</v>
+        <v>858.7</v>
       </c>
       <c r="Q148">
-        <v>765.7</v>
+        <v>858.7</v>
       </c>
       <c r="R148">
-        <v>7.67</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -9193,13 +9205,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C149" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D149" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E149">
         <v>2</v>
@@ -9217,7 +9229,7 @@
         <v>9212.5</v>
       </c>
       <c r="J149">
-        <v>2040.5</v>
+        <v>2086.8</v>
       </c>
       <c r="L149">
         <v>1934.62</v>
@@ -9229,13 +9241,13 @@
         <v>368.5000000000005</v>
       </c>
       <c r="P149">
-        <v>594</v>
+        <v>732.9</v>
       </c>
       <c r="Q149">
-        <v>962.5</v>
+        <v>1101.4</v>
       </c>
       <c r="R149">
-        <v>10.45</v>
+        <v>11.96</v>
       </c>
       <c r="S149" t="s">
         <v>70</v>
@@ -9246,13 +9258,13 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C150" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D150" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -9270,7 +9282,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>422.9</v>
+        <v>431.6</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9282,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>460.8</v>
+        <v>669.6</v>
       </c>
       <c r="Q150">
-        <v>460.8</v>
+        <v>669.6</v>
       </c>
       <c r="R150">
-        <v>4.76</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -9296,13 +9308,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D151" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9320,7 +9332,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4439.8</v>
+        <v>4505</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9332,13 +9344,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>387.4</v>
+        <v>517.8</v>
       </c>
       <c r="Q151">
-        <v>387.4</v>
+        <v>517.8</v>
       </c>
       <c r="R151">
-        <v>4.56</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -9346,13 +9358,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C152" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D152" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9370,7 +9382,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>378.65</v>
+        <v>380.15</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9382,13 +9394,13 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>338.85</v>
+        <v>379.35</v>
       </c>
       <c r="Q152">
-        <v>338.85</v>
+        <v>379.35</v>
       </c>
       <c r="R152">
-        <v>3.43</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9396,13 +9408,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C153" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D153" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9420,7 +9432,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1063.35</v>
+        <v>1078.1</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9432,13 +9444,13 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>307.8</v>
+        <v>440.55</v>
       </c>
       <c r="Q153">
-        <v>307.8</v>
+        <v>440.55</v>
       </c>
       <c r="R153">
-        <v>3.32</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -9446,13 +9458,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C154" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D154" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9470,7 +9482,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2133.2</v>
+        <v>2155.3</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9482,13 +9494,13 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>90.40000000000001</v>
+        <v>178.8</v>
       </c>
       <c r="Q154">
-        <v>90.40000000000001</v>
+        <v>178.8</v>
       </c>
       <c r="R154">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9496,13 +9508,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C155" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D155" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9520,7 +9532,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1257</v>
+        <v>1281.7</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9532,13 +9544,13 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>183.2</v>
+        <v>380.8</v>
       </c>
       <c r="Q155">
-        <v>183.2</v>
+        <v>380.8</v>
       </c>
       <c r="R155">
-        <v>1.86</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -9546,13 +9558,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C156" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D156" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -9570,7 +9582,7 @@
         <v>9800.639999999999</v>
       </c>
       <c r="J156">
-        <v>205.2</v>
+        <v>206.61</v>
       </c>
       <c r="L156">
         <v>193.97</v>
@@ -9582,13 +9594,13 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>48.96</v>
+        <v>116.64</v>
       </c>
       <c r="Q156">
-        <v>48.96</v>
+        <v>116.64</v>
       </c>
       <c r="R156">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9596,13 +9608,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C157" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D157" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -9620,7 +9632,7 @@
         <v>9535</v>
       </c>
       <c r="J157">
-        <v>1906.7</v>
+        <v>1939.1</v>
       </c>
       <c r="L157">
         <v>1811.65</v>
@@ -9632,13 +9644,13 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>-1.5</v>
+        <v>160.5</v>
       </c>
       <c r="Q157">
-        <v>-1.5</v>
+        <v>160.5</v>
       </c>
       <c r="R157">
-        <v>-0.02</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -9646,13 +9658,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C158" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -9670,7 +9682,7 @@
         <v>9331</v>
       </c>
       <c r="J158">
-        <v>1318.5</v>
+        <v>1350.8</v>
       </c>
       <c r="L158">
         <v>1266.35</v>
@@ -9682,13 +9694,13 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>-101.5</v>
+        <v>124.6</v>
       </c>
       <c r="Q158">
-        <v>-101.5</v>
+        <v>124.6</v>
       </c>
       <c r="R158">
-        <v>-1.09</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -9696,13 +9708,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C159" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D159" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -9720,7 +9732,7 @@
         <v>9678</v>
       </c>
       <c r="J159">
-        <v>963</v>
+        <v>981.8</v>
       </c>
       <c r="L159">
         <v>919.41</v>
@@ -9732,13 +9744,13 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>-48</v>
+        <v>140</v>
       </c>
       <c r="Q159">
-        <v>-48</v>
+        <v>140</v>
       </c>
       <c r="R159">
-        <v>-0.5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -9746,13 +9758,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C160" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D160" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -9770,7 +9782,7 @@
         <v>9748.799999999999</v>
       </c>
       <c r="J160">
-        <v>541.95</v>
+        <v>547</v>
       </c>
       <c r="L160">
         <v>514.52</v>
@@ -9782,13 +9794,13 @@
         <v>0</v>
       </c>
       <c r="P160">
-        <v>6.3</v>
+        <v>97.2</v>
       </c>
       <c r="Q160">
-        <v>6.3</v>
+        <v>97.2</v>
       </c>
       <c r="R160">
-        <v>0.06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:18">
@@ -9796,13 +9808,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C161" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D161" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -9820,7 +9832,7 @@
         <v>9845.15</v>
       </c>
       <c r="J161">
-        <v>428.05</v>
+        <v>434.9</v>
       </c>
       <c r="L161">
         <v>406.65</v>
@@ -9832,13 +9844,13 @@
         <v>0</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>157.55</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>157.55</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="162" spans="1:18">
@@ -9846,13 +9858,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C162" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D162" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -9870,7 +9882,7 @@
         <v>9517</v>
       </c>
       <c r="J162">
-        <v>9517</v>
+        <v>9813.5</v>
       </c>
       <c r="L162">
         <v>9041.15</v>
@@ -9882,13 +9894,13 @@
         <v>0</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>296.5</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>296.5</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="163" spans="1:18">
@@ -9896,13 +9908,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C163" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D163" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -9917,10 +9929,10 @@
         <v>36</v>
       </c>
       <c r="I163">
-        <v>9979.199999999999</v>
+        <v>9979.200000000001</v>
       </c>
       <c r="J163">
-        <v>277.2</v>
+        <v>284.71</v>
       </c>
       <c r="L163">
         <v>263.34</v>
@@ -9932,13 +9944,13 @@
         <v>0</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>270.36</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>270.36</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -9946,13 +9958,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C164" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D164" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -9970,7 +9982,7 @@
         <v>9677.6</v>
       </c>
       <c r="J164">
-        <v>1209.7</v>
+        <v>1214.8</v>
       </c>
       <c r="L164">
         <v>1149.21</v>
@@ -9982,12 +9994,162 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="R164">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18">
+      <c r="A165" t="s">
+        <v>72</v>
+      </c>
+      <c r="B165" t="s">
+        <v>152</v>
+      </c>
+      <c r="C165" t="s">
+        <v>155</v>
+      </c>
+      <c r="D165" t="s">
+        <v>157</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>7424</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <v>7424</v>
+      </c>
+      <c r="J165">
+        <v>7424</v>
+      </c>
+      <c r="L165">
+        <v>7052.8</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>0</v>
+      </c>
+      <c r="R165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18">
+      <c r="A166" t="s">
+        <v>72</v>
+      </c>
+      <c r="B166" t="s">
+        <v>144</v>
+      </c>
+      <c r="C166" t="s">
+        <v>153</v>
+      </c>
+      <c r="D166" t="s">
+        <v>157</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>435.7</v>
+      </c>
+      <c r="G166">
+        <v>22</v>
+      </c>
+      <c r="H166">
+        <v>22</v>
+      </c>
+      <c r="I166">
+        <v>9585.4</v>
+      </c>
+      <c r="J166">
+        <v>435.7</v>
+      </c>
+      <c r="L166">
+        <v>413.91</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>0</v>
+      </c>
+      <c r="R166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18">
+      <c r="A167" t="s">
+        <v>72</v>
+      </c>
+      <c r="B167" t="s">
+        <v>108</v>
+      </c>
+      <c r="C167" t="s">
+        <v>155</v>
+      </c>
+      <c r="D167" t="s">
+        <v>157</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>122.16</v>
+      </c>
+      <c r="G167">
+        <v>81</v>
+      </c>
+      <c r="H167">
+        <v>81</v>
+      </c>
+      <c r="I167">
+        <v>9894.959999999999</v>
+      </c>
+      <c r="J167">
+        <v>122.16</v>
+      </c>
+      <c r="L167">
+        <v>116.05</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
+        <v>0</v>
+      </c>
+      <c r="R167">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="170">
   <si>
     <t>Buy Date</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
   </si>
   <si>
     <t>SL Hit</t>
@@ -997,7 +1000,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1053,7 +1056,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1112,7 +1115,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1168,7 +1171,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1224,7 +1227,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1280,7 +1283,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1336,7 +1339,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1392,7 +1395,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1448,7 +1451,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1504,7 +1507,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1563,7 +1566,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1622,7 +1625,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1678,7 +1681,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1734,7 +1737,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1790,7 +1793,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1846,7 +1849,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1902,7 +1905,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1958,7 +1961,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -2014,7 +2017,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2070,7 +2073,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2126,7 +2129,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2182,7 +2185,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2238,7 +2241,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2294,7 +2297,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2350,7 +2353,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2406,7 +2409,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2462,7 +2465,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2518,7 +2521,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2574,7 +2577,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2630,7 +2633,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2686,7 +2689,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2742,7 +2745,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2798,7 +2801,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2854,7 +2857,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2910,7 +2913,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2966,7 +2969,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -3022,7 +3025,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3081,7 +3084,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3137,7 +3140,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3193,7 +3196,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3249,7 +3252,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3305,7 +3308,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3361,7 +3364,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3417,7 +3420,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3473,7 +3476,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3532,7 +3535,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3588,7 +3591,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3644,7 +3647,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3703,7 +3706,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3759,7 +3762,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3815,7 +3818,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3874,7 +3877,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3930,7 +3933,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3989,7 +3992,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4048,7 +4051,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4104,7 +4107,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4160,7 +4163,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4216,7 +4219,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4275,7 +4278,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4331,7 +4334,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4390,7 +4393,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4405,7 +4408,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4449,7 +4452,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4505,7 +4508,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4561,7 +4564,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4617,7 +4620,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4673,7 +4676,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4729,7 +4732,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4785,7 +4788,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4841,7 +4844,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4897,7 +4900,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4953,7 +4956,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5009,7 +5012,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5065,7 +5068,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5121,7 +5124,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5177,7 +5180,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5233,7 +5236,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5289,7 +5292,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5345,7 +5348,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5401,7 +5404,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5457,7 +5460,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5513,7 +5516,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5572,7 +5575,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5628,7 +5631,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5684,7 +5687,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5740,7 +5743,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5796,7 +5799,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5852,7 +5855,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5908,7 +5911,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5964,7 +5967,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -6008,7 +6011,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>302.75</v>
+        <v>300.35</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6020,13 +6023,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>267.3</v>
+        <v>188.1</v>
       </c>
       <c r="Q91">
-        <v>267.3</v>
+        <v>188.1</v>
       </c>
       <c r="R91">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6070,7 +6073,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6126,7 +6129,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6182,7 +6185,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6238,7 +6241,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6294,7 +6297,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6350,7 +6353,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6406,7 +6409,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6465,7 +6468,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6521,7 +6524,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6577,7 +6580,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6633,7 +6636,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6689,7 +6692,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6745,7 +6748,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6801,7 +6804,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6857,7 +6860,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6913,7 +6916,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6969,7 +6972,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -7025,7 +7028,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7081,7 +7084,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7137,7 +7140,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7193,7 +7196,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7249,7 +7252,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7305,7 +7308,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7361,7 +7364,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7417,7 +7420,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7473,7 +7476,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7517,7 +7520,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1219.2</v>
+        <v>1218.5</v>
       </c>
       <c r="L118">
         <v>1086.89</v>
@@ -7529,13 +7532,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>600.8</v>
+        <v>595.2</v>
       </c>
       <c r="Q118">
-        <v>600.8</v>
+        <v>595.2</v>
       </c>
       <c r="R118">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7579,7 +7582,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7635,7 +7638,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7691,7 +7694,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7747,7 +7750,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7803,7 +7806,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7859,7 +7862,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7915,7 +7918,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7959,10 +7962,10 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>175.81</v>
+        <v>181.35</v>
       </c>
       <c r="L126">
-        <v>164.02</v>
+        <v>169.31</v>
       </c>
       <c r="M126">
         <v>0</v>
@@ -7971,13 +7974,13 @@
         <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>480.6</v>
+        <v>580.3200000000001</v>
       </c>
       <c r="Q126">
-        <v>1330.53</v>
+        <v>1430.25</v>
       </c>
       <c r="R126">
-        <v>13.32</v>
+        <v>14.32</v>
       </c>
       <c r="S126" t="s">
         <v>70</v>
@@ -8024,7 +8027,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8080,7 +8083,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8139,7 +8142,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8195,7 +8198,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8251,7 +8254,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8307,7 +8310,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8363,7 +8366,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8419,7 +8422,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8475,7 +8478,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8531,16 +8534,16 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O136">
-        <v>-499.6199999999995</v>
+        <v>-499.6199999999996</v>
       </c>
       <c r="P136">
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>-499.6199999999995</v>
+        <v>-499.6199999999996</v>
       </c>
       <c r="R136">
         <v>-5</v>
@@ -8587,7 +8590,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8646,7 +8649,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8702,7 +8705,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8758,7 +8761,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8814,7 +8817,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8870,7 +8873,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8914,7 +8917,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6859.5</v>
+        <v>6828.5</v>
       </c>
       <c r="L143">
         <v>6523.12</v>
@@ -8926,13 +8929,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>647</v>
+        <v>616</v>
       </c>
       <c r="Q143">
-        <v>647</v>
+        <v>616</v>
       </c>
       <c r="R143">
-        <v>10.41</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8976,7 +8979,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9032,7 +9035,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9076,7 +9079,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3388.5</v>
+        <v>3343.5</v>
       </c>
       <c r="L146">
         <v>3228.5</v>
@@ -9088,13 +9091,13 @@
         <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>907</v>
+        <v>817</v>
       </c>
       <c r="Q146">
-        <v>1200.5</v>
+        <v>1110.5</v>
       </c>
       <c r="R146">
-        <v>13.63</v>
+        <v>12.61</v>
       </c>
       <c r="S146" t="s">
         <v>70</v>
@@ -9129,7 +9132,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>830.9</v>
+        <v>818.9</v>
       </c>
       <c r="L147">
         <v>746.37</v>
@@ -9141,13 +9144,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>543</v>
+        <v>399</v>
       </c>
       <c r="Q147">
-        <v>543</v>
+        <v>399</v>
       </c>
       <c r="R147">
-        <v>5.76</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9179,7 +9182,7 @@
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>349.8</v>
+        <v>347</v>
       </c>
       <c r="L148">
         <v>322.1</v>
@@ -9191,13 +9194,13 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>858.7</v>
+        <v>771.9</v>
       </c>
       <c r="Q148">
-        <v>858.7</v>
+        <v>771.9</v>
       </c>
       <c r="R148">
-        <v>8.6</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -9211,10 +9214,10 @@
         <v>153</v>
       </c>
       <c r="D149" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F149">
         <v>1842.5</v>
@@ -9223,7 +9226,7 @@
         <v>5</v>
       </c>
       <c r="H149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I149">
         <v>9212.5</v>
@@ -9231,23 +9234,29 @@
       <c r="J149">
         <v>2086.8</v>
       </c>
+      <c r="K149" t="s">
+        <v>166</v>
+      </c>
       <c r="L149">
-        <v>1934.62</v>
+        <v>2040.5</v>
       </c>
       <c r="M149">
-        <v>0</v>
+        <v>2010.2</v>
+      </c>
+      <c r="N149" t="s">
+        <v>168</v>
       </c>
       <c r="O149">
-        <v>368.5000000000005</v>
+        <v>871.6000000000006</v>
       </c>
       <c r="P149">
-        <v>732.9</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>1101.4</v>
+        <v>871.6000000000006</v>
       </c>
       <c r="R149">
-        <v>11.96</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="S149" t="s">
         <v>70</v>
@@ -9282,7 +9291,7 @@
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>431.6</v>
+        <v>430.6</v>
       </c>
       <c r="L150">
         <v>383.51</v>
@@ -9294,13 +9303,13 @@
         <v>0</v>
       </c>
       <c r="P150">
-        <v>669.6</v>
+        <v>645.6</v>
       </c>
       <c r="Q150">
-        <v>669.6</v>
+        <v>645.6</v>
       </c>
       <c r="R150">
-        <v>6.91</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -9332,7 +9341,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4505</v>
+        <v>4439.3</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9344,13 +9353,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>517.8</v>
+        <v>386.4</v>
       </c>
       <c r="Q151">
-        <v>517.8</v>
+        <v>386.4</v>
       </c>
       <c r="R151">
-        <v>6.1</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -9382,7 +9391,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>380.15</v>
+        <v>386.25</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9394,13 +9403,13 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>379.35</v>
+        <v>544.05</v>
       </c>
       <c r="Q152">
-        <v>379.35</v>
+        <v>544.05</v>
       </c>
       <c r="R152">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9432,7 +9441,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1078.1</v>
+        <v>1059.9</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9444,13 +9453,13 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>440.55</v>
+        <v>276.75</v>
       </c>
       <c r="Q153">
-        <v>440.55</v>
+        <v>276.75</v>
       </c>
       <c r="R153">
-        <v>4.76</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -9482,7 +9491,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2155.3</v>
+        <v>2127.2</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9494,13 +9503,13 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>178.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Q154">
-        <v>178.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R154">
-        <v>2.12</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9532,7 +9541,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1281.7</v>
+        <v>1273.9</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9544,13 +9553,13 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>380.8</v>
+        <v>318.4</v>
       </c>
       <c r="Q155">
-        <v>380.8</v>
+        <v>318.4</v>
       </c>
       <c r="R155">
-        <v>3.86</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -9582,7 +9591,7 @@
         <v>9800.639999999999</v>
       </c>
       <c r="J156">
-        <v>206.61</v>
+        <v>206.39</v>
       </c>
       <c r="L156">
         <v>193.97</v>
@@ -9594,13 +9603,13 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>116.64</v>
+        <v>106.08</v>
       </c>
       <c r="Q156">
-        <v>116.64</v>
+        <v>106.08</v>
       </c>
       <c r="R156">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9632,7 +9641,7 @@
         <v>9535</v>
       </c>
       <c r="J157">
-        <v>1939.1</v>
+        <v>1915.9</v>
       </c>
       <c r="L157">
         <v>1811.65</v>
@@ -9644,13 +9653,13 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>160.5</v>
+        <v>44.5</v>
       </c>
       <c r="Q157">
-        <v>160.5</v>
+        <v>44.5</v>
       </c>
       <c r="R157">
-        <v>1.68</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -9682,7 +9691,7 @@
         <v>9331</v>
       </c>
       <c r="J158">
-        <v>1350.8</v>
+        <v>1353.6</v>
       </c>
       <c r="L158">
         <v>1266.35</v>
@@ -9694,13 +9703,13 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>124.6</v>
+        <v>144.2</v>
       </c>
       <c r="Q158">
-        <v>124.6</v>
+        <v>144.2</v>
       </c>
       <c r="R158">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -9732,7 +9741,7 @@
         <v>9678</v>
       </c>
       <c r="J159">
-        <v>981.8</v>
+        <v>979.05</v>
       </c>
       <c r="L159">
         <v>919.41</v>
@@ -9744,13 +9753,13 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>140</v>
+        <v>112.5</v>
       </c>
       <c r="Q159">
-        <v>140</v>
+        <v>112.5</v>
       </c>
       <c r="R159">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -9782,7 +9791,7 @@
         <v>9748.799999999999</v>
       </c>
       <c r="J160">
-        <v>547</v>
+        <v>546.5</v>
       </c>
       <c r="L160">
         <v>514.52</v>
@@ -9794,13 +9803,13 @@
         <v>0</v>
       </c>
       <c r="P160">
-        <v>97.2</v>
+        <v>88.2</v>
       </c>
       <c r="Q160">
-        <v>97.2</v>
+        <v>88.2</v>
       </c>
       <c r="R160">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="161" spans="1:18">
@@ -9832,7 +9841,7 @@
         <v>9845.15</v>
       </c>
       <c r="J161">
-        <v>434.9</v>
+        <v>433.55</v>
       </c>
       <c r="L161">
         <v>406.65</v>
@@ -9844,13 +9853,13 @@
         <v>0</v>
       </c>
       <c r="P161">
-        <v>157.55</v>
+        <v>126.5</v>
       </c>
       <c r="Q161">
-        <v>157.55</v>
+        <v>126.5</v>
       </c>
       <c r="R161">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="162" spans="1:18">
@@ -9882,7 +9891,7 @@
         <v>9517</v>
       </c>
       <c r="J162">
-        <v>9813.5</v>
+        <v>9816</v>
       </c>
       <c r="L162">
         <v>9041.15</v>
@@ -9894,13 +9903,13 @@
         <v>0</v>
       </c>
       <c r="P162">
-        <v>296.5</v>
+        <v>299</v>
       </c>
       <c r="Q162">
-        <v>296.5</v>
+        <v>299</v>
       </c>
       <c r="R162">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="163" spans="1:18">
@@ -9932,7 +9941,7 @@
         <v>9979.200000000001</v>
       </c>
       <c r="J163">
-        <v>284.71</v>
+        <v>287.77</v>
       </c>
       <c r="L163">
         <v>263.34</v>
@@ -9944,13 +9953,13 @@
         <v>0</v>
       </c>
       <c r="P163">
-        <v>270.36</v>
+        <v>380.52</v>
       </c>
       <c r="Q163">
-        <v>270.36</v>
+        <v>380.52</v>
       </c>
       <c r="R163">
-        <v>2.71</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -9982,7 +9991,7 @@
         <v>9677.6</v>
       </c>
       <c r="J164">
-        <v>1214.8</v>
+        <v>1204.2</v>
       </c>
       <c r="L164">
         <v>1149.21</v>
@@ -9994,13 +10003,13 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>40.8</v>
+        <v>-44</v>
       </c>
       <c r="Q164">
-        <v>40.8</v>
+        <v>-44</v>
       </c>
       <c r="R164">
-        <v>0.42</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="165" spans="1:18">
@@ -10014,7 +10023,7 @@
         <v>155</v>
       </c>
       <c r="D165" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10026,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165">
         <v>7424</v>
@@ -10034,23 +10043,29 @@
       <c r="J165">
         <v>7424</v>
       </c>
+      <c r="K165" t="s">
+        <v>166</v>
+      </c>
       <c r="L165">
         <v>7052.8</v>
       </c>
       <c r="M165">
-        <v>0</v>
+        <v>7052.8</v>
+      </c>
+      <c r="N165" t="s">
+        <v>167</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>-371.1999999999998</v>
       </c>
       <c r="P165">
         <v>0</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>-371.1999999999998</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="166" spans="1:18">
@@ -10082,7 +10097,7 @@
         <v>9585.4</v>
       </c>
       <c r="J166">
-        <v>435.7</v>
+        <v>424.75</v>
       </c>
       <c r="L166">
         <v>413.91</v>
@@ -10094,13 +10109,13 @@
         <v>0</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>-240.9</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>-240.9</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="167" spans="1:18">
@@ -10132,7 +10147,7 @@
         <v>9894.959999999999</v>
       </c>
       <c r="J167">
-        <v>122.16</v>
+        <v>119.11</v>
       </c>
       <c r="L167">
         <v>116.05</v>
@@ -10144,13 +10159,13 @@
         <v>0</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>-247.05</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>-247.05</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="172">
   <si>
     <t>Buy Date</t>
   </si>
@@ -235,6 +235,9 @@
     <t>2026-04-10</t>
   </si>
   <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
     <t>ADANIENT</t>
   </si>
   <si>
@@ -473,6 +476,9 @@
   </si>
   <si>
     <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>LT</t>
   </si>
   <si>
     <t>Value Buy</t>
@@ -887,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S167"/>
+  <dimension ref="A1:S171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -964,13 +970,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1000,7 +1006,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1020,13 +1026,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1056,7 +1062,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1079,13 +1085,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1115,7 +1121,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1135,13 +1141,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1171,7 +1177,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1191,13 +1197,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1227,7 +1233,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1247,13 +1253,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1283,7 +1289,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1303,13 +1309,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1339,7 +1345,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1359,13 +1365,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1395,7 +1401,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1415,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1451,7 +1457,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1471,13 +1477,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1498,7 +1504,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1507,7 +1513,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1522,7 +1528,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1530,13 +1536,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1566,7 +1572,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1589,13 +1595,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1625,7 +1631,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1645,13 +1651,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1681,7 +1687,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1701,13 +1707,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1737,7 +1743,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1757,13 +1763,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1793,7 +1799,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1813,13 +1819,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1849,7 +1855,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1869,13 +1875,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1905,7 +1911,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1925,13 +1931,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1961,7 +1967,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1981,13 +1987,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2017,7 +2023,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2037,13 +2043,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2064,7 +2070,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2073,7 +2079,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2093,13 +2099,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2120,7 +2126,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2129,7 +2135,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2149,13 +2155,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2185,7 +2191,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2205,13 +2211,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2241,7 +2247,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2261,13 +2267,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2297,7 +2303,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2317,13 +2323,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2344,7 +2350,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2353,7 +2359,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2373,13 +2379,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2409,7 +2415,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2429,13 +2435,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2465,7 +2471,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2485,13 +2491,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2521,7 +2527,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2541,13 +2547,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2577,7 +2583,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2597,13 +2603,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2624,7 +2630,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2633,7 +2639,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2653,13 +2659,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2689,7 +2695,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2709,13 +2715,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2745,7 +2751,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2765,13 +2771,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2792,7 +2798,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2801,7 +2807,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2821,13 +2827,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2848,7 +2854,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2857,7 +2863,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2877,13 +2883,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2913,7 +2919,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2933,13 +2939,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2969,7 +2975,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2989,13 +2995,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3025,7 +3031,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3048,13 +3054,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3084,7 +3090,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3104,13 +3110,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3140,7 +3146,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3160,13 +3166,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3196,7 +3202,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3216,13 +3222,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3243,7 +3249,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3252,7 +3258,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3272,13 +3278,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3299,7 +3305,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3308,7 +3314,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3328,13 +3334,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3364,7 +3370,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3384,13 +3390,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3420,7 +3426,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3440,13 +3446,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3476,7 +3482,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3499,13 +3505,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3535,7 +3541,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3555,13 +3561,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3591,7 +3597,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3611,13 +3617,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3647,7 +3653,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3670,13 +3676,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3706,7 +3712,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3726,13 +3732,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3762,7 +3768,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3782,13 +3788,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3818,7 +3824,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3841,13 +3847,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3877,7 +3883,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3897,13 +3903,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3933,7 +3939,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3956,13 +3962,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3992,7 +3998,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4015,13 +4021,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4051,7 +4057,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4071,13 +4077,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4098,7 +4104,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4107,7 +4113,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4127,13 +4133,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4163,7 +4169,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4183,13 +4189,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4219,7 +4225,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4242,13 +4248,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4278,7 +4284,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4298,13 +4304,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4334,7 +4340,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4357,13 +4363,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4393,7 +4399,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4408,7 +4414,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4416,13 +4422,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4452,7 +4458,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4472,13 +4478,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4508,7 +4514,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4528,13 +4534,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4564,7 +4570,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4584,13 +4590,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D66" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4620,7 +4626,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4640,13 +4646,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4676,7 +4682,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4696,13 +4702,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4732,7 +4738,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4752,13 +4758,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4779,7 +4785,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4788,7 +4794,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4808,13 +4814,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4844,7 +4850,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4864,13 +4870,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4900,7 +4906,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4920,13 +4926,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4956,7 +4962,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4976,13 +4982,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5012,7 +5018,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5032,13 +5038,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C74" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5068,7 +5074,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5088,13 +5094,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5124,7 +5130,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5144,13 +5150,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5180,7 +5186,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5200,13 +5206,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5236,7 +5242,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5256,13 +5262,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5292,7 +5298,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5312,13 +5318,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C79" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5348,7 +5354,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5368,13 +5374,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C80" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D80" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5404,7 +5410,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5424,13 +5430,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D81" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5460,7 +5466,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5480,13 +5486,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C82" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5516,7 +5522,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5539,13 +5545,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5575,7 +5581,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5595,13 +5601,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5631,7 +5637,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5651,13 +5657,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5687,7 +5693,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5707,13 +5713,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D86" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5743,7 +5749,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5763,13 +5769,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D87" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5799,7 +5805,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5819,13 +5825,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5855,7 +5861,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5875,13 +5881,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5911,7 +5917,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5931,13 +5937,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5967,7 +5973,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5987,13 +5993,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D91" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -6011,7 +6017,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>300.35</v>
+        <v>312.45</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6023,13 +6029,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>188.1</v>
+        <v>587.4</v>
       </c>
       <c r="Q91">
-        <v>188.1</v>
+        <v>587.4</v>
       </c>
       <c r="R91">
-        <v>1.93</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6037,13 +6043,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6073,7 +6079,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6093,13 +6099,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D93" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6129,7 +6135,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6149,13 +6155,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6185,7 +6191,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6205,13 +6211,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C95" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6241,7 +6247,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6261,13 +6267,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C96" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6297,7 +6303,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6317,13 +6323,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D97" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6353,7 +6359,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6373,13 +6379,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D98" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6409,7 +6415,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6432,13 +6438,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C99" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D99" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6468,7 +6474,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6488,13 +6494,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D100" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6524,7 +6530,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6544,13 +6550,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6580,7 +6586,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6600,13 +6606,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C102" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6636,7 +6642,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6656,13 +6662,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6692,7 +6698,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6712,13 +6718,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6748,7 +6754,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6768,13 +6774,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D105" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6804,7 +6810,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6824,13 +6830,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C106" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6851,7 +6857,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6860,7 +6866,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6880,13 +6886,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C107" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6916,7 +6922,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6936,13 +6942,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C108" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D108" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6972,7 +6978,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6992,13 +6998,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D109" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7019,7 +7025,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7028,7 +7034,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7048,13 +7054,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D110" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7084,7 +7090,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7104,13 +7110,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D111" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7140,7 +7146,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7160,13 +7166,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C112" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D112" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7196,7 +7202,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7216,13 +7222,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C113" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D113" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7252,7 +7258,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7272,13 +7278,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C114" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D114" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7308,7 +7314,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7328,13 +7334,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C115" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D115" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7364,7 +7370,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7384,13 +7390,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D116" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7420,7 +7426,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7440,13 +7446,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C117" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D117" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7476,7 +7482,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7496,16 +7502,16 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D118" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118">
         <v>1144.1</v>
@@ -7520,10 +7526,10 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1218.5</v>
+        <v>1221.3</v>
       </c>
       <c r="L118">
-        <v>1086.89</v>
+        <v>1144.1</v>
       </c>
       <c r="M118">
         <v>0</v>
@@ -7532,13 +7538,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>595.2</v>
+        <v>617.6</v>
       </c>
       <c r="Q118">
-        <v>595.2</v>
+        <v>617.6</v>
       </c>
       <c r="R118">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7546,13 +7552,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C119" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D119" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7582,7 +7588,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7602,13 +7608,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C120" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D120" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7638,7 +7644,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7658,13 +7664,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D121" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7694,7 +7700,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7714,13 +7720,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C122" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D122" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7750,7 +7756,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7770,13 +7776,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7797,7 +7803,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7806,7 +7812,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7826,13 +7832,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C124" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D124" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7862,7 +7868,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7882,13 +7888,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D125" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7918,7 +7924,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7938,13 +7944,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D126" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -7962,10 +7968,10 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>181.35</v>
+        <v>183.43</v>
       </c>
       <c r="L126">
-        <v>169.31</v>
+        <v>172.33</v>
       </c>
       <c r="M126">
         <v>0</v>
@@ -7974,13 +7980,13 @@
         <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>580.3200000000001</v>
+        <v>617.76</v>
       </c>
       <c r="Q126">
-        <v>1430.25</v>
+        <v>1467.69</v>
       </c>
       <c r="R126">
-        <v>14.32</v>
+        <v>14.69</v>
       </c>
       <c r="S126" t="s">
         <v>70</v>
@@ -7991,13 +7997,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C127" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D127" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8027,7 +8033,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8047,13 +8053,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D128" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8083,7 +8089,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8106,13 +8112,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8142,7 +8148,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8162,13 +8168,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8198,7 +8204,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8218,13 +8224,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D131" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8254,7 +8260,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8274,13 +8280,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D132" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8310,7 +8316,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8330,13 +8336,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8357,7 +8363,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8366,7 +8372,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8386,13 +8392,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D134" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8422,7 +8428,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8442,13 +8448,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C135" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D135" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8478,7 +8484,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8498,13 +8504,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C136" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D136" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8534,7 +8540,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8554,13 +8560,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D137" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8590,7 +8596,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8613,13 +8619,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C138" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D138" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8649,7 +8655,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8669,13 +8675,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D139" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8705,7 +8711,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8725,13 +8731,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C140" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D140" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8761,7 +8767,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8781,13 +8787,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C141" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8817,7 +8823,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8837,13 +8843,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D142" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8873,7 +8879,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8893,13 +8899,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D143" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E143">
         <v>2</v>
@@ -8917,7 +8923,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6828.5</v>
+        <v>6873</v>
       </c>
       <c r="L143">
         <v>6523.12</v>
@@ -8929,13 +8935,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>616</v>
+        <v>660.5</v>
       </c>
       <c r="Q143">
-        <v>616</v>
+        <v>660.5</v>
       </c>
       <c r="R143">
-        <v>9.92</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8943,13 +8949,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C144" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D144" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8979,7 +8985,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -8999,13 +9005,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D145" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9035,7 +9041,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9055,13 +9061,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C146" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D146" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9079,7 +9085,7 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3343.5</v>
+        <v>3576.1</v>
       </c>
       <c r="L146">
         <v>3228.5</v>
@@ -9091,13 +9097,13 @@
         <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>817</v>
+        <v>1282.2</v>
       </c>
       <c r="Q146">
-        <v>1110.5</v>
+        <v>1575.7</v>
       </c>
       <c r="R146">
-        <v>12.61</v>
+        <v>17.9</v>
       </c>
       <c r="S146" t="s">
         <v>70</v>
@@ -9108,16 +9114,16 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C147" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D147" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147">
         <v>785.65</v>
@@ -9132,10 +9138,10 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>818.9</v>
+        <v>840.1</v>
       </c>
       <c r="L147">
-        <v>746.37</v>
+        <v>785.65</v>
       </c>
       <c r="M147">
         <v>0</v>
@@ -9144,13 +9150,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>399</v>
+        <v>653.4</v>
       </c>
       <c r="Q147">
-        <v>399</v>
+        <v>653.4</v>
       </c>
       <c r="R147">
-        <v>4.23</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9158,16 +9164,16 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C148" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D148" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148">
         <v>322.1</v>
@@ -9176,31 +9182,34 @@
         <v>31</v>
       </c>
       <c r="H148">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I148">
         <v>9985.1</v>
       </c>
       <c r="J148">
-        <v>347</v>
+        <v>352.65</v>
       </c>
       <c r="L148">
-        <v>322.1</v>
+        <v>338.21</v>
       </c>
       <c r="M148">
         <v>0</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>483.1500000000005</v>
       </c>
       <c r="P148">
-        <v>771.9</v>
+        <v>488.8</v>
       </c>
       <c r="Q148">
-        <v>771.9</v>
+        <v>971.95</v>
       </c>
       <c r="R148">
-        <v>7.73</v>
+        <v>9.73</v>
+      </c>
+      <c r="S148" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -9208,13 +9217,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C149" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D149" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9235,7 +9244,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9244,7 +9253,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9267,16 +9276,16 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D150" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150">
         <v>403.7</v>
@@ -9285,31 +9294,34 @@
         <v>24</v>
       </c>
       <c r="H150">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I150">
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>430.6</v>
+        <v>445.55</v>
       </c>
       <c r="L150">
-        <v>383.51</v>
+        <v>423.88</v>
       </c>
       <c r="M150">
         <v>0</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>484.4400000000007</v>
       </c>
       <c r="P150">
-        <v>645.6</v>
+        <v>502.2</v>
       </c>
       <c r="Q150">
-        <v>645.6</v>
+        <v>986.64</v>
       </c>
       <c r="R150">
-        <v>6.66</v>
+        <v>10.18</v>
+      </c>
+      <c r="S150" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -9317,13 +9329,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C151" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D151" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9341,7 +9353,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4439.3</v>
+        <v>4522.2</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9353,13 +9365,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>386.4</v>
+        <v>552.2</v>
       </c>
       <c r="Q151">
-        <v>386.4</v>
+        <v>552.2</v>
       </c>
       <c r="R151">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -9367,13 +9379,13 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C152" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D152" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -9391,7 +9403,7 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>386.25</v>
+        <v>392.6</v>
       </c>
       <c r="L152">
         <v>347.8</v>
@@ -9403,13 +9415,13 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>544.05</v>
+        <v>715.5</v>
       </c>
       <c r="Q152">
-        <v>544.05</v>
+        <v>715.5</v>
       </c>
       <c r="R152">
-        <v>5.5</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9417,13 +9429,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C153" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D153" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9441,7 +9453,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1059.9</v>
+        <v>1085.5</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9453,13 +9465,13 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>276.75</v>
+        <v>507.15</v>
       </c>
       <c r="Q153">
-        <v>276.75</v>
+        <v>507.15</v>
       </c>
       <c r="R153">
-        <v>2.99</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -9467,13 +9479,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C154" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D154" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9491,7 +9503,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2127.2</v>
+        <v>2157.6</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9503,13 +9515,13 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>66.40000000000001</v>
+        <v>188</v>
       </c>
       <c r="Q154">
-        <v>66.40000000000001</v>
+        <v>188</v>
       </c>
       <c r="R154">
-        <v>0.79</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9517,13 +9529,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C155" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D155" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9541,7 +9553,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1273.9</v>
+        <v>1285.2</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9553,13 +9565,13 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>318.4</v>
+        <v>408.8</v>
       </c>
       <c r="Q155">
-        <v>318.4</v>
+        <v>408.8</v>
       </c>
       <c r="R155">
-        <v>3.23</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -9567,13 +9579,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C156" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D156" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -9591,7 +9603,7 @@
         <v>9800.639999999999</v>
       </c>
       <c r="J156">
-        <v>206.39</v>
+        <v>208.72</v>
       </c>
       <c r="L156">
         <v>193.97</v>
@@ -9603,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>106.08</v>
+        <v>217.92</v>
       </c>
       <c r="Q156">
-        <v>106.08</v>
+        <v>217.92</v>
       </c>
       <c r="R156">
-        <v>1.08</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9617,13 +9629,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C157" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D157" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -9641,7 +9653,7 @@
         <v>9535</v>
       </c>
       <c r="J157">
-        <v>1915.9</v>
+        <v>1946.7</v>
       </c>
       <c r="L157">
         <v>1811.65</v>
@@ -9653,13 +9665,13 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>44.5</v>
+        <v>198.5</v>
       </c>
       <c r="Q157">
-        <v>44.5</v>
+        <v>198.5</v>
       </c>
       <c r="R157">
-        <v>0.47</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -9667,13 +9679,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C158" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D158" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -9691,7 +9703,7 @@
         <v>9331</v>
       </c>
       <c r="J158">
-        <v>1353.6</v>
+        <v>1355.5</v>
       </c>
       <c r="L158">
         <v>1266.35</v>
@@ -9703,13 +9715,13 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>144.2</v>
+        <v>157.5</v>
       </c>
       <c r="Q158">
-        <v>144.2</v>
+        <v>157.5</v>
       </c>
       <c r="R158">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -9717,13 +9729,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C159" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -9741,7 +9753,7 @@
         <v>9678</v>
       </c>
       <c r="J159">
-        <v>979.05</v>
+        <v>981.1</v>
       </c>
       <c r="L159">
         <v>919.41</v>
@@ -9753,13 +9765,13 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>112.5</v>
+        <v>133</v>
       </c>
       <c r="Q159">
-        <v>112.5</v>
+        <v>133</v>
       </c>
       <c r="R159">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -9767,13 +9779,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C160" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -9791,7 +9803,7 @@
         <v>9748.799999999999</v>
       </c>
       <c r="J160">
-        <v>546.5</v>
+        <v>561.25</v>
       </c>
       <c r="L160">
         <v>514.52</v>
@@ -9803,13 +9815,13 @@
         <v>0</v>
       </c>
       <c r="P160">
-        <v>88.2</v>
+        <v>353.7</v>
       </c>
       <c r="Q160">
-        <v>88.2</v>
+        <v>353.7</v>
       </c>
       <c r="R160">
-        <v>0.9</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="161" spans="1:18">
@@ -9817,13 +9829,13 @@
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C161" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -9841,7 +9853,7 @@
         <v>9845.15</v>
       </c>
       <c r="J161">
-        <v>433.55</v>
+        <v>444.75</v>
       </c>
       <c r="L161">
         <v>406.65</v>
@@ -9853,13 +9865,13 @@
         <v>0</v>
       </c>
       <c r="P161">
-        <v>126.5</v>
+        <v>384.1</v>
       </c>
       <c r="Q161">
-        <v>126.5</v>
+        <v>384.1</v>
       </c>
       <c r="R161">
-        <v>1.28</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="162" spans="1:18">
@@ -9867,13 +9879,13 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C162" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -9891,7 +9903,7 @@
         <v>9517</v>
       </c>
       <c r="J162">
-        <v>9816</v>
+        <v>9865</v>
       </c>
       <c r="L162">
         <v>9041.15</v>
@@ -9903,13 +9915,13 @@
         <v>0</v>
       </c>
       <c r="P162">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="Q162">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="R162">
-        <v>3.14</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="163" spans="1:18">
@@ -9917,13 +9929,13 @@
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C163" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D163" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -9941,7 +9953,7 @@
         <v>9979.200000000001</v>
       </c>
       <c r="J163">
-        <v>287.77</v>
+        <v>292.5</v>
       </c>
       <c r="L163">
         <v>263.34</v>
@@ -9953,13 +9965,13 @@
         <v>0</v>
       </c>
       <c r="P163">
-        <v>380.52</v>
+        <v>550.8</v>
       </c>
       <c r="Q163">
-        <v>380.52</v>
+        <v>550.8</v>
       </c>
       <c r="R163">
-        <v>3.81</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -9967,13 +9979,13 @@
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C164" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D164" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -9991,7 +10003,7 @@
         <v>9677.6</v>
       </c>
       <c r="J164">
-        <v>1204.2</v>
+        <v>1218.6</v>
       </c>
       <c r="L164">
         <v>1149.21</v>
@@ -10003,13 +10015,13 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>-44</v>
+        <v>71.2</v>
       </c>
       <c r="Q164">
-        <v>-44</v>
+        <v>71.2</v>
       </c>
       <c r="R164">
-        <v>-0.45</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="165" spans="1:18">
@@ -10017,13 +10029,13 @@
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C165" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D165" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10044,7 +10056,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10053,7 +10065,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10073,13 +10085,13 @@
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C166" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D166" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -10097,7 +10109,7 @@
         <v>9585.4</v>
       </c>
       <c r="J166">
-        <v>424.75</v>
+        <v>433.25</v>
       </c>
       <c r="L166">
         <v>413.91</v>
@@ -10109,13 +10121,13 @@
         <v>0</v>
       </c>
       <c r="P166">
-        <v>-240.9</v>
+        <v>-53.9</v>
       </c>
       <c r="Q166">
-        <v>-240.9</v>
+        <v>-53.9</v>
       </c>
       <c r="R166">
-        <v>-2.51</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:18">
@@ -10123,13 +10135,13 @@
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C167" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D167" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -10147,7 +10159,7 @@
         <v>9894.959999999999</v>
       </c>
       <c r="J167">
-        <v>119.11</v>
+        <v>123.55</v>
       </c>
       <c r="L167">
         <v>116.05</v>
@@ -10159,13 +10171,213 @@
         <v>0</v>
       </c>
       <c r="P167">
-        <v>-247.05</v>
+        <v>112.59</v>
       </c>
       <c r="Q167">
-        <v>-247.05</v>
+        <v>112.59</v>
       </c>
       <c r="R167">
-        <v>-2.5</v>
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18">
+      <c r="A168" t="s">
+        <v>73</v>
+      </c>
+      <c r="B168" t="s">
+        <v>154</v>
+      </c>
+      <c r="C168" t="s">
+        <v>157</v>
+      </c>
+      <c r="D168" t="s">
+        <v>159</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>4076.3</v>
+      </c>
+      <c r="G168">
+        <v>2</v>
+      </c>
+      <c r="H168">
+        <v>2</v>
+      </c>
+      <c r="I168">
+        <v>8152.6</v>
+      </c>
+      <c r="J168">
+        <v>4076.3</v>
+      </c>
+      <c r="L168">
+        <v>3872.49</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+      <c r="Q168">
+        <v>0</v>
+      </c>
+      <c r="R168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18">
+      <c r="A169" t="s">
+        <v>73</v>
+      </c>
+      <c r="B169" t="s">
+        <v>146</v>
+      </c>
+      <c r="C169" t="s">
+        <v>157</v>
+      </c>
+      <c r="D169" t="s">
+        <v>159</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>548.45</v>
+      </c>
+      <c r="G169">
+        <v>18</v>
+      </c>
+      <c r="H169">
+        <v>18</v>
+      </c>
+      <c r="I169">
+        <v>9872.1</v>
+      </c>
+      <c r="J169">
+        <v>548.45</v>
+      </c>
+      <c r="L169">
+        <v>521.03</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="Q169">
+        <v>0</v>
+      </c>
+      <c r="R169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18">
+      <c r="A170" t="s">
+        <v>73</v>
+      </c>
+      <c r="B170" t="s">
+        <v>125</v>
+      </c>
+      <c r="C170" t="s">
+        <v>157</v>
+      </c>
+      <c r="D170" t="s">
+        <v>159</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>1511.8</v>
+      </c>
+      <c r="G170">
+        <v>6</v>
+      </c>
+      <c r="H170">
+        <v>6</v>
+      </c>
+      <c r="I170">
+        <v>9070.799999999999</v>
+      </c>
+      <c r="J170">
+        <v>1511.8</v>
+      </c>
+      <c r="L170">
+        <v>1436.21</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="Q170">
+        <v>0</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18">
+      <c r="A171" t="s">
+        <v>73</v>
+      </c>
+      <c r="B171" t="s">
+        <v>144</v>
+      </c>
+      <c r="C171" t="s">
+        <v>157</v>
+      </c>
+      <c r="D171" t="s">
+        <v>159</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>7642</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171">
+        <v>7642</v>
+      </c>
+      <c r="J171">
+        <v>7642</v>
+      </c>
+      <c r="L171">
+        <v>7259.9</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="Q171">
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="173">
   <si>
     <t>Buy Date</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -893,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S171"/>
+  <dimension ref="A1:S173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -970,13 +973,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1006,7 +1009,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1026,13 +1029,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1062,7 +1065,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1085,13 +1088,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1121,7 +1124,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1141,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1177,7 +1180,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1197,13 +1200,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1233,7 +1236,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1253,13 +1256,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1289,7 +1292,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1309,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1345,7 +1348,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1365,13 +1368,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1401,7 +1404,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1421,13 +1424,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1457,7 +1460,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1477,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1504,7 +1507,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1513,7 +1516,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1528,7 +1531,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1536,13 +1539,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1572,7 +1575,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1595,13 +1598,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1631,7 +1634,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1651,13 +1654,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1687,7 +1690,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1707,13 +1710,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1743,7 +1746,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1763,13 +1766,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1799,7 +1802,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1819,13 +1822,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1855,7 +1858,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1875,13 +1878,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1911,7 +1914,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1931,13 +1934,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1967,7 +1970,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1987,13 +1990,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2023,7 +2026,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2043,13 +2046,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2070,7 +2073,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2079,7 +2082,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2099,13 +2102,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2126,7 +2129,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2135,7 +2138,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2155,13 +2158,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2191,7 +2194,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2211,13 +2214,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2247,7 +2250,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2267,13 +2270,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2303,7 +2306,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2323,13 +2326,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2350,7 +2353,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2359,7 +2362,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2379,13 +2382,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2415,7 +2418,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2435,13 +2438,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2471,7 +2474,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2491,13 +2494,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2527,7 +2530,7 @@
         <v>854</v>
       </c>
       <c r="N29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O29">
         <v>-523.0499999999995</v>
@@ -2547,13 +2550,13 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2583,7 +2586,7 @@
         <v>6310.38</v>
       </c>
       <c r="N30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O30">
         <v>-332.1199999999999</v>
@@ -2603,13 +2606,13 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2630,7 +2633,7 @@
         <v>546.75</v>
       </c>
       <c r="K31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L31">
         <v>541.83</v>
@@ -2639,7 +2642,7 @@
         <v>541.83</v>
       </c>
       <c r="N31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O31">
         <v>-484.8399999999997</v>
@@ -2659,13 +2662,13 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2695,7 +2698,7 @@
         <v>738.96</v>
       </c>
       <c r="N32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O32">
         <v>-466.6799999999998</v>
@@ -2715,13 +2718,13 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2751,7 +2754,7 @@
         <v>637.64</v>
       </c>
       <c r="N33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O33">
         <v>-469.8400000000008</v>
@@ -2771,13 +2774,13 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2798,7 +2801,7 @@
         <v>1728.7</v>
       </c>
       <c r="K34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L34">
         <v>1693.47</v>
@@ -2807,7 +2810,7 @@
         <v>1693.47</v>
       </c>
       <c r="N34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O34">
         <v>-445.6499999999994</v>
@@ -2827,13 +2830,13 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2854,7 +2857,7 @@
         <v>414.55</v>
       </c>
       <c r="K35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L35">
         <v>409.31</v>
@@ -2863,7 +2866,7 @@
         <v>409.31</v>
       </c>
       <c r="N35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O35">
         <v>-495.4200000000005</v>
@@ -2883,13 +2886,13 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2919,7 +2922,7 @@
         <v>4769.95</v>
       </c>
       <c r="N36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O36">
         <v>-251.0500000000001</v>
@@ -2939,13 +2942,13 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2975,7 +2978,7 @@
         <v>109.86</v>
       </c>
       <c r="N37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O37">
         <v>-497.0800000000001</v>
@@ -2995,13 +2998,13 @@
         <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -3031,7 +3034,7 @@
         <v>439.27</v>
       </c>
       <c r="N38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O38">
         <v>711.2249999999999</v>
@@ -3054,13 +3057,13 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3090,7 +3093,7 @@
         <v>260.54</v>
       </c>
       <c r="N39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O39">
         <v>-493.5599999999993</v>
@@ -3110,13 +3113,13 @@
         <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3146,7 +3149,7 @@
         <v>1578.33</v>
       </c>
       <c r="N40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O40">
         <v>-498.420000000001</v>
@@ -3166,13 +3169,13 @@
         <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3202,7 +3205,7 @@
         <v>2751.58</v>
       </c>
       <c r="N41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O41">
         <v>-434.4600000000005</v>
@@ -3222,13 +3225,13 @@
         <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3249,7 +3252,7 @@
         <v>1375.8</v>
       </c>
       <c r="K42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L42">
         <v>1342.44</v>
@@ -3258,7 +3261,7 @@
         <v>1342.44</v>
       </c>
       <c r="N42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O42">
         <v>-494.619999999999</v>
@@ -3278,13 +3281,13 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3305,7 +3308,7 @@
         <v>4056.4</v>
       </c>
       <c r="K43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L43">
         <v>3853.58</v>
@@ -3314,7 +3317,7 @@
         <v>3853.58</v>
       </c>
       <c r="N43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O43">
         <v>-405.6400000000003</v>
@@ -3334,13 +3337,13 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3370,7 +3373,7 @@
         <v>358.75</v>
       </c>
       <c r="N44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3390,13 +3393,13 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3426,7 +3429,7 @@
         <v>1574</v>
       </c>
       <c r="N45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O45">
         <v>-578.9999999999998</v>
@@ -3446,13 +3449,13 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -3482,7 +3485,7 @@
         <v>363.67</v>
       </c>
       <c r="N46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O46">
         <v>727.3700000000006</v>
@@ -3505,13 +3508,13 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3541,7 +3544,7 @@
         <v>2947.18</v>
       </c>
       <c r="N47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47">
         <v>-465.360000000001</v>
@@ -3561,13 +3564,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3597,7 +3600,7 @@
         <v>3700</v>
       </c>
       <c r="N48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48">
         <v>-48.19999999999982</v>
@@ -3617,13 +3620,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -3653,7 +3656,7 @@
         <v>3074.61</v>
       </c>
       <c r="N49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49">
         <v>585.6400000000008</v>
@@ -3676,13 +3679,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3712,7 +3715,7 @@
         <v>1982.08</v>
       </c>
       <c r="N50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50">
         <v>-417.2800000000007</v>
@@ -3732,13 +3735,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3768,7 +3771,7 @@
         <v>520.6</v>
       </c>
       <c r="N51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O51">
         <v>-493.1999999999996</v>
@@ -3788,13 +3791,13 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3824,7 +3827,7 @@
         <v>466.6</v>
       </c>
       <c r="N52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52">
         <v>1137.180000000001</v>
@@ -3847,13 +3850,13 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3883,7 +3886,7 @@
         <v>185.38</v>
       </c>
       <c r="N53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53">
         <v>-118.190000000001</v>
@@ -3903,13 +3906,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -3939,7 +3942,7 @@
         <v>4173.96</v>
       </c>
       <c r="N54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O54">
         <v>596.2800000000007</v>
@@ -3962,13 +3965,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E55">
         <v>2</v>
@@ -3998,7 +4001,7 @@
         <v>2093</v>
       </c>
       <c r="N55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O55">
         <v>693.8399999999999</v>
@@ -4021,13 +4024,13 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4057,7 +4060,7 @@
         <v>814.2</v>
       </c>
       <c r="N56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O56">
         <v>-490.599999999999</v>
@@ -4077,13 +4080,13 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4104,7 +4107,7 @@
         <v>611.2</v>
       </c>
       <c r="K57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L57">
         <v>606.62</v>
@@ -4113,7 +4116,7 @@
         <v>606.62</v>
       </c>
       <c r="N57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O57">
         <v>-478.9499999999993</v>
@@ -4133,13 +4136,13 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4169,7 +4172,7 @@
         <v>922.92</v>
       </c>
       <c r="N58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O58">
         <v>-485.8000000000004</v>
@@ -4189,13 +4192,13 @@
         <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -4225,7 +4228,7 @@
         <v>172.84</v>
       </c>
       <c r="N59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O59">
         <v>740.73</v>
@@ -4248,13 +4251,13 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4284,7 +4287,7 @@
         <v>152</v>
       </c>
       <c r="N60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O60">
         <v>-520.1799999999992</v>
@@ -4304,13 +4307,13 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4340,7 +4343,7 @@
         <v>468</v>
       </c>
       <c r="N61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O61">
         <v>678.1500000000003</v>
@@ -4363,13 +4366,13 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4399,7 +4402,7 @@
         <v>967.15</v>
       </c>
       <c r="N62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O62">
         <v>1167.96</v>
@@ -4414,7 +4417,7 @@
         <v>12.58</v>
       </c>
       <c r="S62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4422,13 +4425,13 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4458,7 +4461,7 @@
         <v>116.49</v>
       </c>
       <c r="N63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O63">
         <v>-496.5300000000008</v>
@@ -4478,13 +4481,13 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4514,7 +4517,7 @@
         <v>412.3</v>
       </c>
       <c r="N64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O64">
         <v>-497.1999999999993</v>
@@ -4534,13 +4537,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4570,7 +4573,7 @@
         <v>1462</v>
       </c>
       <c r="N65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O65">
         <v>-635.4000000000005</v>
@@ -4590,13 +4593,13 @@
         <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4626,7 +4629,7 @@
         <v>266.95</v>
       </c>
       <c r="N66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -4646,13 +4649,13 @@
         <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4682,7 +4685,7 @@
         <v>5558.93</v>
       </c>
       <c r="N67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O67">
         <v>-292.5699999999997</v>
@@ -4702,13 +4705,13 @@
         <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C68" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4738,7 +4741,7 @@
         <v>456.1</v>
       </c>
       <c r="N68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O68">
         <v>-480</v>
@@ -4758,13 +4761,13 @@
         <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D69" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4785,7 +4788,7 @@
         <v>1754.5</v>
       </c>
       <c r="K69" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L69">
         <v>1652.52</v>
@@ -4794,7 +4797,7 @@
         <v>1652.52</v>
       </c>
       <c r="N69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O69">
         <v>-434.9000000000001</v>
@@ -4814,13 +4817,13 @@
         <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C70" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4850,7 +4853,7 @@
         <v>4850</v>
       </c>
       <c r="N70" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O70">
         <v>-348.5</v>
@@ -4870,13 +4873,13 @@
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4906,7 +4909,7 @@
         <v>752.75</v>
       </c>
       <c r="N71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -4926,13 +4929,13 @@
         <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C72" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -4962,7 +4965,7 @@
         <v>124.41</v>
       </c>
       <c r="N72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4982,13 +4985,13 @@
         <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D73" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5018,7 +5021,7 @@
         <v>1540.62</v>
       </c>
       <c r="N73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O73">
         <v>-486.4800000000009</v>
@@ -5038,13 +5041,13 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5074,7 +5077,7 @@
         <v>261.9</v>
       </c>
       <c r="N74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O74">
         <v>-511.2000000000016</v>
@@ -5094,13 +5097,13 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5130,7 +5133,7 @@
         <v>141.6</v>
       </c>
       <c r="N75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O75">
         <v>-499.1500000000011</v>
@@ -5150,13 +5153,13 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5186,7 +5189,7 @@
         <v>1134.58</v>
       </c>
       <c r="N76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O76">
         <v>-477.7600000000002</v>
@@ -5206,13 +5209,13 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D77" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5242,7 +5245,7 @@
         <v>2835.37</v>
       </c>
       <c r="N77" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O77">
         <v>-447.6900000000001</v>
@@ -5262,13 +5265,13 @@
         <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D78" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5298,7 +5301,7 @@
         <v>5718.05</v>
       </c>
       <c r="N78" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O78">
         <v>-300.9499999999998</v>
@@ -5318,13 +5321,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5354,7 +5357,7 @@
         <v>489.85</v>
       </c>
       <c r="N79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O79">
         <v>-829.8000000000004</v>
@@ -5374,13 +5377,13 @@
         <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5410,7 +5413,7 @@
         <v>329.55</v>
       </c>
       <c r="N80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O80">
         <v>-485.7999999999991</v>
@@ -5430,13 +5433,13 @@
         <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5466,7 +5469,7 @@
         <v>1326</v>
       </c>
       <c r="N81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O81">
         <v>-620.1999999999994</v>
@@ -5486,13 +5489,13 @@
         <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C82" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D82" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -5522,7 +5525,7 @@
         <v>301.82</v>
       </c>
       <c r="N82" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O82">
         <v>732.9550000000002</v>
@@ -5545,13 +5548,13 @@
         <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D83" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5581,7 +5584,7 @@
         <v>563.21</v>
       </c>
       <c r="N83" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O83">
         <v>-474.2399999999998</v>
@@ -5601,13 +5604,13 @@
         <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5637,7 +5640,7 @@
         <v>962.11</v>
       </c>
       <c r="N84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O84">
         <v>-455.7599999999999</v>
@@ -5657,13 +5660,13 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5693,7 +5696,7 @@
         <v>2260.7</v>
       </c>
       <c r="N85" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O85">
         <v>-546</v>
@@ -5713,13 +5716,13 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D86" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5749,7 +5752,7 @@
         <v>396.1</v>
       </c>
       <c r="N86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O86">
         <v>-479.5499999999992</v>
@@ -5769,13 +5772,13 @@
         <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C87" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5805,7 +5808,7 @@
         <v>1220.56</v>
       </c>
       <c r="N87" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O87">
         <v>-449.6800000000001</v>
@@ -5825,13 +5828,13 @@
         <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D88" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5861,7 +5864,7 @@
         <v>4673.05</v>
       </c>
       <c r="N88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O88">
         <v>-491.8999999999997</v>
@@ -5881,13 +5884,13 @@
         <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C89" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D89" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E89">
         <v>2</v>
@@ -5917,7 +5920,7 @@
         <v>930</v>
       </c>
       <c r="N89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O89">
         <v>438.8999999999997</v>
@@ -5937,13 +5940,13 @@
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C90" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D90" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5973,7 +5976,7 @@
         <v>2165.1</v>
       </c>
       <c r="N90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O90">
         <v>-456.8000000000011</v>
@@ -5993,13 +5996,13 @@
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D91" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -6017,7 +6020,7 @@
         <v>9723.450000000001</v>
       </c>
       <c r="J91">
-        <v>312.45</v>
+        <v>312.25</v>
       </c>
       <c r="L91">
         <v>279.92</v>
@@ -6029,13 +6032,13 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>587.4</v>
+        <v>580.8</v>
       </c>
       <c r="Q91">
-        <v>587.4</v>
+        <v>580.8</v>
       </c>
       <c r="R91">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6043,13 +6046,13 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D92" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -6079,7 +6082,7 @@
         <v>714.75</v>
       </c>
       <c r="N92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O92">
         <v>-653.8999999999994</v>
@@ -6099,13 +6102,13 @@
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D93" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6135,7 +6138,7 @@
         <v>116.25</v>
       </c>
       <c r="N93" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O93">
         <v>-778.1499999999995</v>
@@ -6155,13 +6158,13 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D94" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -6191,7 +6194,7 @@
         <v>174.3</v>
       </c>
       <c r="N94" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -6211,13 +6214,13 @@
         <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D95" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6247,7 +6250,7 @@
         <v>630.9400000000001</v>
       </c>
       <c r="N95" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O95">
         <v>-498.1499999999989</v>
@@ -6267,13 +6270,13 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C96" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D96" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6303,7 +6306,7 @@
         <v>409.16</v>
       </c>
       <c r="N96" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O96">
         <v>-495.4199999999992</v>
@@ -6323,13 +6326,13 @@
         <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6359,7 +6362,7 @@
         <v>1110.8</v>
       </c>
       <c r="N97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O97">
         <v>-537.6000000000004</v>
@@ -6379,13 +6382,13 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C98" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6415,7 +6418,7 @@
         <v>452.5</v>
       </c>
       <c r="N98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O98">
         <v>732.6450000000004</v>
@@ -6438,13 +6441,13 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6474,7 +6477,7 @@
         <v>3734.74</v>
       </c>
       <c r="N99" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O99">
         <v>-393.1200000000008</v>
@@ -6494,13 +6497,13 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6530,7 +6533,7 @@
         <v>5450.62</v>
       </c>
       <c r="N100" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O100">
         <v>-286.8800000000001</v>
@@ -6550,13 +6553,13 @@
         <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D101" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6586,7 +6589,7 @@
         <v>938.84</v>
       </c>
       <c r="N101" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O101">
         <v>-494.0999999999997</v>
@@ -6606,13 +6609,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D102" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6642,7 +6645,7 @@
         <v>475.38</v>
       </c>
       <c r="N102" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O102">
         <v>-475.3799999999997</v>
@@ -6662,13 +6665,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C103" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D103" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6698,7 +6701,7 @@
         <v>895.05</v>
       </c>
       <c r="N103" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O103">
         <v>-633.0000000000007</v>
@@ -6718,13 +6721,13 @@
         <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6754,7 +6757,7 @@
         <v>573.66</v>
       </c>
       <c r="N104" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O104">
         <v>-483.0400000000009</v>
@@ -6774,13 +6777,13 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D105" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6810,7 +6813,7 @@
         <v>1664.88</v>
       </c>
       <c r="N105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O105">
         <v>-438.0999999999995</v>
@@ -6830,13 +6833,13 @@
         <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6857,7 +6860,7 @@
         <v>1310.2</v>
       </c>
       <c r="K106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L106">
         <v>1286.3</v>
@@ -6866,7 +6869,7 @@
         <v>1286.3</v>
       </c>
       <c r="N106" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O106">
         <v>-473.9000000000003</v>
@@ -6886,13 +6889,13 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C107" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D107" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6922,7 +6925,7 @@
         <v>841</v>
       </c>
       <c r="N107" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O107">
         <v>-688.0499999999995</v>
@@ -6942,13 +6945,13 @@
         <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C108" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D108" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6978,7 +6981,7 @@
         <v>903.6900000000001</v>
       </c>
       <c r="N108" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O108">
         <v>-475.5999999999995</v>
@@ -6998,13 +7001,13 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C109" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D109" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -7025,7 +7028,7 @@
         <v>423.95</v>
       </c>
       <c r="K109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L109">
         <v>420.19</v>
@@ -7034,7 +7037,7 @@
         <v>420.19</v>
       </c>
       <c r="N109" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O109">
         <v>-486.4200000000003</v>
@@ -7054,13 +7057,13 @@
         <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -7090,7 +7093,7 @@
         <v>186.89</v>
       </c>
       <c r="N110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O110">
         <v>-492.0000000000002</v>
@@ -7110,13 +7113,13 @@
         <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C111" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D111" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -7146,7 +7149,7 @@
         <v>7282.7</v>
       </c>
       <c r="N111" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O111">
         <v>-383.3000000000002</v>
@@ -7166,13 +7169,13 @@
         <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C112" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D112" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -7202,7 +7205,7 @@
         <v>1972.67</v>
       </c>
       <c r="N112" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O112">
         <v>-415.3199999999997</v>
@@ -7222,13 +7225,13 @@
         <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C113" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D113" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -7258,7 +7261,7 @@
         <v>116.74</v>
       </c>
       <c r="N113" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O113">
         <v>-497.34</v>
@@ -7278,13 +7281,13 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C114" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -7314,7 +7317,7 @@
         <v>158</v>
       </c>
       <c r="N114" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O114">
         <v>-721.5199999999999</v>
@@ -7334,13 +7337,13 @@
         <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D115" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -7370,7 +7373,7 @@
         <v>324.76</v>
       </c>
       <c r="N115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O115">
         <v>-495.6100000000009</v>
@@ -7390,13 +7393,13 @@
         <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C116" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -7426,7 +7429,7 @@
         <v>3601.36</v>
       </c>
       <c r="N116" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O116">
         <v>-379.0799999999999</v>
@@ -7446,13 +7449,13 @@
         <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C117" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D117" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7482,7 +7485,7 @@
         <v>463.5</v>
       </c>
       <c r="N117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O117">
         <v>-487.9999999999996</v>
@@ -7502,13 +7505,13 @@
         <v>55</v>
       </c>
       <c r="B118" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -7526,7 +7529,7 @@
         <v>9152.799999999999</v>
       </c>
       <c r="J118">
-        <v>1221.3</v>
+        <v>1228.3</v>
       </c>
       <c r="L118">
         <v>1144.1</v>
@@ -7538,13 +7541,13 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>617.6</v>
+        <v>673.6</v>
       </c>
       <c r="Q118">
-        <v>617.6</v>
+        <v>673.6</v>
       </c>
       <c r="R118">
-        <v>6.75</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7552,13 +7555,13 @@
         <v>56</v>
       </c>
       <c r="B119" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C119" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7588,7 +7591,7 @@
         <v>317.68</v>
       </c>
       <c r="N119" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O119">
         <v>-484.8799999999992</v>
@@ -7608,13 +7611,13 @@
         <v>56</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C120" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D120" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7644,7 +7647,7 @@
         <v>1243.2</v>
       </c>
       <c r="N120" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O120">
         <v>-500.5</v>
@@ -7664,13 +7667,13 @@
         <v>56</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7700,7 +7703,7 @@
         <v>814.05</v>
       </c>
       <c r="N121" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O121">
         <v>-471.3500000000003</v>
@@ -7720,13 +7723,13 @@
         <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D122" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7756,7 +7759,7 @@
         <v>1896.67</v>
       </c>
       <c r="N122" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O122">
         <v>-499.1499999999997</v>
@@ -7776,13 +7779,13 @@
         <v>57</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D123" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7803,7 +7806,7 @@
         <v>147.78</v>
       </c>
       <c r="K123" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L123">
         <v>144.73</v>
@@ -7812,7 +7815,7 @@
         <v>144.73</v>
       </c>
       <c r="N123" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O123">
         <v>-495.3000000000003</v>
@@ -7832,13 +7835,13 @@
         <v>57</v>
       </c>
       <c r="B124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C124" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D124" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7868,7 +7871,7 @@
         <v>3923.12</v>
       </c>
       <c r="N124" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O124">
         <v>-412.9600000000009</v>
@@ -7888,13 +7891,13 @@
         <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D125" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7924,7 +7927,7 @@
         <v>395.1</v>
       </c>
       <c r="N125" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O125">
         <v>-499.1999999999989</v>
@@ -7944,13 +7947,13 @@
         <v>57</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D126" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -7968,10 +7971,10 @@
         <v>9990.370000000001</v>
       </c>
       <c r="J126">
-        <v>183.43</v>
+        <v>193.19</v>
       </c>
       <c r="L126">
-        <v>172.33</v>
+        <v>175.81</v>
       </c>
       <c r="M126">
         <v>0</v>
@@ -7980,13 +7983,13 @@
         <v>849.9270000000001</v>
       </c>
       <c r="P126">
-        <v>617.76</v>
+        <v>793.4400000000001</v>
       </c>
       <c r="Q126">
-        <v>1467.69</v>
+        <v>1643.37</v>
       </c>
       <c r="R126">
-        <v>14.69</v>
+        <v>16.45</v>
       </c>
       <c r="S126" t="s">
         <v>70</v>
@@ -7997,13 +8000,13 @@
         <v>57</v>
       </c>
       <c r="B127" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D127" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -8033,7 +8036,7 @@
         <v>500.98</v>
       </c>
       <c r="N127" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O127">
         <v>-474.6600000000001</v>
@@ -8053,13 +8056,13 @@
         <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D128" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -8089,7 +8092,7 @@
         <v>277.31</v>
       </c>
       <c r="N128" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O128">
         <v>726.3700000000001</v>
@@ -8112,13 +8115,13 @@
         <v>59</v>
       </c>
       <c r="B129" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D129" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8148,7 +8151,7 @@
         <v>3452.77</v>
       </c>
       <c r="N129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O129">
         <v>-363.46</v>
@@ -8168,13 +8171,13 @@
         <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8204,7 +8207,7 @@
         <v>2126.29</v>
       </c>
       <c r="N130" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O130">
         <v>-447.6399999999994</v>
@@ -8224,13 +8227,13 @@
         <v>59</v>
       </c>
       <c r="B131" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C131" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8260,7 +8263,7 @@
         <v>1251.24</v>
       </c>
       <c r="N131" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O131">
         <v>-461.0199999999993</v>
@@ -8280,13 +8283,13 @@
         <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C132" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D132" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -8316,7 +8319,7 @@
         <v>261.35</v>
       </c>
       <c r="N132" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O132">
         <v>-495</v>
@@ -8336,13 +8339,13 @@
         <v>60</v>
       </c>
       <c r="B133" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C133" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D133" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -8363,7 +8366,7 @@
         <v>144.27</v>
       </c>
       <c r="K133" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L133">
         <v>143.4</v>
@@ -8372,7 +8375,7 @@
         <v>143.4</v>
       </c>
       <c r="N133" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O133">
         <v>-498.2999999999989</v>
@@ -8392,13 +8395,13 @@
         <v>60</v>
       </c>
       <c r="B134" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D134" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -8428,7 +8431,7 @@
         <v>394.35</v>
       </c>
       <c r="N134" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O134">
         <v>-498</v>
@@ -8448,13 +8451,13 @@
         <v>61</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C135" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D135" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -8484,7 +8487,7 @@
         <v>2925.05</v>
       </c>
       <c r="N135" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O135">
         <v>-461.8499999999995</v>
@@ -8504,13 +8507,13 @@
         <v>61</v>
       </c>
       <c r="B136" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C136" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D136" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -8540,7 +8543,7 @@
         <v>431.49</v>
       </c>
       <c r="N136" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O136">
         <v>-499.6199999999996</v>
@@ -8560,13 +8563,13 @@
         <v>62</v>
       </c>
       <c r="B137" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D137" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -8596,7 +8599,7 @@
         <v>4362.4</v>
       </c>
       <c r="N137" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O137">
         <v>1072.36</v>
@@ -8619,13 +8622,13 @@
         <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D138" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -8655,7 +8658,7 @@
         <v>857</v>
       </c>
       <c r="N138" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O138">
         <v>191.9500000000005</v>
@@ -8675,13 +8678,13 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C139" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D139" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8711,7 +8714,7 @@
         <v>311.31</v>
       </c>
       <c r="N139" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O139">
         <v>-491.6999999999996</v>
@@ -8731,13 +8734,13 @@
         <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C140" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D140" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8767,7 +8770,7 @@
         <v>255.41</v>
       </c>
       <c r="N140" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O140">
         <v>-497.280000000001</v>
@@ -8787,13 +8790,13 @@
         <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C141" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D141" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -8823,7 +8826,7 @@
         <v>987.62</v>
       </c>
       <c r="N141" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O141">
         <v>-467.8199999999992</v>
@@ -8843,13 +8846,13 @@
         <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C142" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D142" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -8879,7 +8882,7 @@
         <v>2028.06</v>
       </c>
       <c r="N142" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O142">
         <v>-426.9600000000009</v>
@@ -8899,13 +8902,13 @@
         <v>64</v>
       </c>
       <c r="B143" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C143" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D143" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E143">
         <v>2</v>
@@ -8923,7 +8926,7 @@
         <v>6212.5</v>
       </c>
       <c r="J143">
-        <v>6873</v>
+        <v>6883.5</v>
       </c>
       <c r="L143">
         <v>6523.12</v>
@@ -8935,13 +8938,13 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>660.5</v>
+        <v>671</v>
       </c>
       <c r="Q143">
-        <v>660.5</v>
+        <v>671</v>
       </c>
       <c r="R143">
-        <v>10.63</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8949,13 +8952,13 @@
         <v>64</v>
       </c>
       <c r="B144" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D144" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -8985,7 +8988,7 @@
         <v>1792.27</v>
       </c>
       <c r="N144" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O144">
         <v>-471.6499999999997</v>
@@ -9005,13 +9008,13 @@
         <v>64</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D145" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -9041,7 +9044,7 @@
         <v>777.48</v>
       </c>
       <c r="N145" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O145">
         <v>-491.0399999999995</v>
@@ -9061,13 +9064,13 @@
         <v>65</v>
       </c>
       <c r="B146" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C146" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D146" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -9085,10 +9088,10 @@
         <v>8805</v>
       </c>
       <c r="J146">
-        <v>3576.1</v>
+        <v>3563.8</v>
       </c>
       <c r="L146">
-        <v>3228.5</v>
+        <v>3343.5</v>
       </c>
       <c r="M146">
         <v>0</v>
@@ -9097,13 +9100,13 @@
         <v>293.5000000000005</v>
       </c>
       <c r="P146">
-        <v>1282.2</v>
+        <v>1257.6</v>
       </c>
       <c r="Q146">
-        <v>1575.7</v>
+        <v>1551.1</v>
       </c>
       <c r="R146">
-        <v>17.9</v>
+        <v>17.62</v>
       </c>
       <c r="S146" t="s">
         <v>70</v>
@@ -9114,13 +9117,13 @@
         <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D147" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -9138,7 +9141,7 @@
         <v>9427.799999999999</v>
       </c>
       <c r="J147">
-        <v>840.1</v>
+        <v>847.9</v>
       </c>
       <c r="L147">
         <v>785.65</v>
@@ -9150,13 +9153,13 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>653.4</v>
+        <v>747</v>
       </c>
       <c r="Q147">
-        <v>653.4</v>
+        <v>747</v>
       </c>
       <c r="R147">
-        <v>6.93</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -9164,16 +9167,16 @@
         <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C148" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D148" t="s">
         <v>159</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148">
         <v>322.1</v>
@@ -9182,7 +9185,7 @@
         <v>31</v>
       </c>
       <c r="H148">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I148">
         <v>9985.1</v>
@@ -9190,23 +9193,29 @@
       <c r="J148">
         <v>352.65</v>
       </c>
+      <c r="K148" t="s">
+        <v>74</v>
+      </c>
       <c r="L148">
-        <v>338.21</v>
+        <v>354.31</v>
       </c>
       <c r="M148">
-        <v>0</v>
+        <v>354.3100000000001</v>
+      </c>
+      <c r="N148" t="s">
+        <v>170</v>
       </c>
       <c r="O148">
-        <v>483.1500000000005</v>
+        <v>998.5100000000011</v>
       </c>
       <c r="P148">
-        <v>488.8</v>
+        <v>0</v>
       </c>
       <c r="Q148">
-        <v>971.95</v>
+        <v>998.5100000000011</v>
       </c>
       <c r="R148">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="S148" t="s">
         <v>73</v>
@@ -9217,13 +9226,13 @@
         <v>66</v>
       </c>
       <c r="B149" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C149" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D149" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -9244,7 +9253,7 @@
         <v>2086.8</v>
       </c>
       <c r="K149" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L149">
         <v>2040.5</v>
@@ -9253,7 +9262,7 @@
         <v>2010.2</v>
       </c>
       <c r="N149" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O149">
         <v>871.6000000000006</v>
@@ -9276,16 +9285,16 @@
         <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C150" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D150" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150">
         <v>403.7</v>
@@ -9294,34 +9303,34 @@
         <v>24</v>
       </c>
       <c r="H150">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I150">
         <v>9688.799999999999</v>
       </c>
       <c r="J150">
-        <v>445.55</v>
+        <v>460.4</v>
       </c>
       <c r="L150">
-        <v>423.88</v>
+        <v>444.07</v>
       </c>
       <c r="M150">
         <v>0</v>
       </c>
       <c r="O150">
-        <v>484.4400000000007</v>
+        <v>847.7700000000004</v>
       </c>
       <c r="P150">
-        <v>502.2</v>
+        <v>340.2</v>
       </c>
       <c r="Q150">
-        <v>986.64</v>
+        <v>1187.97</v>
       </c>
       <c r="R150">
-        <v>10.18</v>
+        <v>12.26</v>
       </c>
       <c r="S150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -9329,13 +9338,13 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -9353,7 +9362,7 @@
         <v>8492.200000000001</v>
       </c>
       <c r="J151">
-        <v>4522.2</v>
+        <v>4461.4</v>
       </c>
       <c r="L151">
         <v>4033.8</v>
@@ -9365,13 +9374,13 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>552.2</v>
+        <v>430.6</v>
       </c>
       <c r="Q151">
-        <v>552.2</v>
+        <v>430.6</v>
       </c>
       <c r="R151">
-        <v>6.5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -9379,16 +9388,16 @@
         <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C152" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D152" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152">
         <v>366.1</v>
@@ -9403,10 +9412,10 @@
         <v>9884.700000000001</v>
       </c>
       <c r="J152">
-        <v>392.6</v>
+        <v>390.8</v>
       </c>
       <c r="L152">
-        <v>347.8</v>
+        <v>366.1</v>
       </c>
       <c r="M152">
         <v>0</v>
@@ -9415,13 +9424,13 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>715.5</v>
+        <v>666.9</v>
       </c>
       <c r="Q152">
-        <v>715.5</v>
+        <v>666.9</v>
       </c>
       <c r="R152">
-        <v>7.24</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -9429,13 +9438,13 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C153" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D153" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -9453,7 +9462,7 @@
         <v>9262.35</v>
       </c>
       <c r="J153">
-        <v>1085.5</v>
+        <v>1081.15</v>
       </c>
       <c r="L153">
         <v>977.6900000000001</v>
@@ -9465,13 +9474,13 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>507.15</v>
+        <v>468</v>
       </c>
       <c r="Q153">
-        <v>507.15</v>
+        <v>468</v>
       </c>
       <c r="R153">
-        <v>5.48</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -9479,13 +9488,13 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C154" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D154" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9503,7 +9512,7 @@
         <v>8442.4</v>
       </c>
       <c r="J154">
-        <v>2157.6</v>
+        <v>2139.1</v>
       </c>
       <c r="L154">
         <v>2005.07</v>
@@ -9515,13 +9524,13 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="Q154">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="R154">
-        <v>2.23</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -9529,13 +9538,13 @@
         <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C155" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D155" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -9553,7 +9562,7 @@
         <v>9872.799999999999</v>
       </c>
       <c r="J155">
-        <v>1285.2</v>
+        <v>1291.1</v>
       </c>
       <c r="L155">
         <v>1172.39</v>
@@ -9565,13 +9574,13 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>408.8</v>
+        <v>456</v>
       </c>
       <c r="Q155">
-        <v>408.8</v>
+        <v>456</v>
       </c>
       <c r="R155">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -9579,13 +9588,13 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C156" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D156" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -9603,7 +9612,7 @@
         <v>9800.639999999999</v>
       </c>
       <c r="J156">
-        <v>208.72</v>
+        <v>210.69</v>
       </c>
       <c r="L156">
         <v>193.97</v>
@@ -9615,13 +9624,13 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>217.92</v>
+        <v>312.48</v>
       </c>
       <c r="Q156">
-        <v>217.92</v>
+        <v>312.48</v>
       </c>
       <c r="R156">
-        <v>2.22</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -9629,13 +9638,13 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C157" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D157" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -9653,7 +9662,7 @@
         <v>9535</v>
       </c>
       <c r="J157">
-        <v>1946.7</v>
+        <v>1977.4</v>
       </c>
       <c r="L157">
         <v>1811.65</v>
@@ -9665,13 +9674,13 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>198.5</v>
+        <v>352</v>
       </c>
       <c r="Q157">
-        <v>198.5</v>
+        <v>352</v>
       </c>
       <c r="R157">
-        <v>2.08</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -9679,13 +9688,13 @@
         <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C158" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D158" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -9703,7 +9712,7 @@
         <v>9331</v>
       </c>
       <c r="J158">
-        <v>1355.5</v>
+        <v>1349.6</v>
       </c>
       <c r="L158">
         <v>1266.35</v>
@@ -9715,13 +9724,13 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>157.5</v>
+        <v>116.2</v>
       </c>
       <c r="Q158">
-        <v>157.5</v>
+        <v>116.2</v>
       </c>
       <c r="R158">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -9729,13 +9738,13 @@
         <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C159" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D159" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -9753,7 +9762,7 @@
         <v>9678</v>
       </c>
       <c r="J159">
-        <v>981.1</v>
+        <v>983.95</v>
       </c>
       <c r="L159">
         <v>919.41</v>
@@ -9765,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>133</v>
+        <v>161.5</v>
       </c>
       <c r="Q159">
-        <v>133</v>
+        <v>161.5</v>
       </c>
       <c r="R159">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -9779,13 +9788,13 @@
         <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D160" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -9803,7 +9812,7 @@
         <v>9748.799999999999</v>
       </c>
       <c r="J160">
-        <v>561.25</v>
+        <v>557.95</v>
       </c>
       <c r="L160">
         <v>514.52</v>
@@ -9815,30 +9824,30 @@
         <v>0</v>
       </c>
       <c r="P160">
-        <v>353.7</v>
+        <v>294.3</v>
       </c>
       <c r="Q160">
-        <v>353.7</v>
+        <v>294.3</v>
       </c>
       <c r="R160">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19">
       <c r="A161" t="s">
         <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C161" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D161" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161">
         <v>428.05</v>
@@ -9853,10 +9862,10 @@
         <v>9845.15</v>
       </c>
       <c r="J161">
-        <v>444.75</v>
+        <v>458.9</v>
       </c>
       <c r="L161">
-        <v>406.65</v>
+        <v>428.05</v>
       </c>
       <c r="M161">
         <v>0</v>
@@ -9865,27 +9874,27 @@
         <v>0</v>
       </c>
       <c r="P161">
-        <v>384.1</v>
+        <v>709.55</v>
       </c>
       <c r="Q161">
-        <v>384.1</v>
+        <v>709.55</v>
       </c>
       <c r="R161">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19">
       <c r="A162" t="s">
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C162" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D162" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -9903,7 +9912,7 @@
         <v>9517</v>
       </c>
       <c r="J162">
-        <v>9865</v>
+        <v>9825</v>
       </c>
       <c r="L162">
         <v>9041.15</v>
@@ -9915,30 +9924,30 @@
         <v>0</v>
       </c>
       <c r="P162">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="Q162">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="R162">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19">
       <c r="A163" t="s">
         <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C163" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D163" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F163">
         <v>277.2</v>
@@ -9947,45 +9956,48 @@
         <v>36</v>
       </c>
       <c r="H163">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I163">
         <v>9979.200000000001</v>
       </c>
       <c r="J163">
-        <v>292.5</v>
+        <v>309.26</v>
       </c>
       <c r="L163">
-        <v>263.34</v>
+        <v>291.06</v>
       </c>
       <c r="M163">
         <v>0</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>498.9600000000005</v>
       </c>
       <c r="P163">
-        <v>550.8</v>
+        <v>577.08</v>
       </c>
       <c r="Q163">
-        <v>550.8</v>
+        <v>1076.04</v>
       </c>
       <c r="R163">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18">
+        <v>10.78</v>
+      </c>
+      <c r="S163" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19">
       <c r="A164" t="s">
         <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -10003,7 +10015,7 @@
         <v>9677.6</v>
       </c>
       <c r="J164">
-        <v>1218.6</v>
+        <v>1214.9</v>
       </c>
       <c r="L164">
         <v>1149.21</v>
@@ -10015,27 +10027,27 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>71.2</v>
+        <v>41.6</v>
       </c>
       <c r="Q164">
-        <v>71.2</v>
+        <v>41.6</v>
       </c>
       <c r="R164">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="165" spans="1:18">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19">
       <c r="A165" t="s">
         <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C165" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D165" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -10056,7 +10068,7 @@
         <v>7424</v>
       </c>
       <c r="K165" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L165">
         <v>7052.8</v>
@@ -10065,7 +10077,7 @@
         <v>7052.8</v>
       </c>
       <c r="N165" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O165">
         <v>-371.1999999999998</v>
@@ -10080,18 +10092,18 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:19">
       <c r="A166" t="s">
         <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C166" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D166" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -10109,7 +10121,7 @@
         <v>9585.4</v>
       </c>
       <c r="J166">
-        <v>433.25</v>
+        <v>427.55</v>
       </c>
       <c r="L166">
         <v>413.91</v>
@@ -10121,27 +10133,27 @@
         <v>0</v>
       </c>
       <c r="P166">
-        <v>-53.9</v>
+        <v>-179.3</v>
       </c>
       <c r="Q166">
-        <v>-53.9</v>
+        <v>-179.3</v>
       </c>
       <c r="R166">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19">
       <c r="A167" t="s">
         <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C167" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D167" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -10159,7 +10171,7 @@
         <v>9894.959999999999</v>
       </c>
       <c r="J167">
-        <v>123.55</v>
+        <v>122.82</v>
       </c>
       <c r="L167">
         <v>116.05</v>
@@ -10171,27 +10183,27 @@
         <v>0</v>
       </c>
       <c r="P167">
-        <v>112.59</v>
+        <v>53.46</v>
       </c>
       <c r="Q167">
-        <v>112.59</v>
+        <v>53.46</v>
       </c>
       <c r="R167">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19">
       <c r="A168" t="s">
         <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C168" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D168" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -10209,7 +10221,7 @@
         <v>8152.6</v>
       </c>
       <c r="J168">
-        <v>4076.3</v>
+        <v>4119.8</v>
       </c>
       <c r="L168">
         <v>3872.49</v>
@@ -10221,27 +10233,27 @@
         <v>0</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="R168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19">
       <c r="A169" t="s">
         <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C169" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D169" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -10259,7 +10271,7 @@
         <v>9872.1</v>
       </c>
       <c r="J169">
-        <v>548.45</v>
+        <v>563.75</v>
       </c>
       <c r="L169">
         <v>521.03</v>
@@ -10271,27 +10283,27 @@
         <v>0</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>275.4</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>275.4</v>
       </c>
       <c r="R169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
       <c r="A170" t="s">
         <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C170" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D170" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -10309,7 +10321,7 @@
         <v>9070.799999999999</v>
       </c>
       <c r="J170">
-        <v>1511.8</v>
+        <v>1549.8</v>
       </c>
       <c r="L170">
         <v>1436.21</v>
@@ -10321,27 +10333,27 @@
         <v>0</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="R170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:18">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19">
       <c r="A171" t="s">
         <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C171" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D171" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -10359,7 +10371,7 @@
         <v>7642</v>
       </c>
       <c r="J171">
-        <v>7642</v>
+        <v>7553</v>
       </c>
       <c r="L171">
         <v>7259.9</v>
@@ -10371,12 +10383,112 @@
         <v>0</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="R171">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19">
+      <c r="A172" t="s">
+        <v>74</v>
+      </c>
+      <c r="B172" t="s">
+        <v>136</v>
+      </c>
+      <c r="C172" t="s">
+        <v>158</v>
+      </c>
+      <c r="D172" t="s">
+        <v>160</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+      <c r="F172">
+        <v>592.5</v>
+      </c>
+      <c r="G172">
+        <v>16</v>
+      </c>
+      <c r="H172">
+        <v>16</v>
+      </c>
+      <c r="I172">
+        <v>9480</v>
+      </c>
+      <c r="J172">
+        <v>592.5</v>
+      </c>
+      <c r="L172">
+        <v>562.88</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+      <c r="Q172">
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173" t="s">
+        <v>74</v>
+      </c>
+      <c r="B173" t="s">
+        <v>127</v>
+      </c>
+      <c r="C173" t="s">
+        <v>158</v>
+      </c>
+      <c r="D173" t="s">
+        <v>160</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>282.75</v>
+      </c>
+      <c r="G173">
+        <v>35</v>
+      </c>
+      <c r="H173">
+        <v>35</v>
+      </c>
+      <c r="I173">
+        <v>9896.25</v>
+      </c>
+      <c r="J173">
+        <v>282.75</v>
+      </c>
+      <c r="L173">
+        <v>268.61</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <v>0</v>
+      </c>
+      <c r="R173">
         <v>0</v>
       </c>
     </row>

--- a/Paper Trading Simulator/paper_trade_book.xlsx
+++ b/Paper Trading Simulator/paper_trade_book.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="174">
   <si>
     <t>Buy Date</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
   </si>
   <si>
     <t>ADANIENT</t>
@@ -896,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -973,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1009,7 +1012,7 @@
         <v>2093.04</v>
       </c>
       <c r="N2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O2">
         <v>-440.6399999999994</v>
@@ -1029,13 +1032,13 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1065,7 +1068,7 @@
         <v>1282.2</v>
       </c>
       <c r="N3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O3">
         <v>693.6000000000004</v>
@@ -1088,13 +1091,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1124,7 +1127,7 @@
         <v>5739.43</v>
       </c>
       <c r="N4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O4">
         <v>-302.0699999999997</v>
@@ -1144,13 +1147,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1180,7 +1183,7 @@
         <v>2700.28</v>
       </c>
       <c r="N5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O5">
         <v>-426.3599999999997</v>
@@ -1200,13 +1203,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1236,7 +1239,7 @@
         <v>2293.3</v>
       </c>
       <c r="N6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1256,13 +1259,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1292,7 +1295,7 @@
         <v>1216</v>
       </c>
       <c r="N7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O7">
         <v>-448</v>
@@ -1312,13 +1315,13 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1348,7 +1351,7 @@
         <v>3066.4</v>
       </c>
       <c r="N8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O8">
         <v>-522.8999999999992</v>
@@ -1368,13 +1371,13 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1404,7 +1407,7 @@
         <v>2901.59</v>
       </c>
       <c r="N9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O9">
         <v>-458.1300000000001</v>
@@ -1424,13 +1427,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1460,7 +1463,7 @@
         <v>2922.11</v>
       </c>
       <c r="N10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O10">
         <v>-461.3699999999999</v>
@@ -1480,13 +1483,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1507,7 +1510,7 @@
         <v>183.56</v>
       </c>
       <c r="K11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L11">
         <v>180.92</v>
@@ -1516,7 +1519,7 @@
         <v>180.92</v>
       </c>
       <c r="N11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O11">
         <v>749.6499999999999</v>
@@ -1531,7 +1534,7 @@
         <v>7.5</v>
       </c>
       <c r="S11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1539,13 +1542,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1575,7 +1578,7 @@
         <v>1651</v>
       </c>
       <c r="N12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O12">
         <v>599.5200000000004</v>
@@ -1598,13 +1601,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1634,7 +1637,7 @@
         <v>732.4</v>
       </c>
       <c r="N13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O13">
         <v>-462.6000000000008</v>
@@ -1654,13 +1657,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1690,7 +1693,7 @@
         <v>651.2</v>
       </c>
       <c r="N14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1710,13 +1713,13 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1746,7 +1749,7 @@
         <v>1135.44</v>
       </c>
       <c r="N15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O15">
         <v>-478.0799999999999</v>
@@ -1766,13 +1769,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1802,7 +1805,7 @@
         <v>5731.82</v>
       </c>
       <c r="N16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O16">
         <v>-301.6800000000003</v>
@@ -1822,13 +1825,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1858,7 +1861,7 @@
         <v>9280</v>
       </c>
       <c r="N17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O17">
         <v>-2</v>
@@ -1878,13 +1881,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1914,7 +1917,7 @@
         <v>282.8</v>
       </c>
       <c r="N18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1934,13 +1937,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1970,7 +1973,7 @@
         <v>1342.35</v>
       </c>
       <c r="N19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O19">
         <v>-494.5500000000006</v>
@@ -1990,13 +1993,13 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2026,7 +2029,7 @@
         <v>5425.45</v>
       </c>
       <c r="N20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O20">
         <v>-285.5500000000002</v>
@@ -2046,13 +2049,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2073,7 +2076,7 @@
         <v>132.36</v>
       </c>
       <c r="K21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L21">
         <v>128.5</v>
@@ -2082,7 +2085,7 @@
         <v>128.499</v>
       </c>
       <c r="N21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O21">
         <v>495.639</v>
@@ -2102,13 +2105,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2129,7 +2132,7 @@
         <v>4021.8</v>
       </c>
       <c r="K22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L22">
         <v>3974.1</v>
@@ -2138,7 +2141,7 @@
         <v>3974.1</v>
       </c>
       <c r="N22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2158,13 +2161,13 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2194,7 +2197,7 @@
         <v>972.9400000000001</v>
       </c>
       <c r="N23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O23">
         <v>-460.8900000000003</v>
@@ -2214,13 +2217,13 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2250,7 +2253,7 @@
         <v>158.14</v>
       </c>
       <c r="N24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O24">
         <v>-499.2000000000013</v>
@@ -2270,13 +2273,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2306,7 +2309,7 @@
         <v>1001.11</v>
       </c>
       <c r="N25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O25">
         <v>-474.2099999999995</v>
@@ -2326,13 +2329,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2353,7 +2356,7 @@
         <v>267.45</v>
       </c>
       <c r="K26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L26">
         <v>253.98</v>
@@ -2362,7 +2365,7 @@
         <v>252</v>
       </c>
       <c r="N26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O26">
         <v>-567.9500000000008</v>
@@ -2382,13 +2385,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2418,7 +2421,7 @@
         <v>951.52</v>
       </c>
       <c r="N27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O27">
         <v>-450.7200000000004</v>
@@ -2438,13 +2441,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2474,7 +2477,7 @@
         <v>1880.9</v>
       </c>
       <c r="N28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O28">
         <v>-495</v>
@@ -2494,13 +2497,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
